--- a/Financial Analysis/OPRA.xlsx
+++ b/Financial Analysis/OPRA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1453FAC-8B23-4CDA-8A29-E60336EBFCEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101D13D7-1D5C-4AC7-AF8C-BE6EF1E851A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
   </bookViews>
@@ -849,14 +849,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>16.87</v>
+        <v>17.59</v>
       </c>
       <c r="E3" s="5">
-        <v>45776</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45776</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="5">
         <v>45890</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>1509.865</v>
+        <v>1574.3050000000001</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -920,7 +920,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>1383.0650000000001</v>
+        <v>1447.5050000000001</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AO46" s="2">
         <f>Main!D3</f>
-        <v>16.87</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="47" spans="2:41" x14ac:dyDescent="0.3">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AO47" s="9">
         <f>AO45/AO46-1</f>
-        <v>0.11399138868960712</v>
+        <v>6.8393105582357894E-2</v>
       </c>
     </row>
     <row r="48" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7990,13 +7990,13 @@
     <row r="74" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO74" s="2">
         <f>Main!D3</f>
-        <v>16.87</v>
+        <v>17.59</v>
       </c>
     </row>
     <row r="75" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO75" s="9">
         <f>AO73/AO74-1</f>
-        <v>0.25644163047603397</v>
+        <v>0.2050125245099883</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/OPRA.xlsx
+++ b/Financial Analysis/OPRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101D13D7-1D5C-4AC7-AF8C-BE6EF1E851A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9C8520-9998-4998-A3F2-A177AD33C1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="98">
   <si>
     <t>OPRA</t>
   </si>
@@ -316,13 +316,10 @@
     <t>look at competitors, MAU, etc.</t>
   </si>
   <si>
-    <t>Q125 6K</t>
-  </si>
-  <si>
     <t>depends on gross margin</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -425,13 +422,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -449,8 +446,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9540240" y="0"/>
-          <a:ext cx="0" cy="12908280"/>
+          <a:off x="12588240" y="0"/>
+          <a:ext cx="0" cy="13822680"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -849,17 +846,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>17.59</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="E3" s="5">
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45918</v>
       </c>
       <c r="G3" s="5">
-        <v>45890</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -870,7 +867,7 @@
         <v>89.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -879,7 +876,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>1574.3050000000001</v>
+        <v>1731.825</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -887,11 +884,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>126.8</f>
-        <v>126.8</v>
+        <f>126.8+1.2</f>
+        <v>128</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -911,7 +908,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>126.8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -920,7 +917,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>1447.5050000000001</v>
+        <v>1603.825</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -1107,8 +1104,7 @@
         <v>95.6</v>
       </c>
       <c r="T3" s="11">
-        <f>P3*1.5</f>
-        <v>96.899999999999991</v>
+        <v>92.9</v>
       </c>
       <c r="U3" s="11">
         <f>Q3*1.27</f>
@@ -1136,47 +1132,47 @@
       </c>
       <c r="AB3" s="3">
         <f>SUM(S3:V3)</f>
-        <v>389.86700000000002</v>
+        <v>385.86700000000002</v>
       </c>
       <c r="AC3" s="3">
         <f>AB3*1.18</f>
-        <v>460.04306000000003</v>
+        <v>455.32306</v>
       </c>
       <c r="AD3" s="3">
         <f>AC3*1.12</f>
-        <v>515.24822720000009</v>
+        <v>509.96182720000007</v>
       </c>
       <c r="AE3" s="3">
         <f>AD3*1.06</f>
-        <v>546.16312083200012</v>
+        <v>540.55953683200005</v>
       </c>
       <c r="AF3" s="3">
         <f>AE3*1.04</f>
-        <v>568.00964566528012</v>
+        <v>562.18191830528008</v>
       </c>
       <c r="AG3" s="3">
         <f>AF3*1.03</f>
-        <v>585.04993503523849</v>
+        <v>579.04737585443854</v>
       </c>
       <c r="AH3" s="3">
         <f>AG3*1.02</f>
-        <v>596.75093373594325</v>
+        <v>590.62832337152736</v>
       </c>
       <c r="AI3" s="3">
         <f t="shared" ref="AI3:AL4" si="1">AH3*1.02</f>
-        <v>608.68595241066214</v>
+        <v>602.4408898389579</v>
       </c>
       <c r="AJ3" s="3">
         <f t="shared" si="1"/>
-        <v>620.85967145887537</v>
+        <v>614.48970763573709</v>
       </c>
       <c r="AK3" s="3">
         <f t="shared" si="1"/>
-        <v>633.27686488805284</v>
+        <v>626.77950178845185</v>
       </c>
       <c r="AL3" s="3">
         <f t="shared" si="1"/>
-        <v>645.94240218581388</v>
+        <v>639.31509182422087</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1235,8 +1231,7 @@
         <v>46.6</v>
       </c>
       <c r="T4" s="11">
-        <f>P4*1.07</f>
-        <v>47.615000000000002</v>
+        <v>49.6</v>
       </c>
       <c r="U4" s="11">
         <f t="shared" ref="U4" si="2">Q4*1.07</f>
@@ -1264,47 +1259,47 @@
       </c>
       <c r="AB4" s="3">
         <f t="shared" ref="AB4:AB5" si="5">SUM(S4:V4)</f>
-        <v>197.102</v>
+        <v>199.08699999999999</v>
       </c>
       <c r="AC4" s="3">
         <f>AB4*1.05</f>
-        <v>206.95710000000003</v>
+        <v>209.04134999999999</v>
       </c>
       <c r="AD4" s="3">
         <f>AC4*1.04</f>
-        <v>215.23538400000004</v>
+        <v>217.40300400000001</v>
       </c>
       <c r="AE4" s="3">
         <f>AD4*1.03</f>
-        <v>221.69244552000004</v>
+        <v>223.92509412000001</v>
       </c>
       <c r="AF4" s="3">
         <f>AE4*1.02</f>
-        <v>226.12629443040004</v>
+        <v>228.40359600240001</v>
       </c>
       <c r="AG4" s="3">
         <f t="shared" ref="AG4:AH4" si="6">AF4*1.02</f>
-        <v>230.64882031900805</v>
+        <v>232.97166792244801</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="6"/>
-        <v>235.26179672538822</v>
+        <v>237.63110128089696</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="1"/>
-        <v>239.96703265989598</v>
+        <v>242.3837233065149</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="1"/>
-        <v>244.76637331309391</v>
+        <v>247.23139777264521</v>
       </c>
       <c r="AK4" s="3">
         <f t="shared" si="1"/>
-        <v>249.66170077935578</v>
+        <v>252.17602572809813</v>
       </c>
       <c r="AL4" s="3">
         <f t="shared" si="1"/>
-        <v>254.6549347949429</v>
+        <v>257.2195462426601</v>
       </c>
     </row>
     <row r="5" spans="2:38" x14ac:dyDescent="0.3">
@@ -1363,16 +1358,13 @@
         <v>0.5</v>
       </c>
       <c r="T5" s="11">
-        <f t="shared" ref="T5:V5" si="7">P5*0.3</f>
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="U5" s="11">
-        <f t="shared" si="7"/>
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="V5" s="11">
-        <f t="shared" si="7"/>
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="X5" s="3">
         <f>SUM(C5:F5)</f>
@@ -1392,7 +1384,7 @@
       </c>
       <c r="AB5" s="3">
         <f t="shared" si="5"/>
-        <v>0.77</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="3">
         <v>0</v>
@@ -1430,51 +1422,51 @@
         <v>23</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6" si="8">SUM(F3:F5)</f>
+        <f t="shared" ref="F6" si="7">SUM(F3:F5)</f>
         <v>72.7</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" ref="G6" si="9">SUM(G3:G5)</f>
+        <f t="shared" ref="G6" si="8">SUM(G3:G5)</f>
         <v>71.599999999999994</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" ref="H6" si="10">SUM(H3:H5)</f>
+        <f t="shared" ref="H6" si="9">SUM(H3:H5)</f>
         <v>77.800000000000011</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:Q6" si="11">SUM(I3:I5)</f>
+        <f t="shared" ref="I6:Q6" si="10">SUM(I3:I5)</f>
         <v>85.3</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>96.3</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>87</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>94.199999999999989</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>102.6</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>113</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>101.8</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>109.69999999999999</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>123.19999999999999</v>
       </c>
       <c r="R6" s="3">
@@ -1482,20 +1474,20 @@
         <v>145.79999999999998</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" ref="S6:V6" si="12">SUM(S3:S5)</f>
+        <f t="shared" ref="S6:V6" si="11">SUM(S3:S5)</f>
         <v>142.69999999999999</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="12"/>
-        <v>144.69499999999999</v>
+        <f t="shared" si="11"/>
+        <v>143</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="12"/>
-        <v>147.107</v>
+        <f t="shared" si="11"/>
+        <v>147.577</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="12"/>
-        <v>153.23699999999999</v>
+        <f t="shared" si="11"/>
+        <v>153.67699999999999</v>
       </c>
       <c r="X6" s="3">
         <v>251</v>
@@ -1513,47 +1505,47 @@
       </c>
       <c r="AB6" s="3">
         <f>SUM(S6:V6)</f>
-        <v>587.73899999999992</v>
+        <v>586.95399999999995</v>
       </c>
       <c r="AC6" s="3">
         <f>SUM(AC3:AC5)</f>
-        <v>667.00016000000005</v>
+        <v>664.36441000000002</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" ref="AD6:AL6" si="13">SUM(AD3:AD5)</f>
-        <v>730.48361120000015</v>
+        <f t="shared" ref="AD6:AL6" si="12">SUM(AD3:AD5)</f>
+        <v>727.36483120000003</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="13"/>
-        <v>767.8555663520001</v>
+        <f t="shared" si="12"/>
+        <v>764.48463095200009</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="13"/>
-        <v>794.1359400956801</v>
+        <f t="shared" si="12"/>
+        <v>790.58551430768011</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="13"/>
-        <v>815.69875535424649</v>
+        <f t="shared" si="12"/>
+        <v>812.01904377688652</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="13"/>
-        <v>832.01273046133144</v>
+        <f t="shared" si="12"/>
+        <v>828.25942465242429</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="13"/>
-        <v>848.65298507055809</v>
+        <f t="shared" si="12"/>
+        <v>844.82461314547277</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="13"/>
-        <v>865.6260447719693</v>
+        <f t="shared" si="12"/>
+        <v>861.7211054083823</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="13"/>
-        <v>882.93856566740862</v>
+        <f t="shared" si="12"/>
+        <v>878.95552751654998</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="13"/>
-        <v>900.59733698075684</v>
+        <f t="shared" si="12"/>
+        <v>896.53463806688092</v>
       </c>
     </row>
     <row r="7" spans="2:38" x14ac:dyDescent="0.3">
@@ -1594,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="T7" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U7" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X7" s="3">
         <v>0.5</v>
@@ -1618,108 +1610,78 @@
       </c>
       <c r="AB7" s="3">
         <f>SUM(S7:V7)</f>
-        <v>1.5</v>
-      </c>
-      <c r="AC7" s="3">
-        <f t="shared" ref="AC7:AF7" si="14">AB7*1.2</f>
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="AD7" s="3">
-        <f t="shared" si="14"/>
-        <v>2.1599999999999997</v>
-      </c>
-      <c r="AE7" s="3">
-        <f t="shared" si="14"/>
-        <v>2.5919999999999996</v>
-      </c>
-      <c r="AF7" s="3">
-        <f t="shared" si="14"/>
-        <v>3.1103999999999994</v>
-      </c>
-      <c r="AG7" s="3">
-        <f>AF7*1.1</f>
-        <v>3.4214399999999996</v>
-      </c>
-      <c r="AH7" s="3">
-        <f t="shared" ref="AH7:AL7" si="15">AG7*1.1</f>
-        <v>3.7635839999999998</v>
-      </c>
-      <c r="AI7" s="3">
-        <f t="shared" si="15"/>
-        <v>4.1399423999999998</v>
-      </c>
-      <c r="AJ7" s="3">
-        <f t="shared" si="15"/>
-        <v>4.5539366399999999</v>
-      </c>
-      <c r="AK7" s="3">
-        <f t="shared" si="15"/>
-        <v>5.0093303040000006</v>
-      </c>
-      <c r="AL7" s="3">
-        <f t="shared" si="15"/>
-        <v>5.5102633344000012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
     </row>
     <row r="8" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" ref="I8:P8" si="16">I6+I7</f>
+        <f t="shared" ref="I8:P8" si="13">I6+I7</f>
         <v>85.399999999999991</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>96.399999999999991</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>87.1</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>94.299999999999983</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>102.6</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>113.5</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>102.1</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>110.99999999999999</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" ref="Q8:V8" si="17">Q6+Q7</f>
+        <f t="shared" ref="Q8:V8" si="14">Q6+Q7</f>
         <v>123.89999999999999</v>
       </c>
       <c r="R8" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>145.89999999999998</v>
       </c>
       <c r="S8" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>142.69999999999999</v>
       </c>
       <c r="T8" s="8">
-        <f t="shared" si="17"/>
-        <v>145.19499999999999</v>
+        <f t="shared" si="14"/>
+        <v>143</v>
       </c>
       <c r="U8" s="8">
-        <f t="shared" si="17"/>
-        <v>147.607</v>
+        <f t="shared" si="14"/>
+        <v>147.577</v>
       </c>
       <c r="V8" s="8">
-        <f t="shared" si="17"/>
-        <v>153.73699999999999</v>
+        <f t="shared" si="14"/>
+        <v>153.67699999999999</v>
       </c>
       <c r="X8" s="8">
         <f>X6+X7</f>
@@ -1739,47 +1701,47 @@
       </c>
       <c r="AB8" s="8">
         <f>AB6+AB7</f>
-        <v>589.23899999999992</v>
+        <v>586.95399999999995</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AL8" si="18">AC6+AC7</f>
-        <v>668.80016000000001</v>
+        <f t="shared" ref="AC8:AL8" si="15">AC6+AC7</f>
+        <v>664.36441000000002</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="18"/>
-        <v>732.64361120000012</v>
+        <f t="shared" si="15"/>
+        <v>727.36483120000003</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" si="18"/>
-        <v>770.44756635200008</v>
+        <f t="shared" si="15"/>
+        <v>764.48463095200009</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" si="18"/>
-        <v>797.24634009568013</v>
+        <f t="shared" si="15"/>
+        <v>790.58551430768011</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="18"/>
-        <v>819.12019535424645</v>
+        <f t="shared" si="15"/>
+        <v>812.01904377688652</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="18"/>
-        <v>835.77631446133148</v>
+        <f t="shared" si="15"/>
+        <v>828.25942465242429</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="18"/>
-        <v>852.79292747055808</v>
+        <f t="shared" si="15"/>
+        <v>844.82461314547277</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="18"/>
-        <v>870.17998141196927</v>
+        <f t="shared" si="15"/>
+        <v>861.7211054083823</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" si="18"/>
-        <v>887.94789597140857</v>
+        <f t="shared" si="15"/>
+        <v>878.95552751654998</v>
       </c>
       <c r="AL8" s="8">
-        <f t="shared" si="18"/>
-        <v>906.10760031515679</v>
+        <f t="shared" si="15"/>
+        <v>896.53463806688092</v>
       </c>
     </row>
     <row r="9" spans="2:38" x14ac:dyDescent="0.3">
@@ -1820,16 +1782,15 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" ref="T9" si="19">T8*0.02</f>
-        <v>2.9038999999999997</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" ref="U9" si="20">U8*0.02</f>
-        <v>2.95214</v>
+        <f t="shared" ref="U9" si="16">U8*0.02</f>
+        <v>2.9515400000000001</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" ref="V9" si="21">V8*0.02</f>
-        <v>3.0747399999999998</v>
+        <f t="shared" ref="V9" si="17">V8*0.02</f>
+        <v>3.0735399999999999</v>
       </c>
       <c r="X9" s="3">
         <v>4.5</v>
@@ -1842,12 +1803,12 @@
         <v>3.1</v>
       </c>
       <c r="AA9" s="3">
-        <f t="shared" ref="AA9:AA11" si="22">SUM(O9:R9)</f>
+        <f t="shared" ref="AA9:AA11" si="18">SUM(O9:R9)</f>
         <v>10</v>
       </c>
       <c r="AB9" s="3">
         <f>SUM(S9:V9)</f>
-        <v>11.13078</v>
+        <v>10.525079999999999</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -1898,16 +1859,15 @@
         <v>0.9</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" ref="T10:V10" si="23">T8*0.01</f>
-        <v>1.4519499999999999</v>
+        <v>1.5</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" si="23"/>
-        <v>1.47607</v>
+        <f t="shared" ref="U10:V10" si="19">U8*0.01</f>
+        <v>1.47577</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" si="23"/>
-        <v>1.5373699999999999</v>
+        <f t="shared" si="19"/>
+        <v>1.53677</v>
       </c>
       <c r="X10" s="3">
         <v>3.7</v>
@@ -1920,12 +1880,12 @@
         <v>4.3000000000000007</v>
       </c>
       <c r="AA10" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>3.9</v>
       </c>
       <c r="AB10" s="3">
         <f>SUM(S10:V10)</f>
-        <v>5.3653899999999997</v>
+        <v>5.4125399999999999</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1976,16 +1936,15 @@
         <v>47.5</v>
       </c>
       <c r="T11" s="3">
-        <f>T8*0.33</f>
-        <v>47.914349999999999</v>
+        <v>47.1</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" ref="U11:V11" si="24">U8*0.33</f>
-        <v>48.71031</v>
+        <f t="shared" ref="U11:V11" si="20">U8*0.33</f>
+        <v>48.700410000000005</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" si="24"/>
-        <v>50.73321</v>
+        <f t="shared" si="20"/>
+        <v>50.713410000000003</v>
       </c>
       <c r="X11" s="3">
         <v>5.5</v>
@@ -1998,12 +1957,12 @@
         <v>85.899999999999991</v>
       </c>
       <c r="AA11" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>118.6</v>
       </c>
       <c r="AB11" s="3">
         <f>SUM(S11:V11)</f>
-        <v>194.85786999999999</v>
+        <v>194.01382000000001</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2021,60 +1980,60 @@
         <v>29</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" ref="I12:S12" si="25">I9+I10+I11</f>
+        <f t="shared" ref="I12:S12" si="21">I9+I10+I11</f>
         <v>15.700000000000001</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>19</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>16.899999999999999</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>22.599999999999998</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>25.2</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>28.6</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>24.1</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>27.7</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>47.7</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>50.6</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ref="T12" si="26">T9+T10+T11</f>
-        <v>52.270199999999996</v>
+        <f t="shared" ref="T12" si="22">T9+T10+T11</f>
+        <v>50.9</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ref="U12" si="27">U9+U10+U11</f>
-        <v>53.13852</v>
+        <f t="shared" ref="U12" si="23">U9+U10+U11</f>
+        <v>53.127720000000004</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ref="V12" si="28">V9+V10+V11</f>
-        <v>55.345320000000001</v>
+        <f t="shared" ref="V12" si="24">V9+V10+V11</f>
+        <v>55.323720000000002</v>
       </c>
       <c r="X12" s="3">
         <f>X9+X10+X11</f>
@@ -2094,47 +2053,47 @@
       </c>
       <c r="AB12" s="3">
         <f>AB9+AB10+AB11</f>
-        <v>211.35404</v>
+        <v>209.95144000000002</v>
       </c>
       <c r="AC12" s="3">
-        <f t="shared" ref="AC12:AL12" si="29">AC8-AC13</f>
-        <v>247.45605920000003</v>
+        <f t="shared" ref="AC12:AL12" si="25">AC8-AC13</f>
+        <v>245.81483170000001</v>
       </c>
       <c r="AD12" s="3">
-        <f t="shared" si="29"/>
-        <v>271.07813614400004</v>
+        <f t="shared" si="25"/>
+        <v>269.12498754400002</v>
       </c>
       <c r="AE12" s="3">
-        <f t="shared" si="29"/>
-        <v>285.06559955024005</v>
+        <f t="shared" si="25"/>
+        <v>282.85931345224003</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="29"/>
-        <v>294.98114583540166</v>
+        <f t="shared" si="25"/>
+        <v>292.51664029384165</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="29"/>
-        <v>303.07447228107117</v>
+        <f t="shared" si="25"/>
+        <v>300.447046197448</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="29"/>
-        <v>309.23723635069268</v>
+        <f t="shared" si="25"/>
+        <v>306.45598712139702</v>
       </c>
       <c r="AI12" s="3">
-        <f t="shared" si="29"/>
-        <v>315.53338316410645</v>
+        <f t="shared" si="25"/>
+        <v>312.58510686382488</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="29"/>
-        <v>321.96659312242866</v>
+        <f t="shared" si="25"/>
+        <v>318.83680900110141</v>
       </c>
       <c r="AK12" s="3">
-        <f t="shared" si="29"/>
-        <v>328.54072150942113</v>
+        <f t="shared" si="25"/>
+        <v>325.21354518112344</v>
       </c>
       <c r="AL12" s="3">
-        <f t="shared" si="29"/>
-        <v>335.25981211660803</v>
+        <f t="shared" si="25"/>
+        <v>331.71781608474589</v>
       </c>
     </row>
     <row r="13" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2142,60 +2101,60 @@
         <v>30</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" ref="I13:S13" si="30">I8-I12</f>
+        <f t="shared" ref="I13:S13" si="26">I8-I12</f>
         <v>69.699999999999989</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>77.399999999999991</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>70.199999999999989</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>71.699999999999989</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>77.399999999999991</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>84.9</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>78</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>83.299999999999983</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>90.899999999999991</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>98.199999999999974</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>92.1</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="31">T8-T12</f>
-        <v>92.924800000000005</v>
+        <f t="shared" ref="T13" si="27">T8-T12</f>
+        <v>92.1</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13" si="32">U8-U12</f>
-        <v>94.46848</v>
+        <f t="shared" ref="U13" si="28">U8-U12</f>
+        <v>94.449279999999987</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="33">V8-V12</f>
-        <v>98.391679999999994</v>
+        <f t="shared" ref="V13" si="29">V8-V12</f>
+        <v>98.353279999999984</v>
       </c>
       <c r="X13" s="8">
         <f>X8-X12</f>
@@ -2215,47 +2174,47 @@
       </c>
       <c r="AB13" s="8">
         <f>AB8-AB12</f>
-        <v>377.88495999999992</v>
+        <v>377.0025599999999</v>
       </c>
       <c r="AC13" s="8">
         <f>AC8*0.63</f>
-        <v>421.34410079999998</v>
+        <v>418.54957830000001</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13:AL13" si="34">AD8*0.63</f>
-        <v>461.56547505600008</v>
+        <f t="shared" ref="AD13:AL13" si="30">AD8*0.63</f>
+        <v>458.23984365600001</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="34"/>
-        <v>485.38196680176003</v>
+        <f t="shared" si="30"/>
+        <v>481.62531749976006</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="34"/>
-        <v>502.26519426027846</v>
+        <f t="shared" si="30"/>
+        <v>498.06887401383847</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="34"/>
-        <v>516.04572307317528</v>
+        <f t="shared" si="30"/>
+        <v>511.57199757943852</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="34"/>
-        <v>526.5390781106388</v>
+        <f t="shared" si="30"/>
+        <v>521.80343753102727</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="34"/>
-        <v>537.25954430645163</v>
+        <f t="shared" si="30"/>
+        <v>532.23950628164789</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="34"/>
-        <v>548.2133882895406</v>
+        <f t="shared" si="30"/>
+        <v>542.88429640728089</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="34"/>
-        <v>559.40717446198744</v>
+        <f t="shared" si="30"/>
+        <v>553.74198233542654</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="34"/>
-        <v>570.84778819854876</v>
+        <f t="shared" si="30"/>
+        <v>564.81682198213502</v>
       </c>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.3">
@@ -2296,8 +2255,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="T14" s="3">
-        <f>P14*0.9</f>
-        <v>17.82</v>
+        <v>18.7</v>
       </c>
       <c r="U14" s="3">
         <f>Q14*0.8</f>
@@ -2322,48 +2280,48 @@
         <v>77.099999999999994</v>
       </c>
       <c r="AB14" s="3">
-        <f>SUM(S14:V14)</f>
-        <v>72.67</v>
+        <f t="shared" ref="AB14:AB20" si="31">SUM(S14:V14)</f>
+        <v>73.55</v>
       </c>
       <c r="AC14" s="3">
         <f>AB14*1.08</f>
-        <v>78.48360000000001</v>
+        <v>79.433999999999997</v>
       </c>
       <c r="AD14" s="3">
         <f>AC14*1.05</f>
-        <v>82.407780000000017</v>
+        <v>83.405699999999996</v>
       </c>
       <c r="AE14" s="3">
         <f>AD14*1.04</f>
-        <v>85.704091200000022</v>
+        <v>86.741928000000001</v>
       </c>
       <c r="AF14" s="3">
         <f>AE14*1.03</f>
-        <v>88.275213936000029</v>
+        <v>89.344185840000009</v>
       </c>
       <c r="AG14" s="3">
         <f>AF14*1.03</f>
-        <v>90.923470354080038</v>
+        <v>92.02451141520001</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" ref="AH14:AL14" si="35">AG14*1.01</f>
-        <v>91.832705057620842</v>
+        <f t="shared" ref="AH14:AL14" si="32">AG14*1.01</f>
+        <v>92.944756529352006</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="35"/>
-        <v>92.751032108197052</v>
+        <f t="shared" si="32"/>
+        <v>93.874204094645521</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="35"/>
-        <v>93.67854242927902</v>
+        <f t="shared" si="32"/>
+        <v>94.812946135591972</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="35"/>
-        <v>94.615327853571813</v>
+        <f t="shared" si="32"/>
+        <v>95.76107559694789</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="35"/>
-        <v>95.561481132107531</v>
+        <f t="shared" si="32"/>
+        <v>96.718686352917373</v>
       </c>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.3">
@@ -2385,14 +2343,19 @@
       <c r="S15" s="3">
         <v>6</v>
       </c>
-      <c r="T15" s="3"/>
+      <c r="T15" s="3">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
+      <c r="AB15" s="3">
+        <f t="shared" si="31"/>
+        <v>14.8</v>
+      </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
@@ -2442,16 +2405,15 @@
         <v>34.200000000000003</v>
       </c>
       <c r="T16" s="3">
-        <f>T8*0.24</f>
-        <v>34.846799999999995</v>
+        <v>34</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" ref="U16:V16" si="36">U8*0.24</f>
-        <v>35.42568</v>
+        <f t="shared" ref="U16:V16" si="33">U8*0.24</f>
+        <v>35.418479999999995</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" si="36"/>
-        <v>36.896879999999996</v>
+        <f t="shared" si="33"/>
+        <v>36.882479999999994</v>
       </c>
       <c r="X16" s="3">
         <v>120.9</v>
@@ -2468,48 +2430,48 @@
         <v>131.9</v>
       </c>
       <c r="AB16" s="3">
-        <f>SUM(S16:V16)</f>
-        <v>141.36935999999997</v>
+        <f t="shared" si="31"/>
+        <v>140.50095999999999</v>
       </c>
       <c r="AC16" s="3">
         <f>AC8*0.23</f>
-        <v>153.82403680000002</v>
+        <v>152.8038143</v>
       </c>
       <c r="AD16" s="3">
         <f>AD8*0.22</f>
-        <v>161.18159446400003</v>
+        <v>160.02026286400002</v>
       </c>
       <c r="AE16" s="3">
-        <f t="shared" ref="AE16:AL16" si="37">AE8*0.22</f>
-        <v>169.49846459744001</v>
+        <f t="shared" ref="AE16:AL16" si="34">AE8*0.22</f>
+        <v>168.18661880944003</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" si="37"/>
-        <v>175.39419482104964</v>
+        <f t="shared" si="34"/>
+        <v>173.92881314768962</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="37"/>
-        <v>180.20644297793422</v>
+        <f t="shared" si="34"/>
+        <v>178.64418963091504</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="37"/>
-        <v>183.87078918149294</v>
+        <f t="shared" si="34"/>
+        <v>182.21707342353335</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="37"/>
-        <v>187.61444404352278</v>
+        <f t="shared" si="34"/>
+        <v>185.86141489200401</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="37"/>
-        <v>191.43959591063324</v>
+        <f t="shared" si="34"/>
+        <v>189.57864318984412</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="37"/>
-        <v>195.34853711370988</v>
+        <f t="shared" si="34"/>
+        <v>193.370216053641</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="37"/>
-        <v>199.3436720693345</v>
+        <f t="shared" si="34"/>
+        <v>197.2376203747138</v>
       </c>
     </row>
     <row r="17" spans="2:144" x14ac:dyDescent="0.3">
@@ -2550,7 +2512,7 @@
         <v>0.2</v>
       </c>
       <c r="T17" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U17" s="3">
         <v>0</v>
@@ -2573,8 +2535,8 @@
         <v>-0.8</v>
       </c>
       <c r="AB17" s="3">
-        <f>SUM(S17:V17)</f>
-        <v>0.2</v>
+        <f t="shared" si="31"/>
+        <v>0.4</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
@@ -2645,7 +2607,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="T18" s="3">
-        <v>4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="U18" s="3">
         <v>5</v>
@@ -2668,49 +2630,19 @@
         <v>15.6</v>
       </c>
       <c r="AB18" s="3">
-        <f>SUM(S18:V18)</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="AC18" s="3">
-        <f t="shared" ref="AC18:AL18" si="38">AB18*1.01</f>
-        <v>18.584</v>
-      </c>
-      <c r="AD18" s="3">
-        <f t="shared" si="38"/>
-        <v>18.769839999999999</v>
-      </c>
-      <c r="AE18" s="3">
-        <f t="shared" si="38"/>
-        <v>18.957538399999997</v>
-      </c>
-      <c r="AF18" s="3">
-        <f t="shared" si="38"/>
-        <v>19.147113783999998</v>
-      </c>
-      <c r="AG18" s="3">
-        <f t="shared" si="38"/>
-        <v>19.338584921839999</v>
-      </c>
-      <c r="AH18" s="3">
-        <f t="shared" si="38"/>
-        <v>19.531970771058401</v>
-      </c>
-      <c r="AI18" s="3">
-        <f t="shared" si="38"/>
-        <v>19.727290478768985</v>
-      </c>
-      <c r="AJ18" s="3">
-        <f t="shared" si="38"/>
-        <v>19.924563383556677</v>
-      </c>
-      <c r="AK18" s="3">
-        <f t="shared" si="38"/>
-        <v>20.123809017392244</v>
-      </c>
-      <c r="AL18" s="3">
-        <f t="shared" si="38"/>
-        <v>20.325047107566167</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>19</v>
+      </c>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
     </row>
     <row r="19" spans="2:144" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
@@ -2729,14 +2661,19 @@
       <c r="S19" s="3">
         <v>0.7</v>
       </c>
-      <c r="T19" s="3"/>
+      <c r="T19" s="3">
+        <v>0.6</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
+      <c r="AB19" s="3">
+        <f t="shared" si="31"/>
+        <v>1.2999999999999998</v>
+      </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
@@ -2790,7 +2727,7 @@
         <v>7.8</v>
       </c>
       <c r="T20" s="3">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="U20" s="3">
         <v>9</v>
@@ -2815,48 +2752,48 @@
         <v>31.799999999999997</v>
       </c>
       <c r="AB20" s="3">
-        <f>SUM(S20:V20)</f>
-        <v>34.799999999999997</v>
+        <f t="shared" si="31"/>
+        <v>34.299999999999997</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" ref="AC20:AL20" si="39">AB20*1.01</f>
-        <v>35.147999999999996</v>
+        <f t="shared" ref="AC20:AL20" si="35">AB20*1.01</f>
+        <v>34.643000000000001</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="39"/>
-        <v>35.499479999999998</v>
+        <f t="shared" si="35"/>
+        <v>34.989429999999999</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="39"/>
-        <v>35.854474799999998</v>
+        <f t="shared" si="35"/>
+        <v>35.339324300000001</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="39"/>
-        <v>36.213019547999998</v>
+        <f t="shared" si="35"/>
+        <v>35.692717543000001</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="39"/>
-        <v>36.575149743479997</v>
+        <f t="shared" si="35"/>
+        <v>36.049644718430002</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="39"/>
-        <v>36.940901240914798</v>
+        <f t="shared" si="35"/>
+        <v>36.410141165614306</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="39"/>
-        <v>37.310310253323948</v>
+        <f t="shared" si="35"/>
+        <v>36.774242577270449</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="39"/>
-        <v>37.683413355857191</v>
+        <f t="shared" si="35"/>
+        <v>37.141985003043153</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="39"/>
-        <v>38.060247489415765</v>
+        <f t="shared" si="35"/>
+        <v>37.513404853073588</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="39"/>
-        <v>38.440849964309926</v>
+        <f t="shared" si="35"/>
+        <v>37.888538901604328</v>
       </c>
     </row>
     <row r="21" spans="2:144" x14ac:dyDescent="0.3">
@@ -2864,60 +2801,60 @@
         <v>36</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:P21" si="40">SUM(I14:I20)</f>
+        <f t="shared" ref="I21:P21" si="36">SUM(I14:I20)</f>
         <v>53.499999999999993</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>65.7</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>56.4</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>59.199999999999996</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>61.4</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>64.5</v>
       </c>
       <c r="O21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>58.600000000000009</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>61.399999999999991</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" ref="Q21:R21" si="41">SUM(Q14:Q20)</f>
+        <f t="shared" ref="Q21:R21" si="37">SUM(Q14:Q20)</f>
         <v>67.5</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="37"/>
         <v>70.7</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" ref="S21:V21" si="42">SUM(S14:S20)</f>
+        <f t="shared" ref="S21:V21" si="38">SUM(S14:S20)</f>
         <v>70.900000000000006</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="42"/>
-        <v>64.666799999999995</v>
+        <f t="shared" si="38"/>
+        <v>74.399999999999991</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" si="42"/>
-        <v>67.985680000000002</v>
+        <f t="shared" si="38"/>
+        <v>67.97847999999999</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" si="42"/>
-        <v>70.586879999999994</v>
+        <f t="shared" si="38"/>
+        <v>70.572479999999999</v>
       </c>
       <c r="X21" s="3">
         <f>SUM(X14:X20)</f>
@@ -2937,47 +2874,47 @@
       </c>
       <c r="AB21" s="3">
         <f>SUM(AB14:AB20)</f>
-        <v>267.43935999999997</v>
+        <v>283.85095999999999</v>
       </c>
       <c r="AC21" s="3">
-        <f t="shared" ref="AC21:AL21" si="43">SUM(AC14:AC20)</f>
-        <v>286.03963680000004</v>
+        <f t="shared" ref="AC21:AL21" si="39">SUM(AC14:AC20)</f>
+        <v>266.8808143</v>
       </c>
       <c r="AD21" s="3">
-        <f t="shared" si="43"/>
-        <v>297.85869446400005</v>
+        <f t="shared" si="39"/>
+        <v>278.41539286400001</v>
       </c>
       <c r="AE21" s="3">
-        <f t="shared" si="43"/>
-        <v>310.01456899743999</v>
+        <f t="shared" si="39"/>
+        <v>290.26787110944002</v>
       </c>
       <c r="AF21" s="3">
-        <f t="shared" si="43"/>
-        <v>319.02954208904964</v>
+        <f t="shared" si="39"/>
+        <v>298.96571653068963</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" si="43"/>
-        <v>327.04364799733423</v>
+        <f t="shared" si="39"/>
+        <v>306.71834576454506</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="43"/>
-        <v>332.17636625108696</v>
+        <f t="shared" si="39"/>
+        <v>311.57197111849962</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="43"/>
-        <v>337.40307688381273</v>
+        <f t="shared" si="39"/>
+        <v>316.50986156391997</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="43"/>
-        <v>342.72611507932612</v>
+        <f t="shared" si="39"/>
+        <v>321.53357432847923</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="43"/>
-        <v>348.14792147408969</v>
+        <f t="shared" si="39"/>
+        <v>326.64469650366249</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="43"/>
-        <v>353.67105027331809</v>
+        <f t="shared" si="39"/>
+        <v>331.84484562923546</v>
       </c>
     </row>
     <row r="22" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2985,60 +2922,60 @@
         <v>37</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" ref="I22:P22" si="44">I13-I21</f>
+        <f t="shared" ref="I22:P22" si="40">I13-I21</f>
         <v>16.199999999999996</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>11.699999999999989</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>13.79999999999999</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>12.499999999999993</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>15.999999999999993</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>20.400000000000006</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>21.899999999999991</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" ref="Q22:R22" si="45">Q13-Q21</f>
+        <f t="shared" ref="Q22:R22" si="41">Q13-Q21</f>
         <v>23.399999999999991</v>
       </c>
       <c r="R22" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="41"/>
         <v>27.499999999999972</v>
       </c>
       <c r="S22" s="8">
-        <f t="shared" ref="S22:V22" si="46">S13-S21</f>
+        <f t="shared" ref="S22:V22" si="42">S13-S21</f>
         <v>21.199999999999989</v>
       </c>
       <c r="T22" s="8">
-        <f t="shared" si="46"/>
-        <v>28.25800000000001</v>
+        <f t="shared" si="42"/>
+        <v>17.700000000000003</v>
       </c>
       <c r="U22" s="8">
-        <f t="shared" si="46"/>
-        <v>26.482799999999997</v>
+        <f t="shared" si="42"/>
+        <v>26.470799999999997</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" si="46"/>
-        <v>27.8048</v>
+        <f t="shared" si="42"/>
+        <v>27.780799999999985</v>
       </c>
       <c r="X22" s="8">
         <f>X13-X21</f>
@@ -3058,47 +2995,47 @@
       </c>
       <c r="AB22" s="8">
         <f>AB13-AB21</f>
-        <v>110.44559999999996</v>
+        <v>93.151599999999917</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AL22" si="47">AC13-AC21</f>
-        <v>135.30446399999994</v>
+        <f t="shared" ref="AC22:AL22" si="43">AC13-AC21</f>
+        <v>151.66876400000001</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="47"/>
-        <v>163.70678059200003</v>
+        <f t="shared" si="43"/>
+        <v>179.82445079199999</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="47"/>
-        <v>175.36739780432003</v>
+        <f t="shared" si="43"/>
+        <v>191.35744639032004</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="47"/>
-        <v>183.23565217122882</v>
+        <f t="shared" si="43"/>
+        <v>199.10315748314883</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="47"/>
-        <v>189.00207507584105</v>
+        <f t="shared" si="43"/>
+        <v>204.85365181489345</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="47"/>
-        <v>194.36271185955184</v>
+        <f t="shared" si="43"/>
+        <v>210.23146641252765</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="47"/>
-        <v>199.8564674226389</v>
+        <f t="shared" si="43"/>
+        <v>215.72964471772792</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="47"/>
-        <v>205.48727321021448</v>
+        <f t="shared" si="43"/>
+        <v>221.35072207880165</v>
       </c>
       <c r="AK22" s="8">
-        <f t="shared" si="47"/>
-        <v>211.25925298789775</v>
+        <f t="shared" si="43"/>
+        <v>227.09728583176405</v>
       </c>
       <c r="AL22" s="8">
-        <f t="shared" si="47"/>
-        <v>217.17673792523067</v>
+        <f t="shared" si="43"/>
+        <v>232.97197635289956</v>
       </c>
     </row>
     <row r="23" spans="2:144" x14ac:dyDescent="0.3">
@@ -3142,7 +3079,7 @@
         <v>-0.7</v>
       </c>
       <c r="T23" s="3">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="U23" s="3">
         <v>-2</v>
@@ -3168,47 +3105,47 @@
       </c>
       <c r="AB23" s="3">
         <f>SUM(S23:V23)</f>
-        <v>-6.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AC23" s="3">
         <f>AB23*1.01</f>
-        <v>-6.7670000000000003</v>
+        <v>-5.6559999999999997</v>
       </c>
       <c r="AD23" s="3">
-        <f t="shared" ref="AD23:AL23" si="48">AC23*1.01</f>
-        <v>-6.83467</v>
+        <f t="shared" ref="AD23:AL23" si="44">AC23*1.01</f>
+        <v>-5.7125599999999999</v>
       </c>
       <c r="AE23" s="3">
-        <f t="shared" si="48"/>
-        <v>-6.9030167000000002</v>
+        <f t="shared" si="44"/>
+        <v>-5.7696855999999999</v>
       </c>
       <c r="AF23" s="3">
-        <f t="shared" si="48"/>
-        <v>-6.9720468670000004</v>
+        <f t="shared" si="44"/>
+        <v>-5.8273824559999996</v>
       </c>
       <c r="AG23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.0417673356700003</v>
+        <f t="shared" si="44"/>
+        <v>-5.8856562805599992</v>
       </c>
       <c r="AH23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.1121850090267005</v>
+        <f t="shared" si="44"/>
+        <v>-5.9445128433655992</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.1833068591169678</v>
+        <f t="shared" si="44"/>
+        <v>-6.0039579717992551</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.2551399277081376</v>
+        <f t="shared" si="44"/>
+        <v>-6.0639975515172475</v>
       </c>
       <c r="AK23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.3276913269852191</v>
+        <f t="shared" si="44"/>
+        <v>-6.1246375270324203</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="48"/>
-        <v>-7.4009682402550716</v>
+        <f t="shared" si="44"/>
+        <v>-6.1858839023027441</v>
       </c>
     </row>
     <row r="24" spans="2:144" x14ac:dyDescent="0.3">
@@ -3249,7 +3186,7 @@
         <v>0.1</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -3273,7 +3210,7 @@
       </c>
       <c r="AB24" s="3">
         <f>SUM(S24:V24)</f>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -3375,39 +3312,39 @@
         <v>3.8379999999999996</v>
       </c>
       <c r="AD25" s="3">
-        <f t="shared" ref="AD25:AL25" si="49">AC25*1.01</f>
+        <f t="shared" ref="AD25:AL25" si="45">AC25*1.01</f>
         <v>3.8763799999999997</v>
       </c>
       <c r="AE25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>3.9151437999999996</v>
       </c>
       <c r="AF25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>3.9542952379999998</v>
       </c>
       <c r="AG25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>3.99383819038</v>
       </c>
       <c r="AH25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>4.0337765722838004</v>
       </c>
       <c r="AI25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>4.0741143380066385</v>
       </c>
       <c r="AJ25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>4.1148554813867051</v>
       </c>
       <c r="AK25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>4.1560040362005726</v>
       </c>
       <c r="AL25" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>4.1975640765625784</v>
       </c>
     </row>
@@ -3416,59 +3353,59 @@
         <v>41</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" ref="I26:P26" si="50">SUM(I23:I25)</f>
+        <f t="shared" ref="I26:P26" si="46">SUM(I23:I25)</f>
         <v>1.6</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-8.4</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-4.8</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-2.1999999999999997</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-0.99999999999999989</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-89.100000000000009</v>
       </c>
       <c r="O26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" ref="Q26:R26" si="51">SUM(Q23:Q25)</f>
+        <f t="shared" ref="Q26:R26" si="47">SUM(Q23:Q25)</f>
         <v>0.4</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>-6.3999999999999995</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" ref="S26:V26" si="52">SUM(S23:S25)</f>
+        <f t="shared" ref="S26:V26" si="48">SUM(S23:S25)</f>
         <v>0.20000000000000007</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
-      <c r="U26" s="3">
-        <f t="shared" si="52"/>
-        <v>-1</v>
-      </c>
       <c r="V26" s="3">
-        <f t="shared" si="52"/>
+        <f t="shared" si="48"/>
         <v>-1</v>
       </c>
       <c r="X26" s="3">
@@ -3489,47 +3426,47 @@
       </c>
       <c r="AB26" s="3">
         <f>SUM(AB23:AB25)</f>
-        <v>-2.8000000000000007</v>
+        <v>-1.5</v>
       </c>
       <c r="AC26" s="3">
-        <f t="shared" ref="AC26:AL26" si="53">SUM(AC23:AC25)</f>
-        <v>-2.9290000000000007</v>
+        <f t="shared" ref="AC26:AL26" si="49">SUM(AC23:AC25)</f>
+        <v>-1.8180000000000001</v>
       </c>
       <c r="AD26" s="3">
-        <f t="shared" si="53"/>
-        <v>-2.9582900000000003</v>
+        <f t="shared" si="49"/>
+        <v>-1.8361800000000001</v>
       </c>
       <c r="AE26" s="3">
-        <f t="shared" si="53"/>
-        <v>-2.9878729000000006</v>
+        <f t="shared" si="49"/>
+        <v>-1.8545418000000002</v>
       </c>
       <c r="AF26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.0177516290000006</v>
+        <f t="shared" si="49"/>
+        <v>-1.8730872179999998</v>
       </c>
       <c r="AG26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.0479291452900004</v>
+        <f t="shared" si="49"/>
+        <v>-1.8918180901799992</v>
       </c>
       <c r="AH26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.0784084367429001</v>
+        <f t="shared" si="49"/>
+        <v>-1.9107362710817988</v>
       </c>
       <c r="AI26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.1091925211103293</v>
+        <f t="shared" si="49"/>
+        <v>-1.9298436337926166</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.1402844463214326</v>
+        <f t="shared" si="49"/>
+        <v>-1.9491420701305424</v>
       </c>
       <c r="AK26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.1716872907846465</v>
+        <f t="shared" si="49"/>
+        <v>-1.9686334908318477</v>
       </c>
       <c r="AL26" s="3">
-        <f t="shared" si="53"/>
-        <v>-3.2034041636924933</v>
+        <f t="shared" si="49"/>
+        <v>-1.9883198257401657</v>
       </c>
     </row>
     <row r="27" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3537,60 +3474,60 @@
         <v>45</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:P27" si="54">I22-I26</f>
+        <f t="shared" ref="I27:P27" si="50">I22-I26</f>
         <v>14.599999999999996</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>20.099999999999987</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>18.599999999999991</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>14.699999999999992</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>16.999999999999993</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>109.50000000000001</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>21.999999999999993</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" ref="Q27:R27" si="55">Q22-Q26</f>
+        <f t="shared" ref="Q27:R27" si="51">Q22-Q26</f>
         <v>22.999999999999993</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>33.89999999999997</v>
       </c>
       <c r="S27" s="8">
-        <f t="shared" ref="S27:V27" si="56">S22-S26</f>
+        <f t="shared" ref="S27:V27" si="52">S22-S26</f>
         <v>20.999999999999989</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" si="56"/>
-        <v>29.25800000000001</v>
+        <f t="shared" si="52"/>
+        <v>17.400000000000002</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="56"/>
-        <v>27.482799999999997</v>
+        <f t="shared" si="52"/>
+        <v>27.470799999999997</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="56"/>
-        <v>28.8048</v>
+        <f t="shared" si="52"/>
+        <v>28.780799999999985</v>
       </c>
       <c r="X27" s="8">
         <f>X22-X26</f>
@@ -3610,47 +3547,47 @@
       </c>
       <c r="AB27" s="8">
         <f>AB22-AB26</f>
-        <v>113.24559999999995</v>
+        <v>94.651599999999917</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AL27" si="57">AC22-AC26</f>
-        <v>138.23346399999994</v>
+        <f t="shared" ref="AC27:AL27" si="53">AC22-AC26</f>
+        <v>153.48676400000002</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="57"/>
-        <v>166.66507059200003</v>
+        <f t="shared" si="53"/>
+        <v>181.66063079200001</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="57"/>
-        <v>178.35527070432005</v>
+        <f t="shared" si="53"/>
+        <v>193.21198819032003</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="57"/>
-        <v>186.25340380022882</v>
+        <f t="shared" si="53"/>
+        <v>200.97624470114883</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="57"/>
-        <v>192.05000422113105</v>
+        <f t="shared" si="53"/>
+        <v>206.74546990507346</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="57"/>
-        <v>197.44112029629474</v>
+        <f t="shared" si="53"/>
+        <v>212.14220268360944</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="57"/>
-        <v>202.96565994374922</v>
+        <f t="shared" si="53"/>
+        <v>217.65948835152054</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="57"/>
-        <v>208.62755765653591</v>
+        <f t="shared" si="53"/>
+        <v>223.29986414893219</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="57"/>
-        <v>214.43094027868239</v>
+        <f t="shared" si="53"/>
+        <v>229.0659193225959</v>
       </c>
       <c r="AL27" s="8">
-        <f t="shared" si="57"/>
-        <v>220.38014208892315</v>
+        <f t="shared" si="53"/>
+        <v>234.96029617863974</v>
       </c>
     </row>
     <row r="28" spans="2:144" x14ac:dyDescent="0.3">
@@ -3691,16 +3628,15 @@
         <v>2.5</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" ref="T28:V28" si="58">T27*0.15</f>
-        <v>4.3887000000000009</v>
+        <v>2.1</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" si="58"/>
-        <v>4.1224199999999991</v>
+        <f t="shared" ref="U28:V28" si="54">U27*0.15</f>
+        <v>4.1206199999999997</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" si="58"/>
-        <v>4.3207199999999997</v>
+        <f t="shared" si="54"/>
+        <v>4.3171199999999974</v>
       </c>
       <c r="X28" s="3">
         <v>0</v>
@@ -3718,47 +3654,47 @@
       </c>
       <c r="AB28" s="3">
         <f>SUM(S28:V28)</f>
-        <v>15.33184</v>
+        <v>13.037739999999998</v>
       </c>
       <c r="AC28" s="3">
-        <f t="shared" ref="AC28:AL28" si="59">AC27*0.15</f>
-        <v>20.73501959999999</v>
+        <f>AC27*0.14</f>
+        <v>21.488146960000005</v>
       </c>
       <c r="AD28" s="3">
-        <f t="shared" si="59"/>
-        <v>24.999760588800005</v>
+        <f t="shared" ref="AD28:AL28" si="55">AD27*0.14</f>
+        <v>25.432488310880004</v>
       </c>
       <c r="AE28" s="3">
-        <f t="shared" si="59"/>
-        <v>26.753290605648008</v>
+        <f t="shared" si="55"/>
+        <v>27.049678346644807</v>
       </c>
       <c r="AF28" s="3">
-        <f t="shared" si="59"/>
-        <v>27.938010570034322</v>
+        <f t="shared" si="55"/>
+        <v>28.136674258160838</v>
       </c>
       <c r="AG28" s="3">
-        <f t="shared" si="59"/>
-        <v>28.807500633169656</v>
+        <f t="shared" si="55"/>
+        <v>28.944365786710289</v>
       </c>
       <c r="AH28" s="3">
-        <f t="shared" si="59"/>
-        <v>29.616168044444208</v>
+        <f t="shared" si="55"/>
+        <v>29.699908375705323</v>
       </c>
       <c r="AI28" s="3">
-        <f t="shared" si="59"/>
-        <v>30.444848991562381</v>
+        <f t="shared" si="55"/>
+        <v>30.472328369212878</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="59"/>
-        <v>31.294133648480386</v>
+        <f t="shared" si="55"/>
+        <v>31.26198098085051</v>
       </c>
       <c r="AK28" s="3">
-        <f t="shared" si="59"/>
-        <v>32.164641041802355</v>
+        <f t="shared" si="55"/>
+        <v>32.069228705163432</v>
       </c>
       <c r="AL28" s="3">
-        <f t="shared" si="59"/>
-        <v>33.057021313338474</v>
+        <f t="shared" si="55"/>
+        <v>32.894441465009564</v>
       </c>
     </row>
     <row r="29" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3766,60 +3702,60 @@
         <v>43</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" ref="I29:P29" si="60">I27-I28</f>
+        <f t="shared" ref="I29:P29" si="56">I27-I28</f>
         <v>9.399999999999995</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>20.799999999999986</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>15.29999999999999</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>13.599999999999993</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>16.799999999999994</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>107.40000000000002</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>14.799999999999992</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="56"/>
         <v>19.199999999999992</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" ref="Q29:R29" si="61">Q27-Q28</f>
+        <f t="shared" ref="Q29:R29" si="57">Q27-Q28</f>
         <v>18.199999999999992</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="57"/>
         <v>28.599999999999969</v>
       </c>
       <c r="S29" s="8">
-        <f t="shared" ref="S29:V29" si="62">S27-S28</f>
+        <f t="shared" ref="S29:V29" si="58">S27-S28</f>
         <v>18.499999999999989</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" si="62"/>
-        <v>24.86930000000001</v>
+        <f t="shared" si="58"/>
+        <v>15.300000000000002</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="62"/>
-        <v>23.360379999999999</v>
+        <f t="shared" si="58"/>
+        <v>23.350179999999998</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="62"/>
-        <v>24.484079999999999</v>
+        <f t="shared" si="58"/>
+        <v>24.463679999999989</v>
       </c>
       <c r="X29" s="8">
         <f>X27-X28</f>
@@ -3839,471 +3775,471 @@
       </c>
       <c r="AB29" s="8">
         <f>AB27-AB28</f>
-        <v>97.913759999999954</v>
+        <v>81.613859999999917</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" ref="AC29:AL29" si="63">AC27-AC28</f>
-        <v>117.49844439999995</v>
+        <f t="shared" ref="AC29:AL29" si="59">AC27-AC28</f>
+        <v>131.99861704000003</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="63"/>
-        <v>141.66531000320003</v>
+        <f t="shared" si="59"/>
+        <v>156.22814248112002</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="63"/>
-        <v>151.60198009867204</v>
+        <f t="shared" si="59"/>
+        <v>166.16230984367522</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="63"/>
-        <v>158.3153932301945</v>
+        <f t="shared" si="59"/>
+        <v>172.83957044298799</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="63"/>
-        <v>163.24250358796138</v>
+        <f t="shared" si="59"/>
+        <v>177.80110411836318</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="63"/>
-        <v>167.82495225185053</v>
+        <f t="shared" si="59"/>
+        <v>182.44229430790412</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="63"/>
-        <v>172.52081095218682</v>
+        <f t="shared" si="59"/>
+        <v>187.18715998230766</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="63"/>
-        <v>177.33342400805552</v>
+        <f t="shared" si="59"/>
+        <v>192.03788316808169</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="63"/>
-        <v>182.26629923688003</v>
+        <f t="shared" si="59"/>
+        <v>196.99669061743248</v>
       </c>
       <c r="AL29" s="8">
-        <f t="shared" si="63"/>
-        <v>187.32312077558467</v>
+        <f t="shared" si="59"/>
+        <v>202.06585471363019</v>
       </c>
       <c r="AM29" s="1">
         <f>AL29*(1+$AO$40)</f>
-        <v>185.44988956782882</v>
+        <v>200.04519616649389</v>
       </c>
       <c r="AN29" s="1">
-        <f t="shared" ref="AN29:CY29" si="64">AM29*(1+$AO$40)</f>
-        <v>183.59539067215053</v>
+        <f t="shared" ref="AN29:CY29" si="60">AM29*(1+$AO$40)</f>
+        <v>198.04474420482896</v>
       </c>
       <c r="AO29" s="1">
-        <f t="shared" si="64"/>
-        <v>181.75943676542903</v>
+        <f t="shared" si="60"/>
+        <v>196.06429676278066</v>
       </c>
       <c r="AP29" s="1">
-        <f t="shared" si="64"/>
-        <v>179.94184239777474</v>
+        <f t="shared" si="60"/>
+        <v>194.10365379515284</v>
       </c>
       <c r="AQ29" s="1">
-        <f t="shared" si="64"/>
-        <v>178.14242397379698</v>
+        <f t="shared" si="60"/>
+        <v>192.1626172572013</v>
       </c>
       <c r="AR29" s="1">
-        <f t="shared" si="64"/>
-        <v>176.36099973405902</v>
+        <f t="shared" si="60"/>
+        <v>190.24099108462929</v>
       </c>
       <c r="AS29" s="1">
-        <f t="shared" si="64"/>
-        <v>174.59738973671844</v>
+        <f t="shared" si="60"/>
+        <v>188.33858117378298</v>
       </c>
       <c r="AT29" s="1">
-        <f t="shared" si="64"/>
-        <v>172.85141583935126</v>
+        <f t="shared" si="60"/>
+        <v>186.45519536204515</v>
       </c>
       <c r="AU29" s="1">
-        <f t="shared" si="64"/>
-        <v>171.12290168095774</v>
+        <f t="shared" si="60"/>
+        <v>184.59064340842468</v>
       </c>
       <c r="AV29" s="1">
-        <f t="shared" si="64"/>
-        <v>169.41167266414817</v>
+        <f t="shared" si="60"/>
+        <v>182.74473697434044</v>
       </c>
       <c r="AW29" s="1">
-        <f t="shared" si="64"/>
-        <v>167.71755593750669</v>
+        <f t="shared" si="60"/>
+        <v>180.91728960459704</v>
       </c>
       <c r="AX29" s="1">
-        <f t="shared" si="64"/>
-        <v>166.04038037813163</v>
+        <f t="shared" si="60"/>
+        <v>179.10811670855108</v>
       </c>
       <c r="AY29" s="1">
-        <f t="shared" si="64"/>
-        <v>164.37997657435031</v>
+        <f t="shared" si="60"/>
+        <v>177.31703554146557</v>
       </c>
       <c r="AZ29" s="1">
-        <f t="shared" si="64"/>
-        <v>162.73617680860681</v>
+        <f t="shared" si="60"/>
+        <v>175.54386518605091</v>
       </c>
       <c r="BA29" s="1">
-        <f t="shared" si="64"/>
-        <v>161.10881504052074</v>
+        <f t="shared" si="60"/>
+        <v>173.78842653419039</v>
       </c>
       <c r="BB29" s="1">
-        <f t="shared" si="64"/>
-        <v>159.49772689011553</v>
+        <f t="shared" si="60"/>
+        <v>172.05054226884849</v>
       </c>
       <c r="BC29" s="1">
-        <f t="shared" si="64"/>
-        <v>157.90274962121438</v>
+        <f t="shared" si="60"/>
+        <v>170.33003684616</v>
       </c>
       <c r="BD29" s="1">
-        <f t="shared" si="64"/>
-        <v>156.32372212500223</v>
+        <f t="shared" si="60"/>
+        <v>168.62673647769839</v>
       </c>
       <c r="BE29" s="1">
-        <f t="shared" si="64"/>
-        <v>154.7604849037522</v>
+        <f t="shared" si="60"/>
+        <v>166.94046911292139</v>
       </c>
       <c r="BF29" s="1">
-        <f t="shared" si="64"/>
-        <v>153.21288005471467</v>
+        <f t="shared" si="60"/>
+        <v>165.27106442179218</v>
       </c>
       <c r="BG29" s="1">
-        <f t="shared" si="64"/>
-        <v>151.68075125416752</v>
+        <f t="shared" si="60"/>
+        <v>163.61835377757424</v>
       </c>
       <c r="BH29" s="1">
-        <f t="shared" si="64"/>
-        <v>150.16394374162584</v>
+        <f t="shared" si="60"/>
+        <v>161.98217023979851</v>
       </c>
       <c r="BI29" s="1">
-        <f t="shared" si="64"/>
-        <v>148.66230430420958</v>
+        <f t="shared" si="60"/>
+        <v>160.36234853740052</v>
       </c>
       <c r="BJ29" s="1">
-        <f t="shared" si="64"/>
-        <v>147.17568126116748</v>
+        <f t="shared" si="60"/>
+        <v>158.75872505202651</v>
       </c>
       <c r="BK29" s="1">
-        <f t="shared" si="64"/>
-        <v>145.7039244485558</v>
+        <f t="shared" si="60"/>
+        <v>157.17113780150623</v>
       </c>
       <c r="BL29" s="1">
-        <f t="shared" si="64"/>
-        <v>144.24688520407022</v>
+        <f t="shared" si="60"/>
+        <v>155.59942642349117</v>
       </c>
       <c r="BM29" s="1">
-        <f t="shared" si="64"/>
-        <v>142.80441635202953</v>
+        <f t="shared" si="60"/>
+        <v>154.04343215925624</v>
       </c>
       <c r="BN29" s="1">
-        <f t="shared" si="64"/>
-        <v>141.37637218850924</v>
+        <f t="shared" si="60"/>
+        <v>152.50299783766368</v>
       </c>
       <c r="BO29" s="1">
-        <f t="shared" si="64"/>
-        <v>139.96260846662415</v>
+        <f t="shared" si="60"/>
+        <v>150.97796785928705</v>
       </c>
       <c r="BP29" s="1">
-        <f t="shared" si="64"/>
-        <v>138.56298238195791</v>
+        <f t="shared" si="60"/>
+        <v>149.46818818069417</v>
       </c>
       <c r="BQ29" s="1">
-        <f t="shared" si="64"/>
-        <v>137.17735255813832</v>
+        <f t="shared" si="60"/>
+        <v>147.97350629888723</v>
       </c>
       <c r="BR29" s="1">
-        <f t="shared" si="64"/>
-        <v>135.80557903255695</v>
+        <f t="shared" si="60"/>
+        <v>146.49377123589835</v>
       </c>
       <c r="BS29" s="1">
-        <f t="shared" si="64"/>
-        <v>134.44752324223137</v>
+        <f t="shared" si="60"/>
+        <v>145.02883352353936</v>
       </c>
       <c r="BT29" s="1">
-        <f t="shared" si="64"/>
-        <v>133.10304800980904</v>
+        <f t="shared" si="60"/>
+        <v>143.57854518830396</v>
       </c>
       <c r="BU29" s="1">
-        <f t="shared" si="64"/>
-        <v>131.77201752971095</v>
+        <f t="shared" si="60"/>
+        <v>142.14275973642091</v>
       </c>
       <c r="BV29" s="1">
-        <f t="shared" si="64"/>
-        <v>130.45429735441385</v>
+        <f t="shared" si="60"/>
+        <v>140.7213321390567</v>
       </c>
       <c r="BW29" s="1">
-        <f t="shared" si="64"/>
-        <v>129.14975438086972</v>
+        <f t="shared" si="60"/>
+        <v>139.31411881766613</v>
       </c>
       <c r="BX29" s="1">
-        <f t="shared" si="64"/>
-        <v>127.85825683706102</v>
+        <f t="shared" si="60"/>
+        <v>137.92097762948947</v>
       </c>
       <c r="BY29" s="1">
-        <f t="shared" si="64"/>
-        <v>126.57967426869041</v>
+        <f t="shared" si="60"/>
+        <v>136.54176785319459</v>
       </c>
       <c r="BZ29" s="1">
-        <f t="shared" si="64"/>
-        <v>125.31387752600351</v>
+        <f t="shared" si="60"/>
+        <v>135.17635017466264</v>
       </c>
       <c r="CA29" s="1">
-        <f t="shared" si="64"/>
-        <v>124.06073875074347</v>
+        <f t="shared" si="60"/>
+        <v>133.82458667291601</v>
       </c>
       <c r="CB29" s="1">
-        <f t="shared" si="64"/>
-        <v>122.82013136323603</v>
+        <f t="shared" si="60"/>
+        <v>132.48634080618686</v>
       </c>
       <c r="CC29" s="1">
-        <f t="shared" si="64"/>
-        <v>121.59193004960366</v>
+        <f t="shared" si="60"/>
+        <v>131.16147739812499</v>
       </c>
       <c r="CD29" s="1">
-        <f t="shared" si="64"/>
-        <v>120.37601074910762</v>
+        <f t="shared" si="60"/>
+        <v>129.84986262414373</v>
       </c>
       <c r="CE29" s="1">
-        <f t="shared" si="64"/>
-        <v>119.17225064161654</v>
+        <f t="shared" si="60"/>
+        <v>128.55136399790229</v>
       </c>
       <c r="CF29" s="1">
-        <f t="shared" si="64"/>
-        <v>117.98052813520037</v>
+        <f t="shared" si="60"/>
+        <v>127.26585035792326</v>
       </c>
       <c r="CG29" s="1">
-        <f t="shared" si="64"/>
-        <v>116.80072285384837</v>
+        <f t="shared" si="60"/>
+        <v>125.99319185434402</v>
       </c>
       <c r="CH29" s="1">
-        <f t="shared" si="64"/>
-        <v>115.63271562530988</v>
+        <f t="shared" si="60"/>
+        <v>124.73325993580058</v>
       </c>
       <c r="CI29" s="1">
-        <f t="shared" si="64"/>
-        <v>114.47638846905679</v>
+        <f t="shared" si="60"/>
+        <v>123.48592733644257</v>
       </c>
       <c r="CJ29" s="1">
-        <f t="shared" si="64"/>
-        <v>113.33162458436622</v>
+        <f t="shared" si="60"/>
+        <v>122.25106806307815</v>
       </c>
       <c r="CK29" s="1">
-        <f t="shared" si="64"/>
-        <v>112.19830833852257</v>
+        <f t="shared" si="60"/>
+        <v>121.02855738244737</v>
       </c>
       <c r="CL29" s="1">
-        <f t="shared" si="64"/>
-        <v>111.07632525513733</v>
+        <f t="shared" si="60"/>
+        <v>119.8182718086229</v>
       </c>
       <c r="CM29" s="1">
-        <f t="shared" si="64"/>
-        <v>109.96556200258595</v>
+        <f t="shared" si="60"/>
+        <v>118.62008909053667</v>
       </c>
       <c r="CN29" s="1">
-        <f t="shared" si="64"/>
-        <v>108.8659063825601</v>
+        <f t="shared" si="60"/>
+        <v>117.4338881996313</v>
       </c>
       <c r="CO29" s="1">
-        <f t="shared" si="64"/>
-        <v>107.7772473187345</v>
+        <f t="shared" si="60"/>
+        <v>116.25954931763498</v>
       </c>
       <c r="CP29" s="1">
-        <f t="shared" si="64"/>
-        <v>106.69947484554714</v>
+        <f t="shared" si="60"/>
+        <v>115.09695382445862</v>
       </c>
       <c r="CQ29" s="1">
-        <f t="shared" si="64"/>
-        <v>105.63248009709167</v>
+        <f t="shared" si="60"/>
+        <v>113.94598428621404</v>
       </c>
       <c r="CR29" s="1">
-        <f t="shared" si="64"/>
-        <v>104.57615529612076</v>
+        <f t="shared" si="60"/>
+        <v>112.8065244433519</v>
       </c>
       <c r="CS29" s="1">
-        <f t="shared" si="64"/>
-        <v>103.53039374315955</v>
+        <f t="shared" si="60"/>
+        <v>111.67845919891839</v>
       </c>
       <c r="CT29" s="1">
-        <f t="shared" si="64"/>
-        <v>102.49508980572796</v>
+        <f t="shared" si="60"/>
+        <v>110.5616746069292</v>
       </c>
       <c r="CU29" s="1">
-        <f t="shared" si="64"/>
-        <v>101.47013890767067</v>
+        <f t="shared" si="60"/>
+        <v>109.45605786085991</v>
       </c>
       <c r="CV29" s="1">
-        <f t="shared" si="64"/>
-        <v>100.45543751859397</v>
+        <f t="shared" si="60"/>
+        <v>108.36149728225132</v>
       </c>
       <c r="CW29" s="1">
-        <f t="shared" si="64"/>
-        <v>99.450883143408021</v>
+        <f t="shared" si="60"/>
+        <v>107.2778823094288</v>
       </c>
       <c r="CX29" s="1">
-        <f t="shared" si="64"/>
-        <v>98.456374311973946</v>
+        <f t="shared" si="60"/>
+        <v>106.20510348633452</v>
       </c>
       <c r="CY29" s="1">
-        <f t="shared" si="64"/>
-        <v>97.47181056885421</v>
+        <f t="shared" si="60"/>
+        <v>105.14305245147118</v>
       </c>
       <c r="CZ29" s="1">
-        <f t="shared" ref="CZ29:EN29" si="65">CY29*(1+$AO$40)</f>
-        <v>96.497092463165671</v>
+        <f t="shared" ref="CZ29:EN29" si="61">CY29*(1+$AO$40)</f>
+        <v>104.09162192695646</v>
       </c>
       <c r="DA29" s="1">
-        <f t="shared" si="65"/>
-        <v>95.532121538534014</v>
+        <f t="shared" si="61"/>
+        <v>103.0507057076869</v>
       </c>
       <c r="DB29" s="1">
-        <f t="shared" si="65"/>
-        <v>94.576800323148674</v>
+        <f t="shared" si="61"/>
+        <v>102.02019865061003</v>
       </c>
       <c r="DC29" s="1">
-        <f t="shared" si="65"/>
-        <v>93.631032319917182</v>
+        <f t="shared" si="61"/>
+        <v>100.99999666410393</v>
       </c>
       <c r="DD29" s="1">
-        <f t="shared" si="65"/>
-        <v>92.694721996718016</v>
+        <f t="shared" si="61"/>
+        <v>99.989996697462885</v>
       </c>
       <c r="DE29" s="1">
-        <f t="shared" si="65"/>
-        <v>91.767774776750841</v>
+        <f t="shared" si="61"/>
+        <v>98.990096730488261</v>
       </c>
       <c r="DF29" s="1">
-        <f t="shared" si="65"/>
-        <v>90.850097028983328</v>
+        <f t="shared" si="61"/>
+        <v>98.000195763183385</v>
       </c>
       <c r="DG29" s="1">
-        <f t="shared" si="65"/>
-        <v>89.941596058693491</v>
+        <f t="shared" si="61"/>
+        <v>97.020193805551557</v>
       </c>
       <c r="DH29" s="1">
-        <f t="shared" si="65"/>
-        <v>89.042180098106556</v>
+        <f t="shared" si="61"/>
+        <v>96.049991867496047</v>
       </c>
       <c r="DI29" s="1">
-        <f t="shared" si="65"/>
-        <v>88.151758297125482</v>
+        <f t="shared" si="61"/>
+        <v>95.089491948821092</v>
       </c>
       <c r="DJ29" s="1">
-        <f t="shared" si="65"/>
-        <v>87.270240714154227</v>
+        <f t="shared" si="61"/>
+        <v>94.138597029332885</v>
       </c>
       <c r="DK29" s="1">
-        <f t="shared" si="65"/>
-        <v>86.397538307012681</v>
+        <f t="shared" si="61"/>
+        <v>93.19721105903956</v>
       </c>
       <c r="DL29" s="1">
-        <f t="shared" si="65"/>
-        <v>85.533562923942554</v>
+        <f t="shared" si="61"/>
+        <v>92.265238948449166</v>
       </c>
       <c r="DM29" s="1">
-        <f t="shared" si="65"/>
-        <v>84.678227294703134</v>
+        <f t="shared" si="61"/>
+        <v>91.342586558964669</v>
       </c>
       <c r="DN29" s="1">
-        <f t="shared" si="65"/>
-        <v>83.831445021756096</v>
+        <f t="shared" si="61"/>
+        <v>90.429160693375024</v>
       </c>
       <c r="DO29" s="1">
-        <f t="shared" si="65"/>
-        <v>82.993130571538529</v>
+        <f t="shared" si="61"/>
+        <v>89.524869086441271</v>
       </c>
       <c r="DP29" s="1">
-        <f t="shared" si="65"/>
-        <v>82.163199265823138</v>
+        <f t="shared" si="61"/>
+        <v>88.62962039557685</v>
       </c>
       <c r="DQ29" s="1">
-        <f t="shared" si="65"/>
-        <v>81.341567273164912</v>
+        <f t="shared" si="61"/>
+        <v>87.743324191621085</v>
       </c>
       <c r="DR29" s="1">
-        <f t="shared" si="65"/>
-        <v>80.528151600433262</v>
+        <f t="shared" si="61"/>
+        <v>86.865890949704877</v>
       </c>
       <c r="DS29" s="1">
-        <f t="shared" si="65"/>
-        <v>79.722870084428934</v>
+        <f t="shared" si="61"/>
+        <v>85.997232040207834</v>
       </c>
       <c r="DT29" s="1">
-        <f t="shared" si="65"/>
-        <v>78.925641383584647</v>
+        <f t="shared" si="61"/>
+        <v>85.137259719805755</v>
       </c>
       <c r="DU29" s="1">
-        <f t="shared" si="65"/>
-        <v>78.136384969748804</v>
+        <f t="shared" si="61"/>
+        <v>84.28588712260769</v>
       </c>
       <c r="DV29" s="1">
-        <f t="shared" si="65"/>
-        <v>77.355021120051319</v>
+        <f t="shared" si="61"/>
+        <v>83.443028251381605</v>
       </c>
       <c r="DW29" s="1">
-        <f t="shared" si="65"/>
-        <v>76.581470908850804</v>
+        <f t="shared" si="61"/>
+        <v>82.608597968867784</v>
       </c>
       <c r="DX29" s="1">
-        <f t="shared" si="65"/>
-        <v>75.815656199762302</v>
+        <f t="shared" si="61"/>
+        <v>81.782511989179099</v>
       </c>
       <c r="DY29" s="1">
-        <f t="shared" si="65"/>
-        <v>75.057499637764678</v>
+        <f t="shared" si="61"/>
+        <v>80.964686869287306</v>
       </c>
       <c r="DZ29" s="1">
-        <f t="shared" si="65"/>
-        <v>74.306924641387027</v>
+        <f t="shared" si="61"/>
+        <v>80.155040000594425</v>
       </c>
       <c r="EA29" s="1">
-        <f t="shared" si="65"/>
-        <v>73.56385539497316</v>
+        <f t="shared" si="61"/>
+        <v>79.353489600588475</v>
       </c>
       <c r="EB29" s="1">
-        <f t="shared" si="65"/>
-        <v>72.828216841023433</v>
+        <f t="shared" si="61"/>
+        <v>78.559954704582594</v>
       </c>
       <c r="EC29" s="1">
-        <f t="shared" si="65"/>
-        <v>72.099934672613202</v>
+        <f t="shared" si="61"/>
+        <v>77.774355157536775</v>
       </c>
       <c r="ED29" s="1">
-        <f t="shared" si="65"/>
-        <v>71.37893532588707</v>
+        <f t="shared" si="61"/>
+        <v>76.996611605961405</v>
       </c>
       <c r="EE29" s="1">
-        <f t="shared" si="65"/>
-        <v>70.665145972628196</v>
+        <f t="shared" si="61"/>
+        <v>76.226645489901784</v>
       </c>
       <c r="EF29" s="1">
-        <f t="shared" si="65"/>
-        <v>69.958494512901908</v>
+        <f t="shared" si="61"/>
+        <v>75.464379035002764</v>
       </c>
       <c r="EG29" s="1">
-        <f t="shared" si="65"/>
-        <v>69.258909567772889</v>
+        <f t="shared" si="61"/>
+        <v>74.709735244652734</v>
       </c>
       <c r="EH29" s="1">
-        <f t="shared" si="65"/>
-        <v>68.566320472095157</v>
+        <f t="shared" si="61"/>
+        <v>73.962637892206203</v>
       </c>
       <c r="EI29" s="1">
-        <f t="shared" si="65"/>
-        <v>67.880657267374204</v>
+        <f t="shared" si="61"/>
+        <v>73.223011513284135</v>
       </c>
       <c r="EJ29" s="1">
-        <f t="shared" si="65"/>
-        <v>67.201850694700468</v>
+        <f t="shared" si="61"/>
+        <v>72.490781398151299</v>
       </c>
       <c r="EK29" s="1">
-        <f t="shared" si="65"/>
-        <v>66.529832187753456</v>
+        <f t="shared" si="61"/>
+        <v>71.765873584169782</v>
       </c>
       <c r="EL29" s="1">
-        <f t="shared" si="65"/>
-        <v>65.864533865875927</v>
+        <f t="shared" si="61"/>
+        <v>71.048214848328087</v>
       </c>
       <c r="EM29" s="1">
-        <f t="shared" si="65"/>
-        <v>65.205888527217169</v>
+        <f t="shared" si="61"/>
+        <v>70.337732699844807</v>
       </c>
       <c r="EN29" s="1">
-        <f t="shared" si="65"/>
-        <v>64.553829641945001</v>
+        <f t="shared" si="61"/>
+        <v>69.634355372846358</v>
       </c>
     </row>
     <row r="30" spans="2:144" x14ac:dyDescent="0.3">
@@ -4403,60 +4339,60 @@
         <v>44</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" ref="I31:P31" si="66">I29/I30</f>
+        <f t="shared" ref="I31:P31" si="62">I29/I30</f>
         <v>0.10621468926553666</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.23502824858757046</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.17288135593220327</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.15367231638418072</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.18983050847457619</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>1.2135593220338985</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.167231638418079</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>0.21694915254237279</v>
       </c>
       <c r="Q31" s="7">
-        <f t="shared" ref="Q31:R31" si="67">Q29/Q30</f>
+        <f t="shared" ref="Q31:R31" si="63">Q29/Q30</f>
         <v>0.2056497175141242</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>0.32316384180790925</v>
       </c>
       <c r="S31" s="7">
-        <f t="shared" ref="S31:V31" si="68">S29/S30</f>
+        <f t="shared" ref="S31:V31" si="64">S29/S30</f>
         <v>0.20670391061452503</v>
       </c>
       <c r="T31" s="7">
-        <f t="shared" si="68"/>
-        <v>0.27786927374301684</v>
+        <f t="shared" si="64"/>
+        <v>0.17094972067039108</v>
       </c>
       <c r="U31" s="7">
-        <f t="shared" si="68"/>
-        <v>0.26100983240223463</v>
+        <f t="shared" si="64"/>
+        <v>0.26089586592178771</v>
       </c>
       <c r="V31" s="7">
-        <f t="shared" si="68"/>
-        <v>0.27356513966480445</v>
+        <f t="shared" si="64"/>
+        <v>0.27333720670391048</v>
       </c>
       <c r="X31" s="7">
         <f>X29/X30</f>
@@ -4476,47 +4412,47 @@
       </c>
       <c r="AB31" s="7">
         <f>AB29/AB30</f>
-        <v>1.0940084916201112</v>
+        <v>0.91188670391061355</v>
       </c>
       <c r="AC31" s="7">
-        <f t="shared" ref="AC31:AL31" si="69">AC29/AC30</f>
-        <v>1.3128317810055861</v>
+        <f t="shared" ref="AC31:AL31" si="65">AC29/AC30</f>
+        <v>1.4748448831284919</v>
       </c>
       <c r="AD31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.5828526257340787</v>
+        <f t="shared" si="65"/>
+        <v>1.7455658377778773</v>
       </c>
       <c r="AE31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.6938768726108608</v>
+        <f t="shared" si="65"/>
+        <v>1.8565621211583823</v>
       </c>
       <c r="AF31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.7688870751977039</v>
+        <f t="shared" si="65"/>
+        <v>1.9311683848378547</v>
       </c>
       <c r="AG31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.8239385875749874</v>
+        <f t="shared" si="65"/>
+        <v>1.9866045152889742</v>
       </c>
       <c r="AH31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.8751391313055925</v>
+        <f t="shared" si="65"/>
+        <v>2.0384613889151297</v>
       </c>
       <c r="AI31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.927606826281417</v>
+        <f t="shared" si="65"/>
+        <v>2.091476647847013</v>
       </c>
       <c r="AJ31" s="7">
-        <f t="shared" si="69"/>
-        <v>1.981379039196151</v>
+        <f t="shared" si="65"/>
+        <v>2.1456746722690694</v>
       </c>
       <c r="AK31" s="7">
-        <f t="shared" si="69"/>
-        <v>2.0364949635405591</v>
+        <f t="shared" si="65"/>
+        <v>2.2010803420942175</v>
       </c>
       <c r="AL31" s="7">
-        <f t="shared" si="69"/>
-        <v>2.0929957628556948</v>
+        <f t="shared" si="65"/>
+        <v>2.2577190470796671</v>
       </c>
     </row>
     <row r="32" spans="2:144" x14ac:dyDescent="0.3">
@@ -4537,71 +4473,71 @@
         <v>0.44194756554307113</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:S33" si="70">H3/D3-1</f>
+        <f t="shared" ref="H33:S33" si="66">H3/D3-1</f>
         <v>0.49134948096885833</v>
       </c>
       <c r="I33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.40687679083094563</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.54768392370572183</v>
+      </c>
+      <c r="K33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.25974025974025983</v>
+      </c>
+      <c r="L33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.24825986078886308</v>
+      </c>
+      <c r="M33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.23828920570264756</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.19366197183098599</v>
+      </c>
+      <c r="O33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.2082474226804123</v>
+      </c>
+      <c r="P33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.2007434944237918</v>
+      </c>
+      <c r="Q33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.26315789473684204</v>
+      </c>
+      <c r="R33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.37610619469026552</v>
+      </c>
+      <c r="S33" s="10">
+        <f t="shared" si="66"/>
+        <v>0.63139931740614319</v>
+      </c>
+      <c r="T33" s="10">
+        <f t="shared" ref="T33:T35" si="67">T3/P3-1</f>
+        <v>0.43808049535603732</v>
+      </c>
+      <c r="U33" s="10">
+        <f t="shared" ref="U33:U35" si="68">U3/Q3-1</f>
+        <v>0.27</v>
+      </c>
+      <c r="V33" s="10">
+        <f t="shared" ref="V33:V35" si="69">V3/R3-1</f>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" ref="Y33:Z33" si="70">Y3/X3-1</f>
+        <v>0.47405660377358494</v>
+      </c>
+      <c r="Z33" s="10">
         <f t="shared" si="70"/>
-        <v>0.40687679083094563</v>
-      </c>
-      <c r="J33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.54768392370572183</v>
-      </c>
-      <c r="K33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.25974025974025983</v>
-      </c>
-      <c r="L33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.24825986078886308</v>
-      </c>
-      <c r="M33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.23828920570264756</v>
-      </c>
-      <c r="N33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.19366197183098599</v>
-      </c>
-      <c r="O33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.2082474226804123</v>
-      </c>
-      <c r="P33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.2007434944237918</v>
-      </c>
-      <c r="Q33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.26315789473684204</v>
-      </c>
-      <c r="R33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.37610619469026552</v>
-      </c>
-      <c r="S33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.63139931740614319</v>
-      </c>
-      <c r="T33" s="10">
-        <f t="shared" ref="T33:T35" si="71">T3/P3-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="U33" s="10">
-        <f t="shared" ref="U33:U35" si="72">U3/Q3-1</f>
-        <v>0.27</v>
-      </c>
-      <c r="V33" s="10">
-        <f t="shared" ref="V33:V35" si="73">V3/R3-1</f>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="Y33" s="10">
-        <f t="shared" ref="Y33:Z33" si="74">Y3/X3-1</f>
-        <v>0.47405660377358494</v>
-      </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="74"/>
         <v>0.23146666666666649</v>
       </c>
       <c r="AA33" s="10">
@@ -4610,46 +4546,46 @@
       </c>
       <c r="AB33" s="10">
         <f>AB3/AA3-1</f>
-        <v>0.3292430958063417</v>
+        <v>0.31560518240709179</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33:AL33" si="75">AC3/AB3-1</f>
+        <f t="shared" ref="AC33:AL33" si="71">AC3/AB3-1</f>
         <v>0.17999999999999994</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -4658,123 +4594,123 @@
         <v>93</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" ref="G34:S34" si="76">G4/C4-1</f>
+        <f t="shared" ref="G34:S34" si="72">G4/C4-1</f>
         <v>0.36752136752136755</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.13087248322147649</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.15309446254071668</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.12068965517241392</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.18124999999999991</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.15430267062314518</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.15254237288135597</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.1461538461538463</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.14021164021164023</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.14395886889460163</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.13480392156862742</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.17002237136465315</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>8.1206496519721671E-2</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="67"/>
+        <v>0.11460674157303363</v>
+      </c>
+      <c r="U34" s="10">
+        <f t="shared" si="68"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="U34" s="10">
-        <f t="shared" si="72"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
       <c r="V34" s="10">
+        <f t="shared" si="69"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" ref="Y34:AA34" si="73">Y4/X4-1</f>
+        <v>0.18028643639427111</v>
+      </c>
+      <c r="Z34" s="10">
         <f t="shared" si="73"/>
+        <v>0.15774446823697352</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" si="73"/>
+        <v>0.14796547472256472</v>
+      </c>
+      <c r="AB34" s="10">
+        <f t="shared" ref="AB34:AL34" si="74">AB4/AA4-1</f>
+        <v>6.9210526315789389E-2</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" si="74"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AD34" s="10">
+        <f t="shared" si="74"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE34" s="10">
+        <f t="shared" si="74"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y34" s="10">
-        <f t="shared" ref="Y34:AA34" si="77">Y4/X4-1</f>
-        <v>0.18028643639427111</v>
-      </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="77"/>
-        <v>0.15774446823697352</v>
-      </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="77"/>
-        <v>0.14796547472256472</v>
-      </c>
-      <c r="AB34" s="10">
-        <f t="shared" ref="AB34:AL34" si="78">AB4/AA4-1</f>
-        <v>5.854994629430732E-2</v>
-      </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="78"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="78"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="78"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="78"/>
+      <c r="AG34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG34" s="10">
-        <f t="shared" si="78"/>
+      <c r="AH34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH34" s="10">
-        <f t="shared" si="78"/>
+      <c r="AI34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI34" s="10">
-        <f t="shared" si="78"/>
+      <c r="AJ34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ34" s="10">
-        <f t="shared" si="78"/>
+      <c r="AK34" s="10">
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK34" s="10">
-        <f t="shared" si="78"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AL34" s="10">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -4783,123 +4719,123 @@
         <v>94</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" ref="G35:S35" si="79">G5/C5-1</f>
+        <f t="shared" ref="G35:S35" si="75">G5/C5-1</f>
         <v>-0.21428571428571419</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.2857142857142857</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.58333333333333326</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.36363636363636376</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.5</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.25</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.8571428571428571</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.9</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>-0.6</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>4</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="71"/>
-        <v>-0.7</v>
+        <f t="shared" si="67"/>
+        <v>-0.16666666666666663</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="72"/>
-        <v>-0.7</v>
+        <f t="shared" si="68"/>
+        <v>4</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="73"/>
-        <v>-0.7</v>
+        <f t="shared" si="69"/>
+        <v>1.5</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" ref="Y35:AA35" si="80">Y5/X5-1</f>
+        <f t="shared" ref="Y35:AA35" si="76">Y5/X5-1</f>
         <v>-0.31999999999999995</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>8.8235294117646967E-2</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>-0.72972972972972983</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" ref="AB35:AL35" si="81">AB5/AA5-1</f>
-        <v>-0.22999999999999998</v>
+        <f t="shared" ref="AB35:AL35" si="77">AB5/AA5-1</f>
+        <v>1</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>-1</v>
       </c>
       <c r="AD35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AF35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL35" s="10" t="e">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4912,40 +4848,40 @@
         <v>0.20140515222482436</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" ref="N36:R36" si="82">N8/J8-1</f>
+        <f t="shared" ref="N36:R36" si="78">N8/J8-1</f>
         <v>0.17738589211618261</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.17221584385763489</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.17709437963944863</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.20760233918128645</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.2854625550660792</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" ref="S36" si="83">S8/O8-1</f>
+        <f t="shared" ref="S36" si="79">S8/O8-1</f>
         <v>0.39764936336924572</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" ref="T36" si="84">T8/P8-1</f>
-        <v>0.30806306306306319</v>
+        <f t="shared" ref="T36" si="80">T8/P8-1</f>
+        <v>0.28828828828828845</v>
       </c>
       <c r="U36" s="9">
-        <f t="shared" ref="U36" si="85">U8/Q8-1</f>
-        <v>0.19133979015334956</v>
+        <f t="shared" ref="U36" si="81">U8/Q8-1</f>
+        <v>0.19109765940274426</v>
       </c>
       <c r="V36" s="9">
-        <f t="shared" ref="V36" si="86">V8/R8-1</f>
-        <v>5.3714873200822577E-2</v>
+        <f t="shared" ref="V36" si="82">V8/R8-1</f>
+        <v>5.3303632625085751E-2</v>
       </c>
       <c r="X36" s="9"/>
       <c r="Y36" s="9">
@@ -4953,56 +4889,56 @@
         <v>0.31809145129224659</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" ref="Z36:AL36" si="87">Z8/Y8-1</f>
+        <f t="shared" ref="Z36:AL36" si="83">Z8/Y8-1</f>
         <v>0.19909502262443413</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.2148427672955977</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="87"/>
-        <v>0.22020915303375421</v>
+        <f t="shared" si="83"/>
+        <v>0.21547732449782564</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="87"/>
-        <v>0.1350235812632905</v>
+        <f t="shared" si="83"/>
+        <v>0.13188496883912548</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="87"/>
-        <v>9.5459682904382337E-2</v>
+        <f t="shared" si="83"/>
+        <v>9.4828109771864622E-2</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="87"/>
-        <v>5.1599378707583021E-2</v>
+        <f t="shared" si="83"/>
+        <v>5.103326165874722E-2</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="87"/>
-        <v>3.4783384248417981E-2</v>
+        <f t="shared" si="83"/>
+        <v>3.4141802593437465E-2</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.7436758450269272E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.7110956476322334E-2</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0334157552887255E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0360247969211764E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0388365547287401E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0418666182838052E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL36" s="9">
-        <f t="shared" si="87"/>
-        <v>2.0451317499752264E-2</v>
+        <f t="shared" si="83"/>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="37" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5014,80 +4950,80 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:R37" si="88">(I8-I9)/I8</f>
+        <f t="shared" ref="I37:R37" si="84">(I8-I9)/I8</f>
         <v>0.98829039812646369</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.99170124481327804</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.99081515499425954</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.98833510074231179</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.99317738791422994</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.99559471365638763</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.9627815866797258</v>
       </c>
       <c r="P37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.98288288288288284</v>
       </c>
       <c r="Q37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.98547215496368046</v>
       </c>
       <c r="R37" s="10">
-        <f t="shared" si="88"/>
+        <f t="shared" si="84"/>
         <v>0.98286497601096645</v>
       </c>
       <c r="S37" s="10">
-        <f t="shared" ref="S37:V37" si="89">(S8-S9)/S8</f>
+        <f t="shared" ref="S37:V37" si="85">(S8-S9)/S8</f>
         <v>0.98458304134548014</v>
       </c>
       <c r="T37" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
+        <v>0.98391608391608387</v>
+      </c>
+      <c r="U37" s="10">
+        <f t="shared" si="85"/>
         <v>0.98000000000000009</v>
       </c>
-      <c r="U37" s="10">
-        <f t="shared" si="89"/>
-        <v>0.97999999999999987</v>
-      </c>
       <c r="V37" s="10">
-        <f t="shared" si="89"/>
-        <v>0.98000000000000009</v>
+        <f t="shared" si="85"/>
+        <v>0.98</v>
       </c>
       <c r="X37" s="10">
-        <f t="shared" ref="X37:AB37" si="90">(X8-X9)/X8</f>
+        <f t="shared" ref="X37:AB37" si="86">(X8-X9)/X8</f>
         <v>0.98210735586481113</v>
       </c>
       <c r="Y37" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.98763197586726992</v>
       </c>
       <c r="Z37" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.99220125786163516</v>
       </c>
       <c r="AA37" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="86"/>
         <v>0.979291778836198</v>
       </c>
       <c r="AB37" s="10">
-        <f t="shared" si="90"/>
-        <v>0.98110990616710714</v>
+        <f t="shared" si="86"/>
+        <v>0.98206830518234822</v>
       </c>
       <c r="AC37" s="10"/>
       <c r="AD37" s="10"/>
@@ -5109,39 +5045,39 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="I38" s="10">
-        <f t="shared" ref="I38:Q38" si="91">(I8-I10)/I8</f>
+        <f t="shared" ref="I38:Q38" si="87">(I8-I10)/I8</f>
         <v>0.99063231850117095</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.99066390041493768</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.98966704936854188</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.98833510074231179</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.98830409356725146</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.99030837004405292</v>
       </c>
       <c r="O38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.99020568070519099</v>
       </c>
       <c r="P38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.99189189189189186</v>
       </c>
       <c r="Q38" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="87"/>
         <v>0.99273607748184012</v>
       </c>
       <c r="R38" s="10">
@@ -5149,40 +5085,40 @@
         <v>0.99246058944482529</v>
       </c>
       <c r="S38" s="10">
-        <f t="shared" ref="S38:V38" si="92">(S8-S10)/S8</f>
+        <f t="shared" ref="S38:V38" si="88">(S8-S10)/S8</f>
         <v>0.99369306236860544</v>
       </c>
       <c r="T38" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
+        <v>0.98951048951048948</v>
+      </c>
+      <c r="U38" s="10">
+        <f t="shared" si="88"/>
         <v>0.98999999999999988</v>
       </c>
-      <c r="U38" s="10">
-        <f t="shared" si="92"/>
+      <c r="V38" s="10">
+        <f t="shared" si="88"/>
         <v>0.9900000000000001</v>
       </c>
-      <c r="V38" s="10">
-        <f t="shared" si="92"/>
-        <v>0.98999999999999988</v>
-      </c>
       <c r="X38" s="10">
-        <f t="shared" ref="X38:AB38" si="93">(X8-X10)/X8</f>
+        <f t="shared" ref="X38:AB38" si="89">(X8-X10)/X8</f>
         <v>0.98528827037773359</v>
       </c>
       <c r="Y38" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.98853695324283553</v>
       </c>
       <c r="Z38" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.98918238993710694</v>
       </c>
       <c r="AA38" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.99192379374611728</v>
       </c>
       <c r="AB38" s="10">
-        <f t="shared" si="93"/>
-        <v>0.99089437392976354</v>
+        <f t="shared" si="89"/>
+        <v>0.99077859593767137</v>
       </c>
       <c r="AC38" s="10"/>
       <c r="AD38" s="10"/>
@@ -5204,39 +5140,39 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="I39" s="10">
-        <f t="shared" ref="I39:Q39" si="94">(I8-I11)/I8</f>
+        <f t="shared" ref="I39:Q39" si="90">(I8-I11)/I8</f>
         <v>0.83723653395784536</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.8205394190871369</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.82548794489092991</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.78366914103923635</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.77290448343079921</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.76211453744493396</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.81096963761018614</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.77567567567567575</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.75544794188861986</v>
       </c>
       <c r="R39" s="10">
@@ -5244,40 +5180,40 @@
         <v>0.69773817683344752</v>
       </c>
       <c r="S39" s="10">
-        <f t="shared" ref="S39:V39" si="95">(S8-S11)/S8</f>
+        <f t="shared" ref="S39:V39" si="91">(S8-S11)/S8</f>
         <v>0.66713384723195512</v>
       </c>
       <c r="T39" s="10">
-        <f t="shared" si="95"/>
-        <v>0.67</v>
+        <f t="shared" si="91"/>
+        <v>0.67062937062937067</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="95"/>
-        <v>0.67</v>
+        <f t="shared" si="91"/>
+        <v>0.66999999999999993</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="95"/>
-        <v>0.67</v>
+        <f t="shared" si="91"/>
+        <v>0.66999999999999993</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" ref="X39:AB39" si="96">(X8-X11)/X8</f>
+        <f t="shared" ref="X39:AB39" si="92">(X8-X11)/X8</f>
         <v>0.97813121272365811</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.8591251885369533</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.78389937106918239</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.75440049699730782</v>
       </c>
       <c r="AB39" s="10">
-        <f t="shared" si="96"/>
-        <v>0.66930588436950034</v>
+        <f t="shared" si="92"/>
+        <v>0.66945651618355095</v>
       </c>
       <c r="AC39" s="10"/>
       <c r="AD39" s="10"/>
@@ -5295,19 +5231,19 @@
         <v>47</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:L40" si="97">I13/I8</f>
+        <f t="shared" ref="I40:L40" si="93">I13/I8</f>
         <v>0.81615925058548</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.80290456431535273</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.80597014925373123</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.76033934252386004</v>
       </c>
       <c r="M40" s="10">
@@ -5315,99 +5251,99 @@
         <v>0.75438596491228072</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" ref="N40:R40" si="98">N13/N8</f>
+        <f t="shared" ref="N40:R40" si="94">N13/N8</f>
         <v>0.74801762114537451</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.76395690499510294</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.75045045045045045</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.73365617433414043</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.67306374228923915</v>
       </c>
       <c r="S40" s="10">
-        <f t="shared" ref="S40:V40" si="99">S13/S8</f>
+        <f t="shared" ref="S40:V40" si="95">S13/S8</f>
         <v>0.6454099509460407</v>
       </c>
       <c r="T40" s="10">
-        <f t="shared" si="99"/>
-        <v>0.64</v>
+        <f t="shared" si="95"/>
+        <v>0.64405594405594402</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="99"/>
-        <v>0.64</v>
+        <f t="shared" si="95"/>
+        <v>0.6399999999999999</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="99"/>
-        <v>0.64</v>
+        <f t="shared" si="95"/>
+        <v>0.6399999999999999</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" ref="X40:AL40" si="100">X13/X8</f>
+        <f t="shared" ref="X40:AL40" si="96">X13/X8</f>
         <v>0.94552683896620282</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.83529411764705874</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.76528301886792449</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.7256160695796231</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" si="100"/>
-        <v>0.64131016446637101</v>
+        <f t="shared" si="96"/>
+        <v>0.64230341730357055</v>
       </c>
       <c r="AC40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AD40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AE40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AF40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AG40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AH40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AI40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AJ40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AK40" s="10">
-        <f t="shared" si="100"/>
-        <v>0.63</v>
+        <f t="shared" si="96"/>
+        <v>0.63000000000000012</v>
       </c>
       <c r="AL40" s="10">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.63</v>
       </c>
       <c r="AN40" t="s">
@@ -5430,39 +5366,39 @@
         <v>0.14999999999999991</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" ref="N41:R41" si="101">N14/J14-1</f>
+        <f t="shared" ref="N41:R41" si="97">N14/J14-1</f>
         <v>-2.3696682464454999E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>-0.18905472636815923</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>-7.4766355140186813E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.12077294685990347</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>-0.13592233009708743</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" ref="S41" si="102">S14/O14-1</f>
+        <f t="shared" ref="S41" si="98">S14/O14-1</f>
         <v>7.9754601226993849E-2</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" ref="T41" si="103">T14/P14-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" ref="T41" si="99">T14/P14-1</f>
+        <v>-5.555555555555558E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" ref="U41" si="104">U14/Q14-1</f>
+        <f t="shared" ref="U41" si="100">U14/Q14-1</f>
         <v>-0.20000000000000007</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" ref="V41" si="105">V14/R14-1</f>
+        <f t="shared" ref="V41" si="101">V14/R14-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X41" s="10"/>
@@ -5471,55 +5407,55 @@
         <v>1.3422818791946067E-3</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" ref="Z41:AL41" si="106">Z14/Y14-1</f>
+        <f t="shared" ref="Z41:AL41" si="102">Z14/Y14-1</f>
         <v>0.1099195710455767</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>-6.8840579710145122E-2</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" si="106"/>
-        <v>-5.7457846952010283E-2</v>
+        <f t="shared" si="102"/>
+        <v>-4.60440985732814E-2</v>
       </c>
       <c r="AC41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AD41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL41" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN41" t="s">
@@ -5534,19 +5470,19 @@
         <v>49</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" ref="I42:L42" si="107">I16/I8</f>
+        <f t="shared" ref="I42:L42" si="103">I16/I8</f>
         <v>0.3044496487119438</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="103"/>
         <v>0.30705394190871371</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="103"/>
         <v>0.28013777267508611</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="103"/>
         <v>0.28632025450689297</v>
       </c>
       <c r="M42" s="10">
@@ -5554,99 +5490,99 @@
         <v>0.27680311890838205</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" ref="N42:R42" si="108">N16/N8</f>
+        <f t="shared" ref="N42:R42" si="104">N16/N8</f>
         <v>0.26519823788546254</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.28893241919686585</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.26126126126126131</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.2623083131557708</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.28032899246058945</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" ref="S42:V42" si="109">S16/S8</f>
+        <f t="shared" ref="S42:V42" si="105">S16/S8</f>
         <v>0.23966362999299234</v>
       </c>
       <c r="T42" s="10">
-        <f t="shared" si="109"/>
+        <f t="shared" si="105"/>
+        <v>0.23776223776223776</v>
+      </c>
+      <c r="U42" s="10">
+        <f t="shared" si="105"/>
         <v>0.23999999999999996</v>
       </c>
-      <c r="U42" s="10">
-        <f t="shared" si="109"/>
-        <v>0.24</v>
-      </c>
       <c r="V42" s="10">
-        <f t="shared" si="109"/>
-        <v>0.24</v>
+        <f t="shared" si="105"/>
+        <v>0.23999999999999996</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" ref="X42:AL42" si="110">X16/X8</f>
+        <f t="shared" ref="X42:AL42" si="106">X16/X8</f>
         <v>0.48071570576540756</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>0.34690799396681749</v>
       </c>
       <c r="Z42" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>0.27647798742138369</v>
       </c>
       <c r="AA42" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>0.27314143715054878</v>
       </c>
       <c r="AB42" s="10">
-        <f t="shared" si="110"/>
-        <v>0.23991853899690957</v>
+        <f t="shared" si="106"/>
+        <v>0.23937303434340682</v>
       </c>
       <c r="AC42" s="10">
-        <f t="shared" si="110"/>
-        <v>0.23</v>
+        <f t="shared" si="106"/>
+        <v>0.22999999999999998</v>
       </c>
       <c r="AD42" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AE42" s="10">
+        <f t="shared" si="106"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AF42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AE42" s="10">
-        <f t="shared" si="110"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="AF42" s="10">
-        <f t="shared" si="110"/>
+      <c r="AG42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AG42" s="10">
-        <f t="shared" si="110"/>
+      <c r="AH42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AH42" s="10">
-        <f t="shared" si="110"/>
+      <c r="AI42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AI42" s="10">
-        <f t="shared" si="110"/>
+      <c r="AJ42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AJ42" s="10">
-        <f t="shared" si="110"/>
+      <c r="AK42" s="10">
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
-      <c r="AK42" s="10">
-        <f t="shared" si="110"/>
-        <v>0.22</v>
-      </c>
       <c r="AL42" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="106"/>
         <v>0.22</v>
       </c>
       <c r="AN42" t="s">
@@ -5654,7 +5590,7 @@
       </c>
       <c r="AO42" s="3">
         <f>NPV(AO41,AB29:EN29)</f>
-        <v>1555.176608083834</v>
+        <v>1668.3946495042082</v>
       </c>
     </row>
     <row r="43" spans="2:41" x14ac:dyDescent="0.3">
@@ -5662,19 +5598,19 @@
         <v>50</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:L43" si="111">I22/I8</f>
+        <f t="shared" ref="I43:L43" si="107">I22/I8</f>
         <v>0.18969555035128802</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>0.12136929460580902</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>0.158438576349024</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>0.13255567338282073</v>
       </c>
       <c r="M43" s="10">
@@ -5682,107 +5618,107 @@
         <v>0.15594541910331378</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" ref="N43:R43" si="112">N22/N8</f>
+        <f t="shared" ref="N43:R43" si="108">N22/N8</f>
         <v>0.17973568281938332</v>
       </c>
       <c r="O43" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.19000979431929474</v>
       </c>
       <c r="P43" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.19729729729729725</v>
       </c>
       <c r="Q43" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.18886198547215491</v>
       </c>
       <c r="R43" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="108"/>
         <v>0.18848526387936926</v>
       </c>
       <c r="S43" s="10">
-        <f t="shared" ref="S43:V43" si="113">S22/S8</f>
+        <f t="shared" ref="S43:V43" si="109">S22/S8</f>
         <v>0.14856341976173784</v>
       </c>
       <c r="T43" s="10">
-        <f t="shared" si="113"/>
-        <v>0.1946210268948656</v>
+        <f t="shared" si="109"/>
+        <v>0.1237762237762238</v>
       </c>
       <c r="U43" s="10">
-        <f t="shared" si="113"/>
-        <v>0.17941425542149084</v>
+        <f t="shared" si="109"/>
+        <v>0.17936941393306544</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="113"/>
-        <v>0.18085951982931892</v>
+        <f t="shared" si="109"/>
+        <v>0.18077396097008652</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" ref="X43:AL43" si="114">X22/X8</f>
+        <f t="shared" ref="X43:AL43" si="110">X22/X8</f>
         <v>-2.4652087475149059E-2</v>
       </c>
       <c r="Y43" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0.1224736048265459</v>
       </c>
       <c r="Z43" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0.15773584905660362</v>
       </c>
       <c r="AA43" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0.19631393663284327</v>
       </c>
       <c r="AB43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.18743769506091751</v>
+        <f t="shared" si="110"/>
+        <v>0.15870340776278877</v>
       </c>
       <c r="AC43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.20230925782075163</v>
+        <f t="shared" si="110"/>
+        <v>0.2282915245264267</v>
       </c>
       <c r="AD43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.22344667733314974</v>
+        <f t="shared" si="110"/>
+        <v>0.24722731025547004</v>
       </c>
       <c r="AE43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.22761756343091444</v>
+        <f t="shared" si="110"/>
+        <v>0.250309082279425</v>
       </c>
       <c r="AF43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.22983567682385109</v>
+        <f t="shared" si="110"/>
+        <v>0.25184265823224006</v>
       </c>
       <c r="AG43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23073790165081079</v>
+        <f t="shared" si="110"/>
+        <v>0.25227690580022877</v>
       </c>
       <c r="AH43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23255350564082578</v>
+        <f t="shared" si="110"/>
+        <v>0.25382321064532459</v>
       </c>
       <c r="AI43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23435521213271174</v>
+        <f t="shared" si="110"/>
+        <v>0.25535435563899794</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23614341584460175</v>
+        <f t="shared" si="110"/>
+        <v>0.25687048940724305</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23791852421338491</v>
+        <f t="shared" si="110"/>
+        <v>0.25837175911893678</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="114"/>
-        <v>0.23968095825450927</v>
+        <f t="shared" si="110"/>
+        <v>0.2598583105001237</v>
       </c>
       <c r="AN43" t="s">
         <v>55</v>
       </c>
       <c r="AO43" s="3">
         <f>Main!D8</f>
-        <v>126.8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="2:41" x14ac:dyDescent="0.3">
@@ -5790,19 +5726,19 @@
         <v>42</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" ref="I44:L44" si="115">I28/I27</f>
+        <f t="shared" ref="I44:L44" si="111">I28/I27</f>
         <v>0.35616438356164393</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>-3.4825870646766191E-2</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>0.17741935483870977</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="111"/>
         <v>7.4829931972789157E-2</v>
       </c>
       <c r="M44" s="10">
@@ -5810,107 +5746,107 @@
         <v>1.1764705882352946E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" ref="N44:R44" si="116">N28/N27</f>
+        <f t="shared" ref="N44:R44" si="112">N28/N27</f>
         <v>1.9178082191780819E-2</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="112"/>
         <v>0.23711340206185574</v>
       </c>
       <c r="P44" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="112"/>
         <v>0.12727272727272732</v>
       </c>
       <c r="Q44" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="112"/>
         <v>0.20869565217391309</v>
       </c>
       <c r="R44" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="112"/>
         <v>0.15634218289085558</v>
       </c>
       <c r="S44" s="10">
-        <f t="shared" ref="S44:V44" si="117">S28/S27</f>
+        <f t="shared" ref="S44:V44" si="113">S28/S27</f>
         <v>0.11904761904761911</v>
       </c>
       <c r="T44" s="10">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
+        <v>0.12068965517241378</v>
+      </c>
+      <c r="U44" s="10">
+        <f t="shared" si="113"/>
         <v>0.15</v>
       </c>
-      <c r="U44" s="10">
-        <f t="shared" si="117"/>
+      <c r="V44" s="10">
+        <f t="shared" si="113"/>
         <v>0.15</v>
       </c>
-      <c r="V44" s="10">
-        <f t="shared" si="117"/>
-        <v>0.15</v>
-      </c>
       <c r="X44" s="10">
-        <f t="shared" ref="X44:AL44" si="118">X28/X27</f>
+        <f t="shared" ref="X44:AL44" si="114">X28/X27</f>
         <v>0</v>
       </c>
       <c r="Y44" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0.3682008368200842</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>4.1927409261576995E-2</v>
       </c>
       <c r="AA44" s="10">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>0.1734390485629336</v>
       </c>
       <c r="AB44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.13538574567135506</v>
+        <f t="shared" si="114"/>
+        <v>0.13774452835451287</v>
       </c>
       <c r="AC44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AD44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AF44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AG44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AH44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AI44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL44" s="10">
-        <f t="shared" si="118"/>
-        <v>0.15</v>
+        <f t="shared" si="114"/>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AN44" t="s">
         <v>56</v>
       </c>
       <c r="AO44" s="3">
         <f>AO42+AO43</f>
-        <v>1681.976608083834</v>
+        <v>1796.3946495042082</v>
       </c>
     </row>
     <row r="45" spans="2:41" x14ac:dyDescent="0.3">
@@ -5918,19 +5854,19 @@
         <v>51</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" ref="I45:L45" si="119">I29/I8</f>
+        <f t="shared" ref="I45:L45" si="115">I29/I8</f>
         <v>0.11007025761124117</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="115"/>
         <v>0.21576763485477166</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="115"/>
         <v>0.17566016073478749</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="119"/>
+        <f t="shared" si="115"/>
         <v>0.14422057264050897</v>
       </c>
       <c r="M45" s="10">
@@ -5938,107 +5874,107 @@
         <v>0.16374269005847947</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" ref="N45:R45" si="120">N29/N8</f>
+        <f t="shared" ref="N45:R45" si="116">N29/N8</f>
         <v>0.94625550660792968</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>0.1449559255631733</v>
       </c>
       <c r="P45" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>0.17297297297297293</v>
       </c>
       <c r="Q45" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>0.14689265536723159</v>
       </c>
       <c r="R45" s="10">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>0.19602467443454402</v>
       </c>
       <c r="S45" s="10">
-        <f t="shared" ref="S45:V45" si="121">S29/S8</f>
+        <f t="shared" ref="S45:V45" si="117">S29/S8</f>
         <v>0.12964260686755424</v>
       </c>
       <c r="T45" s="10">
-        <f t="shared" si="121"/>
-        <v>0.17128206894176803</v>
+        <f t="shared" si="117"/>
+        <v>0.10699300699300701</v>
       </c>
       <c r="U45" s="10">
-        <f t="shared" si="121"/>
-        <v>0.15826065159511404</v>
+        <f t="shared" si="117"/>
+        <v>0.15822370694620436</v>
       </c>
       <c r="V45" s="10">
-        <f t="shared" si="121"/>
-        <v>0.15925951462562687</v>
+        <f t="shared" si="117"/>
+        <v>0.15918894824859928</v>
       </c>
       <c r="X45" s="10">
-        <f t="shared" ref="X45:AL45" si="122">X29/X8</f>
+        <f t="shared" ref="X45:AL45" si="118">X29/X8</f>
         <v>-0.1709741550695825</v>
       </c>
       <c r="Y45" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>4.5550527903468974E-2</v>
       </c>
       <c r="Z45" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>0.38515723270440239</v>
       </c>
       <c r="AA45" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>0.17270656450610894</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.16616985637406886</v>
+        <f t="shared" si="118"/>
+        <v>0.13904643294023028</v>
       </c>
       <c r="AC45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.17568543105611689</v>
+        <f t="shared" si="118"/>
+        <v>0.19868405810600243</v>
       </c>
       <c r="AD45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.19336183082408351</v>
+        <f t="shared" si="118"/>
+        <v>0.21478649472696695</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.19677131412912857</v>
+        <f t="shared" si="118"/>
+        <v>0.21735206061207016</v>
       </c>
       <c r="AF45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.19857776106089689</v>
+        <f t="shared" si="118"/>
+        <v>0.21862223290840904</v>
       </c>
       <c r="AG45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.19929004865685626</v>
+        <f t="shared" si="118"/>
+        <v>0.21896174169927041</v>
       </c>
       <c r="AH45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.20080127822241034</v>
+        <f t="shared" si="118"/>
+        <v>0.22027192070221874</v>
       </c>
       <c r="AI45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.20230094011672364</v>
+        <f t="shared" si="118"/>
+        <v>0.22156925481298137</v>
       </c>
       <c r="AJ45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.20378936288595287</v>
+        <f t="shared" si="118"/>
+        <v>0.2228538699618737</v>
       </c>
       <c r="AK45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.20526688566279219</v>
+        <f t="shared" si="118"/>
+        <v>0.22412589084460044</v>
       </c>
       <c r="AL45" s="10">
-        <f t="shared" si="122"/>
-        <v>0.20673385888213616</v>
+        <f t="shared" si="118"/>
+        <v>0.2253854409343593</v>
       </c>
       <c r="AN45" t="s">
         <v>57</v>
       </c>
       <c r="AO45" s="2">
         <f>AO44/AL30</f>
-        <v>18.793034727193675</v>
+        <v>20.071448597812381</v>
       </c>
     </row>
     <row r="46" spans="2:41" x14ac:dyDescent="0.3">
@@ -6047,7 +5983,7 @@
       </c>
       <c r="AO46" s="2">
         <f>Main!D3</f>
-        <v>17.59</v>
+        <v>19.350000000000001</v>
       </c>
     </row>
     <row r="47" spans="2:41" x14ac:dyDescent="0.3">
@@ -6056,7 +5992,7 @@
       </c>
       <c r="AO47" s="9">
         <f>AO45/AO46-1</f>
-        <v>6.8393105582357894E-2</v>
+        <v>3.7284165261621594E-2</v>
       </c>
     </row>
     <row r="48" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6064,35 +6000,35 @@
         <v>45</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" ref="K48:R48" si="123">K27</f>
+        <f t="shared" ref="K48:R48" si="119">K27</f>
         <v>18.599999999999991</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>14.699999999999992</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>16.999999999999993</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>109.50000000000001</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>21.999999999999993</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>22.999999999999993</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="123"/>
+        <f t="shared" si="119"/>
         <v>33.89999999999997</v>
       </c>
       <c r="Z48" s="8">
@@ -6104,54 +6040,54 @@
         <v>100.9</v>
       </c>
       <c r="AB48" s="8">
-        <f t="shared" ref="AB48:AL48" si="124">AB27</f>
-        <v>113.24559999999995</v>
+        <f t="shared" ref="AB48:AL48" si="120">AB27</f>
+        <v>94.651599999999917</v>
       </c>
       <c r="AC48" s="8">
-        <f t="shared" si="124"/>
-        <v>138.23346399999994</v>
+        <f t="shared" si="120"/>
+        <v>153.48676400000002</v>
       </c>
       <c r="AD48" s="8">
-        <f t="shared" si="124"/>
-        <v>166.66507059200003</v>
+        <f t="shared" si="120"/>
+        <v>181.66063079200001</v>
       </c>
       <c r="AE48" s="8">
-        <f t="shared" si="124"/>
-        <v>178.35527070432005</v>
+        <f t="shared" si="120"/>
+        <v>193.21198819032003</v>
       </c>
       <c r="AF48" s="8">
-        <f t="shared" si="124"/>
-        <v>186.25340380022882</v>
+        <f t="shared" si="120"/>
+        <v>200.97624470114883</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="124"/>
-        <v>192.05000422113105</v>
+        <f t="shared" si="120"/>
+        <v>206.74546990507346</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="124"/>
-        <v>197.44112029629474</v>
+        <f t="shared" si="120"/>
+        <v>212.14220268360944</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="124"/>
-        <v>202.96565994374922</v>
+        <f t="shared" si="120"/>
+        <v>217.65948835152054</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="124"/>
-        <v>208.62755765653591</v>
+        <f t="shared" si="120"/>
+        <v>223.29986414893219</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="124"/>
-        <v>214.43094027868239</v>
+        <f t="shared" si="120"/>
+        <v>229.0659193225959</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="124"/>
-        <v>220.38014208892315</v>
+        <f t="shared" si="120"/>
+        <v>234.96029617863974</v>
       </c>
       <c r="AN48" t="s">
         <v>60</v>
       </c>
       <c r="AO48" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="2:41" x14ac:dyDescent="0.3">
@@ -6241,11 +6177,11 @@
         <v>-5</v>
       </c>
       <c r="Z50" s="3">
-        <f t="shared" ref="Z50:Z61" si="125">SUM(K50:N50)</f>
+        <f t="shared" ref="Z50:Z61" si="121">SUM(K50:N50)</f>
         <v>-89.8</v>
       </c>
       <c r="AA50" s="3">
-        <f t="shared" ref="AA50:AA61" si="126">SUM(O50:R50)</f>
+        <f t="shared" ref="AA50:AA61" si="122">SUM(O50:R50)</f>
         <v>-5</v>
       </c>
       <c r="AB50" s="3">
@@ -6282,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="AO50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="2:41" x14ac:dyDescent="0.3">
@@ -6302,11 +6238,11 @@
         <v>0</v>
       </c>
       <c r="Z51" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>0</v>
       </c>
       <c r="AA51" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>0</v>
       </c>
       <c r="AB51" s="3">
@@ -6364,11 +6300,11 @@
         <v>0.1</v>
       </c>
       <c r="Z52" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>0.7</v>
       </c>
       <c r="AA52" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>0.1</v>
       </c>
       <c r="AB52" s="3">
@@ -6434,11 +6370,11 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="Z53" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>13.2</v>
       </c>
       <c r="AA53" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>15.6</v>
       </c>
       <c r="AB53" s="3">
@@ -6446,43 +6382,43 @@
         <v>15.911999999999999</v>
       </c>
       <c r="AC53" s="3">
-        <f t="shared" ref="AC53:AL53" si="127">AB53*1.02</f>
+        <f t="shared" ref="AC53:AL53" si="123">AB53*1.02</f>
         <v>16.230239999999998</v>
       </c>
       <c r="AD53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>16.554844799999998</v>
       </c>
       <c r="AE53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>16.885941696</v>
       </c>
       <c r="AF53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>17.22366052992</v>
       </c>
       <c r="AG53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>17.568133740518402</v>
       </c>
       <c r="AH53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>17.919496415328769</v>
       </c>
       <c r="AI53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>18.277886343635345</v>
       </c>
       <c r="AJ53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>18.643444070508053</v>
       </c>
       <c r="AK53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>19.016312951918216</v>
       </c>
       <c r="AL53" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="123"/>
         <v>19.396639210956582</v>
       </c>
     </row>
@@ -6515,11 +6451,11 @@
         <v>0.9</v>
       </c>
       <c r="Z54" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>14.799999999999999</v>
       </c>
       <c r="AA54" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="AB54" s="3">
@@ -6527,43 +6463,43 @@
         <v>7.0400000000000009</v>
       </c>
       <c r="AC54" s="3">
-        <f t="shared" ref="AC54:AL54" si="128">AB54*0.8</f>
+        <f t="shared" ref="AC54:AL54" si="124">AB54*0.8</f>
         <v>5.6320000000000014</v>
       </c>
       <c r="AD54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>4.5056000000000012</v>
       </c>
       <c r="AE54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>3.604480000000001</v>
       </c>
       <c r="AF54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>2.8835840000000008</v>
       </c>
       <c r="AG54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>2.3068672000000006</v>
       </c>
       <c r="AH54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>1.8454937600000005</v>
       </c>
       <c r="AI54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>1.4763950080000006</v>
       </c>
       <c r="AJ54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>1.1811160064000006</v>
       </c>
       <c r="AK54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>0.94489280512000051</v>
       </c>
       <c r="AL54" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="124"/>
         <v>0.7559142440960005</v>
       </c>
     </row>
@@ -6596,11 +6532,11 @@
         <v>-0.4</v>
       </c>
       <c r="Z55" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>-0.3</v>
       </c>
       <c r="AA55" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-0.10000000000000003</v>
       </c>
       <c r="AB55" s="3">
@@ -6666,11 +6602,11 @@
         <v>-18.2</v>
       </c>
       <c r="Z56" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>-17.600000000000001</v>
       </c>
       <c r="AA56" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-20.2</v>
       </c>
       <c r="AB56" s="3">
@@ -6736,11 +6672,11 @@
         <v>-3</v>
       </c>
       <c r="Z57" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>-1.0000000000000002</v>
       </c>
       <c r="AA57" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-1.8</v>
       </c>
       <c r="AB57" s="3">
@@ -6806,11 +6742,11 @@
         <v>11.6</v>
       </c>
       <c r="Z58" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>5.3000000000000007</v>
       </c>
       <c r="AA58" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>23.1</v>
       </c>
       <c r="AB58" s="3">
@@ -6876,11 +6812,11 @@
         <v>2</v>
       </c>
       <c r="Z59" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="AA59" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-4.9000000000000004</v>
       </c>
       <c r="AB59" s="3">
@@ -6946,11 +6882,11 @@
         <v>0.1</v>
       </c>
       <c r="Z60" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA60" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-0.10000000000000017</v>
       </c>
       <c r="AB60" s="3">
@@ -7016,11 +6952,11 @@
         <v>-3.4</v>
       </c>
       <c r="Z61" s="3">
-        <f t="shared" si="125"/>
+        <f t="shared" si="121"/>
         <v>-6</v>
       </c>
       <c r="AA61" s="3">
-        <f t="shared" si="126"/>
+        <f t="shared" si="122"/>
         <v>-7.6999999999999993</v>
       </c>
       <c r="AB61" s="3">
@@ -7062,35 +6998,35 @@
         <v>82</v>
       </c>
       <c r="K62" s="8">
-        <f t="shared" ref="K62:R62" si="129">K48+SUM(K49:K61)</f>
+        <f t="shared" ref="K62:R62" si="125">K48+SUM(K49:K61)</f>
         <v>25.499999999999993</v>
       </c>
       <c r="L62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>15.399999999999993</v>
       </c>
       <c r="M62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>16.099999999999994</v>
       </c>
       <c r="N62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>25.300000000000011</v>
       </c>
       <c r="O62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>30.999999999999993</v>
       </c>
       <c r="P62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>17.299999999999994</v>
       </c>
       <c r="Q62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>35.099999999999994</v>
       </c>
       <c r="R62" s="8">
-        <f t="shared" si="129"/>
+        <f t="shared" si="125"/>
         <v>21.499999999999972</v>
       </c>
       <c r="Z62" s="8">
@@ -7102,48 +7038,48 @@
         <v>107.5</v>
       </c>
       <c r="AB62" s="8">
-        <f t="shared" ref="AB62:AL62" si="130">AB48+SUM(AB49:AB61)</f>
-        <v>136.19759999999997</v>
+        <f t="shared" ref="AB62:AL62" si="126">AB48+SUM(AB49:AB61)</f>
+        <v>117.60359999999991</v>
       </c>
       <c r="AC62" s="8">
-        <f t="shared" si="130"/>
-        <v>160.09570399999996</v>
+        <f t="shared" si="126"/>
+        <v>175.34900400000004</v>
       </c>
       <c r="AD62" s="8">
-        <f t="shared" si="130"/>
-        <v>187.72551539200003</v>
+        <f t="shared" si="126"/>
+        <v>202.72107559200001</v>
       </c>
       <c r="AE62" s="8">
-        <f t="shared" si="130"/>
-        <v>198.84569240032005</v>
+        <f t="shared" si="126"/>
+        <v>213.70240988632003</v>
       </c>
       <c r="AF62" s="8">
-        <f t="shared" si="130"/>
-        <v>206.36064833014882</v>
+        <f t="shared" si="126"/>
+        <v>221.08348923106882</v>
       </c>
       <c r="AG62" s="8">
-        <f t="shared" si="130"/>
-        <v>211.92500516164944</v>
+        <f t="shared" si="126"/>
+        <v>226.62047084559185</v>
       </c>
       <c r="AH62" s="8">
-        <f t="shared" si="130"/>
-        <v>217.2061104716235</v>
+        <f t="shared" si="126"/>
+        <v>231.9071928589382</v>
       </c>
       <c r="AI62" s="8">
-        <f t="shared" si="130"/>
-        <v>222.71994129538456</v>
+        <f t="shared" si="126"/>
+        <v>237.41376970315588</v>
       </c>
       <c r="AJ62" s="8">
-        <f t="shared" si="130"/>
-        <v>228.45211773344397</v>
+        <f t="shared" si="126"/>
+        <v>243.12442422584024</v>
       </c>
       <c r="AK62" s="8">
-        <f t="shared" si="130"/>
-        <v>234.3921460357206</v>
+        <f t="shared" si="126"/>
+        <v>249.02712507963412</v>
       </c>
       <c r="AL62" s="8">
-        <f t="shared" si="130"/>
-        <v>240.53269554397573</v>
+        <f t="shared" si="126"/>
+        <v>255.11284963369232</v>
       </c>
     </row>
     <row r="63" spans="2:41" x14ac:dyDescent="0.3">
@@ -7175,11 +7111,11 @@
         <v>0</v>
       </c>
       <c r="Z63" s="3">
-        <f t="shared" ref="Z63:Z65" si="131">SUM(K63:N63)</f>
+        <f t="shared" ref="Z63:Z65" si="127">SUM(K63:N63)</f>
         <v>1.7999999999999998</v>
       </c>
       <c r="AA63" s="3">
-        <f t="shared" ref="AA63:AA65" si="132">SUM(O63:R63)</f>
+        <f t="shared" ref="AA63:AA65" si="128">SUM(O63:R63)</f>
         <v>23.2</v>
       </c>
       <c r="AB63" s="3">
@@ -7190,39 +7126,39 @@
         <v>5.15</v>
       </c>
       <c r="AD63" s="3">
-        <f t="shared" ref="AD63:AL63" si="133">AC63*1.03</f>
+        <f t="shared" ref="AD63:AL63" si="129">AC63*1.03</f>
         <v>5.3045000000000009</v>
       </c>
       <c r="AE63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>5.4636350000000009</v>
       </c>
       <c r="AF63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>5.6275440500000009</v>
       </c>
       <c r="AG63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>5.796370371500001</v>
       </c>
       <c r="AH63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>5.9702614826450011</v>
       </c>
       <c r="AI63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>6.1493693271243517</v>
       </c>
       <c r="AJ63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>6.3338504069380823</v>
       </c>
       <c r="AK63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>6.5238659191462247</v>
       </c>
       <c r="AL63" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="129"/>
         <v>6.7195818967206113</v>
       </c>
     </row>
@@ -7255,11 +7191,11 @@
         <v>0</v>
       </c>
       <c r="Z64" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>0.3</v>
       </c>
       <c r="AA64" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="AB64" s="3">
@@ -7325,11 +7261,11 @@
         <v>1.9</v>
       </c>
       <c r="Z65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="127"/>
         <v>4.3</v>
       </c>
       <c r="AA65" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="128"/>
         <v>7.2999999999999989</v>
       </c>
       <c r="AB65" s="3">
@@ -7341,7 +7277,7 @@
         <v>13.6875</v>
       </c>
       <c r="AD65" s="3">
-        <f t="shared" ref="AD65" si="134">AC65*1.2</f>
+        <f t="shared" ref="AD65" si="130">AC65*1.2</f>
         <v>16.425000000000001</v>
       </c>
       <c r="AE65" s="3">
@@ -7353,27 +7289,27 @@
         <v>18.970875000000003</v>
       </c>
       <c r="AG65" s="3">
-        <f t="shared" ref="AG65:AL65" si="135">AF65*1.05</f>
+        <f t="shared" ref="AG65:AL65" si="131">AF65*1.05</f>
         <v>19.919418750000006</v>
       </c>
       <c r="AH65" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>20.915389687500006</v>
       </c>
       <c r="AI65" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>21.961159171875007</v>
       </c>
       <c r="AJ65" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>23.05921713046876</v>
       </c>
       <c r="AK65" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>24.212177986992199</v>
       </c>
       <c r="AL65" s="3">
-        <f t="shared" si="135"/>
+        <f t="shared" si="131"/>
         <v>25.422786886341811</v>
       </c>
     </row>
@@ -7382,35 +7318,35 @@
         <v>87</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" ref="K66:R66" si="136">SUM(K63:K65)</f>
+        <f t="shared" ref="K66:R66" si="132">SUM(K63:K65)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="L66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.2</v>
       </c>
       <c r="M66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.9</v>
       </c>
       <c r="N66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.9</v>
       </c>
       <c r="O66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>21.599999999999998</v>
       </c>
       <c r="P66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>2.9</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="R66" s="3">
-        <f t="shared" si="136"/>
+        <f t="shared" si="132"/>
         <v>1.9</v>
       </c>
       <c r="Z66" s="3">
@@ -7422,47 +7358,47 @@
         <v>30.5</v>
       </c>
       <c r="AB66" s="3">
-        <f t="shared" ref="AB66:AL66" si="137">SUM(AB63:AB65)</f>
+        <f t="shared" ref="AB66:AL66" si="133">SUM(AB63:AB65)</f>
         <v>15.95</v>
       </c>
       <c r="AC66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>18.837499999999999</v>
       </c>
       <c r="AD66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>21.729500000000002</v>
       </c>
       <c r="AE66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>23.531135000000003</v>
       </c>
       <c r="AF66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>24.598419050000004</v>
       </c>
       <c r="AG66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>25.715789121500006</v>
       </c>
       <c r="AH66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>26.885651170145007</v>
       </c>
       <c r="AI66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>28.110528498999358</v>
       </c>
       <c r="AJ66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>29.393067537406843</v>
       </c>
       <c r="AK66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>30.736043906138423</v>
       </c>
       <c r="AL66" s="3">
-        <f t="shared" si="137"/>
+        <f t="shared" si="133"/>
         <v>32.142368783062423</v>
       </c>
     </row>
@@ -7471,35 +7407,35 @@
         <v>85</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" ref="K67:R67" si="138">K62-K66</f>
+        <f t="shared" ref="K67:R67" si="134">K62-K66</f>
         <v>24.099999999999994</v>
       </c>
       <c r="L67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>14.199999999999994</v>
       </c>
       <c r="M67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>14.199999999999994</v>
       </c>
       <c r="N67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>23.400000000000013</v>
       </c>
       <c r="O67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>9.399999999999995</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>14.399999999999993</v>
       </c>
       <c r="Q67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>30.999999999999993</v>
       </c>
       <c r="R67" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="134"/>
         <v>19.599999999999973</v>
       </c>
       <c r="Z67" s="8">
@@ -7511,492 +7447,492 @@
         <v>77</v>
       </c>
       <c r="AB67" s="8">
-        <f t="shared" ref="AB67:AL67" si="139">AB62-AB66</f>
-        <v>120.24759999999996</v>
+        <f t="shared" ref="AB67:AL67" si="135">AB62-AB66</f>
+        <v>101.65359999999991</v>
       </c>
       <c r="AC67" s="8">
-        <f t="shared" si="139"/>
-        <v>141.25820399999995</v>
+        <f t="shared" si="135"/>
+        <v>156.51150400000003</v>
       </c>
       <c r="AD67" s="8">
-        <f t="shared" si="139"/>
-        <v>165.99601539200003</v>
+        <f t="shared" si="135"/>
+        <v>180.991575592</v>
       </c>
       <c r="AE67" s="8">
-        <f t="shared" si="139"/>
-        <v>175.31455740032004</v>
+        <f t="shared" si="135"/>
+        <v>190.17127488632002</v>
       </c>
       <c r="AF67" s="8">
-        <f t="shared" si="139"/>
-        <v>181.7622292801488</v>
+        <f t="shared" si="135"/>
+        <v>196.48507018106881</v>
       </c>
       <c r="AG67" s="8">
-        <f t="shared" si="139"/>
-        <v>186.20921604014944</v>
+        <f t="shared" si="135"/>
+        <v>200.90468172409186</v>
       </c>
       <c r="AH67" s="8">
-        <f t="shared" si="139"/>
-        <v>190.32045930147851</v>
+        <f t="shared" si="135"/>
+        <v>205.02154168879321</v>
       </c>
       <c r="AI67" s="8">
-        <f t="shared" si="139"/>
-        <v>194.60941279638519</v>
+        <f t="shared" si="135"/>
+        <v>209.30324120415651</v>
       </c>
       <c r="AJ67" s="8">
-        <f t="shared" si="139"/>
-        <v>199.05905019603713</v>
+        <f t="shared" si="135"/>
+        <v>213.73135668843341</v>
       </c>
       <c r="AK67" s="8">
-        <f t="shared" si="139"/>
-        <v>203.65610212958217</v>
+        <f t="shared" si="135"/>
+        <v>218.29108117349568</v>
       </c>
       <c r="AL67" s="8">
-        <f t="shared" si="139"/>
-        <v>208.3903267609133</v>
+        <f t="shared" si="135"/>
+        <v>222.97048085062988</v>
       </c>
       <c r="AM67" s="1">
         <f>AL67*(1+$AO$40)</f>
-        <v>206.30642349330415</v>
+        <v>220.74077604212357</v>
       </c>
       <c r="AN67" s="1">
-        <f t="shared" ref="AN67:CY67" si="140">AM67*(1+$AO$40)</f>
-        <v>204.2433592583711</v>
+        <f t="shared" ref="AN67:CY67" si="136">AM67*(1+$AO$40)</f>
+        <v>218.53336828170234</v>
       </c>
       <c r="AO67" s="1">
-        <f t="shared" si="140"/>
-        <v>202.20092566578739</v>
+        <f t="shared" si="136"/>
+        <v>216.34803459888531</v>
       </c>
       <c r="AP67" s="1">
-        <f t="shared" si="140"/>
-        <v>200.17891640912953</v>
+        <f t="shared" si="136"/>
+        <v>214.18455425289645</v>
       </c>
       <c r="AQ67" s="1">
-        <f t="shared" si="140"/>
-        <v>198.17712724503824</v>
+        <f t="shared" si="136"/>
+        <v>212.04270871036749</v>
       </c>
       <c r="AR67" s="1">
-        <f t="shared" si="140"/>
-        <v>196.19535597258786</v>
+        <f t="shared" si="136"/>
+        <v>209.92228162326381</v>
       </c>
       <c r="AS67" s="1">
-        <f t="shared" si="140"/>
-        <v>194.23340241286198</v>
+        <f t="shared" si="136"/>
+        <v>207.82305880703117</v>
       </c>
       <c r="AT67" s="1">
-        <f t="shared" si="140"/>
-        <v>192.29106838873335</v>
+        <f t="shared" si="136"/>
+        <v>205.74482821896086</v>
       </c>
       <c r="AU67" s="1">
-        <f t="shared" si="140"/>
-        <v>190.36815770484603</v>
+        <f t="shared" si="136"/>
+        <v>203.68737993677126</v>
       </c>
       <c r="AV67" s="1">
-        <f t="shared" si="140"/>
-        <v>188.46447612779755</v>
+        <f t="shared" si="136"/>
+        <v>201.65050613740354</v>
       </c>
       <c r="AW67" s="1">
-        <f t="shared" si="140"/>
-        <v>186.57983136651958</v>
+        <f t="shared" si="136"/>
+        <v>199.63400107602951</v>
       </c>
       <c r="AX67" s="1">
-        <f t="shared" si="140"/>
-        <v>184.71403305285438</v>
+        <f t="shared" si="136"/>
+        <v>197.63766106526921</v>
       </c>
       <c r="AY67" s="1">
-        <f t="shared" si="140"/>
-        <v>182.86689272232584</v>
+        <f t="shared" si="136"/>
+        <v>195.66128445461652</v>
       </c>
       <c r="AZ67" s="1">
-        <f t="shared" si="140"/>
-        <v>181.0382237951026</v>
+        <f t="shared" si="136"/>
+        <v>193.70467161007036</v>
       </c>
       <c r="BA67" s="1">
-        <f t="shared" si="140"/>
-        <v>179.22784155715158</v>
+        <f t="shared" si="136"/>
+        <v>191.76762489396967</v>
       </c>
       <c r="BB67" s="1">
-        <f t="shared" si="140"/>
-        <v>177.43556314158005</v>
+        <f t="shared" si="136"/>
+        <v>189.84994864502997</v>
       </c>
       <c r="BC67" s="1">
-        <f t="shared" si="140"/>
-        <v>175.66120751016425</v>
+        <f t="shared" si="136"/>
+        <v>187.95144915857966</v>
       </c>
       <c r="BD67" s="1">
-        <f t="shared" si="140"/>
-        <v>173.90459543506259</v>
+        <f t="shared" si="136"/>
+        <v>186.07193466699385</v>
       </c>
       <c r="BE67" s="1">
-        <f t="shared" si="140"/>
-        <v>172.16554948071197</v>
+        <f t="shared" si="136"/>
+        <v>184.2112153203239</v>
       </c>
       <c r="BF67" s="1">
-        <f t="shared" si="140"/>
-        <v>170.44389398590485</v>
+        <f t="shared" si="136"/>
+        <v>182.36910316712067</v>
       </c>
       <c r="BG67" s="1">
-        <f t="shared" si="140"/>
-        <v>168.7394550460458</v>
+        <f t="shared" si="136"/>
+        <v>180.54541213544945</v>
       </c>
       <c r="BH67" s="1">
-        <f t="shared" si="140"/>
-        <v>167.05206049558535</v>
+        <f t="shared" si="136"/>
+        <v>178.73995801409495</v>
       </c>
       <c r="BI67" s="1">
-        <f t="shared" si="140"/>
-        <v>165.38153989062948</v>
+        <f t="shared" si="136"/>
+        <v>176.95255843395401</v>
       </c>
       <c r="BJ67" s="1">
-        <f t="shared" si="140"/>
-        <v>163.72772449172319</v>
+        <f t="shared" si="136"/>
+        <v>175.18303284961448</v>
       </c>
       <c r="BK67" s="1">
-        <f t="shared" si="140"/>
-        <v>162.09044724680595</v>
+        <f t="shared" si="136"/>
+        <v>173.43120252111834</v>
       </c>
       <c r="BL67" s="1">
-        <f t="shared" si="140"/>
-        <v>160.4695427743379</v>
+        <f t="shared" si="136"/>
+        <v>171.69689049590716</v>
       </c>
       <c r="BM67" s="1">
-        <f t="shared" si="140"/>
-        <v>158.8648473465945</v>
+        <f t="shared" si="136"/>
+        <v>169.97992159094809</v>
       </c>
       <c r="BN67" s="1">
-        <f t="shared" si="140"/>
-        <v>157.27619887312855</v>
+        <f t="shared" si="136"/>
+        <v>168.28012237503862</v>
       </c>
       <c r="BO67" s="1">
-        <f t="shared" si="140"/>
-        <v>155.70343688439726</v>
+        <f t="shared" si="136"/>
+        <v>166.59732115128824</v>
       </c>
       <c r="BP67" s="1">
-        <f t="shared" si="140"/>
-        <v>154.14640251555329</v>
+        <f t="shared" si="136"/>
+        <v>164.93134793977535</v>
       </c>
       <c r="BQ67" s="1">
-        <f t="shared" si="140"/>
-        <v>152.60493849039776</v>
+        <f t="shared" si="136"/>
+        <v>163.28203446037759</v>
       </c>
       <c r="BR67" s="1">
-        <f t="shared" si="140"/>
-        <v>151.07888910549377</v>
+        <f t="shared" si="136"/>
+        <v>161.64921411577382</v>
       </c>
       <c r="BS67" s="1">
-        <f t="shared" si="140"/>
-        <v>149.56810021443883</v>
+        <f t="shared" si="136"/>
+        <v>160.03272197461607</v>
       </c>
       <c r="BT67" s="1">
-        <f t="shared" si="140"/>
-        <v>148.07241921229445</v>
+        <f t="shared" si="136"/>
+        <v>158.4323947548699</v>
       </c>
       <c r="BU67" s="1">
-        <f t="shared" si="140"/>
-        <v>146.5916950201715</v>
+        <f t="shared" si="136"/>
+        <v>156.84807080732119</v>
       </c>
       <c r="BV67" s="1">
-        <f t="shared" si="140"/>
-        <v>145.12577806996978</v>
+        <f t="shared" si="136"/>
+        <v>155.27959009924797</v>
       </c>
       <c r="BW67" s="1">
-        <f t="shared" si="140"/>
-        <v>143.67452028927008</v>
+        <f t="shared" si="136"/>
+        <v>153.72679419825548</v>
       </c>
       <c r="BX67" s="1">
-        <f t="shared" si="140"/>
-        <v>142.23777508637738</v>
+        <f t="shared" si="136"/>
+        <v>152.18952625627293</v>
       </c>
       <c r="BY67" s="1">
-        <f t="shared" si="140"/>
-        <v>140.81539733551361</v>
+        <f t="shared" si="136"/>
+        <v>150.66763099371019</v>
       </c>
       <c r="BZ67" s="1">
-        <f t="shared" si="140"/>
-        <v>139.40724336215848</v>
+        <f t="shared" si="136"/>
+        <v>149.1609546837731</v>
       </c>
       <c r="CA67" s="1">
-        <f t="shared" si="140"/>
-        <v>138.01317092853691</v>
+        <f t="shared" si="136"/>
+        <v>147.66934513693536</v>
       </c>
       <c r="CB67" s="1">
-        <f t="shared" si="140"/>
-        <v>136.63303921925154</v>
+        <f t="shared" si="136"/>
+        <v>146.19265168556601</v>
       </c>
       <c r="CC67" s="1">
-        <f t="shared" si="140"/>
-        <v>135.26670882705903</v>
+        <f t="shared" si="136"/>
+        <v>144.73072516871034</v>
       </c>
       <c r="CD67" s="1">
-        <f t="shared" si="140"/>
-        <v>133.91404173878846</v>
+        <f t="shared" si="136"/>
+        <v>143.28341791702323</v>
       </c>
       <c r="CE67" s="1">
-        <f t="shared" si="140"/>
-        <v>132.57490132140057</v>
+        <f t="shared" si="136"/>
+        <v>141.85058373785299</v>
       </c>
       <c r="CF67" s="1">
-        <f t="shared" si="140"/>
-        <v>131.24915230818658</v>
+        <f t="shared" si="136"/>
+        <v>140.43207790047447</v>
       </c>
       <c r="CG67" s="1">
-        <f t="shared" si="140"/>
-        <v>129.93666078510472</v>
+        <f t="shared" si="136"/>
+        <v>139.02775712146973</v>
       </c>
       <c r="CH67" s="1">
-        <f t="shared" si="140"/>
-        <v>128.63729417725366</v>
+        <f t="shared" si="136"/>
+        <v>137.63747955025502</v>
       </c>
       <c r="CI67" s="1">
-        <f t="shared" si="140"/>
-        <v>127.35092123548112</v>
+        <f t="shared" si="136"/>
+        <v>136.26110475475247</v>
       </c>
       <c r="CJ67" s="1">
-        <f t="shared" si="140"/>
-        <v>126.07741202312631</v>
+        <f t="shared" si="136"/>
+        <v>134.89849370720495</v>
       </c>
       <c r="CK67" s="1">
-        <f t="shared" si="140"/>
-        <v>124.81663790289505</v>
+        <f t="shared" si="136"/>
+        <v>133.54950877013289</v>
       </c>
       <c r="CL67" s="1">
-        <f t="shared" si="140"/>
-        <v>123.56847152386611</v>
+        <f t="shared" si="136"/>
+        <v>132.21401368243156</v>
       </c>
       <c r="CM67" s="1">
-        <f t="shared" si="140"/>
-        <v>122.33278680862745</v>
+        <f t="shared" si="136"/>
+        <v>130.89187354560724</v>
       </c>
       <c r="CN67" s="1">
-        <f t="shared" si="140"/>
-        <v>121.10945894054117</v>
+        <f t="shared" si="136"/>
+        <v>129.58295481015116</v>
       </c>
       <c r="CO67" s="1">
-        <f t="shared" si="140"/>
-        <v>119.89836435113575</v>
+        <f t="shared" si="136"/>
+        <v>128.28712526204964</v>
       </c>
       <c r="CP67" s="1">
-        <f t="shared" si="140"/>
-        <v>118.6993807076244</v>
+        <f t="shared" si="136"/>
+        <v>127.00425400942915</v>
       </c>
       <c r="CQ67" s="1">
-        <f t="shared" si="140"/>
-        <v>117.51238690054815</v>
+        <f t="shared" si="136"/>
+        <v>125.73421146933485</v>
       </c>
       <c r="CR67" s="1">
-        <f t="shared" si="140"/>
-        <v>116.33726303154266</v>
+        <f t="shared" si="136"/>
+        <v>124.47686935464151</v>
       </c>
       <c r="CS67" s="1">
-        <f t="shared" si="140"/>
-        <v>115.17389040122724</v>
+        <f t="shared" si="136"/>
+        <v>123.23210066109509</v>
       </c>
       <c r="CT67" s="1">
-        <f t="shared" si="140"/>
-        <v>114.02215149721496</v>
+        <f t="shared" si="136"/>
+        <v>121.99977965448414</v>
       </c>
       <c r="CU67" s="1">
-        <f t="shared" si="140"/>
-        <v>112.88192998224281</v>
+        <f t="shared" si="136"/>
+        <v>120.7797818579393</v>
       </c>
       <c r="CV67" s="1">
-        <f t="shared" si="140"/>
-        <v>111.75311068242038</v>
+        <f t="shared" si="136"/>
+        <v>119.5719840393599</v>
       </c>
       <c r="CW67" s="1">
-        <f t="shared" si="140"/>
-        <v>110.63557957559618</v>
+        <f t="shared" si="136"/>
+        <v>118.37626419896631</v>
       </c>
       <c r="CX67" s="1">
-        <f t="shared" si="140"/>
-        <v>109.52922377984022</v>
+        <f t="shared" si="136"/>
+        <v>117.19250155697665</v>
       </c>
       <c r="CY67" s="1">
-        <f t="shared" si="140"/>
-        <v>108.43393154204182</v>
+        <f t="shared" si="136"/>
+        <v>116.02057654140688</v>
       </c>
       <c r="CZ67" s="1">
-        <f t="shared" ref="CZ67:EJ67" si="141">CY67*(1+$AO$40)</f>
-        <v>107.3495922266214</v>
+        <f t="shared" ref="CZ67:EJ67" si="137">CY67*(1+$AO$40)</f>
+        <v>114.86037077599281</v>
       </c>
       <c r="DA67" s="1">
-        <f t="shared" si="141"/>
-        <v>106.27609630435518</v>
+        <f t="shared" si="137"/>
+        <v>113.71176706823287</v>
       </c>
       <c r="DB67" s="1">
-        <f t="shared" si="141"/>
-        <v>105.21333534131162</v>
+        <f t="shared" si="137"/>
+        <v>112.57464939755054</v>
       </c>
       <c r="DC67" s="1">
-        <f t="shared" si="141"/>
-        <v>104.16120198789851</v>
+        <f t="shared" si="137"/>
+        <v>111.44890290357503</v>
       </c>
       <c r="DD67" s="1">
-        <f t="shared" si="141"/>
-        <v>103.11958996801953</v>
+        <f t="shared" si="137"/>
+        <v>110.33441387453928</v>
       </c>
       <c r="DE67" s="1">
-        <f t="shared" si="141"/>
-        <v>102.08839406833933</v>
+        <f t="shared" si="137"/>
+        <v>109.23106973579388</v>
       </c>
       <c r="DF67" s="1">
-        <f t="shared" si="141"/>
-        <v>101.06751012765594</v>
+        <f t="shared" si="137"/>
+        <v>108.13875903843594</v>
       </c>
       <c r="DG67" s="1">
-        <f t="shared" si="141"/>
-        <v>100.05683502637937</v>
+        <f t="shared" si="137"/>
+        <v>107.05737144805157</v>
       </c>
       <c r="DH67" s="1">
-        <f t="shared" si="141"/>
-        <v>99.056266676115584</v>
+        <f t="shared" si="137"/>
+        <v>105.98679773357105</v>
       </c>
       <c r="DI67" s="1">
-        <f t="shared" si="141"/>
-        <v>98.065704009354434</v>
+        <f t="shared" si="137"/>
+        <v>104.92692975623534</v>
       </c>
       <c r="DJ67" s="1">
-        <f t="shared" si="141"/>
-        <v>97.085046969260887</v>
+        <f t="shared" si="137"/>
+        <v>103.87766045867298</v>
       </c>
       <c r="DK67" s="1">
-        <f t="shared" si="141"/>
-        <v>96.11419649956828</v>
+        <f t="shared" si="137"/>
+        <v>102.83888385408625</v>
       </c>
       <c r="DL67" s="1">
-        <f t="shared" si="141"/>
-        <v>95.15305453457259</v>
+        <f t="shared" si="137"/>
+        <v>101.81049501554538</v>
       </c>
       <c r="DM67" s="1">
-        <f t="shared" si="141"/>
-        <v>94.201523989226857</v>
+        <f t="shared" si="137"/>
+        <v>100.79239006538992</v>
       </c>
       <c r="DN67" s="1">
-        <f t="shared" si="141"/>
-        <v>93.259508749334586</v>
+        <f t="shared" si="137"/>
+        <v>99.784466164736017</v>
       </c>
       <c r="DO67" s="1">
-        <f t="shared" si="141"/>
-        <v>92.326913661841246</v>
+        <f t="shared" si="137"/>
+        <v>98.786621503088654</v>
       </c>
       <c r="DP67" s="1">
-        <f t="shared" si="141"/>
-        <v>91.40364452522283</v>
+        <f t="shared" si="137"/>
+        <v>97.798755288057762</v>
       </c>
       <c r="DQ67" s="1">
-        <f t="shared" si="141"/>
-        <v>90.489608079970608</v>
+        <f t="shared" si="137"/>
+        <v>96.820767735177185</v>
       </c>
       <c r="DR67" s="1">
-        <f t="shared" si="141"/>
-        <v>89.584711999170906</v>
+        <f t="shared" si="137"/>
+        <v>95.852560057825414</v>
       </c>
       <c r="DS67" s="1">
-        <f t="shared" si="141"/>
-        <v>88.688864879179192</v>
+        <f t="shared" si="137"/>
+        <v>94.894034457247159</v>
       </c>
       <c r="DT67" s="1">
-        <f t="shared" si="141"/>
-        <v>87.801976230387396</v>
+        <f t="shared" si="137"/>
+        <v>93.945094112674681</v>
       </c>
       <c r="DU67" s="1">
-        <f t="shared" si="141"/>
-        <v>86.923956468083517</v>
+        <f t="shared" si="137"/>
+        <v>93.005643171547931</v>
       </c>
       <c r="DV67" s="1">
-        <f t="shared" si="141"/>
-        <v>86.054716903402678</v>
+        <f t="shared" si="137"/>
+        <v>92.075586739832445</v>
       </c>
       <c r="DW67" s="1">
-        <f t="shared" si="141"/>
-        <v>85.194169734368657</v>
+        <f t="shared" si="137"/>
+        <v>91.154830872434118</v>
       </c>
       <c r="DX67" s="1">
-        <f t="shared" si="141"/>
-        <v>84.342228037024967</v>
+        <f t="shared" si="137"/>
+        <v>90.243282563709769</v>
       </c>
       <c r="DY67" s="1">
-        <f t="shared" si="141"/>
-        <v>83.498805756654718</v>
+        <f t="shared" si="137"/>
+        <v>89.340849738072677</v>
       </c>
       <c r="DZ67" s="1">
-        <f t="shared" si="141"/>
-        <v>82.66381769908817</v>
+        <f t="shared" si="137"/>
+        <v>88.447441240691944</v>
       </c>
       <c r="EA67" s="1">
-        <f t="shared" si="141"/>
-        <v>81.837179522097287</v>
+        <f t="shared" si="137"/>
+        <v>87.562966828285028</v>
       </c>
       <c r="EB67" s="1">
-        <f t="shared" si="141"/>
-        <v>81.018807726876318</v>
+        <f t="shared" si="137"/>
+        <v>86.687337160002173</v>
       </c>
       <c r="EC67" s="1">
-        <f t="shared" si="141"/>
-        <v>80.208619649607556</v>
+        <f t="shared" si="137"/>
+        <v>85.820463788402151</v>
       </c>
       <c r="ED67" s="1">
-        <f t="shared" si="141"/>
-        <v>79.406533453111479</v>
+        <f t="shared" si="137"/>
+        <v>84.962259150518122</v>
       </c>
       <c r="EE67" s="1">
-        <f t="shared" si="141"/>
-        <v>78.612468118580367</v>
+        <f t="shared" si="137"/>
+        <v>84.112636559012941</v>
       </c>
       <c r="EF67" s="1">
-        <f t="shared" si="141"/>
-        <v>77.826343437394556</v>
+        <f t="shared" si="137"/>
+        <v>83.271510193422813</v>
       </c>
       <c r="EG67" s="1">
-        <f t="shared" si="141"/>
-        <v>77.048080003020615</v>
+        <f t="shared" si="137"/>
+        <v>82.438795091488586</v>
       </c>
       <c r="EH67" s="1">
-        <f t="shared" si="141"/>
-        <v>76.277599202990402</v>
+        <f t="shared" si="137"/>
+        <v>81.614407140573704</v>
       </c>
       <c r="EI67" s="1">
-        <f t="shared" si="141"/>
-        <v>75.5148232109605</v>
+        <f t="shared" si="137"/>
+        <v>80.798263069167959</v>
       </c>
       <c r="EJ67" s="1">
-        <f t="shared" si="141"/>
-        <v>74.759674978850896</v>
+        <f t="shared" si="137"/>
+        <v>79.990280438476276</v>
       </c>
     </row>
     <row r="70" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO70" s="3">
         <f>NPV(AO41,AB67:EJ67)</f>
-        <v>1770.2572423986971</v>
+        <v>1882.1755249623011</v>
       </c>
     </row>
     <row r="71" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO71" s="3">
         <f>AO43</f>
-        <v>126.8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO72" s="3">
         <f>AO70+AO71</f>
-        <v>1897.0572423986971</v>
+        <v>2010.1755249623011</v>
       </c>
     </row>
     <row r="73" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO73" s="2">
         <f>AO72/AL30</f>
-        <v>21.196170306130693</v>
+        <v>22.460061731422357</v>
       </c>
     </row>
     <row r="74" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO74" s="2">
         <f>Main!D3</f>
-        <v>17.59</v>
+        <v>19.350000000000001</v>
       </c>
     </row>
     <row r="75" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO75" s="9">
         <f>AO73/AO74-1</f>
-        <v>0.2050125245099883</v>
+        <v>0.16072670446627169</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/OPRA.xlsx
+++ b/Financial Analysis/OPRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9C8520-9998-4998-A3F2-A177AD33C1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B516FD2E-DF40-4FEA-B6A8-CDA10376FDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
   </bookViews>
@@ -319,7 +319,7 @@
     <t>depends on gross margin</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -846,14 +846,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>19.350000000000001</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="E3" s="5">
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="5">
         <v>45953</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>1731.825</v>
+        <v>1605.63</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -917,7 +917,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>1603.825</v>
+        <v>1477.63</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AO46" s="2">
         <f>Main!D3</f>
-        <v>19.350000000000001</v>
+        <v>17.940000000000001</v>
       </c>
     </row>
     <row r="47" spans="2:41" x14ac:dyDescent="0.3">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AO47" s="9">
         <f>AO45/AO46-1</f>
-        <v>3.7284165261621594E-2</v>
+        <v>0.1188098438022509</v>
       </c>
     </row>
     <row r="48" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7926,13 +7926,13 @@
     <row r="74" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO74" s="2">
         <f>Main!D3</f>
-        <v>19.350000000000001</v>
+        <v>17.940000000000001</v>
       </c>
     </row>
     <row r="75" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO75" s="9">
         <f>AO73/AO74-1</f>
-        <v>0.16072670446627169</v>
+        <v>0.25195438859656383</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/OPRA.xlsx
+++ b/Financial Analysis/OPRA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B516FD2E-DF40-4FEA-B6A8-CDA10376FDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14334821-BB23-40AC-810C-C13806BAF574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
   <si>
     <t>OPRA</t>
   </si>
@@ -316,10 +316,7 @@
     <t>look at competitors, MAU, etc.</t>
   </si>
   <si>
-    <t>depends on gross margin</t>
-  </si>
-  <si>
-    <t>Slightly undervalued</t>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -422,13 +419,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -446,7 +443,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12588240" y="0"/>
+          <a:off x="13807440" y="0"/>
           <a:ext cx="0" cy="13822680"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -846,17 +843,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>17.940000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="E3" s="5">
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="5">
-        <v>45953</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -864,10 +861,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>89.5</v>
+        <f>89.6</f>
+        <v>89.6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -876,7 +874,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>1605.63</v>
+        <v>1205.1199999999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -888,7 +886,7 @@
         <v>128</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -899,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -917,7 +915,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>1477.63</v>
+        <v>1077.1199999999999</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -1107,12 +1105,11 @@
         <v>92.9</v>
       </c>
       <c r="U3" s="11">
-        <f>Q3*1.27</f>
-        <v>97.536000000000001</v>
+        <v>95.9</v>
       </c>
       <c r="V3" s="11">
-        <f>R3*1.07</f>
-        <v>99.831000000000003</v>
+        <f>R3*1.1</f>
+        <v>102.63000000000001</v>
       </c>
       <c r="X3" s="3">
         <f>SUM(C3:F3)</f>
@@ -1132,47 +1129,47 @@
       </c>
       <c r="AB3" s="3">
         <f>SUM(S3:V3)</f>
-        <v>385.86700000000002</v>
+        <v>387.03</v>
       </c>
       <c r="AC3" s="3">
         <f>AB3*1.18</f>
-        <v>455.32306</v>
+        <v>456.69539999999995</v>
       </c>
       <c r="AD3" s="3">
         <f>AC3*1.12</f>
-        <v>509.96182720000007</v>
+        <v>511.49884800000001</v>
       </c>
       <c r="AE3" s="3">
         <f>AD3*1.06</f>
-        <v>540.55953683200005</v>
+        <v>542.18877888000009</v>
       </c>
       <c r="AF3" s="3">
         <f>AE3*1.04</f>
-        <v>562.18191830528008</v>
+        <v>563.87633003520011</v>
       </c>
       <c r="AG3" s="3">
         <f>AF3*1.03</f>
-        <v>579.04737585443854</v>
+        <v>580.79261993625619</v>
       </c>
       <c r="AH3" s="3">
         <f>AG3*1.02</f>
-        <v>590.62832337152736</v>
+        <v>592.4084723349813</v>
       </c>
       <c r="AI3" s="3">
         <f t="shared" ref="AI3:AL4" si="1">AH3*1.02</f>
-        <v>602.4408898389579</v>
+        <v>604.25664178168097</v>
       </c>
       <c r="AJ3" s="3">
         <f t="shared" si="1"/>
-        <v>614.48970763573709</v>
+        <v>616.34177461731463</v>
       </c>
       <c r="AK3" s="3">
         <f t="shared" si="1"/>
-        <v>626.77950178845185</v>
+        <v>628.6686101096609</v>
       </c>
       <c r="AL3" s="3">
         <f t="shared" si="1"/>
-        <v>639.31509182422087</v>
+        <v>641.24198231185414</v>
       </c>
     </row>
     <row r="4" spans="2:38" x14ac:dyDescent="0.3">
@@ -1234,19 +1231,18 @@
         <v>49.6</v>
       </c>
       <c r="U4" s="11">
-        <f t="shared" ref="U4" si="2">Q4*1.07</f>
-        <v>49.540999999999997</v>
+        <v>55.6</v>
       </c>
       <c r="V4" s="11">
-        <f>R4*1.02</f>
-        <v>53.345999999999997</v>
+        <f>R4*1.1</f>
+        <v>57.53</v>
       </c>
       <c r="X4" s="3">
         <f>SUM(C4:F4)</f>
         <v>118.7</v>
       </c>
       <c r="Y4" s="3">
-        <f t="shared" ref="Y4:Y5" si="3">SUM(G4:J4)</f>
+        <f t="shared" ref="Y4:Y5" si="2">SUM(G4:J4)</f>
         <v>140.1</v>
       </c>
       <c r="Z4" s="3">
@@ -1254,52 +1250,52 @@
         <v>162.19999999999999</v>
       </c>
       <c r="AA4" s="3">
-        <f t="shared" ref="AA4:AA5" si="4">SUM(O4:R4)</f>
+        <f t="shared" ref="AA4:AA5" si="3">SUM(O4:R4)</f>
         <v>186.2</v>
       </c>
       <c r="AB4" s="3">
-        <f t="shared" ref="AB4:AB5" si="5">SUM(S4:V4)</f>
-        <v>199.08699999999999</v>
+        <f t="shared" ref="AB4:AB5" si="4">SUM(S4:V4)</f>
+        <v>209.33</v>
       </c>
       <c r="AC4" s="3">
-        <f>AB4*1.05</f>
-        <v>209.04134999999999</v>
+        <f>AB4*1.06</f>
+        <v>221.88980000000004</v>
       </c>
       <c r="AD4" s="3">
         <f>AC4*1.04</f>
-        <v>217.40300400000001</v>
+        <v>230.76539200000005</v>
       </c>
       <c r="AE4" s="3">
         <f>AD4*1.03</f>
-        <v>223.92509412000001</v>
+        <v>237.68835376000007</v>
       </c>
       <c r="AF4" s="3">
         <f>AE4*1.02</f>
-        <v>228.40359600240001</v>
+        <v>242.44212083520009</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" ref="AG4:AH4" si="6">AF4*1.02</f>
-        <v>232.97166792244801</v>
+        <f t="shared" ref="AG4:AH4" si="5">AF4*1.02</f>
+        <v>247.29096325190409</v>
       </c>
       <c r="AH4" s="3">
-        <f t="shared" si="6"/>
-        <v>237.63110128089696</v>
+        <f t="shared" si="5"/>
+        <v>252.23678251694218</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="1"/>
-        <v>242.3837233065149</v>
+        <v>257.28151816728104</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="1"/>
-        <v>247.23139777264521</v>
+        <v>262.42714853062665</v>
       </c>
       <c r="AK4" s="3">
         <f t="shared" si="1"/>
-        <v>252.17602572809813</v>
+        <v>267.67569150123921</v>
       </c>
       <c r="AL4" s="3">
         <f t="shared" si="1"/>
-        <v>257.2195462426601</v>
+        <v>273.029205331264</v>
       </c>
     </row>
     <row r="5" spans="2:38" x14ac:dyDescent="0.3">
@@ -1361,7 +1357,7 @@
         <v>0.5</v>
       </c>
       <c r="U5" s="11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V5" s="11">
         <v>0.5</v>
@@ -1371,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="Y5" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.4000000000000004</v>
       </c>
       <c r="Z5" s="3">
@@ -1379,12 +1375,12 @@
         <v>3.7</v>
       </c>
       <c r="AA5" s="3">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AB5" s="3">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="AB5" s="3">
-        <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" s="3">
         <v>0</v>
@@ -1422,51 +1418,51 @@
         <v>23</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6" si="7">SUM(F3:F5)</f>
+        <f t="shared" ref="F6" si="6">SUM(F3:F5)</f>
         <v>72.7</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" ref="G6" si="8">SUM(G3:G5)</f>
+        <f t="shared" ref="G6" si="7">SUM(G3:G5)</f>
         <v>71.599999999999994</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" ref="H6" si="9">SUM(H3:H5)</f>
+        <f t="shared" ref="H6" si="8">SUM(H3:H5)</f>
         <v>77.800000000000011</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:Q6" si="10">SUM(I3:I5)</f>
+        <f t="shared" ref="I6:Q6" si="9">SUM(I3:I5)</f>
         <v>85.3</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>96.3</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>94.199999999999989</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>102.6</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>113</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>101.8</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>109.69999999999999</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>123.19999999999999</v>
       </c>
       <c r="R6" s="3">
@@ -1474,20 +1470,20 @@
         <v>145.79999999999998</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" ref="S6:V6" si="11">SUM(S3:S5)</f>
+        <f t="shared" ref="S6:V6" si="10">SUM(S3:S5)</f>
         <v>142.69999999999999</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>143</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="11"/>
-        <v>147.577</v>
+        <f t="shared" si="10"/>
+        <v>151.9</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="11"/>
-        <v>153.67699999999999</v>
+        <f t="shared" si="10"/>
+        <v>160.66000000000003</v>
       </c>
       <c r="X6" s="3">
         <v>251</v>
@@ -1505,47 +1501,47 @@
       </c>
       <c r="AB6" s="3">
         <f>SUM(S6:V6)</f>
-        <v>586.95399999999995</v>
+        <v>598.26</v>
       </c>
       <c r="AC6" s="3">
         <f>SUM(AC3:AC5)</f>
-        <v>664.36441000000002</v>
+        <v>678.58519999999999</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" ref="AD6:AL6" si="12">SUM(AD3:AD5)</f>
-        <v>727.36483120000003</v>
+        <f t="shared" ref="AD6:AL6" si="11">SUM(AD3:AD5)</f>
+        <v>742.26424000000009</v>
       </c>
       <c r="AE6" s="3">
-        <f t="shared" si="12"/>
-        <v>764.48463095200009</v>
+        <f t="shared" si="11"/>
+        <v>779.87713264000013</v>
       </c>
       <c r="AF6" s="3">
-        <f t="shared" si="12"/>
-        <v>790.58551430768011</v>
+        <f t="shared" si="11"/>
+        <v>806.31845087040017</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="12"/>
-        <v>812.01904377688652</v>
+        <f t="shared" si="11"/>
+        <v>828.08358318816022</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="12"/>
-        <v>828.25942465242429</v>
+        <f t="shared" si="11"/>
+        <v>844.64525485192348</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="12"/>
-        <v>844.82461314547277</v>
+        <f t="shared" si="11"/>
+        <v>861.53815994896195</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="12"/>
-        <v>861.7211054083823</v>
+        <f t="shared" si="11"/>
+        <v>878.76892314794122</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="12"/>
-        <v>878.95552751654998</v>
+        <f t="shared" si="11"/>
+        <v>896.34430161090017</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="12"/>
-        <v>896.53463806688092</v>
+        <f t="shared" si="11"/>
+        <v>914.27118764311808</v>
       </c>
     </row>
     <row r="7" spans="2:38" x14ac:dyDescent="0.3">
@@ -1589,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V7" s="3">
         <v>0</v>
@@ -1610,7 +1606,7 @@
       </c>
       <c r="AB7" s="3">
         <f>SUM(S7:V7)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1628,60 +1624,60 @@
         <v>25</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" ref="I8:P8" si="13">I6+I7</f>
+        <f t="shared" ref="I8:P8" si="12">I6+I7</f>
         <v>85.399999999999991</v>
       </c>
       <c r="J8" s="8">
+        <f t="shared" si="12"/>
+        <v>96.399999999999991</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="12"/>
+        <v>87.1</v>
+      </c>
+      <c r="L8" s="8">
+        <f t="shared" si="12"/>
+        <v>94.299999999999983</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" si="12"/>
+        <v>102.6</v>
+      </c>
+      <c r="N8" s="8">
+        <f t="shared" si="12"/>
+        <v>113.5</v>
+      </c>
+      <c r="O8" s="8">
+        <f t="shared" si="12"/>
+        <v>102.1</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="12"/>
+        <v>110.99999999999999</v>
+      </c>
+      <c r="Q8" s="8">
+        <f t="shared" ref="Q8:V8" si="13">Q6+Q7</f>
+        <v>123.89999999999999</v>
+      </c>
+      <c r="R8" s="8">
         <f t="shared" si="13"/>
-        <v>96.399999999999991</v>
-      </c>
-      <c r="K8" s="8">
+        <v>145.89999999999998</v>
+      </c>
+      <c r="S8" s="8">
         <f t="shared" si="13"/>
-        <v>87.1</v>
-      </c>
-      <c r="L8" s="8">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="T8" s="8">
         <f t="shared" si="13"/>
-        <v>94.299999999999983</v>
-      </c>
-      <c r="M8" s="8">
+        <v>143</v>
+      </c>
+      <c r="U8" s="8">
         <f t="shared" si="13"/>
-        <v>102.6</v>
-      </c>
-      <c r="N8" s="8">
+        <v>152.1</v>
+      </c>
+      <c r="V8" s="8">
         <f t="shared" si="13"/>
-        <v>113.5</v>
-      </c>
-      <c r="O8" s="8">
-        <f t="shared" si="13"/>
-        <v>102.1</v>
-      </c>
-      <c r="P8" s="8">
-        <f t="shared" si="13"/>
-        <v>110.99999999999999</v>
-      </c>
-      <c r="Q8" s="8">
-        <f t="shared" ref="Q8:V8" si="14">Q6+Q7</f>
-        <v>123.89999999999999</v>
-      </c>
-      <c r="R8" s="8">
-        <f t="shared" si="14"/>
-        <v>145.89999999999998</v>
-      </c>
-      <c r="S8" s="8">
-        <f t="shared" si="14"/>
-        <v>142.69999999999999</v>
-      </c>
-      <c r="T8" s="8">
-        <f t="shared" si="14"/>
-        <v>143</v>
-      </c>
-      <c r="U8" s="8">
-        <f t="shared" si="14"/>
-        <v>147.577</v>
-      </c>
-      <c r="V8" s="8">
-        <f t="shared" si="14"/>
-        <v>153.67699999999999</v>
+        <v>160.66000000000003</v>
       </c>
       <c r="X8" s="8">
         <f>X6+X7</f>
@@ -1701,47 +1697,47 @@
       </c>
       <c r="AB8" s="8">
         <f>AB6+AB7</f>
-        <v>586.95399999999995</v>
+        <v>598.46</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AL8" si="15">AC6+AC7</f>
-        <v>664.36441000000002</v>
+        <f t="shared" ref="AC8:AL8" si="14">AC6+AC7</f>
+        <v>678.58519999999999</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="15"/>
-        <v>727.36483120000003</v>
+        <f t="shared" si="14"/>
+        <v>742.26424000000009</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" si="15"/>
-        <v>764.48463095200009</v>
+        <f t="shared" si="14"/>
+        <v>779.87713264000013</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" si="15"/>
-        <v>790.58551430768011</v>
+        <f t="shared" si="14"/>
+        <v>806.31845087040017</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="15"/>
-        <v>812.01904377688652</v>
+        <f t="shared" si="14"/>
+        <v>828.08358318816022</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="15"/>
-        <v>828.25942465242429</v>
+        <f t="shared" si="14"/>
+        <v>844.64525485192348</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="15"/>
-        <v>844.82461314547277</v>
+        <f t="shared" si="14"/>
+        <v>861.53815994896195</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="15"/>
-        <v>861.7211054083823</v>
+        <f t="shared" si="14"/>
+        <v>878.76892314794122</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" si="15"/>
-        <v>878.95552751654998</v>
+        <f t="shared" si="14"/>
+        <v>896.34430161090017</v>
       </c>
       <c r="AL8" s="8">
-        <f t="shared" si="15"/>
-        <v>896.53463806688092</v>
+        <f t="shared" si="14"/>
+        <v>914.27118764311808</v>
       </c>
     </row>
     <row r="9" spans="2:38" x14ac:dyDescent="0.3">
@@ -1785,12 +1781,11 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" ref="U9" si="16">U8*0.02</f>
-        <v>2.9515400000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" ref="V9" si="17">V8*0.02</f>
-        <v>3.0735399999999999</v>
+        <f t="shared" ref="V9" si="15">V8*0.02</f>
+        <v>3.2132000000000005</v>
       </c>
       <c r="X9" s="3">
         <v>4.5</v>
@@ -1803,12 +1798,12 @@
         <v>3.1</v>
       </c>
       <c r="AA9" s="3">
-        <f t="shared" ref="AA9:AA11" si="18">SUM(O9:R9)</f>
+        <f t="shared" ref="AA9:AA11" si="16">SUM(O9:R9)</f>
         <v>10</v>
       </c>
       <c r="AB9" s="3">
         <f>SUM(S9:V9)</f>
-        <v>10.525079999999999</v>
+        <v>9.9131999999999998</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -1862,12 +1857,11 @@
         <v>1.5</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" ref="U10:V10" si="19">U8*0.01</f>
-        <v>1.47577</v>
+        <v>1.9</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" si="19"/>
-        <v>1.53677</v>
+        <f t="shared" ref="V10" si="17">V8*0.01</f>
+        <v>1.6066000000000003</v>
       </c>
       <c r="X10" s="3">
         <v>3.7</v>
@@ -1880,12 +1874,12 @@
         <v>4.3000000000000007</v>
       </c>
       <c r="AA10" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>3.9</v>
       </c>
       <c r="AB10" s="3">
         <f>SUM(S10:V10)</f>
-        <v>5.4125399999999999</v>
+        <v>5.9066000000000001</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -1939,12 +1933,11 @@
         <v>47.1</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" ref="U11:V11" si="20">U8*0.33</f>
-        <v>48.700410000000005</v>
+        <v>48.5</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" si="20"/>
-        <v>50.713410000000003</v>
+        <f t="shared" ref="V11" si="18">V8*0.33</f>
+        <v>53.017800000000008</v>
       </c>
       <c r="X11" s="3">
         <v>5.5</v>
@@ -1957,12 +1950,12 @@
         <v>85.899999999999991</v>
       </c>
       <c r="AA11" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>118.6</v>
       </c>
       <c r="AB11" s="3">
         <f>SUM(S11:V11)</f>
-        <v>194.01382000000001</v>
+        <v>196.11779999999999</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -1980,60 +1973,60 @@
         <v>29</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" ref="I12:S12" si="21">I9+I10+I11</f>
+        <f t="shared" ref="I12:S12" si="19">I9+I10+I11</f>
         <v>15.700000000000001</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>19</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>16.899999999999999</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>22.599999999999998</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>25.2</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>28.6</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>24.1</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>27.7</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>33</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>47.7</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>50.6</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ref="T12" si="22">T9+T10+T11</f>
+        <f t="shared" ref="T12" si="20">T9+T10+T11</f>
         <v>50.9</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ref="U12" si="23">U9+U10+U11</f>
-        <v>53.127720000000004</v>
+        <f t="shared" ref="U12" si="21">U9+U10+U11</f>
+        <v>52.6</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ref="V12" si="24">V9+V10+V11</f>
-        <v>55.323720000000002</v>
+        <f t="shared" ref="V12" si="22">V9+V10+V11</f>
+        <v>57.837600000000009</v>
       </c>
       <c r="X12" s="3">
         <f>X9+X10+X11</f>
@@ -2053,47 +2046,47 @@
       </c>
       <c r="AB12" s="3">
         <f>AB9+AB10+AB11</f>
-        <v>209.95144000000002</v>
+        <v>211.93759999999997</v>
       </c>
       <c r="AC12" s="3">
-        <f t="shared" ref="AC12:AL12" si="25">AC8-AC13</f>
-        <v>245.81483170000001</v>
+        <f t="shared" ref="AC12:AL12" si="23">AC8-AC13</f>
+        <v>251.07652400000001</v>
       </c>
       <c r="AD12" s="3">
-        <f t="shared" si="25"/>
-        <v>269.12498754400002</v>
+        <f t="shared" si="23"/>
+        <v>274.6377688</v>
       </c>
       <c r="AE12" s="3">
-        <f t="shared" si="25"/>
-        <v>282.85931345224003</v>
+        <f t="shared" si="23"/>
+        <v>288.55453907680004</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="25"/>
-        <v>292.51664029384165</v>
+        <f t="shared" si="23"/>
+        <v>298.33782682204804</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="25"/>
-        <v>300.447046197448</v>
+        <f t="shared" si="23"/>
+        <v>306.39092577961924</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="25"/>
-        <v>306.45598712139702</v>
+        <f t="shared" si="23"/>
+        <v>312.51874429521172</v>
       </c>
       <c r="AI12" s="3">
-        <f t="shared" si="25"/>
-        <v>312.58510686382488</v>
+        <f t="shared" si="23"/>
+        <v>318.76911918111591</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="25"/>
-        <v>318.83680900110141</v>
+        <f t="shared" si="23"/>
+        <v>325.14450156473822</v>
       </c>
       <c r="AK12" s="3">
-        <f t="shared" si="25"/>
-        <v>325.21354518112344</v>
+        <f t="shared" si="23"/>
+        <v>331.64739159603312</v>
       </c>
       <c r="AL12" s="3">
-        <f t="shared" si="25"/>
-        <v>331.71781608474589</v>
+        <f t="shared" si="23"/>
+        <v>338.28033942795366</v>
       </c>
     </row>
     <row r="13" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2101,60 +2094,60 @@
         <v>30</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" ref="I13:S13" si="26">I8-I12</f>
+        <f t="shared" ref="I13:S13" si="24">I8-I12</f>
         <v>69.699999999999989</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>77.399999999999991</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>70.199999999999989</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>71.699999999999989</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>77.399999999999991</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>84.9</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>78</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>83.299999999999983</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>90.899999999999991</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>98.199999999999974</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>92.1</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="27">T8-T12</f>
+        <f t="shared" ref="T13" si="25">T8-T12</f>
         <v>92.1</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13" si="28">U8-U12</f>
-        <v>94.449279999999987</v>
+        <f t="shared" ref="U13" si="26">U8-U12</f>
+        <v>99.5</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="29">V8-V12</f>
-        <v>98.353279999999984</v>
+        <f t="shared" ref="V13" si="27">V8-V12</f>
+        <v>102.82240000000002</v>
       </c>
       <c r="X13" s="8">
         <f>X8-X12</f>
@@ -2174,47 +2167,47 @@
       </c>
       <c r="AB13" s="8">
         <f>AB8-AB12</f>
-        <v>377.0025599999999</v>
+        <v>386.52240000000006</v>
       </c>
       <c r="AC13" s="8">
         <f>AC8*0.63</f>
-        <v>418.54957830000001</v>
+        <v>427.50867599999998</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" ref="AD13:AL13" si="30">AD8*0.63</f>
-        <v>458.23984365600001</v>
+        <f t="shared" ref="AD13:AL13" si="28">AD8*0.63</f>
+        <v>467.62647120000008</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="30"/>
-        <v>481.62531749976006</v>
+        <f t="shared" si="28"/>
+        <v>491.32259356320009</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" si="30"/>
-        <v>498.06887401383847</v>
+        <f t="shared" si="28"/>
+        <v>507.98062404835213</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="30"/>
-        <v>511.57199757943852</v>
+        <f t="shared" si="28"/>
+        <v>521.69265740854098</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="30"/>
-        <v>521.80343753102727</v>
+        <f t="shared" si="28"/>
+        <v>532.12651055671176</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="30"/>
-        <v>532.23950628164789</v>
+        <f t="shared" si="28"/>
+        <v>542.76904076784604</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="30"/>
-        <v>542.88429640728089</v>
+        <f t="shared" si="28"/>
+        <v>553.624421583203</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="30"/>
-        <v>553.74198233542654</v>
+        <f t="shared" si="28"/>
+        <v>564.69691001486706</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="30"/>
-        <v>564.81682198213502</v>
+        <f t="shared" si="28"/>
+        <v>575.99084821516442</v>
       </c>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.3">
@@ -2258,12 +2251,11 @@
         <v>18.7</v>
       </c>
       <c r="U14" s="3">
-        <f>Q14*0.8</f>
-        <v>18.559999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="V14" s="3">
-        <f>R14*1.05</f>
-        <v>18.690000000000001</v>
+        <f>R14*1.25</f>
+        <v>22.25</v>
       </c>
       <c r="X14" s="3">
         <v>74.5</v>
@@ -2280,48 +2272,48 @@
         <v>77.099999999999994</v>
       </c>
       <c r="AB14" s="3">
-        <f t="shared" ref="AB14:AB20" si="31">SUM(S14:V14)</f>
-        <v>73.55</v>
+        <f t="shared" ref="AB14:AB20" si="29">SUM(S14:V14)</f>
+        <v>79.449999999999989</v>
       </c>
       <c r="AC14" s="3">
         <f>AB14*1.08</f>
-        <v>79.433999999999997</v>
+        <v>85.805999999999997</v>
       </c>
       <c r="AD14" s="3">
         <f>AC14*1.05</f>
-        <v>83.405699999999996</v>
+        <v>90.096299999999999</v>
       </c>
       <c r="AE14" s="3">
         <f>AD14*1.04</f>
-        <v>86.741928000000001</v>
+        <v>93.700152000000003</v>
       </c>
       <c r="AF14" s="3">
         <f>AE14*1.03</f>
-        <v>89.344185840000009</v>
+        <v>96.511156560000003</v>
       </c>
       <c r="AG14" s="3">
-        <f>AF14*1.03</f>
-        <v>92.02451141520001</v>
+        <f>AF14*1.02</f>
+        <v>98.441379691200012</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" ref="AH14:AL14" si="32">AG14*1.01</f>
-        <v>92.944756529352006</v>
+        <f t="shared" ref="AH14:AL14" si="30">AG14*1.01</f>
+        <v>99.425793488112006</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="32"/>
-        <v>93.874204094645521</v>
+        <f t="shared" si="30"/>
+        <v>100.42005142299313</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="32"/>
-        <v>94.812946135591972</v>
+        <f t="shared" si="30"/>
+        <v>101.42425193722306</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="32"/>
-        <v>95.76107559694789</v>
+        <f t="shared" si="30"/>
+        <v>102.43849445659529</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="32"/>
-        <v>96.718686352917373</v>
+        <f t="shared" si="30"/>
+        <v>103.46287940116125</v>
       </c>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.3">
@@ -2346,15 +2338,17 @@
       <c r="T15" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="U15" s="3"/>
+      <c r="U15" s="3">
+        <v>9.1</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3">
-        <f t="shared" si="31"/>
-        <v>14.8</v>
+        <f t="shared" si="29"/>
+        <v>23.9</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2408,12 +2402,11 @@
         <v>34</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" ref="U16:V16" si="33">U8*0.24</f>
-        <v>35.418479999999995</v>
+        <v>35.9</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" si="33"/>
-        <v>36.882479999999994</v>
+        <f t="shared" ref="V16" si="31">V8*0.24</f>
+        <v>38.558400000000006</v>
       </c>
       <c r="X16" s="3">
         <v>120.9</v>
@@ -2430,48 +2423,48 @@
         <v>131.9</v>
       </c>
       <c r="AB16" s="3">
-        <f t="shared" si="31"/>
-        <v>140.50095999999999</v>
+        <f t="shared" si="29"/>
+        <v>142.6584</v>
       </c>
       <c r="AC16" s="3">
         <f>AC8*0.23</f>
-        <v>152.8038143</v>
+        <v>156.07459600000001</v>
       </c>
       <c r="AD16" s="3">
         <f>AD8*0.22</f>
-        <v>160.02026286400002</v>
+        <v>163.29813280000002</v>
       </c>
       <c r="AE16" s="3">
-        <f t="shared" ref="AE16:AL16" si="34">AE8*0.22</f>
-        <v>168.18661880944003</v>
+        <f t="shared" ref="AE16:AL16" si="32">AE8*0.22</f>
+        <v>171.57296918080002</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" si="34"/>
-        <v>173.92881314768962</v>
+        <f t="shared" si="32"/>
+        <v>177.39005919148804</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="34"/>
-        <v>178.64418963091504</v>
+        <f t="shared" si="32"/>
+        <v>182.17838830139524</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="34"/>
-        <v>182.21707342353335</v>
+        <f t="shared" si="32"/>
+        <v>185.82195606742317</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="34"/>
-        <v>185.86141489200401</v>
+        <f t="shared" si="32"/>
+        <v>189.53839518877163</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="34"/>
-        <v>189.57864318984412</v>
+        <f t="shared" si="32"/>
+        <v>193.32916309254708</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="34"/>
-        <v>193.370216053641</v>
+        <f t="shared" si="32"/>
+        <v>197.19574635439804</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="34"/>
-        <v>197.2376203747138</v>
+        <f t="shared" si="32"/>
+        <v>201.13966128148599</v>
       </c>
     </row>
     <row r="17" spans="2:144" x14ac:dyDescent="0.3">
@@ -2515,7 +2508,7 @@
         <v>0.2</v>
       </c>
       <c r="U17" s="3">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
@@ -2535,8 +2528,8 @@
         <v>-0.8</v>
       </c>
       <c r="AB17" s="3">
-        <f t="shared" si="31"/>
-        <v>0.4</v>
+        <f t="shared" si="29"/>
+        <v>0.10000000000000003</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
@@ -2610,7 +2603,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="U18" s="3">
-        <v>5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="V18" s="3">
         <v>5</v>
@@ -2630,8 +2623,8 @@
         <v>15.6</v>
       </c>
       <c r="AB18" s="3">
-        <f t="shared" si="31"/>
-        <v>19</v>
+        <f t="shared" si="29"/>
+        <v>18.899999999999999</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2664,15 +2657,17 @@
       <c r="T19" s="3">
         <v>0.6</v>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="3">
+        <v>0.2</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3">
-        <f t="shared" si="31"/>
-        <v>1.2999999999999998</v>
+        <f t="shared" si="29"/>
+        <v>1.4999999999999998</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2730,7 +2725,7 @@
         <v>7.5</v>
       </c>
       <c r="U20" s="3">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="V20" s="3">
         <v>10</v>
@@ -2752,48 +2747,48 @@
         <v>31.799999999999997</v>
       </c>
       <c r="AB20" s="3">
-        <f t="shared" si="31"/>
-        <v>34.299999999999997</v>
+        <f t="shared" si="29"/>
+        <v>31.9</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" ref="AC20:AL20" si="35">AB20*1.01</f>
-        <v>34.643000000000001</v>
+        <f t="shared" ref="AC20:AL20" si="33">AB20*1.01</f>
+        <v>32.219000000000001</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="35"/>
-        <v>34.989429999999999</v>
+        <f t="shared" si="33"/>
+        <v>32.54119</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="35"/>
-        <v>35.339324300000001</v>
+        <f t="shared" si="33"/>
+        <v>32.866601899999999</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="35"/>
-        <v>35.692717543000001</v>
+        <f t="shared" si="33"/>
+        <v>33.195267919000003</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="35"/>
-        <v>36.049644718430002</v>
+        <f t="shared" si="33"/>
+        <v>33.527220598190006</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="35"/>
-        <v>36.410141165614306</v>
+        <f t="shared" si="33"/>
+        <v>33.862492804171907</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="35"/>
-        <v>36.774242577270449</v>
+        <f t="shared" si="33"/>
+        <v>34.201117732213625</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="35"/>
-        <v>37.141985003043153</v>
+        <f t="shared" si="33"/>
+        <v>34.54312890953576</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="35"/>
-        <v>37.513404853073588</v>
+        <f t="shared" si="33"/>
+        <v>34.888560198631119</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="35"/>
-        <v>37.888538901604328</v>
+        <f t="shared" si="33"/>
+        <v>35.237445800617429</v>
       </c>
     </row>
     <row r="21" spans="2:144" x14ac:dyDescent="0.3">
@@ -2801,60 +2796,60 @@
         <v>36</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:P21" si="36">SUM(I14:I20)</f>
+        <f t="shared" ref="I21:P21" si="34">SUM(I14:I20)</f>
         <v>53.499999999999993</v>
       </c>
       <c r="J21" s="3">
+        <f t="shared" si="34"/>
+        <v>65.7</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="34"/>
+        <v>56.4</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="34"/>
+        <v>59.199999999999996</v>
+      </c>
+      <c r="M21" s="3">
+        <f t="shared" si="34"/>
+        <v>61.4</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="34"/>
+        <v>64.5</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="34"/>
+        <v>58.600000000000009</v>
+      </c>
+      <c r="P21" s="3">
+        <f t="shared" si="34"/>
+        <v>61.399999999999991</v>
+      </c>
+      <c r="Q21" s="3">
+        <f t="shared" ref="Q21:R21" si="35">SUM(Q14:Q20)</f>
+        <v>67.5</v>
+      </c>
+      <c r="R21" s="3">
+        <f t="shared" si="35"/>
+        <v>70.7</v>
+      </c>
+      <c r="S21" s="3">
+        <f t="shared" ref="S21:V21" si="36">SUM(S14:S20)</f>
+        <v>70.900000000000006</v>
+      </c>
+      <c r="T21" s="3">
         <f t="shared" si="36"/>
-        <v>65.7</v>
-      </c>
-      <c r="K21" s="3">
+        <v>74.399999999999991</v>
+      </c>
+      <c r="U21" s="3">
         <f t="shared" si="36"/>
-        <v>56.4</v>
-      </c>
-      <c r="L21" s="3">
+        <v>77.300000000000011</v>
+      </c>
+      <c r="V21" s="3">
         <f t="shared" si="36"/>
-        <v>59.199999999999996</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="36"/>
-        <v>61.4</v>
-      </c>
-      <c r="N21" s="3">
-        <f t="shared" si="36"/>
-        <v>64.5</v>
-      </c>
-      <c r="O21" s="3">
-        <f t="shared" si="36"/>
-        <v>58.600000000000009</v>
-      </c>
-      <c r="P21" s="3">
-        <f t="shared" si="36"/>
-        <v>61.399999999999991</v>
-      </c>
-      <c r="Q21" s="3">
-        <f t="shared" ref="Q21:R21" si="37">SUM(Q14:Q20)</f>
-        <v>67.5</v>
-      </c>
-      <c r="R21" s="3">
-        <f t="shared" si="37"/>
-        <v>70.7</v>
-      </c>
-      <c r="S21" s="3">
-        <f t="shared" ref="S21:V21" si="38">SUM(S14:S20)</f>
-        <v>70.900000000000006</v>
-      </c>
-      <c r="T21" s="3">
-        <f t="shared" si="38"/>
-        <v>74.399999999999991</v>
-      </c>
-      <c r="U21" s="3">
-        <f t="shared" si="38"/>
-        <v>67.97847999999999</v>
-      </c>
-      <c r="V21" s="3">
-        <f t="shared" si="38"/>
-        <v>70.572479999999999</v>
+        <v>75.808400000000006</v>
       </c>
       <c r="X21" s="3">
         <f>SUM(X14:X20)</f>
@@ -2874,47 +2869,47 @@
       </c>
       <c r="AB21" s="3">
         <f>SUM(AB14:AB20)</f>
-        <v>283.85095999999999</v>
+        <v>298.40839999999997</v>
       </c>
       <c r="AC21" s="3">
-        <f t="shared" ref="AC21:AL21" si="39">SUM(AC14:AC20)</f>
-        <v>266.8808143</v>
+        <f t="shared" ref="AC21:AL21" si="37">SUM(AC14:AC20)</f>
+        <v>274.09959600000002</v>
       </c>
       <c r="AD21" s="3">
-        <f t="shared" si="39"/>
-        <v>278.41539286400001</v>
+        <f t="shared" si="37"/>
+        <v>285.93562280000003</v>
       </c>
       <c r="AE21" s="3">
-        <f t="shared" si="39"/>
-        <v>290.26787110944002</v>
+        <f t="shared" si="37"/>
+        <v>298.13972308079997</v>
       </c>
       <c r="AF21" s="3">
-        <f t="shared" si="39"/>
-        <v>298.96571653068963</v>
+        <f t="shared" si="37"/>
+        <v>307.09648367048806</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" si="39"/>
-        <v>306.71834576454506</v>
+        <f t="shared" si="37"/>
+        <v>314.14698859078527</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="39"/>
-        <v>311.57197111849962</v>
+        <f t="shared" si="37"/>
+        <v>319.11024235970706</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="39"/>
-        <v>316.50986156391997</v>
+        <f t="shared" si="37"/>
+        <v>324.15956434397839</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="39"/>
-        <v>321.53357432847923</v>
+        <f t="shared" si="37"/>
+        <v>329.29654393930593</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="39"/>
-        <v>326.64469650366249</v>
+        <f t="shared" si="37"/>
+        <v>334.52280100962446</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="39"/>
-        <v>331.84484562923546</v>
+        <f t="shared" si="37"/>
+        <v>339.83998648326468</v>
       </c>
     </row>
     <row r="22" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2922,60 +2917,60 @@
         <v>37</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" ref="I22:P22" si="40">I13-I21</f>
+        <f t="shared" ref="I22:P22" si="38">I13-I21</f>
         <v>16.199999999999996</v>
       </c>
       <c r="J22" s="8">
+        <f t="shared" si="38"/>
+        <v>11.699999999999989</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="38"/>
+        <v>13.79999999999999</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="38"/>
+        <v>12.499999999999993</v>
+      </c>
+      <c r="M22" s="8">
+        <f t="shared" si="38"/>
+        <v>15.999999999999993</v>
+      </c>
+      <c r="N22" s="8">
+        <f t="shared" si="38"/>
+        <v>20.400000000000006</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="38"/>
+        <v>19.399999999999991</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="38"/>
+        <v>21.899999999999991</v>
+      </c>
+      <c r="Q22" s="8">
+        <f t="shared" ref="Q22:R22" si="39">Q13-Q21</f>
+        <v>23.399999999999991</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" si="39"/>
+        <v>27.499999999999972</v>
+      </c>
+      <c r="S22" s="8">
+        <f t="shared" ref="S22:V22" si="40">S13-S21</f>
+        <v>21.199999999999989</v>
+      </c>
+      <c r="T22" s="8">
         <f t="shared" si="40"/>
-        <v>11.699999999999989</v>
-      </c>
-      <c r="K22" s="8">
+        <v>17.700000000000003</v>
+      </c>
+      <c r="U22" s="8">
         <f t="shared" si="40"/>
-        <v>13.79999999999999</v>
-      </c>
-      <c r="L22" s="8">
+        <v>22.199999999999989</v>
+      </c>
+      <c r="V22" s="8">
         <f t="shared" si="40"/>
-        <v>12.499999999999993</v>
-      </c>
-      <c r="M22" s="8">
-        <f t="shared" si="40"/>
-        <v>15.999999999999993</v>
-      </c>
-      <c r="N22" s="8">
-        <f t="shared" si="40"/>
-        <v>20.400000000000006</v>
-      </c>
-      <c r="O22" s="8">
-        <f t="shared" si="40"/>
-        <v>19.399999999999991</v>
-      </c>
-      <c r="P22" s="8">
-        <f t="shared" si="40"/>
-        <v>21.899999999999991</v>
-      </c>
-      <c r="Q22" s="8">
-        <f t="shared" ref="Q22:R22" si="41">Q13-Q21</f>
-        <v>23.399999999999991</v>
-      </c>
-      <c r="R22" s="8">
-        <f t="shared" si="41"/>
-        <v>27.499999999999972</v>
-      </c>
-      <c r="S22" s="8">
-        <f t="shared" ref="S22:V22" si="42">S13-S21</f>
-        <v>21.199999999999989</v>
-      </c>
-      <c r="T22" s="8">
-        <f t="shared" si="42"/>
-        <v>17.700000000000003</v>
-      </c>
-      <c r="U22" s="8">
-        <f t="shared" si="42"/>
-        <v>26.470799999999997</v>
-      </c>
-      <c r="V22" s="8">
-        <f t="shared" si="42"/>
-        <v>27.780799999999985</v>
+        <v>27.01400000000001</v>
       </c>
       <c r="X22" s="8">
         <f>X13-X21</f>
@@ -2995,47 +2990,47 @@
       </c>
       <c r="AB22" s="8">
         <f>AB13-AB21</f>
-        <v>93.151599999999917</v>
+        <v>88.11400000000009</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AL22" si="43">AC13-AC21</f>
-        <v>151.66876400000001</v>
+        <f t="shared" ref="AC22:AL22" si="41">AC13-AC21</f>
+        <v>153.40907999999996</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="43"/>
-        <v>179.82445079199999</v>
+        <f t="shared" si="41"/>
+        <v>181.69084840000005</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="43"/>
-        <v>191.35744639032004</v>
+        <f t="shared" si="41"/>
+        <v>193.18287048240012</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="43"/>
-        <v>199.10315748314883</v>
+        <f t="shared" si="41"/>
+        <v>200.88414037786407</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="43"/>
-        <v>204.85365181489345</v>
+        <f t="shared" si="41"/>
+        <v>207.54566881775571</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="43"/>
-        <v>210.23146641252765</v>
+        <f t="shared" si="41"/>
+        <v>213.01626819700471</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="43"/>
-        <v>215.72964471772792</v>
+        <f t="shared" si="41"/>
+        <v>218.60947642386765</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="43"/>
-        <v>221.35072207880165</v>
+        <f t="shared" si="41"/>
+        <v>224.32787764389707</v>
       </c>
       <c r="AK22" s="8">
-        <f t="shared" si="43"/>
-        <v>227.09728583176405</v>
+        <f t="shared" si="41"/>
+        <v>230.1741090052426</v>
       </c>
       <c r="AL22" s="8">
-        <f t="shared" si="43"/>
-        <v>232.97197635289956</v>
+        <f t="shared" si="41"/>
+        <v>236.15086173189974</v>
       </c>
     </row>
     <row r="23" spans="2:144" x14ac:dyDescent="0.3">
@@ -3082,10 +3077,10 @@
         <v>-0.9</v>
       </c>
       <c r="U23" s="3">
-        <v>-2</v>
+        <v>-0.8</v>
       </c>
       <c r="V23" s="3">
-        <v>-2</v>
+        <v>-0.9</v>
       </c>
       <c r="X23" s="3">
         <f>29.4+115.4-116.6-0.1</f>
@@ -3105,47 +3100,47 @@
       </c>
       <c r="AB23" s="3">
         <f>SUM(S23:V23)</f>
-        <v>-5.6</v>
+        <v>-3.3000000000000003</v>
       </c>
       <c r="AC23" s="3">
         <f>AB23*1.01</f>
-        <v>-5.6559999999999997</v>
+        <v>-3.3330000000000002</v>
       </c>
       <c r="AD23" s="3">
-        <f t="shared" ref="AD23:AL23" si="44">AC23*1.01</f>
-        <v>-5.7125599999999999</v>
+        <f t="shared" ref="AD23:AL23" si="42">AC23*1.01</f>
+        <v>-3.36633</v>
       </c>
       <c r="AE23" s="3">
-        <f t="shared" si="44"/>
-        <v>-5.7696855999999999</v>
+        <f t="shared" si="42"/>
+        <v>-3.3999933000000002</v>
       </c>
       <c r="AF23" s="3">
-        <f t="shared" si="44"/>
-        <v>-5.8273824559999996</v>
+        <f t="shared" si="42"/>
+        <v>-3.4339932330000003</v>
       </c>
       <c r="AG23" s="3">
-        <f t="shared" si="44"/>
-        <v>-5.8856562805599992</v>
+        <f t="shared" si="42"/>
+        <v>-3.4683331653300002</v>
       </c>
       <c r="AH23" s="3">
-        <f t="shared" si="44"/>
-        <v>-5.9445128433655992</v>
+        <f t="shared" si="42"/>
+        <v>-3.5030164969833004</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" si="44"/>
-        <v>-6.0039579717992551</v>
+        <f t="shared" si="42"/>
+        <v>-3.5380466619531337</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="44"/>
-        <v>-6.0639975515172475</v>
+        <f t="shared" si="42"/>
+        <v>-3.5734271285726651</v>
       </c>
       <c r="AK23" s="3">
-        <f t="shared" si="44"/>
-        <v>-6.1246375270324203</v>
+        <f t="shared" si="42"/>
+        <v>-3.6091613998583916</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="44"/>
-        <v>-6.1858839023027441</v>
+        <f t="shared" si="42"/>
+        <v>-3.6452530138569754</v>
       </c>
     </row>
     <row r="24" spans="2:144" x14ac:dyDescent="0.3">
@@ -3189,10 +3184,10 @@
         <v>0.2</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X24" s="3">
         <v>6.9</v>
@@ -3210,7 +3205,7 @@
       </c>
       <c r="AB24" s="3">
         <f>SUM(S24:V24)</f>
-        <v>0.30000000000000004</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -3284,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="U25" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V25" s="3">
         <v>1</v>
@@ -3305,47 +3300,47 @@
       </c>
       <c r="AB25" s="3">
         <f>SUM(S25:V25)</f>
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AC25" s="3">
         <f>AB25*1.01</f>
-        <v>3.8379999999999996</v>
+        <v>3.3329999999999997</v>
       </c>
       <c r="AD25" s="3">
-        <f t="shared" ref="AD25:AL25" si="45">AC25*1.01</f>
-        <v>3.8763799999999997</v>
+        <f t="shared" ref="AD25:AL25" si="43">AC25*1.01</f>
+        <v>3.3663299999999996</v>
       </c>
       <c r="AE25" s="3">
-        <f t="shared" si="45"/>
-        <v>3.9151437999999996</v>
+        <f t="shared" si="43"/>
+        <v>3.3999932999999998</v>
       </c>
       <c r="AF25" s="3">
-        <f t="shared" si="45"/>
-        <v>3.9542952379999998</v>
+        <f t="shared" si="43"/>
+        <v>3.4339932329999998</v>
       </c>
       <c r="AG25" s="3">
-        <f t="shared" si="45"/>
-        <v>3.99383819038</v>
+        <f t="shared" si="43"/>
+        <v>3.4683331653299998</v>
       </c>
       <c r="AH25" s="3">
-        <f t="shared" si="45"/>
-        <v>4.0337765722838004</v>
+        <f t="shared" si="43"/>
+        <v>3.5030164969833</v>
       </c>
       <c r="AI25" s="3">
-        <f t="shared" si="45"/>
-        <v>4.0741143380066385</v>
+        <f t="shared" si="43"/>
+        <v>3.5380466619531332</v>
       </c>
       <c r="AJ25" s="3">
-        <f t="shared" si="45"/>
-        <v>4.1148554813867051</v>
+        <f t="shared" si="43"/>
+        <v>3.5734271285726646</v>
       </c>
       <c r="AK25" s="3">
-        <f t="shared" si="45"/>
-        <v>4.1560040362005726</v>
+        <f t="shared" si="43"/>
+        <v>3.6091613998583911</v>
       </c>
       <c r="AL25" s="3">
-        <f t="shared" si="45"/>
-        <v>4.1975640765625784</v>
+        <f t="shared" si="43"/>
+        <v>3.645253013856975</v>
       </c>
     </row>
     <row r="26" spans="2:144" x14ac:dyDescent="0.3">
@@ -3353,60 +3348,60 @@
         <v>41</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" ref="I26:P26" si="46">SUM(I23:I25)</f>
+        <f t="shared" ref="I26:P26" si="44">SUM(I23:I25)</f>
         <v>1.6</v>
       </c>
       <c r="J26" s="3">
+        <f t="shared" si="44"/>
+        <v>-8.4</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" si="44"/>
+        <v>-4.8</v>
+      </c>
+      <c r="L26" s="3">
+        <f t="shared" si="44"/>
+        <v>-2.1999999999999997</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="44"/>
+        <v>-0.99999999999999989</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="44"/>
+        <v>-89.100000000000009</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" si="44"/>
+        <v>-9.9999999999999978E-2</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" ref="Q26:R26" si="45">SUM(Q23:Q25)</f>
+        <v>0.4</v>
+      </c>
+      <c r="R26" s="3">
+        <f t="shared" si="45"/>
+        <v>-6.3999999999999995</v>
+      </c>
+      <c r="S26" s="3">
+        <f t="shared" ref="S26:V26" si="46">SUM(S23:S25)</f>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="T26" s="3">
         <f t="shared" si="46"/>
-        <v>-8.4</v>
-      </c>
-      <c r="K26" s="3">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="U26" s="3">
         <f t="shared" si="46"/>
-        <v>-4.8</v>
-      </c>
-      <c r="L26" s="3">
+        <v>-0.20000000000000007</v>
+      </c>
+      <c r="V26" s="3">
         <f t="shared" si="46"/>
-        <v>-2.1999999999999997</v>
-      </c>
-      <c r="M26" s="3">
-        <f t="shared" si="46"/>
-        <v>-0.99999999999999989</v>
-      </c>
-      <c r="N26" s="3">
-        <f t="shared" si="46"/>
-        <v>-89.100000000000009</v>
-      </c>
-      <c r="O26" s="3">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <f t="shared" si="46"/>
-        <v>-9.9999999999999978E-2</v>
-      </c>
-      <c r="Q26" s="3">
-        <f t="shared" ref="Q26:R26" si="47">SUM(Q23:Q25)</f>
-        <v>0.4</v>
-      </c>
-      <c r="R26" s="3">
-        <f t="shared" si="47"/>
-        <v>-6.3999999999999995</v>
-      </c>
-      <c r="S26" s="3">
-        <f t="shared" ref="S26:V26" si="48">SUM(S23:S25)</f>
-        <v>0.20000000000000007</v>
-      </c>
-      <c r="T26" s="3">
-        <f t="shared" si="48"/>
         <v>0.30000000000000004</v>
-      </c>
-      <c r="U26" s="3">
-        <f t="shared" si="48"/>
-        <v>-1</v>
-      </c>
-      <c r="V26" s="3">
-        <f t="shared" si="48"/>
-        <v>-1</v>
       </c>
       <c r="X26" s="3">
         <f>SUM(X23:X25)</f>
@@ -3426,47 +3421,47 @@
       </c>
       <c r="AB26" s="3">
         <f>SUM(AB23:AB25)</f>
-        <v>-1.5</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="AC26" s="3">
-        <f t="shared" ref="AC26:AL26" si="49">SUM(AC23:AC25)</f>
-        <v>-1.8180000000000001</v>
+        <f t="shared" ref="AC26:AL26" si="47">SUM(AC23:AC25)</f>
+        <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.8361800000000001</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.8545418000000002</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AF26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.8730872179999998</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.8918180901799992</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.9107362710817988</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AI26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.9298436337926166</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.9491420701305424</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AK26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.9686334908318477</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
       <c r="AL26" s="3">
-        <f t="shared" si="49"/>
-        <v>-1.9883198257401657</v>
+        <f t="shared" si="47"/>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3474,60 +3469,60 @@
         <v>45</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:P27" si="50">I22-I26</f>
+        <f t="shared" ref="I27:P27" si="48">I22-I26</f>
         <v>14.599999999999996</v>
       </c>
       <c r="J27" s="8">
+        <f t="shared" si="48"/>
+        <v>20.099999999999987</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="48"/>
+        <v>18.599999999999991</v>
+      </c>
+      <c r="L27" s="8">
+        <f t="shared" si="48"/>
+        <v>14.699999999999992</v>
+      </c>
+      <c r="M27" s="8">
+        <f t="shared" si="48"/>
+        <v>16.999999999999993</v>
+      </c>
+      <c r="N27" s="8">
+        <f t="shared" si="48"/>
+        <v>109.50000000000001</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="48"/>
+        <v>19.399999999999991</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="48"/>
+        <v>21.999999999999993</v>
+      </c>
+      <c r="Q27" s="8">
+        <f t="shared" ref="Q27:R27" si="49">Q22-Q26</f>
+        <v>22.999999999999993</v>
+      </c>
+      <c r="R27" s="8">
+        <f t="shared" si="49"/>
+        <v>33.89999999999997</v>
+      </c>
+      <c r="S27" s="8">
+        <f t="shared" ref="S27:V27" si="50">S22-S26</f>
+        <v>20.999999999999989</v>
+      </c>
+      <c r="T27" s="8">
         <f t="shared" si="50"/>
-        <v>20.099999999999987</v>
-      </c>
-      <c r="K27" s="8">
+        <v>17.400000000000002</v>
+      </c>
+      <c r="U27" s="8">
         <f t="shared" si="50"/>
-        <v>18.599999999999991</v>
-      </c>
-      <c r="L27" s="8">
+        <v>22.399999999999988</v>
+      </c>
+      <c r="V27" s="8">
         <f t="shared" si="50"/>
-        <v>14.699999999999992</v>
-      </c>
-      <c r="M27" s="8">
-        <f t="shared" si="50"/>
-        <v>16.999999999999993</v>
-      </c>
-      <c r="N27" s="8">
-        <f t="shared" si="50"/>
-        <v>109.50000000000001</v>
-      </c>
-      <c r="O27" s="8">
-        <f t="shared" si="50"/>
-        <v>19.399999999999991</v>
-      </c>
-      <c r="P27" s="8">
-        <f t="shared" si="50"/>
-        <v>21.999999999999993</v>
-      </c>
-      <c r="Q27" s="8">
-        <f t="shared" ref="Q27:R27" si="51">Q22-Q26</f>
-        <v>22.999999999999993</v>
-      </c>
-      <c r="R27" s="8">
-        <f t="shared" si="51"/>
-        <v>33.89999999999997</v>
-      </c>
-      <c r="S27" s="8">
-        <f t="shared" ref="S27:V27" si="52">S22-S26</f>
-        <v>20.999999999999989</v>
-      </c>
-      <c r="T27" s="8">
-        <f t="shared" si="52"/>
-        <v>17.400000000000002</v>
-      </c>
-      <c r="U27" s="8">
-        <f t="shared" si="52"/>
-        <v>27.470799999999997</v>
-      </c>
-      <c r="V27" s="8">
-        <f t="shared" si="52"/>
-        <v>28.780799999999985</v>
+        <v>26.714000000000009</v>
       </c>
       <c r="X27" s="8">
         <f>X22-X26</f>
@@ -3547,47 +3542,47 @@
       </c>
       <c r="AB27" s="8">
         <f>AB22-AB26</f>
-        <v>94.651599999999917</v>
+        <v>87.514000000000095</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AL27" si="53">AC22-AC26</f>
-        <v>153.48676400000002</v>
+        <f t="shared" ref="AC27:AL27" si="51">AC22-AC26</f>
+        <v>153.40907999999996</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="53"/>
-        <v>181.66063079200001</v>
+        <f t="shared" si="51"/>
+        <v>181.69084840000005</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="53"/>
-        <v>193.21198819032003</v>
+        <f t="shared" si="51"/>
+        <v>193.18287048240012</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="53"/>
-        <v>200.97624470114883</v>
+        <f t="shared" si="51"/>
+        <v>200.88414037786407</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="53"/>
-        <v>206.74546990507346</v>
+        <f t="shared" si="51"/>
+        <v>207.54566881775571</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="53"/>
-        <v>212.14220268360944</v>
+        <f t="shared" si="51"/>
+        <v>213.01626819700471</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="53"/>
-        <v>217.65948835152054</v>
+        <f t="shared" si="51"/>
+        <v>218.60947642386765</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="53"/>
-        <v>223.29986414893219</v>
+        <f t="shared" si="51"/>
+        <v>224.32787764389707</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="53"/>
-        <v>229.0659193225959</v>
+        <f t="shared" si="51"/>
+        <v>230.1741090052426</v>
       </c>
       <c r="AL27" s="8">
-        <f t="shared" si="53"/>
-        <v>234.96029617863974</v>
+        <f t="shared" si="51"/>
+        <v>236.15086173189974</v>
       </c>
     </row>
     <row r="28" spans="2:144" x14ac:dyDescent="0.3">
@@ -3631,12 +3626,11 @@
         <v>2.1</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" ref="U28:V28" si="54">U27*0.15</f>
-        <v>4.1206199999999997</v>
+        <v>4</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" si="54"/>
-        <v>4.3171199999999974</v>
+        <f t="shared" ref="V28" si="52">V27*0.15</f>
+        <v>4.0071000000000012</v>
       </c>
       <c r="X28" s="3">
         <v>0</v>
@@ -3654,47 +3648,47 @@
       </c>
       <c r="AB28" s="3">
         <f>SUM(S28:V28)</f>
-        <v>13.037739999999998</v>
+        <v>12.607100000000001</v>
       </c>
       <c r="AC28" s="3">
-        <f>AC27*0.14</f>
-        <v>21.488146960000005</v>
+        <f>AC27*0.15</f>
+        <v>23.011361999999995</v>
       </c>
       <c r="AD28" s="3">
-        <f t="shared" ref="AD28:AL28" si="55">AD27*0.14</f>
-        <v>25.432488310880004</v>
+        <f t="shared" ref="AD28:AL28" si="53">AD27*0.15</f>
+        <v>27.253627260000005</v>
       </c>
       <c r="AE28" s="3">
-        <f t="shared" si="55"/>
-        <v>27.049678346644807</v>
+        <f t="shared" si="53"/>
+        <v>28.977430572360017</v>
       </c>
       <c r="AF28" s="3">
-        <f t="shared" si="55"/>
-        <v>28.136674258160838</v>
+        <f t="shared" si="53"/>
+        <v>30.132621056679611</v>
       </c>
       <c r="AG28" s="3">
-        <f t="shared" si="55"/>
-        <v>28.944365786710289</v>
+        <f t="shared" si="53"/>
+        <v>31.131850322663354</v>
       </c>
       <c r="AH28" s="3">
-        <f t="shared" si="55"/>
-        <v>29.699908375705323</v>
+        <f t="shared" si="53"/>
+        <v>31.952440229550703</v>
       </c>
       <c r="AI28" s="3">
-        <f t="shared" si="55"/>
-        <v>30.472328369212878</v>
+        <f t="shared" si="53"/>
+        <v>32.791421463580143</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="55"/>
-        <v>31.26198098085051</v>
+        <f t="shared" si="53"/>
+        <v>33.649181646584559</v>
       </c>
       <c r="AK28" s="3">
-        <f t="shared" si="55"/>
-        <v>32.069228705163432</v>
+        <f t="shared" si="53"/>
+        <v>34.526116350786388</v>
       </c>
       <c r="AL28" s="3">
-        <f t="shared" si="55"/>
-        <v>32.894441465009564</v>
+        <f t="shared" si="53"/>
+        <v>35.422629259784962</v>
       </c>
     </row>
     <row r="29" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3702,60 +3696,60 @@
         <v>43</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" ref="I29:P29" si="56">I27-I28</f>
+        <f t="shared" ref="I29:P29" si="54">I27-I28</f>
         <v>9.399999999999995</v>
       </c>
       <c r="J29" s="8">
+        <f t="shared" si="54"/>
+        <v>20.799999999999986</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="54"/>
+        <v>15.29999999999999</v>
+      </c>
+      <c r="L29" s="8">
+        <f t="shared" si="54"/>
+        <v>13.599999999999993</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="54"/>
+        <v>16.799999999999994</v>
+      </c>
+      <c r="N29" s="8">
+        <f t="shared" si="54"/>
+        <v>107.40000000000002</v>
+      </c>
+      <c r="O29" s="8">
+        <f t="shared" si="54"/>
+        <v>14.799999999999992</v>
+      </c>
+      <c r="P29" s="8">
+        <f t="shared" si="54"/>
+        <v>19.199999999999992</v>
+      </c>
+      <c r="Q29" s="8">
+        <f t="shared" ref="Q29:R29" si="55">Q27-Q28</f>
+        <v>18.199999999999992</v>
+      </c>
+      <c r="R29" s="8">
+        <f t="shared" si="55"/>
+        <v>28.599999999999969</v>
+      </c>
+      <c r="S29" s="8">
+        <f t="shared" ref="S29:V29" si="56">S27-S28</f>
+        <v>18.499999999999989</v>
+      </c>
+      <c r="T29" s="8">
         <f t="shared" si="56"/>
-        <v>20.799999999999986</v>
-      </c>
-      <c r="K29" s="8">
+        <v>15.300000000000002</v>
+      </c>
+      <c r="U29" s="8">
         <f t="shared" si="56"/>
-        <v>15.29999999999999</v>
-      </c>
-      <c r="L29" s="8">
+        <v>18.399999999999988</v>
+      </c>
+      <c r="V29" s="8">
         <f t="shared" si="56"/>
-        <v>13.599999999999993</v>
-      </c>
-      <c r="M29" s="8">
-        <f t="shared" si="56"/>
-        <v>16.799999999999994</v>
-      </c>
-      <c r="N29" s="8">
-        <f t="shared" si="56"/>
-        <v>107.40000000000002</v>
-      </c>
-      <c r="O29" s="8">
-        <f t="shared" si="56"/>
-        <v>14.799999999999992</v>
-      </c>
-      <c r="P29" s="8">
-        <f t="shared" si="56"/>
-        <v>19.199999999999992</v>
-      </c>
-      <c r="Q29" s="8">
-        <f t="shared" ref="Q29:R29" si="57">Q27-Q28</f>
-        <v>18.199999999999992</v>
-      </c>
-      <c r="R29" s="8">
-        <f t="shared" si="57"/>
-        <v>28.599999999999969</v>
-      </c>
-      <c r="S29" s="8">
-        <f t="shared" ref="S29:V29" si="58">S27-S28</f>
-        <v>18.499999999999989</v>
-      </c>
-      <c r="T29" s="8">
-        <f t="shared" si="58"/>
-        <v>15.300000000000002</v>
-      </c>
-      <c r="U29" s="8">
-        <f t="shared" si="58"/>
-        <v>23.350179999999998</v>
-      </c>
-      <c r="V29" s="8">
-        <f t="shared" si="58"/>
-        <v>24.463679999999989</v>
+        <v>22.706900000000008</v>
       </c>
       <c r="X29" s="8">
         <f>X27-X28</f>
@@ -3775,471 +3769,471 @@
       </c>
       <c r="AB29" s="8">
         <f>AB27-AB28</f>
-        <v>81.613859999999917</v>
+        <v>74.906900000000093</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" ref="AC29:AL29" si="59">AC27-AC28</f>
-        <v>131.99861704000003</v>
+        <f t="shared" ref="AC29:AL29" si="57">AC27-AC28</f>
+        <v>130.39771799999997</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="59"/>
-        <v>156.22814248112002</v>
+        <f t="shared" si="57"/>
+        <v>154.43722114000005</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="59"/>
-        <v>166.16230984367522</v>
+        <f t="shared" si="57"/>
+        <v>164.2054399100401</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="59"/>
-        <v>172.83957044298799</v>
+        <f t="shared" si="57"/>
+        <v>170.75151932118445</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="59"/>
-        <v>177.80110411836318</v>
+        <f t="shared" si="57"/>
+        <v>176.41381849509236</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="59"/>
-        <v>182.44229430790412</v>
+        <f t="shared" si="57"/>
+        <v>181.06382796745402</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="59"/>
-        <v>187.18715998230766</v>
+        <f t="shared" si="57"/>
+        <v>185.8180549602875</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="59"/>
-        <v>192.03788316808169</v>
+        <f t="shared" si="57"/>
+        <v>190.6786959973125</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="59"/>
-        <v>196.99669061743248</v>
+        <f t="shared" si="57"/>
+        <v>195.6479926544562</v>
       </c>
       <c r="AL29" s="8">
-        <f t="shared" si="59"/>
-        <v>202.06585471363019</v>
+        <f t="shared" si="57"/>
+        <v>200.72823247211477</v>
       </c>
       <c r="AM29" s="1">
         <f>AL29*(1+$AO$40)</f>
-        <v>200.04519616649389</v>
+        <v>198.72095014739361</v>
       </c>
       <c r="AN29" s="1">
-        <f t="shared" ref="AN29:CY29" si="60">AM29*(1+$AO$40)</f>
-        <v>198.04474420482896</v>
+        <f t="shared" ref="AN29:CY29" si="58">AM29*(1+$AO$40)</f>
+        <v>196.73374064591968</v>
       </c>
       <c r="AO29" s="1">
-        <f t="shared" si="60"/>
-        <v>196.06429676278066</v>
+        <f t="shared" si="58"/>
+        <v>194.76640323946049</v>
       </c>
       <c r="AP29" s="1">
-        <f t="shared" si="60"/>
-        <v>194.10365379515284</v>
+        <f t="shared" si="58"/>
+        <v>192.81873920706587</v>
       </c>
       <c r="AQ29" s="1">
-        <f t="shared" si="60"/>
-        <v>192.1626172572013</v>
+        <f t="shared" si="58"/>
+        <v>190.89055181499521</v>
       </c>
       <c r="AR29" s="1">
-        <f t="shared" si="60"/>
-        <v>190.24099108462929</v>
+        <f t="shared" si="58"/>
+        <v>188.98164629684524</v>
       </c>
       <c r="AS29" s="1">
-        <f t="shared" si="60"/>
-        <v>188.33858117378298</v>
+        <f t="shared" si="58"/>
+        <v>187.0918298338768</v>
       </c>
       <c r="AT29" s="1">
-        <f t="shared" si="60"/>
-        <v>186.45519536204515</v>
+        <f t="shared" si="58"/>
+        <v>185.22091153553802</v>
       </c>
       <c r="AU29" s="1">
-        <f t="shared" si="60"/>
-        <v>184.59064340842468</v>
+        <f t="shared" si="58"/>
+        <v>183.36870242018264</v>
       </c>
       <c r="AV29" s="1">
-        <f t="shared" si="60"/>
-        <v>182.74473697434044</v>
+        <f t="shared" si="58"/>
+        <v>181.53501539598082</v>
       </c>
       <c r="AW29" s="1">
-        <f t="shared" si="60"/>
-        <v>180.91728960459704</v>
+        <f t="shared" si="58"/>
+        <v>179.71966524202102</v>
       </c>
       <c r="AX29" s="1">
-        <f t="shared" si="60"/>
-        <v>179.10811670855108</v>
+        <f t="shared" si="58"/>
+        <v>177.92246858960081</v>
       </c>
       <c r="AY29" s="1">
-        <f t="shared" si="60"/>
-        <v>177.31703554146557</v>
+        <f t="shared" si="58"/>
+        <v>176.14324390370481</v>
       </c>
       <c r="AZ29" s="1">
-        <f t="shared" si="60"/>
-        <v>175.54386518605091</v>
+        <f t="shared" si="58"/>
+        <v>174.38181146466778</v>
       </c>
       <c r="BA29" s="1">
-        <f t="shared" si="60"/>
-        <v>173.78842653419039</v>
+        <f t="shared" si="58"/>
+        <v>172.63799335002111</v>
       </c>
       <c r="BB29" s="1">
-        <f t="shared" si="60"/>
-        <v>172.05054226884849</v>
+        <f t="shared" si="58"/>
+        <v>170.91161341652088</v>
       </c>
       <c r="BC29" s="1">
-        <f t="shared" si="60"/>
-        <v>170.33003684616</v>
+        <f t="shared" si="58"/>
+        <v>169.20249728235567</v>
       </c>
       <c r="BD29" s="1">
-        <f t="shared" si="60"/>
-        <v>168.62673647769839</v>
+        <f t="shared" si="58"/>
+        <v>167.5104723095321</v>
       </c>
       <c r="BE29" s="1">
-        <f t="shared" si="60"/>
-        <v>166.94046911292139</v>
+        <f t="shared" si="58"/>
+        <v>165.83536758643677</v>
       </c>
       <c r="BF29" s="1">
-        <f t="shared" si="60"/>
-        <v>165.27106442179218</v>
+        <f t="shared" si="58"/>
+        <v>164.17701391057241</v>
       </c>
       <c r="BG29" s="1">
-        <f t="shared" si="60"/>
-        <v>163.61835377757424</v>
+        <f t="shared" si="58"/>
+        <v>162.5352437714667</v>
       </c>
       <c r="BH29" s="1">
-        <f t="shared" si="60"/>
-        <v>161.98217023979851</v>
+        <f t="shared" si="58"/>
+        <v>160.90989133375203</v>
       </c>
       <c r="BI29" s="1">
-        <f t="shared" si="60"/>
-        <v>160.36234853740052</v>
+        <f t="shared" si="58"/>
+        <v>159.3007924204145</v>
       </c>
       <c r="BJ29" s="1">
-        <f t="shared" si="60"/>
-        <v>158.75872505202651</v>
+        <f t="shared" si="58"/>
+        <v>157.70778449621034</v>
       </c>
       <c r="BK29" s="1">
-        <f t="shared" si="60"/>
-        <v>157.17113780150623</v>
+        <f t="shared" si="58"/>
+        <v>156.13070665124823</v>
       </c>
       <c r="BL29" s="1">
-        <f t="shared" si="60"/>
-        <v>155.59942642349117</v>
+        <f t="shared" si="58"/>
+        <v>154.56939958473575</v>
       </c>
       <c r="BM29" s="1">
-        <f t="shared" si="60"/>
-        <v>154.04343215925624</v>
+        <f t="shared" si="58"/>
+        <v>153.02370558888839</v>
       </c>
       <c r="BN29" s="1">
-        <f t="shared" si="60"/>
-        <v>152.50299783766368</v>
+        <f t="shared" si="58"/>
+        <v>151.49346853299951</v>
       </c>
       <c r="BO29" s="1">
-        <f t="shared" si="60"/>
-        <v>150.97796785928705</v>
+        <f t="shared" si="58"/>
+        <v>149.97853384766952</v>
       </c>
       <c r="BP29" s="1">
-        <f t="shared" si="60"/>
-        <v>149.46818818069417</v>
+        <f t="shared" si="58"/>
+        <v>148.47874850919283</v>
       </c>
       <c r="BQ29" s="1">
-        <f t="shared" si="60"/>
-        <v>147.97350629888723</v>
+        <f t="shared" si="58"/>
+        <v>146.99396102410088</v>
       </c>
       <c r="BR29" s="1">
-        <f t="shared" si="60"/>
-        <v>146.49377123589835</v>
+        <f t="shared" si="58"/>
+        <v>145.52402141385988</v>
       </c>
       <c r="BS29" s="1">
-        <f t="shared" si="60"/>
-        <v>145.02883352353936</v>
+        <f t="shared" si="58"/>
+        <v>144.06878119972129</v>
       </c>
       <c r="BT29" s="1">
-        <f t="shared" si="60"/>
-        <v>143.57854518830396</v>
+        <f t="shared" si="58"/>
+        <v>142.62809338772408</v>
       </c>
       <c r="BU29" s="1">
-        <f t="shared" si="60"/>
-        <v>142.14275973642091</v>
+        <f t="shared" si="58"/>
+        <v>141.20181245384683</v>
       </c>
       <c r="BV29" s="1">
-        <f t="shared" si="60"/>
-        <v>140.7213321390567</v>
+        <f t="shared" si="58"/>
+        <v>139.78979432930836</v>
       </c>
       <c r="BW29" s="1">
-        <f t="shared" si="60"/>
-        <v>139.31411881766613</v>
+        <f t="shared" si="58"/>
+        <v>138.39189638601528</v>
       </c>
       <c r="BX29" s="1">
-        <f t="shared" si="60"/>
-        <v>137.92097762948947</v>
+        <f t="shared" si="58"/>
+        <v>137.00797742215511</v>
       </c>
       <c r="BY29" s="1">
-        <f t="shared" si="60"/>
-        <v>136.54176785319459</v>
+        <f t="shared" si="58"/>
+        <v>135.63789764793356</v>
       </c>
       <c r="BZ29" s="1">
-        <f t="shared" si="60"/>
-        <v>135.17635017466264</v>
+        <f t="shared" si="58"/>
+        <v>134.28151867145422</v>
       </c>
       <c r="CA29" s="1">
-        <f t="shared" si="60"/>
-        <v>133.82458667291601</v>
+        <f t="shared" si="58"/>
+        <v>132.93870348473968</v>
       </c>
       <c r="CB29" s="1">
-        <f t="shared" si="60"/>
-        <v>132.48634080618686</v>
+        <f t="shared" si="58"/>
+        <v>131.60931644989228</v>
       </c>
       <c r="CC29" s="1">
-        <f t="shared" si="60"/>
-        <v>131.16147739812499</v>
+        <f t="shared" si="58"/>
+        <v>130.29322328539334</v>
       </c>
       <c r="CD29" s="1">
-        <f t="shared" si="60"/>
-        <v>129.84986262414373</v>
+        <f t="shared" si="58"/>
+        <v>128.99029105253939</v>
       </c>
       <c r="CE29" s="1">
-        <f t="shared" si="60"/>
-        <v>128.55136399790229</v>
+        <f t="shared" si="58"/>
+        <v>127.70038814201399</v>
       </c>
       <c r="CF29" s="1">
-        <f t="shared" si="60"/>
-        <v>127.26585035792326</v>
+        <f t="shared" si="58"/>
+        <v>126.42338426059385</v>
       </c>
       <c r="CG29" s="1">
-        <f t="shared" si="60"/>
-        <v>125.99319185434402</v>
+        <f t="shared" si="58"/>
+        <v>125.15915041798792</v>
       </c>
       <c r="CH29" s="1">
-        <f t="shared" si="60"/>
-        <v>124.73325993580058</v>
+        <f t="shared" si="58"/>
+        <v>123.90755891380803</v>
       </c>
       <c r="CI29" s="1">
-        <f t="shared" si="60"/>
-        <v>123.48592733644257</v>
+        <f t="shared" si="58"/>
+        <v>122.66848332466995</v>
       </c>
       <c r="CJ29" s="1">
-        <f t="shared" si="60"/>
-        <v>122.25106806307815</v>
+        <f t="shared" si="58"/>
+        <v>121.44179849142326</v>
       </c>
       <c r="CK29" s="1">
-        <f t="shared" si="60"/>
-        <v>121.02855738244737</v>
+        <f t="shared" si="58"/>
+        <v>120.22738050650902</v>
       </c>
       <c r="CL29" s="1">
-        <f t="shared" si="60"/>
-        <v>119.8182718086229</v>
+        <f t="shared" si="58"/>
+        <v>119.02510670144393</v>
       </c>
       <c r="CM29" s="1">
-        <f t="shared" si="60"/>
-        <v>118.62008909053667</v>
+        <f t="shared" si="58"/>
+        <v>117.83485563442949</v>
       </c>
       <c r="CN29" s="1">
-        <f t="shared" si="60"/>
-        <v>117.4338881996313</v>
+        <f t="shared" si="58"/>
+        <v>116.6565070780852</v>
       </c>
       <c r="CO29" s="1">
-        <f t="shared" si="60"/>
-        <v>116.25954931763498</v>
+        <f t="shared" si="58"/>
+        <v>115.48994200730435</v>
       </c>
       <c r="CP29" s="1">
-        <f t="shared" si="60"/>
-        <v>115.09695382445862</v>
+        <f t="shared" si="58"/>
+        <v>114.3350425872313</v>
       </c>
       <c r="CQ29" s="1">
-        <f t="shared" si="60"/>
-        <v>113.94598428621404</v>
+        <f t="shared" si="58"/>
+        <v>113.19169216135899</v>
       </c>
       <c r="CR29" s="1">
-        <f t="shared" si="60"/>
-        <v>112.8065244433519</v>
+        <f t="shared" si="58"/>
+        <v>112.05977523974539</v>
       </c>
       <c r="CS29" s="1">
-        <f t="shared" si="60"/>
-        <v>111.67845919891839</v>
+        <f t="shared" si="58"/>
+        <v>110.93917748734793</v>
       </c>
       <c r="CT29" s="1">
-        <f t="shared" si="60"/>
-        <v>110.5616746069292</v>
+        <f t="shared" si="58"/>
+        <v>109.82978571247445</v>
       </c>
       <c r="CU29" s="1">
-        <f t="shared" si="60"/>
-        <v>109.45605786085991</v>
+        <f t="shared" si="58"/>
+        <v>108.7314878553497</v>
       </c>
       <c r="CV29" s="1">
-        <f t="shared" si="60"/>
-        <v>108.36149728225132</v>
+        <f t="shared" si="58"/>
+        <v>107.6441729767962</v>
       </c>
       <c r="CW29" s="1">
-        <f t="shared" si="60"/>
-        <v>107.2778823094288</v>
+        <f t="shared" si="58"/>
+        <v>106.56773124702823</v>
       </c>
       <c r="CX29" s="1">
-        <f t="shared" si="60"/>
-        <v>106.20510348633452</v>
+        <f t="shared" si="58"/>
+        <v>105.50205393455795</v>
       </c>
       <c r="CY29" s="1">
-        <f t="shared" si="60"/>
-        <v>105.14305245147118</v>
+        <f t="shared" si="58"/>
+        <v>104.44703339521237</v>
       </c>
       <c r="CZ29" s="1">
-        <f t="shared" ref="CZ29:EN29" si="61">CY29*(1+$AO$40)</f>
-        <v>104.09162192695646</v>
+        <f t="shared" ref="CZ29:EN29" si="59">CY29*(1+$AO$40)</f>
+        <v>103.40256306126025</v>
       </c>
       <c r="DA29" s="1">
-        <f t="shared" si="61"/>
-        <v>103.0507057076869</v>
+        <f t="shared" si="59"/>
+        <v>102.36853743064765</v>
       </c>
       <c r="DB29" s="1">
-        <f t="shared" si="61"/>
-        <v>102.02019865061003</v>
+        <f t="shared" si="59"/>
+        <v>101.34485205634117</v>
       </c>
       <c r="DC29" s="1">
-        <f t="shared" si="61"/>
-        <v>100.99999666410393</v>
+        <f t="shared" si="59"/>
+        <v>100.33140353577775</v>
       </c>
       <c r="DD29" s="1">
-        <f t="shared" si="61"/>
-        <v>99.989996697462885</v>
+        <f t="shared" si="59"/>
+        <v>99.328089500419978</v>
       </c>
       <c r="DE29" s="1">
-        <f t="shared" si="61"/>
-        <v>98.990096730488261</v>
+        <f t="shared" si="59"/>
+        <v>98.334808605415773</v>
       </c>
       <c r="DF29" s="1">
-        <f t="shared" si="61"/>
-        <v>98.000195763183385</v>
+        <f t="shared" si="59"/>
+        <v>97.351460519361609</v>
       </c>
       <c r="DG29" s="1">
-        <f t="shared" si="61"/>
-        <v>97.020193805551557</v>
+        <f t="shared" si="59"/>
+        <v>96.377945914167995</v>
       </c>
       <c r="DH29" s="1">
-        <f t="shared" si="61"/>
-        <v>96.049991867496047</v>
+        <f t="shared" si="59"/>
+        <v>95.414166455026319</v>
       </c>
       <c r="DI29" s="1">
-        <f t="shared" si="61"/>
-        <v>95.089491948821092</v>
+        <f t="shared" si="59"/>
+        <v>94.460024790476055</v>
       </c>
       <c r="DJ29" s="1">
-        <f t="shared" si="61"/>
-        <v>94.138597029332885</v>
+        <f t="shared" si="59"/>
+        <v>93.515424542571296</v>
       </c>
       <c r="DK29" s="1">
-        <f t="shared" si="61"/>
-        <v>93.19721105903956</v>
+        <f t="shared" si="59"/>
+        <v>92.580270297145589</v>
       </c>
       <c r="DL29" s="1">
-        <f t="shared" si="61"/>
-        <v>92.265238948449166</v>
+        <f t="shared" si="59"/>
+        <v>91.654467594174136</v>
       </c>
       <c r="DM29" s="1">
-        <f t="shared" si="61"/>
-        <v>91.342586558964669</v>
+        <f t="shared" si="59"/>
+        <v>90.7379229182324</v>
       </c>
       <c r="DN29" s="1">
-        <f t="shared" si="61"/>
-        <v>90.429160693375024</v>
+        <f t="shared" si="59"/>
+        <v>89.830543689050074</v>
       </c>
       <c r="DO29" s="1">
-        <f t="shared" si="61"/>
-        <v>89.524869086441271</v>
+        <f t="shared" si="59"/>
+        <v>88.932238252159578</v>
       </c>
       <c r="DP29" s="1">
-        <f t="shared" si="61"/>
-        <v>88.62962039557685</v>
+        <f t="shared" si="59"/>
+        <v>88.04291586963798</v>
       </c>
       <c r="DQ29" s="1">
-        <f t="shared" si="61"/>
-        <v>87.743324191621085</v>
+        <f t="shared" si="59"/>
+        <v>87.162486710941593</v>
       </c>
       <c r="DR29" s="1">
-        <f t="shared" si="61"/>
-        <v>86.865890949704877</v>
+        <f t="shared" si="59"/>
+        <v>86.290861843832175</v>
       </c>
       <c r="DS29" s="1">
-        <f t="shared" si="61"/>
-        <v>85.997232040207834</v>
+        <f t="shared" si="59"/>
+        <v>85.42795322539385</v>
       </c>
       <c r="DT29" s="1">
-        <f t="shared" si="61"/>
-        <v>85.137259719805755</v>
+        <f t="shared" si="59"/>
+        <v>84.573673693139909</v>
       </c>
       <c r="DU29" s="1">
-        <f t="shared" si="61"/>
-        <v>84.28588712260769</v>
+        <f t="shared" si="59"/>
+        <v>83.727936956208509</v>
       </c>
       <c r="DV29" s="1">
-        <f t="shared" si="61"/>
-        <v>83.443028251381605</v>
+        <f t="shared" si="59"/>
+        <v>82.890657586646427</v>
       </c>
       <c r="DW29" s="1">
-        <f t="shared" si="61"/>
-        <v>82.608597968867784</v>
+        <f t="shared" si="59"/>
+        <v>82.061751010779957</v>
       </c>
       <c r="DX29" s="1">
-        <f t="shared" si="61"/>
-        <v>81.782511989179099</v>
+        <f t="shared" si="59"/>
+        <v>81.241133500672163</v>
       </c>
       <c r="DY29" s="1">
-        <f t="shared" si="61"/>
-        <v>80.964686869287306</v>
+        <f t="shared" si="59"/>
+        <v>80.428722165665434</v>
       </c>
       <c r="DZ29" s="1">
-        <f t="shared" si="61"/>
-        <v>80.155040000594425</v>
+        <f t="shared" si="59"/>
+        <v>79.624434944008783</v>
       </c>
       <c r="EA29" s="1">
-        <f t="shared" si="61"/>
-        <v>79.353489600588475</v>
+        <f t="shared" si="59"/>
+        <v>78.828190594568696</v>
       </c>
       <c r="EB29" s="1">
-        <f t="shared" si="61"/>
-        <v>78.559954704582594</v>
+        <f t="shared" si="59"/>
+        <v>78.039908688623015</v>
       </c>
       <c r="EC29" s="1">
-        <f t="shared" si="61"/>
-        <v>77.774355157536775</v>
+        <f t="shared" si="59"/>
+        <v>77.259509601736781</v>
       </c>
       <c r="ED29" s="1">
-        <f t="shared" si="61"/>
-        <v>76.996611605961405</v>
+        <f t="shared" si="59"/>
+        <v>76.486914505719412</v>
       </c>
       <c r="EE29" s="1">
-        <f t="shared" si="61"/>
-        <v>76.226645489901784</v>
+        <f t="shared" si="59"/>
+        <v>75.722045360662221</v>
       </c>
       <c r="EF29" s="1">
-        <f t="shared" si="61"/>
-        <v>75.464379035002764</v>
+        <f t="shared" si="59"/>
+        <v>74.964824907055601</v>
       </c>
       <c r="EG29" s="1">
-        <f t="shared" si="61"/>
-        <v>74.709735244652734</v>
+        <f t="shared" si="59"/>
+        <v>74.21517665798504</v>
       </c>
       <c r="EH29" s="1">
-        <f t="shared" si="61"/>
-        <v>73.962637892206203</v>
+        <f t="shared" si="59"/>
+        <v>73.473024891405188</v>
       </c>
       <c r="EI29" s="1">
-        <f t="shared" si="61"/>
-        <v>73.223011513284135</v>
+        <f t="shared" si="59"/>
+        <v>72.738294642491141</v>
       </c>
       <c r="EJ29" s="1">
-        <f t="shared" si="61"/>
-        <v>72.490781398151299</v>
+        <f t="shared" si="59"/>
+        <v>72.010911696066231</v>
       </c>
       <c r="EK29" s="1">
-        <f t="shared" si="61"/>
-        <v>71.765873584169782</v>
+        <f t="shared" si="59"/>
+        <v>71.290802579105573</v>
       </c>
       <c r="EL29" s="1">
-        <f t="shared" si="61"/>
-        <v>71.048214848328087</v>
+        <f t="shared" si="59"/>
+        <v>70.577894553314522</v>
       </c>
       <c r="EM29" s="1">
-        <f t="shared" si="61"/>
-        <v>70.337732699844807</v>
+        <f t="shared" si="59"/>
+        <v>69.872115607781382</v>
       </c>
       <c r="EN29" s="1">
-        <f t="shared" si="61"/>
-        <v>69.634355372846358</v>
+        <f t="shared" si="59"/>
+        <v>69.173394451703572</v>
       </c>
     </row>
     <row r="30" spans="2:144" x14ac:dyDescent="0.3">
@@ -4280,13 +4274,16 @@
         <v>89.5</v>
       </c>
       <c r="T30" s="3">
-        <v>89.5</v>
+        <f>89.6</f>
+        <v>89.6</v>
       </c>
       <c r="U30" s="3">
-        <v>89.5</v>
+        <f>89.6</f>
+        <v>89.6</v>
       </c>
       <c r="V30" s="3">
-        <v>89.5</v>
+        <f>89.6</f>
+        <v>89.6</v>
       </c>
       <c r="X30" s="3">
         <v>88.5</v>
@@ -4301,37 +4298,48 @@
         <v>88.5</v>
       </c>
       <c r="AB30" s="3">
-        <v>89.5</v>
+        <f t="shared" ref="AB30:AL30" si="60">89.6</f>
+        <v>89.6</v>
       </c>
       <c r="AC30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AD30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AE30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AF30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AG30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AH30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AI30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AJ30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AK30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
       <c r="AL30" s="3">
-        <v>89.5</v>
+        <f t="shared" si="60"/>
+        <v>89.6</v>
       </c>
     </row>
     <row r="31" spans="2:144" x14ac:dyDescent="0.3">
@@ -4339,60 +4347,60 @@
         <v>44</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" ref="I31:P31" si="62">I29/I30</f>
+        <f t="shared" ref="I31:P31" si="61">I29/I30</f>
         <v>0.10621468926553666</v>
       </c>
       <c r="J31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.23502824858757046</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.17288135593220327</v>
+      </c>
+      <c r="L31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.15367231638418072</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.18983050847457619</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="61"/>
+        <v>1.2135593220338985</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.167231638418079</v>
+      </c>
+      <c r="P31" s="7">
+        <f t="shared" si="61"/>
+        <v>0.21694915254237279</v>
+      </c>
+      <c r="Q31" s="7">
+        <f t="shared" ref="Q31:R31" si="62">Q29/Q30</f>
+        <v>0.2056497175141242</v>
+      </c>
+      <c r="R31" s="7">
         <f t="shared" si="62"/>
-        <v>0.23502824858757046</v>
-      </c>
-      <c r="K31" s="7">
-        <f t="shared" si="62"/>
-        <v>0.17288135593220327</v>
-      </c>
-      <c r="L31" s="7">
-        <f t="shared" si="62"/>
-        <v>0.15367231638418072</v>
-      </c>
-      <c r="M31" s="7">
-        <f t="shared" si="62"/>
-        <v>0.18983050847457619</v>
-      </c>
-      <c r="N31" s="7">
-        <f t="shared" si="62"/>
-        <v>1.2135593220338985</v>
-      </c>
-      <c r="O31" s="7">
-        <f t="shared" si="62"/>
-        <v>0.167231638418079</v>
-      </c>
-      <c r="P31" s="7">
-        <f t="shared" si="62"/>
-        <v>0.21694915254237279</v>
-      </c>
-      <c r="Q31" s="7">
-        <f t="shared" ref="Q31:R31" si="63">Q29/Q30</f>
-        <v>0.2056497175141242</v>
-      </c>
-      <c r="R31" s="7">
+        <v>0.32316384180790925</v>
+      </c>
+      <c r="S31" s="7">
+        <f t="shared" ref="S31:V31" si="63">S29/S30</f>
+        <v>0.20670391061452503</v>
+      </c>
+      <c r="T31" s="7">
         <f t="shared" si="63"/>
-        <v>0.32316384180790925</v>
-      </c>
-      <c r="S31" s="7">
-        <f t="shared" ref="S31:V31" si="64">S29/S30</f>
-        <v>0.20670391061452503</v>
-      </c>
-      <c r="T31" s="7">
-        <f t="shared" si="64"/>
-        <v>0.17094972067039108</v>
+        <v>0.1707589285714286</v>
       </c>
       <c r="U31" s="7">
-        <f t="shared" si="64"/>
-        <v>0.26089586592178771</v>
+        <f t="shared" si="63"/>
+        <v>0.20535714285714274</v>
       </c>
       <c r="V31" s="7">
-        <f t="shared" si="64"/>
-        <v>0.27333720670391048</v>
+        <f t="shared" si="63"/>
+        <v>0.25342522321428584</v>
       </c>
       <c r="X31" s="7">
         <f>X29/X30</f>
@@ -4412,47 +4420,47 @@
       </c>
       <c r="AB31" s="7">
         <f>AB29/AB30</f>
-        <v>0.91188670391061355</v>
+        <v>0.83601450892857254</v>
       </c>
       <c r="AC31" s="7">
-        <f t="shared" ref="AC31:AL31" si="65">AC29/AC30</f>
-        <v>1.4748448831284919</v>
+        <f t="shared" ref="AC31:AL31" si="64">AC29/AC30</f>
+        <v>1.4553316741071427</v>
       </c>
       <c r="AD31" s="7">
-        <f t="shared" si="65"/>
-        <v>1.7455658377778773</v>
+        <f t="shared" si="64"/>
+        <v>1.7236297002232148</v>
       </c>
       <c r="AE31" s="7">
-        <f t="shared" si="65"/>
-        <v>1.8565621211583823</v>
+        <f t="shared" si="64"/>
+        <v>1.8326499989959835</v>
       </c>
       <c r="AF31" s="7">
-        <f t="shared" si="65"/>
-        <v>1.9311683848378547</v>
+        <f t="shared" si="64"/>
+        <v>1.9057089209953622</v>
       </c>
       <c r="AG31" s="7">
-        <f t="shared" si="65"/>
-        <v>1.9866045152889742</v>
+        <f t="shared" si="64"/>
+        <v>1.9689042242755845</v>
       </c>
       <c r="AH31" s="7">
-        <f t="shared" si="65"/>
-        <v>2.0384613889151297</v>
+        <f t="shared" si="64"/>
+        <v>2.0208016514224778</v>
       </c>
       <c r="AI31" s="7">
-        <f t="shared" si="65"/>
-        <v>2.091476647847013</v>
+        <f t="shared" si="64"/>
+        <v>2.0738622205389232</v>
       </c>
       <c r="AJ31" s="7">
-        <f t="shared" si="65"/>
-        <v>2.1456746722690694</v>
+        <f t="shared" si="64"/>
+        <v>2.1281104463985772</v>
       </c>
       <c r="AK31" s="7">
-        <f t="shared" si="65"/>
-        <v>2.2010803420942175</v>
+        <f t="shared" si="64"/>
+        <v>2.1835713465899129</v>
       </c>
       <c r="AL31" s="7">
-        <f t="shared" si="65"/>
-        <v>2.2577190470796671</v>
+        <f t="shared" si="64"/>
+        <v>2.2402704516977097</v>
       </c>
     </row>
     <row r="32" spans="2:144" x14ac:dyDescent="0.3">
@@ -4473,71 +4481,71 @@
         <v>0.44194756554307113</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:S33" si="66">H3/D3-1</f>
+        <f t="shared" ref="H33:S33" si="65">H3/D3-1</f>
         <v>0.49134948096885833</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.40687679083094563</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.54768392370572183</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.25974025974025983</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.24825986078886308</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.23828920570264756</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.19366197183098599</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.2082474226804123</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.2007434944237918</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.26315789473684204</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.37610619469026552</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>0.63139931740614319</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:T35" si="67">T3/P3-1</f>
+        <f t="shared" ref="T33:T35" si="66">T3/P3-1</f>
         <v>0.43808049535603732</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" ref="U33:U35" si="68">U3/Q3-1</f>
-        <v>0.27</v>
+        <f t="shared" ref="U33:U35" si="67">U3/Q3-1</f>
+        <v>0.24869791666666674</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33:V35" si="69">V3/R3-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="V33:V35" si="68">V3/R3-1</f>
+        <v>0.10000000000000009</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33:Z33" si="70">Y3/X3-1</f>
+        <f t="shared" ref="Y33:Z33" si="69">Y3/X3-1</f>
         <v>0.47405660377358494</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>0.23146666666666649</v>
       </c>
       <c r="AA33" s="10">
@@ -4546,46 +4554,46 @@
       </c>
       <c r="AB33" s="10">
         <f>AB3/AA3-1</f>
-        <v>0.31560518240709179</v>
+        <v>0.31957040572792339</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33:AL33" si="71">AC3/AB3-1</f>
+        <f t="shared" ref="AC33:AL33" si="70">AC3/AB3-1</f>
         <v>0.17999999999999994</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -4594,123 +4602,123 @@
         <v>93</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" ref="G34:S34" si="72">G4/C4-1</f>
+        <f t="shared" ref="G34:S34" si="71">G4/C4-1</f>
         <v>0.36752136752136755</v>
       </c>
       <c r="H34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.13087248322147649</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.15309446254071668</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.12068965517241392</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.18124999999999991</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.15430267062314518</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.15254237288135597</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.1461538461538463</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.14021164021164023</v>
+      </c>
+      <c r="P34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.14395886889460163</v>
+      </c>
+      <c r="Q34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.13480392156862742</v>
+      </c>
+      <c r="R34" s="10">
+        <f t="shared" si="71"/>
+        <v>0.17002237136465315</v>
+      </c>
+      <c r="S34" s="10">
+        <f t="shared" si="71"/>
+        <v>8.1206496519721671E-2</v>
+      </c>
+      <c r="T34" s="10">
+        <f t="shared" si="66"/>
+        <v>0.11460674157303363</v>
+      </c>
+      <c r="U34" s="10">
+        <f t="shared" si="67"/>
+        <v>0.20086393088552934</v>
+      </c>
+      <c r="V34" s="10">
+        <f t="shared" si="68"/>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" ref="Y34:AA34" si="72">Y4/X4-1</f>
+        <v>0.18028643639427111</v>
+      </c>
+      <c r="Z34" s="10">
         <f t="shared" si="72"/>
-        <v>0.13087248322147649</v>
-      </c>
-      <c r="I34" s="10">
+        <v>0.15774446823697352</v>
+      </c>
+      <c r="AA34" s="10">
         <f t="shared" si="72"/>
-        <v>0.15309446254071668</v>
-      </c>
-      <c r="J34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.12068965517241392</v>
-      </c>
-      <c r="K34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.18124999999999991</v>
-      </c>
-      <c r="L34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.15430267062314518</v>
-      </c>
-      <c r="M34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.15254237288135597</v>
-      </c>
-      <c r="N34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.1461538461538463</v>
-      </c>
-      <c r="O34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.14021164021164023</v>
-      </c>
-      <c r="P34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.14395886889460163</v>
-      </c>
-      <c r="Q34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.13480392156862742</v>
-      </c>
-      <c r="R34" s="10">
-        <f t="shared" si="72"/>
-        <v>0.17002237136465315</v>
-      </c>
-      <c r="S34" s="10">
-        <f t="shared" si="72"/>
-        <v>8.1206496519721671E-2</v>
-      </c>
-      <c r="T34" s="10">
-        <f t="shared" si="67"/>
-        <v>0.11460674157303363</v>
-      </c>
-      <c r="U34" s="10">
-        <f t="shared" si="68"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="V34" s="10">
-        <f t="shared" si="69"/>
+        <v>0.14796547472256472</v>
+      </c>
+      <c r="AB34" s="10">
+        <f t="shared" ref="AB34:AL34" si="73">AB4/AA4-1</f>
+        <v>0.12422126745435036</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" si="73"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AD34" s="10">
+        <f t="shared" si="73"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AE34" s="10">
+        <f t="shared" si="73"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF34" s="10">
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y34" s="10">
-        <f t="shared" ref="Y34:AA34" si="73">Y4/X4-1</f>
-        <v>0.18028643639427111</v>
-      </c>
-      <c r="Z34" s="10">
+      <c r="AG34" s="10">
         <f t="shared" si="73"/>
-        <v>0.15774446823697352</v>
-      </c>
-      <c r="AA34" s="10">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH34" s="10">
         <f t="shared" si="73"/>
-        <v>0.14796547472256472</v>
-      </c>
-      <c r="AB34" s="10">
-        <f t="shared" ref="AB34:AL34" si="74">AB4/AA4-1</f>
-        <v>6.9210526315789389E-2</v>
-      </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="74"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="74"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="74"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="74"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG34" s="10">
-        <f t="shared" si="74"/>
+      <c r="AI34" s="10">
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH34" s="10">
-        <f t="shared" si="74"/>
+      <c r="AJ34" s="10">
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI34" s="10">
-        <f t="shared" si="74"/>
+      <c r="AK34" s="10">
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ34" s="10">
-        <f t="shared" si="74"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AK34" s="10">
-        <f t="shared" si="74"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AL34" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -4719,123 +4727,123 @@
         <v>94</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" ref="G35:S35" si="75">G5/C5-1</f>
+        <f t="shared" ref="G35:S35" si="74">G5/C5-1</f>
         <v>-0.21428571428571419</v>
       </c>
       <c r="H35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="I35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="J35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.58333333333333326</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.36363636363636376</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="74"/>
+        <v>0.5</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="P35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="Q35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.9</v>
+      </c>
+      <c r="R35" s="10">
+        <f t="shared" si="74"/>
+        <v>-0.6</v>
+      </c>
+      <c r="S35" s="10">
+        <f t="shared" si="74"/>
+        <v>4</v>
+      </c>
+      <c r="T35" s="10">
+        <f t="shared" si="66"/>
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="U35" s="10">
+        <f t="shared" si="67"/>
+        <v>3</v>
+      </c>
+      <c r="V35" s="10">
+        <f t="shared" si="68"/>
+        <v>1.5</v>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" ref="Y35:AA35" si="75">Y5/X5-1</f>
+        <v>-0.31999999999999995</v>
+      </c>
+      <c r="Z35" s="10">
         <f t="shared" si="75"/>
-        <v>-0.2857142857142857</v>
-      </c>
-      <c r="I35" s="10">
+        <v>8.8235294117646967E-2</v>
+      </c>
+      <c r="AA35" s="10">
         <f t="shared" si="75"/>
-        <v>-0.19999999999999996</v>
-      </c>
-      <c r="J35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.58333333333333326</v>
-      </c>
-      <c r="K35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.36363636363636376</v>
-      </c>
-      <c r="L35" s="10">
-        <f t="shared" si="75"/>
-        <v>0.5</v>
-      </c>
-      <c r="M35" s="10">
-        <f t="shared" si="75"/>
-        <v>0.25</v>
-      </c>
-      <c r="N35" s="10">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="O35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.8571428571428571</v>
-      </c>
-      <c r="P35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="Q35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.9</v>
-      </c>
-      <c r="R35" s="10">
-        <f t="shared" si="75"/>
-        <v>-0.6</v>
-      </c>
-      <c r="S35" s="10">
-        <f t="shared" si="75"/>
-        <v>4</v>
-      </c>
-      <c r="T35" s="10">
-        <f t="shared" si="67"/>
-        <v>-0.16666666666666663</v>
-      </c>
-      <c r="U35" s="10">
-        <f t="shared" si="68"/>
-        <v>4</v>
-      </c>
-      <c r="V35" s="10">
-        <f t="shared" si="69"/>
-        <v>1.5</v>
-      </c>
-      <c r="Y35" s="10">
-        <f t="shared" ref="Y35:AA35" si="76">Y5/X5-1</f>
-        <v>-0.31999999999999995</v>
-      </c>
-      <c r="Z35" s="10">
+        <v>-0.72972972972972983</v>
+      </c>
+      <c r="AB35" s="10">
+        <f t="shared" ref="AB35:AL35" si="76">AB5/AA5-1</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="AC35" s="10">
         <f t="shared" si="76"/>
-        <v>8.8235294117646967E-2</v>
-      </c>
-      <c r="AA35" s="10">
+        <v>-1</v>
+      </c>
+      <c r="AD35" s="10" t="e">
         <f t="shared" si="76"/>
-        <v>-0.72972972972972983</v>
-      </c>
-      <c r="AB35" s="10">
-        <f t="shared" ref="AB35:AL35" si="77">AB5/AA5-1</f>
-        <v>1</v>
-      </c>
-      <c r="AC35" s="10">
-        <f t="shared" si="77"/>
-        <v>-1</v>
-      </c>
-      <c r="AD35" s="10" t="e">
-        <f t="shared" si="77"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AF35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AI35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AJ35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AK35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AL35" s="10" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4848,40 +4856,40 @@
         <v>0.20140515222482436</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" ref="N36:R36" si="78">N8/J8-1</f>
+        <f t="shared" ref="N36:R36" si="77">N8/J8-1</f>
         <v>0.17738589211618261</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0.17221584385763489</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0.17709437963944863</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0.20760233918128645</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0.2854625550660792</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" ref="S36" si="79">S8/O8-1</f>
+        <f t="shared" ref="S36" si="78">S8/O8-1</f>
         <v>0.39764936336924572</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" ref="T36" si="80">T8/P8-1</f>
+        <f t="shared" ref="T36" si="79">T8/P8-1</f>
         <v>0.28828828828828845</v>
       </c>
       <c r="U36" s="9">
-        <f t="shared" ref="U36" si="81">U8/Q8-1</f>
-        <v>0.19109765940274426</v>
+        <f t="shared" ref="U36" si="80">U8/Q8-1</f>
+        <v>0.2276029055690072</v>
       </c>
       <c r="V36" s="9">
-        <f t="shared" ref="V36" si="82">V8/R8-1</f>
-        <v>5.3303632625085751E-2</v>
+        <f t="shared" ref="V36" si="81">V8/R8-1</f>
+        <v>0.10116518163125465</v>
       </c>
       <c r="X36" s="9"/>
       <c r="Y36" s="9">
@@ -4889,56 +4897,56 @@
         <v>0.31809145129224659</v>
       </c>
       <c r="Z36" s="9">
-        <f t="shared" ref="Z36:AL36" si="83">Z8/Y8-1</f>
+        <f t="shared" ref="Z36:AL36" si="82">Z8/Y8-1</f>
         <v>0.19909502262443413</v>
       </c>
       <c r="AA36" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>0.2148427672955977</v>
       </c>
       <c r="AB36" s="9">
-        <f t="shared" si="83"/>
-        <v>0.21547732449782564</v>
+        <f t="shared" si="82"/>
+        <v>0.23930420376889638</v>
       </c>
       <c r="AC36" s="9">
-        <f t="shared" si="83"/>
-        <v>0.13188496883912548</v>
+        <f t="shared" si="82"/>
+        <v>0.1338856398088426</v>
       </c>
       <c r="AD36" s="9">
-        <f t="shared" si="83"/>
-        <v>9.4828109771864622E-2</v>
+        <f t="shared" si="82"/>
+        <v>9.3840891313279551E-2</v>
       </c>
       <c r="AE36" s="9">
-        <f t="shared" si="83"/>
-        <v>5.103326165874722E-2</v>
+        <f t="shared" si="82"/>
+        <v>5.0673184309673935E-2</v>
       </c>
       <c r="AF36" s="9">
-        <f t="shared" si="83"/>
-        <v>3.4141802593437465E-2</v>
+        <f t="shared" si="82"/>
+        <v>3.3904466644498532E-2</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="83"/>
-        <v>2.7110956476322334E-2</v>
+        <f t="shared" si="82"/>
+        <v>2.6993221219562935E-2</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="82"/>
+        <v>2.000000000000024E-2</v>
       </c>
       <c r="AL36" s="9">
-        <f t="shared" si="83"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="82"/>
+        <v>1.9999999999999796E-2</v>
       </c>
     </row>
     <row r="37" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4950,80 +4958,80 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:R37" si="84">(I8-I9)/I8</f>
+        <f t="shared" ref="I37:R37" si="83">(I8-I9)/I8</f>
         <v>0.98829039812646369</v>
       </c>
       <c r="J37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.99170124481327804</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.99081515499425954</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.98833510074231179</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.99317738791422994</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.99559471365638763</v>
+      </c>
+      <c r="O37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.9627815866797258</v>
+      </c>
+      <c r="P37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.98288288288288284</v>
+      </c>
+      <c r="Q37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.98547215496368046</v>
+      </c>
+      <c r="R37" s="10">
+        <f t="shared" si="83"/>
+        <v>0.98286497601096645</v>
+      </c>
+      <c r="S37" s="10">
+        <f t="shared" ref="S37:V37" si="84">(S8-S9)/S8</f>
+        <v>0.98458304134548014</v>
+      </c>
+      <c r="T37" s="10">
         <f t="shared" si="84"/>
-        <v>0.99170124481327804</v>
-      </c>
-      <c r="K37" s="10">
+        <v>0.98391608391608387</v>
+      </c>
+      <c r="U37" s="10">
         <f t="shared" si="84"/>
-        <v>0.99081515499425954</v>
-      </c>
-      <c r="L37" s="10">
+        <v>0.98553583168967795</v>
+      </c>
+      <c r="V37" s="10">
         <f t="shared" si="84"/>
-        <v>0.98833510074231179</v>
-      </c>
-      <c r="M37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.99317738791422994</v>
-      </c>
-      <c r="N37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.99559471365638763</v>
-      </c>
-      <c r="O37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.9627815866797258</v>
-      </c>
-      <c r="P37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.98288288288288284</v>
-      </c>
-      <c r="Q37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.98547215496368046</v>
-      </c>
-      <c r="R37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.98286497601096645</v>
-      </c>
-      <c r="S37" s="10">
-        <f t="shared" ref="S37:V37" si="85">(S8-S9)/S8</f>
-        <v>0.98458304134548014</v>
-      </c>
-      <c r="T37" s="10">
+        <v>0.98</v>
+      </c>
+      <c r="X37" s="10">
+        <f t="shared" ref="X37:AB37" si="85">(X8-X9)/X8</f>
+        <v>0.98210735586481113</v>
+      </c>
+      <c r="Y37" s="10">
         <f t="shared" si="85"/>
-        <v>0.98391608391608387</v>
-      </c>
-      <c r="U37" s="10">
+        <v>0.98763197586726992</v>
+      </c>
+      <c r="Z37" s="10">
         <f t="shared" si="85"/>
-        <v>0.98000000000000009</v>
-      </c>
-      <c r="V37" s="10">
+        <v>0.99220125786163516</v>
+      </c>
+      <c r="AA37" s="10">
         <f t="shared" si="85"/>
-        <v>0.98</v>
-      </c>
-      <c r="X37" s="10">
-        <f t="shared" ref="X37:AB37" si="86">(X8-X9)/X8</f>
-        <v>0.98210735586481113</v>
-      </c>
-      <c r="Y37" s="10">
-        <f t="shared" si="86"/>
-        <v>0.98763197586726992</v>
-      </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="86"/>
-        <v>0.99220125786163516</v>
-      </c>
-      <c r="AA37" s="10">
-        <f t="shared" si="86"/>
         <v>0.979291778836198</v>
       </c>
       <c r="AB37" s="10">
-        <f t="shared" si="86"/>
-        <v>0.98206830518234822</v>
+        <f t="shared" si="85"/>
+        <v>0.98343548440998574</v>
       </c>
       <c r="AC37" s="10"/>
       <c r="AD37" s="10"/>
@@ -5045,39 +5053,39 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="I38" s="10">
-        <f t="shared" ref="I38:Q38" si="87">(I8-I10)/I8</f>
+        <f t="shared" ref="I38:Q38" si="86">(I8-I10)/I8</f>
         <v>0.99063231850117095</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.99066390041493768</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.98966704936854188</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.98833510074231179</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.98830409356725146</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.99030837004405292</v>
       </c>
       <c r="O38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.99020568070519099</v>
       </c>
       <c r="P38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.99189189189189186</v>
       </c>
       <c r="Q38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0.99273607748184012</v>
       </c>
       <c r="R38" s="10">
@@ -5085,40 +5093,40 @@
         <v>0.99246058944482529</v>
       </c>
       <c r="S38" s="10">
-        <f t="shared" ref="S38:V38" si="88">(S8-S10)/S8</f>
+        <f t="shared" ref="S38:V38" si="87">(S8-S10)/S8</f>
         <v>0.99369306236860544</v>
       </c>
       <c r="T38" s="10">
+        <f t="shared" si="87"/>
+        <v>0.98951048951048948</v>
+      </c>
+      <c r="U38" s="10">
+        <f t="shared" si="87"/>
+        <v>0.98750821827744906</v>
+      </c>
+      <c r="V38" s="10">
+        <f t="shared" si="87"/>
+        <v>0.98999999999999988</v>
+      </c>
+      <c r="X38" s="10">
+        <f t="shared" ref="X38:AB38" si="88">(X8-X10)/X8</f>
+        <v>0.98528827037773359</v>
+      </c>
+      <c r="Y38" s="10">
         <f t="shared" si="88"/>
-        <v>0.98951048951048948</v>
-      </c>
-      <c r="U38" s="10">
+        <v>0.98853695324283553</v>
+      </c>
+      <c r="Z38" s="10">
         <f t="shared" si="88"/>
-        <v>0.98999999999999988</v>
-      </c>
-      <c r="V38" s="10">
+        <v>0.98918238993710694</v>
+      </c>
+      <c r="AA38" s="10">
         <f t="shared" si="88"/>
-        <v>0.9900000000000001</v>
-      </c>
-      <c r="X38" s="10">
-        <f t="shared" ref="X38:AB38" si="89">(X8-X10)/X8</f>
-        <v>0.98528827037773359</v>
-      </c>
-      <c r="Y38" s="10">
-        <f t="shared" si="89"/>
-        <v>0.98853695324283553</v>
-      </c>
-      <c r="Z38" s="10">
-        <f t="shared" si="89"/>
-        <v>0.98918238993710694</v>
-      </c>
-      <c r="AA38" s="10">
-        <f t="shared" si="89"/>
         <v>0.99192379374611728</v>
       </c>
       <c r="AB38" s="10">
-        <f t="shared" si="89"/>
-        <v>0.99077859593767137</v>
+        <f t="shared" si="88"/>
+        <v>0.99013033452528154</v>
       </c>
       <c r="AC38" s="10"/>
       <c r="AD38" s="10"/>
@@ -5140,39 +5148,39 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="I39" s="10">
-        <f t="shared" ref="I39:Q39" si="90">(I8-I11)/I8</f>
+        <f t="shared" ref="I39:Q39" si="89">(I8-I11)/I8</f>
         <v>0.83723653395784536</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.8205394190871369</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.82548794489092991</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.78366914103923635</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.77290448343079921</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.76211453744493396</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.81096963761018614</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.77567567567567575</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0.75544794188861986</v>
       </c>
       <c r="R39" s="10">
@@ -5180,40 +5188,40 @@
         <v>0.69773817683344752</v>
       </c>
       <c r="S39" s="10">
-        <f t="shared" ref="S39:V39" si="91">(S8-S11)/S8</f>
+        <f t="shared" ref="S39:V39" si="90">(S8-S11)/S8</f>
         <v>0.66713384723195512</v>
       </c>
       <c r="T39" s="10">
+        <f t="shared" si="90"/>
+        <v>0.67062937062937067</v>
+      </c>
+      <c r="U39" s="10">
+        <f t="shared" si="90"/>
+        <v>0.68113083497698879</v>
+      </c>
+      <c r="V39" s="10">
+        <f t="shared" si="90"/>
+        <v>0.67</v>
+      </c>
+      <c r="X39" s="10">
+        <f t="shared" ref="X39:AB39" si="91">(X8-X11)/X8</f>
+        <v>0.97813121272365811</v>
+      </c>
+      <c r="Y39" s="10">
         <f t="shared" si="91"/>
-        <v>0.67062937062937067</v>
-      </c>
-      <c r="U39" s="10">
+        <v>0.8591251885369533</v>
+      </c>
+      <c r="Z39" s="10">
         <f t="shared" si="91"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="V39" s="10">
+        <v>0.78389937106918239</v>
+      </c>
+      <c r="AA39" s="10">
         <f t="shared" si="91"/>
-        <v>0.66999999999999993</v>
-      </c>
-      <c r="X39" s="10">
-        <f t="shared" ref="X39:AB39" si="92">(X8-X11)/X8</f>
-        <v>0.97813121272365811</v>
-      </c>
-      <c r="Y39" s="10">
-        <f t="shared" si="92"/>
-        <v>0.8591251885369533</v>
-      </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="92"/>
-        <v>0.78389937106918239</v>
-      </c>
-      <c r="AA39" s="10">
-        <f t="shared" si="92"/>
         <v>0.75440049699730782</v>
       </c>
       <c r="AB39" s="10">
-        <f t="shared" si="92"/>
-        <v>0.66945651618355095</v>
+        <f t="shared" si="91"/>
+        <v>0.67229589279149826</v>
       </c>
       <c r="AC39" s="10"/>
       <c r="AD39" s="10"/>
@@ -5231,19 +5239,19 @@
         <v>47</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:L40" si="93">I13/I8</f>
+        <f t="shared" ref="I40:L40" si="92">I13/I8</f>
         <v>0.81615925058548</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.80290456431535273</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.80597014925373123</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.76033934252386004</v>
       </c>
       <c r="M40" s="10">
@@ -5251,99 +5259,99 @@
         <v>0.75438596491228072</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" ref="N40:R40" si="94">N13/N8</f>
+        <f t="shared" ref="N40:R40" si="93">N13/N8</f>
         <v>0.74801762114537451</v>
       </c>
       <c r="O40" s="10">
+        <f t="shared" si="93"/>
+        <v>0.76395690499510294</v>
+      </c>
+      <c r="P40" s="10">
+        <f t="shared" si="93"/>
+        <v>0.75045045045045045</v>
+      </c>
+      <c r="Q40" s="10">
+        <f t="shared" si="93"/>
+        <v>0.73365617433414043</v>
+      </c>
+      <c r="R40" s="10">
+        <f t="shared" si="93"/>
+        <v>0.67306374228923915</v>
+      </c>
+      <c r="S40" s="10">
+        <f t="shared" ref="S40:V40" si="94">S13/S8</f>
+        <v>0.6454099509460407</v>
+      </c>
+      <c r="T40" s="10">
         <f t="shared" si="94"/>
-        <v>0.76395690499510294</v>
-      </c>
-      <c r="P40" s="10">
+        <v>0.64405594405594402</v>
+      </c>
+      <c r="U40" s="10">
         <f t="shared" si="94"/>
-        <v>0.75045045045045045</v>
-      </c>
-      <c r="Q40" s="10">
+        <v>0.65417488494411569</v>
+      </c>
+      <c r="V40" s="10">
         <f t="shared" si="94"/>
-        <v>0.73365617433414043</v>
-      </c>
-      <c r="R40" s="10">
-        <f t="shared" si="94"/>
-        <v>0.67306374228923915</v>
-      </c>
-      <c r="S40" s="10">
-        <f t="shared" ref="S40:V40" si="95">S13/S8</f>
-        <v>0.6454099509460407</v>
-      </c>
-      <c r="T40" s="10">
+        <v>0.64</v>
+      </c>
+      <c r="X40" s="10">
+        <f t="shared" ref="X40:AL40" si="95">X13/X8</f>
+        <v>0.94552683896620282</v>
+      </c>
+      <c r="Y40" s="10">
         <f t="shared" si="95"/>
-        <v>0.64405594405594402</v>
-      </c>
-      <c r="U40" s="10">
+        <v>0.83529411764705874</v>
+      </c>
+      <c r="Z40" s="10">
         <f t="shared" si="95"/>
-        <v>0.6399999999999999</v>
-      </c>
-      <c r="V40" s="10">
+        <v>0.76528301886792449</v>
+      </c>
+      <c r="AA40" s="10">
         <f t="shared" si="95"/>
-        <v>0.6399999999999999</v>
-      </c>
-      <c r="X40" s="10">
-        <f t="shared" ref="X40:AL40" si="96">X13/X8</f>
-        <v>0.94552683896620282</v>
-      </c>
-      <c r="Y40" s="10">
-        <f t="shared" si="96"/>
-        <v>0.83529411764705874</v>
-      </c>
-      <c r="Z40" s="10">
-        <f t="shared" si="96"/>
-        <v>0.76528301886792449</v>
-      </c>
-      <c r="AA40" s="10">
-        <f t="shared" si="96"/>
         <v>0.7256160695796231</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" si="96"/>
-        <v>0.64230341730357055</v>
+        <f t="shared" si="95"/>
+        <v>0.64586171172676543</v>
       </c>
       <c r="AC40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AD40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AE40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AF40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AG40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AH40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AI40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AJ40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AK40" s="10">
-        <f t="shared" si="96"/>
-        <v>0.63000000000000012</v>
+        <f t="shared" si="95"/>
+        <v>0.62999999999999989</v>
       </c>
       <c r="AL40" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>0.63</v>
       </c>
       <c r="AN40" t="s">
@@ -5366,40 +5374,40 @@
         <v>0.14999999999999991</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" ref="N41:R41" si="97">N14/J14-1</f>
+        <f t="shared" ref="N41:R41" si="96">N14/J14-1</f>
         <v>-2.3696682464454999E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>-0.18905472636815923</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>-7.4766355140186813E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>0.12077294685990347</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>-0.13592233009708743</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" ref="S41" si="98">S14/O14-1</f>
+        <f t="shared" ref="S41" si="97">S14/O14-1</f>
         <v>7.9754601226993849E-2</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" ref="T41" si="99">T14/P14-1</f>
+        <f t="shared" ref="T41" si="98">T14/P14-1</f>
         <v>-5.555555555555558E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" ref="U41" si="100">U14/Q14-1</f>
-        <v>-0.20000000000000007</v>
+        <f t="shared" ref="U41" si="99">U14/Q14-1</f>
+        <v>-9.9137931034482762E-2</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" ref="V41" si="101">V14/R14-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="V41" si="100">V14/R14-1</f>
+        <v>0.25</v>
       </c>
       <c r="X41" s="10"/>
       <c r="Y41" s="10">
@@ -5407,55 +5415,55 @@
         <v>1.3422818791946067E-3</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" ref="Z41:AL41" si="102">Z14/Y14-1</f>
+        <f t="shared" ref="Z41:AL41" si="101">Z14/Y14-1</f>
         <v>0.1099195710455767</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>-6.8840579710145122E-2</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" si="102"/>
-        <v>-4.60440985732814E-2</v>
+        <f t="shared" si="101"/>
+        <v>3.0479896238650994E-2</v>
       </c>
       <c r="AC41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AD41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG41" s="10">
-        <f t="shared" si="102"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="101"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL41" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN41" t="s">
@@ -5470,19 +5478,19 @@
         <v>49</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" ref="I42:L42" si="103">I16/I8</f>
+        <f t="shared" ref="I42:L42" si="102">I16/I8</f>
         <v>0.3044496487119438</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.30705394190871371</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.28013777267508611</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="102"/>
         <v>0.28632025450689297</v>
       </c>
       <c r="M42" s="10">
@@ -5490,99 +5498,99 @@
         <v>0.27680311890838205</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" ref="N42:R42" si="104">N16/N8</f>
+        <f t="shared" ref="N42:R42" si="103">N16/N8</f>
         <v>0.26519823788546254</v>
       </c>
       <c r="O42" s="10">
+        <f t="shared" si="103"/>
+        <v>0.28893241919686585</v>
+      </c>
+      <c r="P42" s="10">
+        <f t="shared" si="103"/>
+        <v>0.26126126126126131</v>
+      </c>
+      <c r="Q42" s="10">
+        <f t="shared" si="103"/>
+        <v>0.2623083131557708</v>
+      </c>
+      <c r="R42" s="10">
+        <f t="shared" si="103"/>
+        <v>0.28032899246058945</v>
+      </c>
+      <c r="S42" s="10">
+        <f t="shared" ref="S42:V42" si="104">S16/S8</f>
+        <v>0.23966362999299234</v>
+      </c>
+      <c r="T42" s="10">
         <f t="shared" si="104"/>
-        <v>0.28893241919686585</v>
-      </c>
-      <c r="P42" s="10">
+        <v>0.23776223776223776</v>
+      </c>
+      <c r="U42" s="10">
         <f t="shared" si="104"/>
-        <v>0.26126126126126131</v>
-      </c>
-      <c r="Q42" s="10">
+        <v>0.23602892833662065</v>
+      </c>
+      <c r="V42" s="10">
         <f t="shared" si="104"/>
-        <v>0.2623083131557708</v>
-      </c>
-      <c r="R42" s="10">
-        <f t="shared" si="104"/>
-        <v>0.28032899246058945</v>
-      </c>
-      <c r="S42" s="10">
-        <f t="shared" ref="S42:V42" si="105">S16/S8</f>
-        <v>0.23966362999299234</v>
-      </c>
-      <c r="T42" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="X42" s="10">
+        <f t="shared" ref="X42:AL42" si="105">X16/X8</f>
+        <v>0.48071570576540756</v>
+      </c>
+      <c r="Y42" s="10">
         <f t="shared" si="105"/>
-        <v>0.23776223776223776</v>
-      </c>
-      <c r="U42" s="10">
+        <v>0.34690799396681749</v>
+      </c>
+      <c r="Z42" s="10">
         <f t="shared" si="105"/>
-        <v>0.23999999999999996</v>
-      </c>
-      <c r="V42" s="10">
+        <v>0.27647798742138369</v>
+      </c>
+      <c r="AA42" s="10">
         <f t="shared" si="105"/>
-        <v>0.23999999999999996</v>
-      </c>
-      <c r="X42" s="10">
-        <f t="shared" ref="X42:AL42" si="106">X16/X8</f>
-        <v>0.48071570576540756</v>
-      </c>
-      <c r="Y42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.34690799396681749</v>
-      </c>
-      <c r="Z42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.27647798742138369</v>
-      </c>
-      <c r="AA42" s="10">
-        <f t="shared" si="106"/>
         <v>0.27314143715054878</v>
       </c>
       <c r="AB42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.23937303434340682</v>
+        <f t="shared" si="105"/>
+        <v>0.23837583130033752</v>
       </c>
       <c r="AC42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.22999999999999998</v>
+        <f t="shared" si="105"/>
+        <v>0.23000000000000004</v>
       </c>
       <c r="AD42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.22000000000000003</v>
+        <f t="shared" si="105"/>
+        <v>0.22</v>
       </c>
       <c r="AE42" s="10">
-        <f t="shared" si="106"/>
-        <v>0.22000000000000003</v>
+        <f t="shared" si="105"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AF42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AG42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AH42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AI42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AJ42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AK42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AL42" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="105"/>
         <v>0.22</v>
       </c>
       <c r="AN42" t="s">
@@ -5590,7 +5598,7 @@
       </c>
       <c r="AO42" s="3">
         <f>NPV(AO41,AB29:EN29)</f>
-        <v>1668.3946495042082</v>
+        <v>1649.0819367687186</v>
       </c>
     </row>
     <row r="43" spans="2:41" x14ac:dyDescent="0.3">
@@ -5598,19 +5606,19 @@
         <v>50</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:L43" si="107">I22/I8</f>
+        <f t="shared" ref="I43:L43" si="106">I22/I8</f>
         <v>0.18969555035128802</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0.12136929460580902</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0.158438576349024</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>0.13255567338282073</v>
       </c>
       <c r="M43" s="10">
@@ -5618,100 +5626,100 @@
         <v>0.15594541910331378</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" ref="N43:R43" si="108">N22/N8</f>
+        <f t="shared" ref="N43:R43" si="107">N22/N8</f>
         <v>0.17973568281938332</v>
       </c>
       <c r="O43" s="10">
+        <f t="shared" si="107"/>
+        <v>0.19000979431929474</v>
+      </c>
+      <c r="P43" s="10">
+        <f t="shared" si="107"/>
+        <v>0.19729729729729725</v>
+      </c>
+      <c r="Q43" s="10">
+        <f t="shared" si="107"/>
+        <v>0.18886198547215491</v>
+      </c>
+      <c r="R43" s="10">
+        <f t="shared" si="107"/>
+        <v>0.18848526387936926</v>
+      </c>
+      <c r="S43" s="10">
+        <f t="shared" ref="S43:V43" si="108">S22/S8</f>
+        <v>0.14856341976173784</v>
+      </c>
+      <c r="T43" s="10">
         <f t="shared" si="108"/>
-        <v>0.19000979431929474</v>
-      </c>
-      <c r="P43" s="10">
+        <v>0.1237762237762238</v>
+      </c>
+      <c r="U43" s="10">
         <f t="shared" si="108"/>
-        <v>0.19729729729729725</v>
-      </c>
-      <c r="Q43" s="10">
+        <v>0.14595660749506897</v>
+      </c>
+      <c r="V43" s="10">
         <f t="shared" si="108"/>
-        <v>0.18886198547215491</v>
-      </c>
-      <c r="R43" s="10">
-        <f t="shared" si="108"/>
-        <v>0.18848526387936926</v>
-      </c>
-      <c r="S43" s="10">
-        <f t="shared" ref="S43:V43" si="109">S22/S8</f>
-        <v>0.14856341976173784</v>
-      </c>
-      <c r="T43" s="10">
+        <v>0.16814390638615714</v>
+      </c>
+      <c r="X43" s="10">
+        <f t="shared" ref="X43:AL43" si="109">X22/X8</f>
+        <v>-2.4652087475149059E-2</v>
+      </c>
+      <c r="Y43" s="10">
         <f t="shared" si="109"/>
-        <v>0.1237762237762238</v>
-      </c>
-      <c r="U43" s="10">
+        <v>0.1224736048265459</v>
+      </c>
+      <c r="Z43" s="10">
         <f t="shared" si="109"/>
-        <v>0.17936941393306544</v>
-      </c>
-      <c r="V43" s="10">
+        <v>0.15773584905660362</v>
+      </c>
+      <c r="AA43" s="10">
         <f t="shared" si="109"/>
-        <v>0.18077396097008652</v>
-      </c>
-      <c r="X43" s="10">
-        <f t="shared" ref="X43:AL43" si="110">X22/X8</f>
-        <v>-2.4652087475149059E-2</v>
-      </c>
-      <c r="Y43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.1224736048265459</v>
-      </c>
-      <c r="Z43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.15773584905660362</v>
-      </c>
-      <c r="AA43" s="10">
-        <f t="shared" si="110"/>
         <v>0.19631393663284327</v>
       </c>
       <c r="AB43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.15870340776278877</v>
+        <f t="shared" si="109"/>
+        <v>0.1472345687263979</v>
       </c>
       <c r="AC43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.2282915245264267</v>
+        <f t="shared" si="109"/>
+        <v>0.22607195087661794</v>
       </c>
       <c r="AD43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.24722731025547004</v>
+        <f t="shared" si="109"/>
+        <v>0.24477920208038048</v>
       </c>
       <c r="AE43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.250309082279425</v>
+        <f t="shared" si="109"/>
+        <v>0.24770936651065451</v>
       </c>
       <c r="AF43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25184265823224006</v>
+        <f t="shared" si="109"/>
+        <v>0.24913747187728963</v>
       </c>
       <c r="AG43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25227690580022877</v>
+        <f t="shared" si="109"/>
+        <v>0.25063371987003447</v>
       </c>
       <c r="AH43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25382321064532459</v>
+        <f t="shared" si="109"/>
+        <v>0.25219613438111249</v>
       </c>
       <c r="AI43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25535435563899794</v>
+        <f t="shared" si="109"/>
+        <v>0.25374323110286628</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25687048940724305</v>
+        <f t="shared" si="109"/>
+        <v>0.25527516020970092</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.25837175911893678</v>
+        <f t="shared" si="109"/>
+        <v>0.25679207040372343</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="110"/>
-        <v>0.2598583105001237</v>
+        <f t="shared" si="109"/>
+        <v>0.2582941089291772</v>
       </c>
       <c r="AN43" t="s">
         <v>55</v>
@@ -5726,19 +5734,19 @@
         <v>42</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" ref="I44:L44" si="111">I28/I27</f>
+        <f t="shared" ref="I44:L44" si="110">I28/I27</f>
         <v>0.35616438356164393</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>-3.4825870646766191E-2</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>0.17741935483870977</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>7.4829931972789157E-2</v>
       </c>
       <c r="M44" s="10">
@@ -5746,107 +5754,107 @@
         <v>1.1764705882352946E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" ref="N44:R44" si="112">N28/N27</f>
+        <f t="shared" ref="N44:R44" si="111">N28/N27</f>
         <v>1.9178082191780819E-2</v>
       </c>
       <c r="O44" s="10">
+        <f t="shared" si="111"/>
+        <v>0.23711340206185574</v>
+      </c>
+      <c r="P44" s="10">
+        <f t="shared" si="111"/>
+        <v>0.12727272727272732</v>
+      </c>
+      <c r="Q44" s="10">
+        <f t="shared" si="111"/>
+        <v>0.20869565217391309</v>
+      </c>
+      <c r="R44" s="10">
+        <f t="shared" si="111"/>
+        <v>0.15634218289085558</v>
+      </c>
+      <c r="S44" s="10">
+        <f t="shared" ref="S44:V44" si="112">S28/S27</f>
+        <v>0.11904761904761911</v>
+      </c>
+      <c r="T44" s="10">
         <f t="shared" si="112"/>
-        <v>0.23711340206185574</v>
-      </c>
-      <c r="P44" s="10">
+        <v>0.12068965517241378</v>
+      </c>
+      <c r="U44" s="10">
         <f t="shared" si="112"/>
-        <v>0.12727272727272732</v>
-      </c>
-      <c r="Q44" s="10">
+        <v>0.17857142857142866</v>
+      </c>
+      <c r="V44" s="10">
         <f t="shared" si="112"/>
-        <v>0.20869565217391309</v>
-      </c>
-      <c r="R44" s="10">
-        <f t="shared" si="112"/>
-        <v>0.15634218289085558</v>
-      </c>
-      <c r="S44" s="10">
-        <f t="shared" ref="S44:V44" si="113">S28/S27</f>
-        <v>0.11904761904761911</v>
-      </c>
-      <c r="T44" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="X44" s="10">
+        <f t="shared" ref="X44:AL44" si="113">X28/X27</f>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="10">
         <f t="shared" si="113"/>
-        <v>0.12068965517241378</v>
-      </c>
-      <c r="U44" s="10">
+        <v>0.3682008368200842</v>
+      </c>
+      <c r="Z44" s="10">
+        <f t="shared" si="113"/>
+        <v>4.1927409261576995E-2</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="113"/>
+        <v>0.1734390485629336</v>
+      </c>
+      <c r="AB44" s="10">
+        <f t="shared" si="113"/>
+        <v>0.14405809356217275</v>
+      </c>
+      <c r="AC44" s="10">
         <f t="shared" si="113"/>
         <v>0.15</v>
       </c>
-      <c r="V44" s="10">
+      <c r="AD44" s="10">
         <f t="shared" si="113"/>
         <v>0.15</v>
       </c>
-      <c r="X44" s="10">
-        <f t="shared" ref="X44:AL44" si="114">X28/X27</f>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.3682008368200842</v>
-      </c>
-      <c r="Z44" s="10">
-        <f t="shared" si="114"/>
-        <v>4.1927409261576995E-2</v>
-      </c>
-      <c r="AA44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.1734390485629336</v>
-      </c>
-      <c r="AB44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.13774452835451287</v>
-      </c>
-      <c r="AC44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AD44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
-      </c>
       <c r="AE44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AF44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AG44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AH44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AI44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.14999999999999997</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AL44" s="10">
-        <f t="shared" si="114"/>
-        <v>0.14000000000000001</v>
+        <f t="shared" si="113"/>
+        <v>0.15</v>
       </c>
       <c r="AN44" t="s">
         <v>56</v>
       </c>
       <c r="AO44" s="3">
         <f>AO42+AO43</f>
-        <v>1796.3946495042082</v>
+        <v>1777.0819367687186</v>
       </c>
     </row>
     <row r="45" spans="2:41" x14ac:dyDescent="0.3">
@@ -5854,19 +5862,19 @@
         <v>51</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" ref="I45:L45" si="115">I29/I8</f>
+        <f t="shared" ref="I45:L45" si="114">I29/I8</f>
         <v>0.11007025761124117</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="114"/>
         <v>0.21576763485477166</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="114"/>
         <v>0.17566016073478749</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="114"/>
         <v>0.14422057264050897</v>
       </c>
       <c r="M45" s="10">
@@ -5874,107 +5882,107 @@
         <v>0.16374269005847947</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" ref="N45:R45" si="116">N29/N8</f>
+        <f t="shared" ref="N45:R45" si="115">N29/N8</f>
         <v>0.94625550660792968</v>
       </c>
       <c r="O45" s="10">
+        <f t="shared" si="115"/>
+        <v>0.1449559255631733</v>
+      </c>
+      <c r="P45" s="10">
+        <f t="shared" si="115"/>
+        <v>0.17297297297297293</v>
+      </c>
+      <c r="Q45" s="10">
+        <f t="shared" si="115"/>
+        <v>0.14689265536723159</v>
+      </c>
+      <c r="R45" s="10">
+        <f t="shared" si="115"/>
+        <v>0.19602467443454402</v>
+      </c>
+      <c r="S45" s="10">
+        <f t="shared" ref="S45:V45" si="116">S29/S8</f>
+        <v>0.12964260686755424</v>
+      </c>
+      <c r="T45" s="10">
         <f t="shared" si="116"/>
-        <v>0.1449559255631733</v>
-      </c>
-      <c r="P45" s="10">
+        <v>0.10699300699300701</v>
+      </c>
+      <c r="U45" s="10">
         <f t="shared" si="116"/>
-        <v>0.17297297297297293</v>
-      </c>
-      <c r="Q45" s="10">
+        <v>0.12097304404996705</v>
+      </c>
+      <c r="V45" s="10">
         <f t="shared" si="116"/>
-        <v>0.14689265536723159</v>
-      </c>
-      <c r="R45" s="10">
-        <f t="shared" si="116"/>
-        <v>0.19602467443454402</v>
-      </c>
-      <c r="S45" s="10">
-        <f t="shared" ref="S45:V45" si="117">S29/S8</f>
-        <v>0.12964260686755424</v>
-      </c>
-      <c r="T45" s="10">
+        <v>0.14133511763973611</v>
+      </c>
+      <c r="X45" s="10">
+        <f t="shared" ref="X45:AL45" si="117">X29/X8</f>
+        <v>-0.1709741550695825</v>
+      </c>
+      <c r="Y45" s="10">
         <f t="shared" si="117"/>
-        <v>0.10699300699300701</v>
-      </c>
-      <c r="U45" s="10">
+        <v>4.5550527903468974E-2</v>
+      </c>
+      <c r="Z45" s="10">
         <f t="shared" si="117"/>
-        <v>0.15822370694620436</v>
-      </c>
-      <c r="V45" s="10">
+        <v>0.38515723270440239</v>
+      </c>
+      <c r="AA45" s="10">
         <f t="shared" si="117"/>
-        <v>0.15918894824859928</v>
-      </c>
-      <c r="X45" s="10">
-        <f t="shared" ref="X45:AL45" si="118">X29/X8</f>
-        <v>-0.1709741550695825</v>
-      </c>
-      <c r="Y45" s="10">
-        <f t="shared" si="118"/>
-        <v>4.5550527903468974E-2</v>
-      </c>
-      <c r="Z45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.38515723270440239</v>
-      </c>
-      <c r="AA45" s="10">
-        <f t="shared" si="118"/>
         <v>0.17270656450610894</v>
       </c>
       <c r="AB45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.13904643294023028</v>
+        <f t="shared" si="117"/>
+        <v>0.12516609297196152</v>
       </c>
       <c r="AC45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.19868405810600243</v>
+        <f t="shared" si="117"/>
+        <v>0.19216115824512525</v>
       </c>
       <c r="AD45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.21478649472696695</v>
+        <f t="shared" si="117"/>
+        <v>0.2080623217683234</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.21735206061207016</v>
+        <f t="shared" si="117"/>
+        <v>0.21055296153405634</v>
       </c>
       <c r="AF45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.21862223290840904</v>
+        <f t="shared" si="117"/>
+        <v>0.21176685109569618</v>
       </c>
       <c r="AG45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.21896174169927041</v>
+        <f t="shared" si="117"/>
+        <v>0.21303866188952927</v>
       </c>
       <c r="AH45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.22027192070221874</v>
+        <f t="shared" si="117"/>
+        <v>0.21436671422394565</v>
       </c>
       <c r="AI45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.22156925481298137</v>
+        <f t="shared" si="117"/>
+        <v>0.21568174643743634</v>
       </c>
       <c r="AJ45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.2228538699618737</v>
+        <f t="shared" si="117"/>
+        <v>0.21698388617824579</v>
       </c>
       <c r="AK45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.22412589084460044</v>
+        <f t="shared" si="117"/>
+        <v>0.21827325984316492</v>
       </c>
       <c r="AL45" s="10">
-        <f t="shared" si="118"/>
-        <v>0.2253854409343593</v>
+        <f t="shared" si="117"/>
+        <v>0.2195499925898006</v>
       </c>
       <c r="AN45" t="s">
         <v>57</v>
       </c>
       <c r="AO45" s="2">
         <f>AO44/AL30</f>
-        <v>20.071448597812381</v>
+        <v>19.83350375857945</v>
       </c>
     </row>
     <row r="46" spans="2:41" x14ac:dyDescent="0.3">
@@ -5983,7 +5991,7 @@
       </c>
       <c r="AO46" s="2">
         <f>Main!D3</f>
-        <v>17.940000000000001</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="47" spans="2:41" x14ac:dyDescent="0.3">
@@ -5992,7 +6000,7 @@
       </c>
       <c r="AO47" s="9">
         <f>AO45/AO46-1</f>
-        <v>0.1188098438022509</v>
+        <v>0.47460994487579566</v>
       </c>
     </row>
     <row r="48" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6000,36 +6008,40 @@
         <v>45</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" ref="K48:R48" si="119">K27</f>
+        <f t="shared" ref="K48:R48" si="118">K27</f>
         <v>18.599999999999991</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>14.699999999999992</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>16.999999999999993</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>109.50000000000001</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>21.999999999999993</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>22.999999999999993</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>33.89999999999997</v>
+      </c>
+      <c r="U48" s="8">
+        <f t="shared" ref="U48" si="119">U27</f>
+        <v>22.399999999999988</v>
       </c>
       <c r="Z48" s="8">
         <f>Z27</f>
@@ -6041,56 +6053,56 @@
       </c>
       <c r="AB48" s="8">
         <f t="shared" ref="AB48:AL48" si="120">AB27</f>
-        <v>94.651599999999917</v>
+        <v>87.514000000000095</v>
       </c>
       <c r="AC48" s="8">
         <f t="shared" si="120"/>
-        <v>153.48676400000002</v>
+        <v>153.40907999999996</v>
       </c>
       <c r="AD48" s="8">
         <f t="shared" si="120"/>
-        <v>181.66063079200001</v>
+        <v>181.69084840000005</v>
       </c>
       <c r="AE48" s="8">
         <f t="shared" si="120"/>
-        <v>193.21198819032003</v>
+        <v>193.18287048240012</v>
       </c>
       <c r="AF48" s="8">
         <f t="shared" si="120"/>
-        <v>200.97624470114883</v>
+        <v>200.88414037786407</v>
       </c>
       <c r="AG48" s="8">
         <f t="shared" si="120"/>
-        <v>206.74546990507346</v>
+        <v>207.54566881775571</v>
       </c>
       <c r="AH48" s="8">
         <f t="shared" si="120"/>
-        <v>212.14220268360944</v>
+        <v>213.01626819700471</v>
       </c>
       <c r="AI48" s="8">
         <f t="shared" si="120"/>
-        <v>217.65948835152054</v>
+        <v>218.60947642386765</v>
       </c>
       <c r="AJ48" s="8">
         <f t="shared" si="120"/>
-        <v>223.29986414893219</v>
+        <v>224.32787764389707</v>
       </c>
       <c r="AK48" s="8">
         <f t="shared" si="120"/>
-        <v>229.0659193225959</v>
+        <v>230.1741090052426</v>
       </c>
       <c r="AL48" s="8">
         <f t="shared" si="120"/>
-        <v>234.96029617863974</v>
+        <v>236.15086173189974</v>
       </c>
       <c r="AN48" t="s">
         <v>60</v>
       </c>
       <c r="AO48" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="49" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>71</v>
       </c>
@@ -6117,6 +6129,9 @@
       </c>
       <c r="R49" s="3">
         <v>-1.5</v>
+      </c>
+      <c r="U49" s="3">
+        <v>-0.2</v>
       </c>
       <c r="Z49" s="3">
         <f>SUM(K49:N49)</f>
@@ -6160,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>72</v>
       </c>
@@ -6176,6 +6191,9 @@
       <c r="R50" s="3">
         <v>-5</v>
       </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
       <c r="Z50" s="3">
         <f t="shared" ref="Z50:Z61" si="121">SUM(K50:N50)</f>
         <v>-89.8</v>
@@ -6217,11 +6235,8 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
-      <c r="AO50" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="51" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>73</v>
       </c>
@@ -6237,6 +6252,9 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
       <c r="Z51" s="3">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -6279,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>74</v>
       </c>
@@ -6299,6 +6317,9 @@
       <c r="R52" s="3">
         <v>0.1</v>
       </c>
+      <c r="U52" s="3">
+        <v>0.2</v>
+      </c>
       <c r="Z52" s="3">
         <f t="shared" si="121"/>
         <v>0.7</v>
@@ -6341,7 +6362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>33</v>
       </c>
@@ -6368,6 +6389,9 @@
       </c>
       <c r="R53" s="3">
         <v>4.4000000000000004</v>
+      </c>
+      <c r="U53" s="3">
+        <v>4.9000000000000004</v>
       </c>
       <c r="Z53" s="3">
         <f t="shared" si="121"/>
@@ -6422,7 +6446,7 @@
         <v>19.396639210956582</v>
       </c>
     </row>
-    <row r="54" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>75</v>
       </c>
@@ -6449,6 +6473,9 @@
       </c>
       <c r="R54" s="3">
         <v>0.9</v>
+      </c>
+      <c r="U54" s="3">
+        <v>8.4</v>
       </c>
       <c r="Z54" s="3">
         <f t="shared" si="121"/>
@@ -6503,7 +6530,7 @@
         <v>0.7559142440960005</v>
       </c>
     </row>
-    <row r="55" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>76</v>
       </c>
@@ -6530,6 +6557,9 @@
       </c>
       <c r="R55" s="3">
         <v>-0.4</v>
+      </c>
+      <c r="U55" s="3">
+        <v>0.2</v>
       </c>
       <c r="Z55" s="3">
         <f t="shared" si="121"/>
@@ -6573,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>77</v>
       </c>
@@ -6600,6 +6630,9 @@
       </c>
       <c r="R56" s="3">
         <v>-18.2</v>
+      </c>
+      <c r="U56" s="3">
+        <v>-5.5</v>
       </c>
       <c r="Z56" s="3">
         <f t="shared" si="121"/>
@@ -6643,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>78</v>
       </c>
@@ -6670,6 +6703,9 @@
       </c>
       <c r="R57" s="3">
         <v>-3</v>
+      </c>
+      <c r="U57" s="3">
+        <v>-0.2</v>
       </c>
       <c r="Z57" s="3">
         <f t="shared" si="121"/>
@@ -6713,7 +6749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>79</v>
       </c>
@@ -6740,6 +6776,9 @@
       </c>
       <c r="R58" s="3">
         <v>11.6</v>
+      </c>
+      <c r="U58" s="3">
+        <v>-2.1</v>
       </c>
       <c r="Z58" s="3">
         <f t="shared" si="121"/>
@@ -6783,7 +6822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>80</v>
       </c>
@@ -6810,6 +6849,9 @@
       </c>
       <c r="R59" s="3">
         <v>2</v>
+      </c>
+      <c r="U59" s="3">
+        <v>-0.2</v>
       </c>
       <c r="Z59" s="3">
         <f t="shared" si="121"/>
@@ -6853,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>81</v>
       </c>
@@ -6880,6 +6922,9 @@
       </c>
       <c r="R60" s="3">
         <v>0.1</v>
+      </c>
+      <c r="U60" s="3">
+        <v>1.5</v>
       </c>
       <c r="Z60" s="3">
         <f t="shared" si="121"/>
@@ -6923,7 +6968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>42</v>
       </c>
@@ -6950,6 +6995,9 @@
       </c>
       <c r="R61" s="3">
         <v>-3.4</v>
+      </c>
+      <c r="U61" s="3">
+        <v>-0.9</v>
       </c>
       <c r="Z61" s="3">
         <f t="shared" si="121"/>
@@ -6993,7 +7041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>82</v>
       </c>
@@ -7029,6 +7077,10 @@
         <f t="shared" si="125"/>
         <v>21.499999999999972</v>
       </c>
+      <c r="U62" s="8">
+        <f t="shared" ref="U62" si="126">U48+SUM(U49:U61)</f>
+        <v>28.499999999999986</v>
+      </c>
       <c r="Z62" s="8">
         <f>Z48+SUM(Z49:Z61)</f>
         <v>82.29999999999994</v>
@@ -7038,51 +7090,51 @@
         <v>107.5</v>
       </c>
       <c r="AB62" s="8">
-        <f t="shared" ref="AB62:AL62" si="126">AB48+SUM(AB49:AB61)</f>
-        <v>117.60359999999991</v>
+        <f t="shared" ref="AB62:AL62" si="127">AB48+SUM(AB49:AB61)</f>
+        <v>110.46600000000009</v>
       </c>
       <c r="AC62" s="8">
-        <f t="shared" si="126"/>
-        <v>175.34900400000004</v>
+        <f t="shared" si="127"/>
+        <v>175.27131999999995</v>
       </c>
       <c r="AD62" s="8">
-        <f t="shared" si="126"/>
-        <v>202.72107559200001</v>
+        <f t="shared" si="127"/>
+        <v>202.75129320000005</v>
       </c>
       <c r="AE62" s="8">
-        <f t="shared" si="126"/>
-        <v>213.70240988632003</v>
+        <f t="shared" si="127"/>
+        <v>213.67329217840012</v>
       </c>
       <c r="AF62" s="8">
-        <f t="shared" si="126"/>
-        <v>221.08348923106882</v>
+        <f t="shared" si="127"/>
+        <v>220.99138490778407</v>
       </c>
       <c r="AG62" s="8">
-        <f t="shared" si="126"/>
-        <v>226.62047084559185</v>
+        <f t="shared" si="127"/>
+        <v>227.4206697582741</v>
       </c>
       <c r="AH62" s="8">
-        <f t="shared" si="126"/>
-        <v>231.9071928589382</v>
+        <f t="shared" si="127"/>
+        <v>232.78125837233347</v>
       </c>
       <c r="AI62" s="8">
-        <f t="shared" si="126"/>
-        <v>237.41376970315588</v>
+        <f t="shared" si="127"/>
+        <v>238.36375777550299</v>
       </c>
       <c r="AJ62" s="8">
-        <f t="shared" si="126"/>
-        <v>243.12442422584024</v>
+        <f t="shared" si="127"/>
+        <v>244.15243772080512</v>
       </c>
       <c r="AK62" s="8">
-        <f t="shared" si="126"/>
-        <v>249.02712507963412</v>
+        <f t="shared" si="127"/>
+        <v>250.13531476228081</v>
       </c>
       <c r="AL62" s="8">
-        <f t="shared" si="126"/>
-        <v>255.11284963369232</v>
+        <f t="shared" si="127"/>
+        <v>256.30341518695229</v>
       </c>
     </row>
-    <row r="63" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>83</v>
       </c>
@@ -7110,12 +7162,15 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
+      <c r="U63" s="3">
+        <v>3.2</v>
+      </c>
       <c r="Z63" s="3">
-        <f t="shared" ref="Z63:Z65" si="127">SUM(K63:N63)</f>
+        <f t="shared" ref="Z63:Z65" si="128">SUM(K63:N63)</f>
         <v>1.7999999999999998</v>
       </c>
       <c r="AA63" s="3">
-        <f t="shared" ref="AA63:AA65" si="128">SUM(O63:R63)</f>
+        <f t="shared" ref="AA63:AA65" si="129">SUM(O63:R63)</f>
         <v>23.2</v>
       </c>
       <c r="AB63" s="3">
@@ -7126,43 +7181,43 @@
         <v>5.15</v>
       </c>
       <c r="AD63" s="3">
-        <f t="shared" ref="AD63:AL63" si="129">AC63*1.03</f>
+        <f t="shared" ref="AD63:AL63" si="130">AC63*1.03</f>
         <v>5.3045000000000009</v>
       </c>
       <c r="AE63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>5.4636350000000009</v>
       </c>
       <c r="AF63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>5.6275440500000009</v>
       </c>
       <c r="AG63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>5.796370371500001</v>
       </c>
       <c r="AH63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>5.9702614826450011</v>
       </c>
       <c r="AI63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.1493693271243517</v>
       </c>
       <c r="AJ63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.3338504069380823</v>
       </c>
       <c r="AK63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.5238659191462247</v>
       </c>
       <c r="AL63" s="3">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.7195818967206113</v>
       </c>
     </row>
-    <row r="64" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>84</v>
       </c>
@@ -7190,12 +7245,15 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
       <c r="Z64" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.3</v>
       </c>
       <c r="AA64" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0</v>
       </c>
       <c r="AB64" s="3">
@@ -7260,12 +7318,15 @@
       <c r="R65" s="3">
         <v>1.9</v>
       </c>
+      <c r="U65" s="3">
+        <v>2.8</v>
+      </c>
       <c r="Z65" s="3">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>4.3</v>
       </c>
       <c r="AA65" s="3">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>7.2999999999999989</v>
       </c>
       <c r="AB65" s="3">
@@ -7277,7 +7338,7 @@
         <v>13.6875</v>
       </c>
       <c r="AD65" s="3">
-        <f t="shared" ref="AD65" si="130">AC65*1.2</f>
+        <f t="shared" ref="AD65" si="131">AC65*1.2</f>
         <v>16.425000000000001</v>
       </c>
       <c r="AE65" s="3">
@@ -7289,27 +7350,27 @@
         <v>18.970875000000003</v>
       </c>
       <c r="AG65" s="3">
-        <f t="shared" ref="AG65:AL65" si="131">AF65*1.05</f>
+        <f t="shared" ref="AG65:AL65" si="132">AF65*1.05</f>
         <v>19.919418750000006</v>
       </c>
       <c r="AH65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>20.915389687500006</v>
       </c>
       <c r="AI65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>21.961159171875007</v>
       </c>
       <c r="AJ65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>23.05921713046876</v>
       </c>
       <c r="AK65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>24.212177986992199</v>
       </c>
       <c r="AL65" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>25.422786886341811</v>
       </c>
     </row>
@@ -7318,36 +7379,40 @@
         <v>87</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" ref="K66:R66" si="132">SUM(K63:K65)</f>
+        <f t="shared" ref="K66:R66" si="133">SUM(K63:K65)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="L66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.2</v>
       </c>
       <c r="M66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.9</v>
       </c>
       <c r="N66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.9</v>
       </c>
       <c r="O66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>21.599999999999998</v>
       </c>
       <c r="P66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>2.9</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="R66" s="3">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.9</v>
+      </c>
+      <c r="U66" s="3">
+        <f t="shared" ref="U66" si="134">SUM(U63:U65)</f>
+        <v>6</v>
       </c>
       <c r="Z66" s="3">
         <f>SUM(Z63:Z65)</f>
@@ -7358,47 +7423,47 @@
         <v>30.5</v>
       </c>
       <c r="AB66" s="3">
-        <f t="shared" ref="AB66:AL66" si="133">SUM(AB63:AB65)</f>
+        <f t="shared" ref="AB66:AL66" si="135">SUM(AB63:AB65)</f>
         <v>15.95</v>
       </c>
       <c r="AC66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>18.837499999999999</v>
       </c>
       <c r="AD66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>21.729500000000002</v>
       </c>
       <c r="AE66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>23.531135000000003</v>
       </c>
       <c r="AF66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>24.598419050000004</v>
       </c>
       <c r="AG66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>25.715789121500006</v>
       </c>
       <c r="AH66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>26.885651170145007</v>
       </c>
       <c r="AI66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>28.110528498999358</v>
       </c>
       <c r="AJ66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>29.393067537406843</v>
       </c>
       <c r="AK66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>30.736043906138423</v>
       </c>
       <c r="AL66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="135"/>
         <v>32.142368783062423</v>
       </c>
     </row>
@@ -7407,36 +7472,40 @@
         <v>85</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" ref="K67:R67" si="134">K62-K66</f>
+        <f t="shared" ref="K67:R67" si="136">K62-K66</f>
         <v>24.099999999999994</v>
       </c>
       <c r="L67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>14.199999999999994</v>
       </c>
       <c r="M67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>14.199999999999994</v>
       </c>
       <c r="N67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>23.400000000000013</v>
       </c>
       <c r="O67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>9.399999999999995</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>14.399999999999993</v>
       </c>
       <c r="Q67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>30.999999999999993</v>
       </c>
       <c r="R67" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="136"/>
         <v>19.599999999999973</v>
+      </c>
+      <c r="U67" s="8">
+        <f t="shared" ref="U67" si="137">U62-U66</f>
+        <v>22.499999999999986</v>
       </c>
       <c r="Z67" s="8">
         <f>Z62-Z66</f>
@@ -7447,462 +7516,462 @@
         <v>77</v>
       </c>
       <c r="AB67" s="8">
-        <f t="shared" ref="AB67:AL67" si="135">AB62-AB66</f>
-        <v>101.65359999999991</v>
+        <f t="shared" ref="AB67:AL67" si="138">AB62-AB66</f>
+        <v>94.516000000000091</v>
       </c>
       <c r="AC67" s="8">
-        <f t="shared" si="135"/>
-        <v>156.51150400000003</v>
+        <f t="shared" si="138"/>
+        <v>156.43381999999994</v>
       </c>
       <c r="AD67" s="8">
-        <f t="shared" si="135"/>
-        <v>180.991575592</v>
+        <f t="shared" si="138"/>
+        <v>181.02179320000005</v>
       </c>
       <c r="AE67" s="8">
-        <f t="shared" si="135"/>
-        <v>190.17127488632002</v>
+        <f t="shared" si="138"/>
+        <v>190.14215717840011</v>
       </c>
       <c r="AF67" s="8">
-        <f t="shared" si="135"/>
-        <v>196.48507018106881</v>
+        <f t="shared" si="138"/>
+        <v>196.39296585778408</v>
       </c>
       <c r="AG67" s="8">
-        <f t="shared" si="135"/>
-        <v>200.90468172409186</v>
+        <f t="shared" si="138"/>
+        <v>201.70488063677411</v>
       </c>
       <c r="AH67" s="8">
-        <f t="shared" si="135"/>
-        <v>205.02154168879321</v>
+        <f t="shared" si="138"/>
+        <v>205.89560720218847</v>
       </c>
       <c r="AI67" s="8">
-        <f t="shared" si="135"/>
-        <v>209.30324120415651</v>
+        <f t="shared" si="138"/>
+        <v>210.25322927650365</v>
       </c>
       <c r="AJ67" s="8">
-        <f t="shared" si="135"/>
-        <v>213.73135668843341</v>
+        <f t="shared" si="138"/>
+        <v>214.75937018339829</v>
       </c>
       <c r="AK67" s="8">
-        <f t="shared" si="135"/>
-        <v>218.29108117349568</v>
+        <f t="shared" si="138"/>
+        <v>219.39927085614238</v>
       </c>
       <c r="AL67" s="8">
-        <f t="shared" si="135"/>
-        <v>222.97048085062988</v>
+        <f t="shared" si="138"/>
+        <v>224.16104640388988</v>
       </c>
       <c r="AM67" s="1">
         <f>AL67*(1+$AO$40)</f>
-        <v>220.74077604212357</v>
+        <v>221.91943593985098</v>
       </c>
       <c r="AN67" s="1">
-        <f t="shared" ref="AN67:CY67" si="136">AM67*(1+$AO$40)</f>
-        <v>218.53336828170234</v>
+        <f t="shared" ref="AN67:CY67" si="139">AM67*(1+$AO$40)</f>
+        <v>219.70024158045248</v>
       </c>
       <c r="AO67" s="1">
-        <f t="shared" si="136"/>
-        <v>216.34803459888531</v>
+        <f t="shared" si="139"/>
+        <v>217.50323916464797</v>
       </c>
       <c r="AP67" s="1">
-        <f t="shared" si="136"/>
-        <v>214.18455425289645</v>
+        <f t="shared" si="139"/>
+        <v>215.32820677300148</v>
       </c>
       <c r="AQ67" s="1">
-        <f t="shared" si="136"/>
-        <v>212.04270871036749</v>
+        <f t="shared" si="139"/>
+        <v>213.17492470527148</v>
       </c>
       <c r="AR67" s="1">
-        <f t="shared" si="136"/>
-        <v>209.92228162326381</v>
+        <f t="shared" si="139"/>
+        <v>211.04317545821877</v>
       </c>
       <c r="AS67" s="1">
-        <f t="shared" si="136"/>
-        <v>207.82305880703117</v>
+        <f t="shared" si="139"/>
+        <v>208.93274370363659</v>
       </c>
       <c r="AT67" s="1">
-        <f t="shared" si="136"/>
-        <v>205.74482821896086</v>
+        <f t="shared" si="139"/>
+        <v>206.84341626660023</v>
       </c>
       <c r="AU67" s="1">
-        <f t="shared" si="136"/>
-        <v>203.68737993677126</v>
+        <f t="shared" si="139"/>
+        <v>204.77498210393424</v>
       </c>
       <c r="AV67" s="1">
-        <f t="shared" si="136"/>
-        <v>201.65050613740354</v>
+        <f t="shared" si="139"/>
+        <v>202.7272322828949</v>
       </c>
       <c r="AW67" s="1">
-        <f t="shared" si="136"/>
-        <v>199.63400107602951</v>
+        <f t="shared" si="139"/>
+        <v>200.69995996006594</v>
       </c>
       <c r="AX67" s="1">
-        <f t="shared" si="136"/>
-        <v>197.63766106526921</v>
+        <f t="shared" si="139"/>
+        <v>198.69296036046526</v>
       </c>
       <c r="AY67" s="1">
-        <f t="shared" si="136"/>
-        <v>195.66128445461652</v>
+        <f t="shared" si="139"/>
+        <v>196.7060307568606</v>
       </c>
       <c r="AZ67" s="1">
-        <f t="shared" si="136"/>
-        <v>193.70467161007036</v>
+        <f t="shared" si="139"/>
+        <v>194.738970449292</v>
       </c>
       <c r="BA67" s="1">
-        <f t="shared" si="136"/>
-        <v>191.76762489396967</v>
+        <f t="shared" si="139"/>
+        <v>192.79158074479906</v>
       </c>
       <c r="BB67" s="1">
-        <f t="shared" si="136"/>
-        <v>189.84994864502997</v>
+        <f t="shared" si="139"/>
+        <v>190.86366493735107</v>
       </c>
       <c r="BC67" s="1">
-        <f t="shared" si="136"/>
-        <v>187.95144915857966</v>
+        <f t="shared" si="139"/>
+        <v>188.95502828797757</v>
       </c>
       <c r="BD67" s="1">
-        <f t="shared" si="136"/>
-        <v>186.07193466699385</v>
+        <f t="shared" si="139"/>
+        <v>187.06547800509779</v>
       </c>
       <c r="BE67" s="1">
-        <f t="shared" si="136"/>
-        <v>184.2112153203239</v>
+        <f t="shared" si="139"/>
+        <v>185.1948232250468</v>
       </c>
       <c r="BF67" s="1">
-        <f t="shared" si="136"/>
-        <v>182.36910316712067</v>
+        <f t="shared" si="139"/>
+        <v>183.34287499279634</v>
       </c>
       <c r="BG67" s="1">
-        <f t="shared" si="136"/>
-        <v>180.54541213544945</v>
+        <f t="shared" si="139"/>
+        <v>181.50944624286836</v>
       </c>
       <c r="BH67" s="1">
-        <f t="shared" si="136"/>
-        <v>178.73995801409495</v>
+        <f t="shared" si="139"/>
+        <v>179.69435178043969</v>
       </c>
       <c r="BI67" s="1">
-        <f t="shared" si="136"/>
-        <v>176.95255843395401</v>
+        <f t="shared" si="139"/>
+        <v>177.89740826263528</v>
       </c>
       <c r="BJ67" s="1">
-        <f t="shared" si="136"/>
-        <v>175.18303284961448</v>
+        <f t="shared" si="139"/>
+        <v>176.11843418000893</v>
       </c>
       <c r="BK67" s="1">
-        <f t="shared" si="136"/>
-        <v>173.43120252111834</v>
+        <f t="shared" si="139"/>
+        <v>174.35724983820884</v>
       </c>
       <c r="BL67" s="1">
-        <f t="shared" si="136"/>
-        <v>171.69689049590716</v>
+        <f t="shared" si="139"/>
+        <v>172.61367733982675</v>
       </c>
       <c r="BM67" s="1">
-        <f t="shared" si="136"/>
-        <v>169.97992159094809</v>
+        <f t="shared" si="139"/>
+        <v>170.88754056642847</v>
       </c>
       <c r="BN67" s="1">
-        <f t="shared" si="136"/>
-        <v>168.28012237503862</v>
+        <f t="shared" si="139"/>
+        <v>169.17866516076418</v>
       </c>
       <c r="BO67" s="1">
-        <f t="shared" si="136"/>
-        <v>166.59732115128824</v>
+        <f t="shared" si="139"/>
+        <v>167.48687850915653</v>
       </c>
       <c r="BP67" s="1">
-        <f t="shared" si="136"/>
-        <v>164.93134793977535</v>
+        <f t="shared" si="139"/>
+        <v>165.81200972406495</v>
       </c>
       <c r="BQ67" s="1">
-        <f t="shared" si="136"/>
-        <v>163.28203446037759</v>
+        <f t="shared" si="139"/>
+        <v>164.15388962682431</v>
       </c>
       <c r="BR67" s="1">
-        <f t="shared" si="136"/>
-        <v>161.64921411577382</v>
+        <f t="shared" si="139"/>
+        <v>162.51235073055605</v>
       </c>
       <c r="BS67" s="1">
-        <f t="shared" si="136"/>
-        <v>160.03272197461607</v>
+        <f t="shared" si="139"/>
+        <v>160.88722722325048</v>
       </c>
       <c r="BT67" s="1">
-        <f t="shared" si="136"/>
-        <v>158.4323947548699</v>
+        <f t="shared" si="139"/>
+        <v>159.27835495101797</v>
       </c>
       <c r="BU67" s="1">
-        <f t="shared" si="136"/>
-        <v>156.84807080732119</v>
+        <f t="shared" si="139"/>
+        <v>157.68557140150779</v>
       </c>
       <c r="BV67" s="1">
-        <f t="shared" si="136"/>
-        <v>155.27959009924797</v>
+        <f t="shared" si="139"/>
+        <v>156.10871568749272</v>
       </c>
       <c r="BW67" s="1">
-        <f t="shared" si="136"/>
-        <v>153.72679419825548</v>
+        <f t="shared" si="139"/>
+        <v>154.5476285306178</v>
       </c>
       <c r="BX67" s="1">
-        <f t="shared" si="136"/>
-        <v>152.18952625627293</v>
+        <f t="shared" si="139"/>
+        <v>153.00215224531163</v>
       </c>
       <c r="BY67" s="1">
-        <f t="shared" si="136"/>
-        <v>150.66763099371019</v>
+        <f t="shared" si="139"/>
+        <v>151.47213072285851</v>
       </c>
       <c r="BZ67" s="1">
-        <f t="shared" si="136"/>
-        <v>149.1609546837731</v>
+        <f t="shared" si="139"/>
+        <v>149.95740941562991</v>
       </c>
       <c r="CA67" s="1">
-        <f t="shared" si="136"/>
-        <v>147.66934513693536</v>
+        <f t="shared" si="139"/>
+        <v>148.45783532147362</v>
       </c>
       <c r="CB67" s="1">
-        <f t="shared" si="136"/>
-        <v>146.19265168556601</v>
+        <f t="shared" si="139"/>
+        <v>146.97325696825888</v>
       </c>
       <c r="CC67" s="1">
-        <f t="shared" si="136"/>
-        <v>144.73072516871034</v>
+        <f t="shared" si="139"/>
+        <v>145.5035243985763</v>
       </c>
       <c r="CD67" s="1">
-        <f t="shared" si="136"/>
-        <v>143.28341791702323</v>
+        <f t="shared" si="139"/>
+        <v>144.04848915459053</v>
       </c>
       <c r="CE67" s="1">
-        <f t="shared" si="136"/>
-        <v>141.85058373785299</v>
+        <f t="shared" si="139"/>
+        <v>142.60800426304462</v>
       </c>
       <c r="CF67" s="1">
-        <f t="shared" si="136"/>
-        <v>140.43207790047447</v>
+        <f t="shared" si="139"/>
+        <v>141.18192422041417</v>
       </c>
       <c r="CG67" s="1">
-        <f t="shared" si="136"/>
-        <v>139.02775712146973</v>
+        <f t="shared" si="139"/>
+        <v>139.77010497821004</v>
       </c>
       <c r="CH67" s="1">
-        <f t="shared" si="136"/>
-        <v>137.63747955025502</v>
+        <f t="shared" si="139"/>
+        <v>138.37240392842793</v>
       </c>
       <c r="CI67" s="1">
-        <f t="shared" si="136"/>
-        <v>136.26110475475247</v>
+        <f t="shared" si="139"/>
+        <v>136.98867988914364</v>
       </c>
       <c r="CJ67" s="1">
-        <f t="shared" si="136"/>
-        <v>134.89849370720495</v>
+        <f t="shared" si="139"/>
+        <v>135.61879309025221</v>
       </c>
       <c r="CK67" s="1">
-        <f t="shared" si="136"/>
-        <v>133.54950877013289</v>
+        <f t="shared" si="139"/>
+        <v>134.26260515934968</v>
       </c>
       <c r="CL67" s="1">
-        <f t="shared" si="136"/>
-        <v>132.21401368243156</v>
+        <f t="shared" si="139"/>
+        <v>132.91997910775618</v>
       </c>
       <c r="CM67" s="1">
-        <f t="shared" si="136"/>
-        <v>130.89187354560724</v>
+        <f t="shared" si="139"/>
+        <v>131.59077931667861</v>
       </c>
       <c r="CN67" s="1">
-        <f t="shared" si="136"/>
-        <v>129.58295481015116</v>
+        <f t="shared" si="139"/>
+        <v>130.27487152351182</v>
       </c>
       <c r="CO67" s="1">
-        <f t="shared" si="136"/>
-        <v>128.28712526204964</v>
+        <f t="shared" si="139"/>
+        <v>128.97212280827671</v>
       </c>
       <c r="CP67" s="1">
-        <f t="shared" si="136"/>
-        <v>127.00425400942915</v>
+        <f t="shared" si="139"/>
+        <v>127.68240158019394</v>
       </c>
       <c r="CQ67" s="1">
-        <f t="shared" si="136"/>
-        <v>125.73421146933485</v>
+        <f t="shared" si="139"/>
+        <v>126.405577564392</v>
       </c>
       <c r="CR67" s="1">
-        <f t="shared" si="136"/>
-        <v>124.47686935464151</v>
+        <f t="shared" si="139"/>
+        <v>125.14152178874808</v>
       </c>
       <c r="CS67" s="1">
-        <f t="shared" si="136"/>
-        <v>123.23210066109509</v>
+        <f t="shared" si="139"/>
+        <v>123.8901065708606</v>
       </c>
       <c r="CT67" s="1">
-        <f t="shared" si="136"/>
-        <v>121.99977965448414</v>
+        <f t="shared" si="139"/>
+        <v>122.65120550515199</v>
       </c>
       <c r="CU67" s="1">
-        <f t="shared" si="136"/>
-        <v>120.7797818579393</v>
+        <f t="shared" si="139"/>
+        <v>121.42469345010048</v>
       </c>
       <c r="CV67" s="1">
-        <f t="shared" si="136"/>
-        <v>119.5719840393599</v>
+        <f t="shared" si="139"/>
+        <v>120.21044651559947</v>
       </c>
       <c r="CW67" s="1">
-        <f t="shared" si="136"/>
-        <v>118.37626419896631</v>
+        <f t="shared" si="139"/>
+        <v>119.00834205044347</v>
       </c>
       <c r="CX67" s="1">
-        <f t="shared" si="136"/>
-        <v>117.19250155697665</v>
+        <f t="shared" si="139"/>
+        <v>117.81825862993904</v>
       </c>
       <c r="CY67" s="1">
-        <f t="shared" si="136"/>
-        <v>116.02057654140688</v>
+        <f t="shared" si="139"/>
+        <v>116.64007604363965</v>
       </c>
       <c r="CZ67" s="1">
-        <f t="shared" ref="CZ67:EJ67" si="137">CY67*(1+$AO$40)</f>
-        <v>114.86037077599281</v>
+        <f t="shared" ref="CZ67:EJ67" si="140">CY67*(1+$AO$40)</f>
+        <v>115.47367528320325</v>
       </c>
       <c r="DA67" s="1">
-        <f t="shared" si="137"/>
-        <v>113.71176706823287</v>
+        <f t="shared" si="140"/>
+        <v>114.31893853037121</v>
       </c>
       <c r="DB67" s="1">
-        <f t="shared" si="137"/>
-        <v>112.57464939755054</v>
+        <f t="shared" si="140"/>
+        <v>113.1757491450675</v>
       </c>
       <c r="DC67" s="1">
-        <f t="shared" si="137"/>
-        <v>111.44890290357503</v>
+        <f t="shared" si="140"/>
+        <v>112.04399165361683</v>
       </c>
       <c r="DD67" s="1">
-        <f t="shared" si="137"/>
-        <v>110.33441387453928</v>
+        <f t="shared" si="140"/>
+        <v>110.92355173708066</v>
       </c>
       <c r="DE67" s="1">
-        <f t="shared" si="137"/>
-        <v>109.23106973579388</v>
+        <f t="shared" si="140"/>
+        <v>109.81431621970985</v>
       </c>
       <c r="DF67" s="1">
-        <f t="shared" si="137"/>
-        <v>108.13875903843594</v>
+        <f t="shared" si="140"/>
+        <v>108.71617305751275</v>
       </c>
       <c r="DG67" s="1">
-        <f t="shared" si="137"/>
-        <v>107.05737144805157</v>
+        <f t="shared" si="140"/>
+        <v>107.62901132693761</v>
       </c>
       <c r="DH67" s="1">
-        <f t="shared" si="137"/>
-        <v>105.98679773357105</v>
+        <f t="shared" si="140"/>
+        <v>106.55272121366824</v>
       </c>
       <c r="DI67" s="1">
-        <f t="shared" si="137"/>
-        <v>104.92692975623534</v>
+        <f t="shared" si="140"/>
+        <v>105.48719400153155</v>
       </c>
       <c r="DJ67" s="1">
-        <f t="shared" si="137"/>
-        <v>103.87766045867298</v>
+        <f t="shared" si="140"/>
+        <v>104.43232206151623</v>
       </c>
       <c r="DK67" s="1">
-        <f t="shared" si="137"/>
-        <v>102.83888385408625</v>
+        <f t="shared" si="140"/>
+        <v>103.38799884090106</v>
       </c>
       <c r="DL67" s="1">
-        <f t="shared" si="137"/>
-        <v>101.81049501554538</v>
+        <f t="shared" si="140"/>
+        <v>102.35411885249205</v>
       </c>
       <c r="DM67" s="1">
-        <f t="shared" si="137"/>
-        <v>100.79239006538992</v>
+        <f t="shared" si="140"/>
+        <v>101.33057766396713</v>
       </c>
       <c r="DN67" s="1">
-        <f t="shared" si="137"/>
-        <v>99.784466164736017</v>
+        <f t="shared" si="140"/>
+        <v>100.31727188732746</v>
       </c>
       <c r="DO67" s="1">
-        <f t="shared" si="137"/>
-        <v>98.786621503088654</v>
+        <f t="shared" si="140"/>
+        <v>99.314099168454192</v>
       </c>
       <c r="DP67" s="1">
-        <f t="shared" si="137"/>
-        <v>97.798755288057762</v>
+        <f t="shared" si="140"/>
+        <v>98.320958176769651</v>
       </c>
       <c r="DQ67" s="1">
-        <f t="shared" si="137"/>
-        <v>96.820767735177185</v>
+        <f t="shared" si="140"/>
+        <v>97.337748595001955</v>
       </c>
       <c r="DR67" s="1">
-        <f t="shared" si="137"/>
-        <v>95.852560057825414</v>
+        <f t="shared" si="140"/>
+        <v>96.36437110905193</v>
       </c>
       <c r="DS67" s="1">
-        <f t="shared" si="137"/>
-        <v>94.894034457247159</v>
+        <f t="shared" si="140"/>
+        <v>95.400727397961404</v>
       </c>
       <c r="DT67" s="1">
-        <f t="shared" si="137"/>
-        <v>93.945094112674681</v>
+        <f t="shared" si="140"/>
+        <v>94.446720123981791</v>
       </c>
       <c r="DU67" s="1">
-        <f t="shared" si="137"/>
-        <v>93.005643171547931</v>
+        <f t="shared" si="140"/>
+        <v>93.502252922741974</v>
       </c>
       <c r="DV67" s="1">
-        <f t="shared" si="137"/>
-        <v>92.075586739832445</v>
+        <f t="shared" si="140"/>
+        <v>92.567230393514549</v>
       </c>
       <c r="DW67" s="1">
-        <f t="shared" si="137"/>
-        <v>91.154830872434118</v>
+        <f t="shared" si="140"/>
+        <v>91.641558089579405</v>
       </c>
       <c r="DX67" s="1">
-        <f t="shared" si="137"/>
-        <v>90.243282563709769</v>
+        <f t="shared" si="140"/>
+        <v>90.725142508683604</v>
       </c>
       <c r="DY67" s="1">
-        <f t="shared" si="137"/>
-        <v>89.340849738072677</v>
+        <f t="shared" si="140"/>
+        <v>89.817891083596763</v>
       </c>
       <c r="DZ67" s="1">
-        <f t="shared" si="137"/>
-        <v>88.447441240691944</v>
+        <f t="shared" si="140"/>
+        <v>88.919712172760796</v>
       </c>
       <c r="EA67" s="1">
-        <f t="shared" si="137"/>
-        <v>87.562966828285028</v>
+        <f t="shared" si="140"/>
+        <v>88.030515051033191</v>
       </c>
       <c r="EB67" s="1">
-        <f t="shared" si="137"/>
-        <v>86.687337160002173</v>
+        <f t="shared" si="140"/>
+        <v>87.150209900522853</v>
       </c>
       <c r="EC67" s="1">
-        <f t="shared" si="137"/>
-        <v>85.820463788402151</v>
+        <f t="shared" si="140"/>
+        <v>86.278707801517626</v>
       </c>
       <c r="ED67" s="1">
-        <f t="shared" si="137"/>
-        <v>84.962259150518122</v>
+        <f t="shared" si="140"/>
+        <v>85.415920723502452</v>
       </c>
       <c r="EE67" s="1">
-        <f t="shared" si="137"/>
-        <v>84.112636559012941</v>
+        <f t="shared" si="140"/>
+        <v>84.561761516267424</v>
       </c>
       <c r="EF67" s="1">
-        <f t="shared" si="137"/>
-        <v>83.271510193422813</v>
+        <f t="shared" si="140"/>
+        <v>83.716143901104743</v>
       </c>
       <c r="EG67" s="1">
-        <f t="shared" si="137"/>
-        <v>82.438795091488586</v>
+        <f t="shared" si="140"/>
+        <v>82.878982462093688</v>
       </c>
       <c r="EH67" s="1">
-        <f t="shared" si="137"/>
-        <v>81.614407140573704</v>
+        <f t="shared" si="140"/>
+        <v>82.050192637472747</v>
       </c>
       <c r="EI67" s="1">
-        <f t="shared" si="137"/>
-        <v>80.798263069167959</v>
+        <f t="shared" si="140"/>
+        <v>81.229690711098016</v>
       </c>
       <c r="EJ67" s="1">
-        <f t="shared" si="137"/>
-        <v>79.990280438476276</v>
+        <f t="shared" si="140"/>
+        <v>80.417393803987039</v>
       </c>
     </row>
     <row r="70" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO70" s="3">
         <f>NPV(AO41,AB67:EJ67)</f>
-        <v>1882.1755249623011</v>
+        <v>1881.9476353380076</v>
       </c>
     </row>
     <row r="71" spans="2:140" x14ac:dyDescent="0.3">
@@ -7914,25 +7983,25 @@
     <row r="72" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO72" s="3">
         <f>AO70+AO71</f>
-        <v>2010.1755249623011</v>
+        <v>2009.9476353380076</v>
       </c>
     </row>
     <row r="73" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO73" s="2">
         <f>AO72/AL30</f>
-        <v>22.460061731422357</v>
+        <v>22.432451287254551</v>
       </c>
     </row>
     <row r="74" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO74" s="2">
         <f>Main!D3</f>
-        <v>17.940000000000001</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="75" spans="2:140" x14ac:dyDescent="0.3">
       <c r="AO75" s="9">
         <f>AO73/AO74-1</f>
-        <v>0.25195438859656383</v>
+        <v>0.6678402444055429</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/OPRA.xlsx
+++ b/Financial Analysis/OPRA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14334821-BB23-40AC-810C-C13806BAF574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FE8011-E1E9-4A6C-870E-C9ADA188D229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7403A8AC-99CC-4876-8521-54E7E6C7B5A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="AG8" authorId="0" shapeId="0" xr:uid="{6BB7C260-325B-4947-8EAD-A7C27C790BE6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+(Q425) 720-735m FY26 guidance</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH18" authorId="0" shapeId="0" xr:uid="{C764A576-1988-43EC-AB41-251AD31D56E7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+refine with proper forecast for then accurate and main FCF DCF value</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
   <si>
     <t>OPRA</t>
   </si>
@@ -316,7 +374,19 @@
     <t>look at competitors, MAU, etc.</t>
   </si>
   <si>
-    <t>Undervalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Heavily undervalued</t>
   </si>
 </sst>
 </file>
@@ -326,7 +396,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,6 +425,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,14 +502,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -443,7 +526,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13807440" y="0"/>
+          <a:off x="14424660" y="0"/>
           <a:ext cx="0" cy="13822680"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -469,16 +552,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -493,8 +576,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15034260" y="22860"/>
-          <a:ext cx="0" cy="12336780"/>
+          <a:off x="20505420" y="0"/>
+          <a:ext cx="0" cy="13251180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -843,17 +926,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>13.45</v>
+        <v>14.31</v>
       </c>
       <c r="E3" s="5">
-        <v>46052</v>
+        <v>46079</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="G3" s="5">
-        <v>46079</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
@@ -861,11 +944,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>89.6</f>
         <v>89.6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -874,7 +956,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>1205.1199999999999</v>
+        <v>1282.1759999999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -886,7 +968,7 @@
         <v>128</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -897,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -915,7 +997,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>1077.1199999999999</v>
+        <v>1154.1759999999999</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -929,17 +1011,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB86974-423B-4A8A-B377-188B73E3D0FA}">
-  <dimension ref="B2:EN75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB86974-423B-4A8A-B377-188B73E3D0FA}">
+  <dimension ref="B2:ER75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.21875" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="40" max="40" width="12" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="44" max="44" width="12" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:42" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>88</v>
       </c>
@@ -1000,53 +1082,65 @@
       <c r="V2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="X2">
+      <c r="W2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2">
         <v>2021</v>
       </c>
-      <c r="Y2">
+      <c r="AC2">
         <v>2022</v>
       </c>
-      <c r="Z2">
+      <c r="AD2">
         <v>2023</v>
       </c>
-      <c r="AA2">
+      <c r="AE2">
         <v>2024</v>
       </c>
-      <c r="AB2">
+      <c r="AF2">
         <v>2025</v>
       </c>
-      <c r="AC2">
+      <c r="AG2">
         <v>2026</v>
       </c>
-      <c r="AD2">
+      <c r="AH2">
         <v>2027</v>
       </c>
-      <c r="AE2">
+      <c r="AI2">
         <v>2028</v>
       </c>
-      <c r="AF2">
+      <c r="AJ2">
         <v>2029</v>
       </c>
-      <c r="AG2">
+      <c r="AK2">
         <v>2030</v>
       </c>
-      <c r="AH2">
+      <c r="AL2">
         <v>2031</v>
       </c>
-      <c r="AI2">
+      <c r="AM2">
         <v>2032</v>
       </c>
-      <c r="AJ2">
+      <c r="AN2">
         <v>2033</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <v>2034</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>68</v>
       </c>
@@ -1108,71 +1202,86 @@
         <v>95.9</v>
       </c>
       <c r="V3" s="11">
-        <f>R3*1.1</f>
-        <v>102.63000000000001</v>
-      </c>
-      <c r="X3" s="3">
+        <v>114.4</v>
+      </c>
+      <c r="W3" s="11">
+        <f>W8*0.67</f>
+        <v>113.9</v>
+      </c>
+      <c r="X3" s="11">
+        <f t="shared" ref="X3:Z3" si="0">X8*0.67</f>
+        <v>114.97200000000001</v>
+      </c>
+      <c r="Y3" s="11">
+        <f t="shared" si="0"/>
+        <v>117.19305</v>
+      </c>
+      <c r="Z3" s="11">
+        <f t="shared" si="0"/>
+        <v>124.23810000000002</v>
+      </c>
+      <c r="AB3" s="3">
         <f>SUM(C3:F3)</f>
         <v>127.2</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="AC3" s="3">
         <f>SUM(G3:J3)</f>
         <v>187.5</v>
       </c>
-      <c r="Z3" s="3">
-        <f t="shared" ref="Z3:Z5" si="0">SUM(K3:N3)</f>
+      <c r="AD3" s="3">
+        <f t="shared" ref="AD3:AD5" si="1">SUM(K3:N3)</f>
         <v>230.89999999999998</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AE3" s="3">
         <f>SUM(O3:R3)</f>
         <v>293.3</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AF3" s="3">
         <f>SUM(S3:V3)</f>
-        <v>387.03</v>
-      </c>
-      <c r="AC3" s="3">
-        <f>AB3*1.18</f>
-        <v>456.69539999999995</v>
-      </c>
-      <c r="AD3" s="3">
-        <f>AC3*1.12</f>
-        <v>511.49884800000001</v>
-      </c>
-      <c r="AE3" s="3">
-        <f>AD3*1.06</f>
-        <v>542.18877888000009</v>
-      </c>
-      <c r="AF3" s="3">
-        <f>AE3*1.04</f>
-        <v>563.87633003520011</v>
+        <v>398.79999999999995</v>
       </c>
       <c r="AG3" s="3">
-        <f>AF3*1.03</f>
-        <v>580.79261993625619</v>
+        <f>SUM(W3:Z3)</f>
+        <v>470.30315000000007</v>
       </c>
       <c r="AH3" s="3">
-        <f>AG3*1.02</f>
-        <v>592.4084723349813</v>
+        <f>AG3*1.14</f>
+        <v>536.14559100000008</v>
       </c>
       <c r="AI3" s="3">
-        <f t="shared" ref="AI3:AL4" si="1">AH3*1.02</f>
-        <v>604.25664178168097</v>
+        <f>AH3*1.07</f>
+        <v>573.67578237000009</v>
       </c>
       <c r="AJ3" s="3">
-        <f t="shared" si="1"/>
-        <v>616.34177461731463</v>
+        <f>AI3*1.04</f>
+        <v>596.62281366480011</v>
       </c>
       <c r="AK3" s="3">
-        <f t="shared" si="1"/>
-        <v>628.6686101096609</v>
+        <f>AJ3*1.03</f>
+        <v>614.52149807474416</v>
       </c>
       <c r="AL3" s="3">
-        <f t="shared" si="1"/>
-        <v>641.24198231185414</v>
+        <f>AK3*1.02</f>
+        <v>626.81192803623901</v>
+      </c>
+      <c r="AM3" s="3">
+        <f t="shared" ref="AM3:AP4" si="2">AL3*1.02</f>
+        <v>639.34816659696378</v>
+      </c>
+      <c r="AN3" s="3">
+        <f t="shared" si="2"/>
+        <v>652.1351299289031</v>
+      </c>
+      <c r="AO3" s="3">
+        <f t="shared" si="2"/>
+        <v>665.1778325274812</v>
+      </c>
+      <c r="AP3" s="3">
+        <f t="shared" si="2"/>
+        <v>678.48138917803078</v>
       </c>
     </row>
-    <row r="4" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>69</v>
       </c>
@@ -1234,71 +1343,86 @@
         <v>55.6</v>
       </c>
       <c r="V4" s="11">
-        <f>R4*1.1</f>
-        <v>57.53</v>
-      </c>
-      <c r="X4" s="3">
+        <v>62.3</v>
+      </c>
+      <c r="W4" s="11">
+        <f>W8*0.325</f>
+        <v>55.25</v>
+      </c>
+      <c r="X4" s="11">
+        <f t="shared" ref="X4:Z4" si="3">X8*0.325</f>
+        <v>55.77</v>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" si="3"/>
+        <v>56.847375</v>
+      </c>
+      <c r="Z4" s="11">
+        <f t="shared" si="3"/>
+        <v>60.264750000000006</v>
+      </c>
+      <c r="AB4" s="3">
         <f>SUM(C4:F4)</f>
         <v>118.7</v>
       </c>
-      <c r="Y4" s="3">
-        <f t="shared" ref="Y4:Y5" si="2">SUM(G4:J4)</f>
+      <c r="AC4" s="3">
+        <f t="shared" ref="AC4:AC5" si="4">SUM(G4:J4)</f>
         <v>140.1</v>
       </c>
-      <c r="Z4" s="3">
-        <f t="shared" si="0"/>
+      <c r="AD4" s="3">
+        <f t="shared" si="1"/>
         <v>162.19999999999999</v>
       </c>
-      <c r="AA4" s="3">
-        <f t="shared" ref="AA4:AA5" si="3">SUM(O4:R4)</f>
+      <c r="AE4" s="3">
+        <f t="shared" ref="AE4:AE5" si="5">SUM(O4:R4)</f>
         <v>186.2</v>
       </c>
-      <c r="AB4" s="3">
-        <f t="shared" ref="AB4:AB5" si="4">SUM(S4:V4)</f>
-        <v>209.33</v>
-      </c>
-      <c r="AC4" s="3">
-        <f>AB4*1.06</f>
-        <v>221.88980000000004</v>
-      </c>
-      <c r="AD4" s="3">
-        <f>AC4*1.04</f>
-        <v>230.76539200000005</v>
-      </c>
-      <c r="AE4" s="3">
-        <f>AD4*1.03</f>
-        <v>237.68835376000007</v>
-      </c>
       <c r="AF4" s="3">
-        <f>AE4*1.02</f>
-        <v>242.44212083520009</v>
+        <f t="shared" ref="AF4:AF5" si="6">SUM(S4:V4)</f>
+        <v>214.10000000000002</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" ref="AG4:AH4" si="5">AF4*1.02</f>
-        <v>247.29096325190409</v>
+        <f>SUM(W4:Z4)</f>
+        <v>228.13212500000003</v>
       </c>
       <c r="AH4" s="3">
-        <f t="shared" si="5"/>
-        <v>252.23678251694218</v>
+        <f>AG4*1.04</f>
+        <v>237.25741000000005</v>
       </c>
       <c r="AI4" s="3">
-        <f t="shared" si="1"/>
-        <v>257.28151816728104</v>
+        <f>AH4*1.03</f>
+        <v>244.37513230000005</v>
       </c>
       <c r="AJ4" s="3">
-        <f t="shared" si="1"/>
-        <v>262.42714853062665</v>
+        <f>AI4*1.02</f>
+        <v>249.26263494600005</v>
       </c>
       <c r="AK4" s="3">
-        <f t="shared" si="1"/>
-        <v>267.67569150123921</v>
+        <f t="shared" ref="AK4:AL4" si="7">AJ4*1.02</f>
+        <v>254.24788764492004</v>
       </c>
       <c r="AL4" s="3">
-        <f t="shared" si="1"/>
-        <v>273.029205331264</v>
+        <f t="shared" si="7"/>
+        <v>259.33284539781846</v>
+      </c>
+      <c r="AM4" s="3">
+        <f t="shared" si="2"/>
+        <v>264.51950230577484</v>
+      </c>
+      <c r="AN4" s="3">
+        <f t="shared" si="2"/>
+        <v>269.80989235189031</v>
+      </c>
+      <c r="AO4" s="3">
+        <f t="shared" si="2"/>
+        <v>275.20609019892811</v>
+      </c>
+      <c r="AP4" s="3">
+        <f t="shared" si="2"/>
+        <v>280.7102120029067</v>
       </c>
     </row>
-    <row r="5" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>70</v>
       </c>
@@ -1362,107 +1486,133 @@
       <c r="V5" s="11">
         <v>0.5</v>
       </c>
-      <c r="X5" s="3">
+      <c r="W5" s="11">
+        <f>W8*0.005</f>
+        <v>0.85</v>
+      </c>
+      <c r="X5" s="11">
+        <f t="shared" ref="X5:Z5" si="8">X8*0.005</f>
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="8"/>
+        <v>0.87457499999999999</v>
+      </c>
+      <c r="Z5" s="11">
+        <f t="shared" si="8"/>
+        <v>0.92715000000000003</v>
+      </c>
+      <c r="AB5" s="3">
         <f>SUM(C5:F5)</f>
         <v>5</v>
       </c>
-      <c r="Y5" s="3">
-        <f t="shared" si="2"/>
+      <c r="AC5" s="3">
+        <f t="shared" si="4"/>
         <v>3.4000000000000004</v>
       </c>
-      <c r="Z5" s="3">
-        <f t="shared" si="0"/>
+      <c r="AD5" s="3">
+        <f t="shared" si="1"/>
         <v>3.7</v>
       </c>
-      <c r="AA5" s="3">
-        <f t="shared" si="3"/>
+      <c r="AE5" s="3">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AB5" s="3">
-        <f t="shared" si="4"/>
+      <c r="AF5" s="3">
+        <f t="shared" si="6"/>
         <v>1.9</v>
       </c>
-      <c r="AC5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="3">
-        <v>0</v>
-      </c>
       <c r="AG5" s="3">
-        <v>0</v>
+        <f>SUM(W5:Z5)</f>
+        <v>3.509725</v>
       </c>
       <c r="AH5" s="3">
-        <v>0</v>
+        <f>AG5*1.2</f>
+        <v>4.2116699999999998</v>
       </c>
       <c r="AI5" s="3">
-        <v>0</v>
+        <f t="shared" ref="AI5:AP5" si="9">AH5*1.2</f>
+        <v>5.0540039999999999</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>6.0648048000000001</v>
       </c>
       <c r="AK5" s="3">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>7.2777657599999994</v>
       </c>
       <c r="AL5" s="3">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>8.7333189119999997</v>
+      </c>
+      <c r="AM5" s="3">
+        <f t="shared" si="9"/>
+        <v>10.479982694399999</v>
+      </c>
+      <c r="AN5" s="3">
+        <f t="shared" si="9"/>
+        <v>12.575979233279998</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="9"/>
+        <v>15.091175079935997</v>
+      </c>
+      <c r="AP5" s="3">
+        <f t="shared" si="9"/>
+        <v>18.109410095923195</v>
       </c>
     </row>
-    <row r="6" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" ref="F6" si="6">SUM(F3:F5)</f>
+        <f t="shared" ref="F6" si="10">SUM(F3:F5)</f>
         <v>72.7</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" ref="G6" si="7">SUM(G3:G5)</f>
+        <f t="shared" ref="G6" si="11">SUM(G3:G5)</f>
         <v>71.599999999999994</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" ref="H6" si="8">SUM(H3:H5)</f>
+        <f t="shared" ref="H6" si="12">SUM(H3:H5)</f>
         <v>77.800000000000011</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:Q6" si="9">SUM(I3:I5)</f>
+        <f t="shared" ref="I6:Q6" si="13">SUM(I3:I5)</f>
         <v>85.3</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>96.3</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>87</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>94.199999999999989</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>102.6</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>113</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>101.8</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>109.69999999999999</v>
       </c>
       <c r="Q6" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>123.19999999999999</v>
       </c>
       <c r="R6" s="3">
@@ -1470,81 +1620,97 @@
         <v>145.79999999999998</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" ref="S6:V6" si="10">SUM(S3:S5)</f>
+        <f t="shared" ref="S6:W6" si="14">SUM(S3:S5)</f>
         <v>142.69999999999999</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>143</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>151.9</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" si="10"/>
-        <v>160.66000000000003</v>
+        <f t="shared" si="14"/>
+        <v>177.2</v>
+      </c>
+      <c r="W6" s="3">
+        <f t="shared" si="14"/>
+        <v>170</v>
       </c>
       <c r="X6" s="3">
+        <f t="shared" ref="X6:Z6" si="15">SUM(X3:X5)</f>
+        <v>171.60000000000002</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="15"/>
+        <v>174.91499999999999</v>
+      </c>
+      <c r="Z6" s="3">
+        <f t="shared" si="15"/>
+        <v>185.43000000000004</v>
+      </c>
+      <c r="AB6" s="3">
         <v>251</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AC6" s="3">
         <v>331</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="AD6" s="3">
         <f>SUM(K6:N6)</f>
         <v>396.79999999999995</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AE6" s="3">
         <f>SUM(O6:R6)</f>
         <v>480.5</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AF6" s="3">
         <f>SUM(S6:V6)</f>
-        <v>598.26</v>
-      </c>
-      <c r="AC6" s="3">
-        <f>SUM(AC3:AC5)</f>
-        <v>678.58519999999999</v>
-      </c>
-      <c r="AD6" s="3">
-        <f t="shared" ref="AD6:AL6" si="11">SUM(AD3:AD5)</f>
-        <v>742.26424000000009</v>
-      </c>
-      <c r="AE6" s="3">
-        <f t="shared" si="11"/>
-        <v>779.87713264000013</v>
-      </c>
-      <c r="AF6" s="3">
-        <f t="shared" si="11"/>
-        <v>806.31845087040017</v>
+        <v>614.79999999999995</v>
       </c>
       <c r="AG6" s="3">
-        <f t="shared" si="11"/>
-        <v>828.08358318816022</v>
+        <f>SUM(AG3:AG5)</f>
+        <v>701.94500000000005</v>
       </c>
       <c r="AH6" s="3">
-        <f t="shared" si="11"/>
-        <v>844.64525485192348</v>
+        <f t="shared" ref="AH6:AP6" si="16">SUM(AH3:AH5)</f>
+        <v>777.61467100000016</v>
       </c>
       <c r="AI6" s="3">
-        <f t="shared" si="11"/>
-        <v>861.53815994896195</v>
+        <f t="shared" si="16"/>
+        <v>823.10491867000007</v>
       </c>
       <c r="AJ6" s="3">
-        <f t="shared" si="11"/>
-        <v>878.76892314794122</v>
+        <f t="shared" si="16"/>
+        <v>851.9502534108002</v>
       </c>
       <c r="AK6" s="3">
-        <f t="shared" si="11"/>
-        <v>896.34430161090017</v>
+        <f t="shared" si="16"/>
+        <v>876.04715147966419</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="11"/>
-        <v>914.27118764311808</v>
+        <f t="shared" si="16"/>
+        <v>894.87809234605743</v>
+      </c>
+      <c r="AM6" s="3">
+        <f t="shared" si="16"/>
+        <v>914.34765159713857</v>
+      </c>
+      <c r="AN6" s="3">
+        <f t="shared" si="16"/>
+        <v>934.52100151407342</v>
+      </c>
+      <c r="AO6" s="3">
+        <f t="shared" si="16"/>
+        <v>955.47509780634527</v>
+      </c>
+      <c r="AP6" s="3">
+        <f t="shared" si="16"/>
+        <v>977.30101127686066</v>
       </c>
     </row>
-    <row r="7" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>24</v>
       </c>
@@ -1588,159 +1754,186 @@
         <v>0.2</v>
       </c>
       <c r="V7" s="3">
+        <v>-0.6</v>
+      </c>
+      <c r="W7" s="3">
         <v>0</v>
       </c>
       <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3">
         <v>0.5</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AC7" s="3">
         <v>0.5</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AD7" s="3">
         <f>SUM(K7:N7)</f>
         <v>0.7</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AE7" s="3">
         <f>SUM(O7:R7)</f>
         <v>2.4</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AF7" s="3">
         <f>SUM(S7:V7)</f>
-        <v>0.2</v>
-      </c>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
+        <v>-0.39999999999999997</v>
+      </c>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" ref="I8:P8" si="12">I6+I7</f>
+        <f t="shared" ref="I8:P8" si="17">I6+I7</f>
         <v>85.399999999999991</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>96.399999999999991</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>87.1</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>94.299999999999983</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>102.6</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>113.5</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>102.1</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>110.99999999999999</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" ref="Q8:V8" si="13">Q6+Q7</f>
+        <f t="shared" ref="Q8:V8" si="18">Q6+Q7</f>
         <v>123.89999999999999</v>
       </c>
       <c r="R8" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>145.89999999999998</v>
       </c>
       <c r="S8" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>142.69999999999999</v>
       </c>
       <c r="T8" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>143</v>
       </c>
       <c r="U8" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>152.1</v>
       </c>
       <c r="V8" s="8">
-        <f t="shared" si="13"/>
-        <v>160.66000000000003</v>
+        <f t="shared" si="18"/>
+        <v>176.6</v>
+      </c>
+      <c r="W8" s="8">
+        <v>170</v>
       </c>
       <c r="X8" s="8">
-        <f>X6+X7</f>
-        <v>251.5</v>
+        <f>T8*1.2</f>
+        <v>171.6</v>
       </c>
       <c r="Y8" s="8">
-        <f>Y6+Y7</f>
-        <v>331.5</v>
+        <f>U8*1.15</f>
+        <v>174.91499999999999</v>
       </c>
       <c r="Z8" s="8">
-        <f>Z6+Z7</f>
-        <v>397.49999999999994</v>
-      </c>
-      <c r="AA8" s="8">
-        <f>AA6+AA7</f>
-        <v>482.9</v>
+        <f>V8*1.05</f>
+        <v>185.43</v>
       </c>
       <c r="AB8" s="8">
         <f>AB6+AB7</f>
-        <v>598.46</v>
+        <v>251.5</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AL8" si="14">AC6+AC7</f>
-        <v>678.58519999999999</v>
+        <f>AC6+AC7</f>
+        <v>331.5</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="14"/>
-        <v>742.26424000000009</v>
+        <f>AD6+AD7</f>
+        <v>397.49999999999994</v>
       </c>
       <c r="AE8" s="8">
-        <f t="shared" si="14"/>
-        <v>779.87713264000013</v>
+        <f>AE6+AE7</f>
+        <v>482.9</v>
       </c>
       <c r="AF8" s="8">
-        <f t="shared" si="14"/>
-        <v>806.31845087040017</v>
+        <f>AF6+AF7</f>
+        <v>614.4</v>
       </c>
       <c r="AG8" s="8">
-        <f t="shared" si="14"/>
-        <v>828.08358318816022</v>
+        <f>SUM(W8:Z8)</f>
+        <v>701.94499999999994</v>
       </c>
       <c r="AH8" s="8">
-        <f t="shared" si="14"/>
-        <v>844.64525485192348</v>
+        <f t="shared" ref="AH8:AP8" si="19">AH6+AH7</f>
+        <v>777.61467100000016</v>
       </c>
       <c r="AI8" s="8">
-        <f t="shared" si="14"/>
-        <v>861.53815994896195</v>
+        <f t="shared" si="19"/>
+        <v>823.10491867000007</v>
       </c>
       <c r="AJ8" s="8">
-        <f t="shared" si="14"/>
-        <v>878.76892314794122</v>
+        <f t="shared" si="19"/>
+        <v>851.9502534108002</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" si="14"/>
-        <v>896.34430161090017</v>
+        <f t="shared" si="19"/>
+        <v>876.04715147966419</v>
       </c>
       <c r="AL8" s="8">
-        <f t="shared" si="14"/>
-        <v>914.27118764311808</v>
+        <f t="shared" si="19"/>
+        <v>894.87809234605743</v>
+      </c>
+      <c r="AM8" s="8">
+        <f t="shared" si="19"/>
+        <v>914.34765159713857</v>
+      </c>
+      <c r="AN8" s="8">
+        <f t="shared" si="19"/>
+        <v>934.52100151407342</v>
+      </c>
+      <c r="AO8" s="8">
+        <f t="shared" si="19"/>
+        <v>955.47509780634527</v>
+      </c>
+      <c r="AP8" s="8">
+        <f t="shared" si="19"/>
+        <v>977.30101127686066</v>
       </c>
     </row>
-    <row r="9" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>26</v>
       </c>
@@ -1784,39 +1977,57 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" ref="V9" si="15">V8*0.02</f>
-        <v>3.2132000000000005</v>
+        <v>2.6</v>
+      </c>
+      <c r="W9" s="3">
+        <f>W8*0.01</f>
+        <v>1.7</v>
       </c>
       <c r="X9" s="3">
+        <f t="shared" ref="X9:Z9" si="20">X8*0.01</f>
+        <v>1.716</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="20"/>
+        <v>1.74915</v>
+      </c>
+      <c r="Z9" s="3">
+        <f t="shared" si="20"/>
+        <v>1.8543000000000001</v>
+      </c>
+      <c r="AB9" s="3">
         <v>4.5</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>4.0999999999999996</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <f>SUM(K9:N9)</f>
         <v>3.1</v>
       </c>
-      <c r="AA9" s="3">
-        <f t="shared" ref="AA9:AA11" si="16">SUM(O9:R9)</f>
+      <c r="AE9" s="3">
+        <f t="shared" ref="AE9:AE11" si="21">SUM(O9:R9)</f>
         <v>10</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <f>SUM(S9:V9)</f>
-        <v>9.9131999999999998</v>
-      </c>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AG9" s="3">
+        <f>SUM(W9:Z9)</f>
+        <v>7.01945</v>
+      </c>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
     </row>
-    <row r="10" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>27</v>
       </c>
@@ -1860,39 +2071,57 @@
         <v>1.9</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" ref="V10" si="17">V8*0.01</f>
-        <v>1.6066000000000003</v>
+        <v>1.7</v>
+      </c>
+      <c r="W10" s="3">
+        <f>W8*0.01</f>
+        <v>1.7</v>
       </c>
       <c r="X10" s="3">
+        <f t="shared" ref="X10:Z10" si="22">X8*0.01</f>
+        <v>1.716</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="22"/>
+        <v>1.74915</v>
+      </c>
+      <c r="Z10" s="3">
+        <f t="shared" si="22"/>
+        <v>1.8543000000000001</v>
+      </c>
+      <c r="AB10" s="3">
         <v>3.7</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>3.8</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <f>SUM(K10:N10)</f>
         <v>4.3000000000000007</v>
       </c>
-      <c r="AA10" s="3">
-        <f t="shared" si="16"/>
+      <c r="AE10" s="3">
+        <f t="shared" si="21"/>
         <v>3.9</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <f>SUM(S10:V10)</f>
-        <v>5.9066000000000001</v>
-      </c>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="AG10" s="3">
+        <f>SUM(W10:Z10)</f>
+        <v>7.01945</v>
+      </c>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
     </row>
-    <row r="11" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>28</v>
       </c>
@@ -1936,281 +2165,331 @@
         <v>48.5</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" ref="V11" si="18">V8*0.33</f>
-        <v>53.017800000000008</v>
+        <v>62</v>
+      </c>
+      <c r="W11" s="3">
+        <f>W8*0.35</f>
+        <v>59.499999999999993</v>
       </c>
       <c r="X11" s="3">
+        <f t="shared" ref="X11:Z11" si="23">X8*0.35</f>
+        <v>60.059999999999995</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="23"/>
+        <v>61.220249999999993</v>
+      </c>
+      <c r="Z11" s="3">
+        <f t="shared" si="23"/>
+        <v>64.900499999999994</v>
+      </c>
+      <c r="AB11" s="3">
         <v>5.5</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AC11" s="3">
         <v>46.7</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="AD11" s="3">
         <f>SUM(K11:N11)</f>
         <v>85.899999999999991</v>
       </c>
-      <c r="AA11" s="3">
-        <f t="shared" si="16"/>
+      <c r="AE11" s="3">
+        <f t="shared" si="21"/>
         <v>118.6</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AF11" s="3">
         <f>SUM(S11:V11)</f>
-        <v>196.11779999999999</v>
-      </c>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
+        <v>205.1</v>
+      </c>
+      <c r="AG11" s="3">
+        <f>SUM(W11:Z11)</f>
+        <v>245.68074999999996</v>
+      </c>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" ref="I12:S12" si="19">I9+I10+I11</f>
+        <f t="shared" ref="I12:S12" si="24">I9+I10+I11</f>
         <v>15.700000000000001</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>19</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>16.899999999999999</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>22.599999999999998</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>25.2</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>28.6</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>24.1</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>27.7</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>47.7</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>50.6</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ref="T12" si="20">T9+T10+T11</f>
+        <f t="shared" ref="T12" si="25">T9+T10+T11</f>
         <v>50.9</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ref="U12" si="21">U9+U10+U11</f>
+        <f t="shared" ref="U12" si="26">U9+U10+U11</f>
         <v>52.6</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ref="V12" si="22">V9+V10+V11</f>
-        <v>57.837600000000009</v>
+        <f t="shared" ref="V12:W12" si="27">V9+V10+V11</f>
+        <v>66.3</v>
+      </c>
+      <c r="W12" s="3">
+        <f t="shared" si="27"/>
+        <v>62.899999999999991</v>
       </c>
       <c r="X12" s="3">
-        <f>X9+X10+X11</f>
+        <f t="shared" ref="X12:Z12" si="28">X9+X10+X11</f>
+        <v>63.491999999999997</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="28"/>
+        <v>64.718549999999993</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" si="28"/>
+        <v>68.609099999999998</v>
+      </c>
+      <c r="AB12" s="3">
+        <f>AB9+AB10+AB11</f>
         <v>13.7</v>
       </c>
-      <c r="Y12" s="3">
-        <f>Y9+Y10+Y11</f>
+      <c r="AC12" s="3">
+        <f>AC9+AC10+AC11</f>
         <v>54.6</v>
       </c>
-      <c r="Z12" s="3">
-        <f>Z9+Z10+Z11</f>
+      <c r="AD12" s="3">
+        <f>AD9+AD10+AD11</f>
         <v>93.3</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AE12" s="3">
         <f>SUM(O12:R12)</f>
         <v>132.5</v>
       </c>
-      <c r="AB12" s="3">
-        <f>AB9+AB10+AB11</f>
-        <v>211.93759999999997</v>
-      </c>
-      <c r="AC12" s="3">
-        <f t="shared" ref="AC12:AL12" si="23">AC8-AC13</f>
-        <v>251.07652400000001</v>
-      </c>
-      <c r="AD12" s="3">
-        <f t="shared" si="23"/>
-        <v>274.6377688</v>
-      </c>
-      <c r="AE12" s="3">
-        <f t="shared" si="23"/>
-        <v>288.55453907680004</v>
-      </c>
       <c r="AF12" s="3">
-        <f t="shared" si="23"/>
-        <v>298.33782682204804</v>
+        <f>AF9+AF10+AF11</f>
+        <v>220.4</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="23"/>
-        <v>306.39092577961924</v>
+        <f>AG9+AG10+AG11</f>
+        <v>259.71964999999994</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="23"/>
-        <v>312.51874429521172</v>
+        <f t="shared" ref="AH12:AP12" si="29">AH8-AH13</f>
+        <v>287.71742827000003</v>
       </c>
       <c r="AI12" s="3">
-        <f t="shared" si="23"/>
-        <v>318.76911918111591</v>
+        <f t="shared" si="29"/>
+        <v>304.5488199079</v>
       </c>
       <c r="AJ12" s="3">
-        <f t="shared" si="23"/>
-        <v>325.14450156473822</v>
+        <f t="shared" si="29"/>
+        <v>315.22159376199602</v>
       </c>
       <c r="AK12" s="3">
-        <f t="shared" si="23"/>
-        <v>331.64739159603312</v>
+        <f t="shared" si="29"/>
+        <v>324.13744604747569</v>
       </c>
       <c r="AL12" s="3">
-        <f t="shared" si="23"/>
-        <v>338.28033942795366</v>
+        <f t="shared" si="29"/>
+        <v>331.10489416804126</v>
+      </c>
+      <c r="AM12" s="3">
+        <f t="shared" si="29"/>
+        <v>338.30863109094128</v>
+      </c>
+      <c r="AN12" s="3">
+        <f t="shared" si="29"/>
+        <v>345.77277056020716</v>
+      </c>
+      <c r="AO12" s="3">
+        <f t="shared" si="29"/>
+        <v>353.52578618834775</v>
+      </c>
+      <c r="AP12" s="3">
+        <f t="shared" si="29"/>
+        <v>361.60137417243845</v>
       </c>
     </row>
-    <row r="13" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" ref="I13:S13" si="24">I8-I12</f>
+        <f t="shared" ref="I13:S13" si="30">I8-I12</f>
         <v>69.699999999999989</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>77.399999999999991</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>70.199999999999989</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>71.699999999999989</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>77.399999999999991</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>84.9</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>78</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>83.299999999999983</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>90.899999999999991</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>98.199999999999974</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>92.1</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="25">T8-T12</f>
+        <f t="shared" ref="T13" si="31">T8-T12</f>
         <v>92.1</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13" si="26">U8-U12</f>
+        <f t="shared" ref="U13" si="32">U8-U12</f>
         <v>99.5</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="27">V8-V12</f>
-        <v>102.82240000000002</v>
+        <f t="shared" ref="V13:W13" si="33">V8-V12</f>
+        <v>110.3</v>
+      </c>
+      <c r="W13" s="8">
+        <f t="shared" si="33"/>
+        <v>107.10000000000001</v>
       </c>
       <c r="X13" s="8">
-        <f>X8-X12</f>
+        <f t="shared" ref="X13:Z13" si="34">X8-X12</f>
+        <v>108.108</v>
+      </c>
+      <c r="Y13" s="8">
+        <f t="shared" si="34"/>
+        <v>110.19645</v>
+      </c>
+      <c r="Z13" s="8">
+        <f t="shared" si="34"/>
+        <v>116.82090000000001</v>
+      </c>
+      <c r="AB13" s="8">
+        <f t="shared" ref="AB13:AG13" si="35">AB8-AB12</f>
         <v>237.8</v>
       </c>
-      <c r="Y13" s="8">
-        <f>Y8-Y12</f>
+      <c r="AC13" s="8">
+        <f t="shared" si="35"/>
         <v>276.89999999999998</v>
       </c>
-      <c r="Z13" s="8">
-        <f>Z8-Z12</f>
+      <c r="AD13" s="8">
+        <f t="shared" si="35"/>
         <v>304.19999999999993</v>
       </c>
-      <c r="AA13" s="8">
-        <f>AA8-AA12</f>
+      <c r="AE13" s="8">
+        <f t="shared" si="35"/>
         <v>350.4</v>
       </c>
-      <c r="AB13" s="8">
-        <f>AB8-AB12</f>
-        <v>386.52240000000006</v>
-      </c>
-      <c r="AC13" s="8">
-        <f>AC8*0.63</f>
-        <v>427.50867599999998</v>
-      </c>
-      <c r="AD13" s="8">
-        <f t="shared" ref="AD13:AL13" si="28">AD8*0.63</f>
-        <v>467.62647120000008</v>
-      </c>
-      <c r="AE13" s="8">
-        <f t="shared" si="28"/>
-        <v>491.32259356320009</v>
-      </c>
       <c r="AF13" s="8">
-        <f t="shared" si="28"/>
-        <v>507.98062404835213</v>
+        <f t="shared" si="35"/>
+        <v>394</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" si="28"/>
-        <v>521.69265740854098</v>
+        <f t="shared" si="35"/>
+        <v>442.22534999999999</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" si="28"/>
-        <v>532.12651055671176</v>
+        <f t="shared" ref="AH13:AP13" si="36">AH8*0.63</f>
+        <v>489.89724273000013</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" si="28"/>
-        <v>542.76904076784604</v>
+        <f t="shared" si="36"/>
+        <v>518.55609876210008</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" si="28"/>
-        <v>553.624421583203</v>
+        <f t="shared" si="36"/>
+        <v>536.72865964880418</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="28"/>
-        <v>564.69691001486706</v>
+        <f t="shared" si="36"/>
+        <v>551.9097054321885</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" si="28"/>
-        <v>575.99084821516442</v>
+        <f t="shared" si="36"/>
+        <v>563.77319817801617</v>
+      </c>
+      <c r="AM13" s="8">
+        <f t="shared" si="36"/>
+        <v>576.03902050619729</v>
+      </c>
+      <c r="AN13" s="8">
+        <f t="shared" si="36"/>
+        <v>588.74823095386625</v>
+      </c>
+      <c r="AO13" s="8">
+        <f t="shared" si="36"/>
+        <v>601.94931161799752</v>
+      </c>
+      <c r="AP13" s="8">
+        <f t="shared" si="36"/>
+        <v>615.69963710442221</v>
       </c>
     </row>
-    <row r="14" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -2254,69 +2533,84 @@
         <v>20.9</v>
       </c>
       <c r="V14" s="3">
-        <f>R14*1.25</f>
-        <v>22.25</v>
+        <v>21.9</v>
+      </c>
+      <c r="W14" s="3">
+        <f>S14*1.2</f>
+        <v>21.12</v>
       </c>
       <c r="X14" s="3">
+        <f t="shared" ref="X14" si="37">T14*1.2</f>
+        <v>22.439999999999998</v>
+      </c>
+      <c r="Y14" s="3">
+        <f>U14*1.1</f>
+        <v>22.990000000000002</v>
+      </c>
+      <c r="Z14" s="3">
+        <f>V14*1.1</f>
+        <v>24.09</v>
+      </c>
+      <c r="AB14" s="3">
         <v>74.5</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>74.599999999999994</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <f>SUM(K14:N14)</f>
         <v>82.800000000000011</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AE14" s="3">
         <f>SUM(O14:R14)</f>
         <v>77.099999999999994</v>
       </c>
-      <c r="AB14" s="3">
-        <f t="shared" ref="AB14:AB20" si="29">SUM(S14:V14)</f>
-        <v>79.449999999999989</v>
-      </c>
-      <c r="AC14" s="3">
-        <f>AB14*1.08</f>
-        <v>85.805999999999997</v>
-      </c>
-      <c r="AD14" s="3">
-        <f>AC14*1.05</f>
-        <v>90.096299999999999</v>
-      </c>
-      <c r="AE14" s="3">
-        <f>AD14*1.04</f>
-        <v>93.700152000000003</v>
-      </c>
       <c r="AF14" s="3">
-        <f>AE14*1.03</f>
-        <v>96.511156560000003</v>
+        <f t="shared" ref="AF14:AF20" si="38">SUM(S14:V14)</f>
+        <v>79.099999999999994</v>
       </c>
       <c r="AG14" s="3">
-        <f>AF14*1.02</f>
-        <v>98.441379691200012</v>
+        <f t="shared" ref="AG14:AG20" si="39">SUM(W14:Z14)</f>
+        <v>90.640000000000015</v>
       </c>
       <c r="AH14" s="3">
-        <f t="shared" ref="AH14:AL14" si="30">AG14*1.01</f>
-        <v>99.425793488112006</v>
+        <f>AG14*1.05</f>
+        <v>95.172000000000025</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" si="30"/>
-        <v>100.42005142299313</v>
+        <f>AH14*1.04</f>
+        <v>98.978880000000032</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="30"/>
-        <v>101.42425193722306</v>
+        <f>AI14*1.03</f>
+        <v>101.94824640000003</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="30"/>
-        <v>102.43849445659529</v>
+        <f>AJ14*1.02</f>
+        <v>103.98721132800003</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="30"/>
-        <v>103.46287940116125</v>
+        <f t="shared" ref="AL14:AP14" si="40">AK14*1.01</f>
+        <v>105.02708344128003</v>
+      </c>
+      <c r="AM14" s="3">
+        <f t="shared" si="40"/>
+        <v>106.07735427569283</v>
+      </c>
+      <c r="AN14" s="3">
+        <f t="shared" si="40"/>
+        <v>107.13812781844976</v>
+      </c>
+      <c r="AO14" s="3">
+        <f t="shared" si="40"/>
+        <v>108.20950909663426</v>
+      </c>
+      <c r="AP14" s="3">
+        <f t="shared" si="40"/>
+        <v>109.29160418760061</v>
       </c>
     </row>
-    <row r="15" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>75</v>
       </c>
@@ -2341,27 +2635,44 @@
       <c r="U15" s="3">
         <v>9.1</v>
       </c>
-      <c r="V15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3">
-        <f t="shared" si="29"/>
-        <v>23.9</v>
-      </c>
+      <c r="V15" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="W15" s="3">
+        <v>9</v>
+      </c>
+      <c r="X15" s="3">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="3"/>
+      <c r="AF15" s="3">
+        <f>SUM(S15:Z15)</f>
+        <v>68.400000000000006</v>
+      </c>
+      <c r="AG15" s="3">
+        <f t="shared" si="39"/>
+        <v>37</v>
+      </c>
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>32</v>
       </c>
@@ -2405,69 +2716,84 @@
         <v>35.9</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" ref="V16" si="31">V8*0.24</f>
-        <v>38.558400000000006</v>
+        <v>38.1</v>
+      </c>
+      <c r="W16" s="3">
+        <f>W8*0.23</f>
+        <v>39.1</v>
       </c>
       <c r="X16" s="3">
+        <f t="shared" ref="X16:Y16" si="41">X8*0.23</f>
+        <v>39.468000000000004</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="41"/>
+        <v>40.230449999999998</v>
+      </c>
+      <c r="Z16" s="3">
+        <f>Z8*0.22</f>
+        <v>40.794600000000003</v>
+      </c>
+      <c r="AB16" s="3">
         <v>120.9</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AC16" s="3">
         <v>115</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AD16" s="3">
         <f>SUM(K16:N16)</f>
         <v>109.9</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AE16" s="3">
         <f>SUM(O16:R16)</f>
         <v>131.9</v>
       </c>
-      <c r="AB16" s="3">
-        <f t="shared" si="29"/>
-        <v>142.6584</v>
-      </c>
-      <c r="AC16" s="3">
-        <f>AC8*0.23</f>
-        <v>156.07459600000001</v>
-      </c>
-      <c r="AD16" s="3">
-        <f>AD8*0.22</f>
-        <v>163.29813280000002</v>
-      </c>
-      <c r="AE16" s="3">
-        <f t="shared" ref="AE16:AL16" si="32">AE8*0.22</f>
-        <v>171.57296918080002</v>
-      </c>
       <c r="AF16" s="3">
-        <f t="shared" si="32"/>
-        <v>177.39005919148804</v>
+        <f t="shared" si="38"/>
+        <v>142.19999999999999</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="32"/>
-        <v>182.17838830139524</v>
+        <f t="shared" si="39"/>
+        <v>159.59305000000001</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="32"/>
-        <v>185.82195606742317</v>
+        <f>AH8*0.22</f>
+        <v>171.07522762000005</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="32"/>
-        <v>189.53839518877163</v>
+        <f t="shared" ref="AI16:AP16" si="42">AI8*0.22</f>
+        <v>181.08308210740003</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="32"/>
-        <v>193.32916309254708</v>
+        <f t="shared" si="42"/>
+        <v>187.42905575037605</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="32"/>
-        <v>197.19574635439804</v>
+        <f t="shared" si="42"/>
+        <v>192.73037332552613</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="32"/>
-        <v>201.13966128148599</v>
+        <f t="shared" si="42"/>
+        <v>196.87318031613265</v>
+      </c>
+      <c r="AM16" s="3">
+        <f t="shared" si="42"/>
+        <v>201.1564833513705</v>
+      </c>
+      <c r="AN16" s="3">
+        <f t="shared" si="42"/>
+        <v>205.59462033309615</v>
+      </c>
+      <c r="AO16" s="3">
+        <f t="shared" si="42"/>
+        <v>210.20452151739596</v>
+      </c>
+      <c r="AP16" s="3">
+        <f t="shared" si="42"/>
+        <v>215.00622248090934</v>
       </c>
     </row>
-    <row r="17" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -2511,39 +2837,40 @@
         <v>-0.3</v>
       </c>
       <c r="V17" s="3">
+        <v>-0.4</v>
+      </c>
+      <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
         <v>0.6</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>1.4</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <f>SUM(K17:N17)</f>
         <v>4</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <f>SUM(O17:R17)</f>
         <v>-0.8</v>
       </c>
-      <c r="AB17" s="3">
-        <f t="shared" si="29"/>
-        <v>0.10000000000000003</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>0</v>
-      </c>
       <c r="AF17" s="3">
-        <v>0</v>
+        <f t="shared" si="38"/>
+        <v>-0.3</v>
       </c>
       <c r="AG17" s="3">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AH17" s="3">
@@ -2561,8 +2888,20 @@
       <c r="AL17" s="3">
         <v>0</v>
       </c>
+      <c r="AM17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>33</v>
       </c>
@@ -2606,38 +2945,53 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="V18" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W18" s="3">
         <v>5</v>
       </c>
       <c r="X18" s="3">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>19.600000000000001</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>13.9</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <f>SUM(K18:N18)</f>
         <v>13.2</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <f>SUM(O18:R18)</f>
         <v>15.6</v>
       </c>
-      <c r="AB18" s="3">
-        <f t="shared" si="29"/>
-        <v>18.899999999999999</v>
-      </c>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="3"/>
+      <c r="AF18" s="3">
+        <f t="shared" si="38"/>
+        <v>18.8</v>
+      </c>
+      <c r="AG18" s="3">
+        <f t="shared" si="39"/>
+        <v>20</v>
+      </c>
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>74</v>
       </c>
@@ -2660,27 +3014,44 @@
       <c r="U19" s="3">
         <v>0.2</v>
       </c>
-      <c r="V19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3">
-        <f t="shared" si="29"/>
-        <v>1.4999999999999998</v>
-      </c>
+      <c r="V19" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
+      <c r="AF19" s="3">
+        <f>SUM(S19:Z19)</f>
+        <v>1.9</v>
+      </c>
+      <c r="AG19" s="3">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -2728,312 +3099,356 @@
         <v>6.6</v>
       </c>
       <c r="V20" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="W20" s="3">
+        <v>9</v>
+      </c>
+      <c r="X20" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>10</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AB20" s="3">
         <f>5.6+22.8</f>
         <v>28.4</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AC20" s="3">
         <f>3.2+1.5+26.7</f>
         <v>31.4</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AD20" s="3">
         <f>SUM(K20:N20)</f>
         <v>31.599999999999994</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AE20" s="3">
         <f>SUM(O20:R20)</f>
         <v>31.799999999999997</v>
       </c>
-      <c r="AB20" s="3">
-        <f t="shared" si="29"/>
-        <v>31.9</v>
-      </c>
-      <c r="AC20" s="3">
-        <f t="shared" ref="AC20:AL20" si="33">AB20*1.01</f>
-        <v>32.219000000000001</v>
-      </c>
-      <c r="AD20" s="3">
-        <f t="shared" si="33"/>
-        <v>32.54119</v>
-      </c>
-      <c r="AE20" s="3">
-        <f t="shared" si="33"/>
-        <v>32.866601899999999</v>
-      </c>
       <c r="AF20" s="3">
-        <f t="shared" si="33"/>
-        <v>33.195267919000003</v>
+        <f t="shared" si="38"/>
+        <v>31.299999999999997</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="33"/>
-        <v>33.527220598190006</v>
+        <f t="shared" si="39"/>
+        <v>37.700000000000003</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="33"/>
-        <v>33.862492804171907</v>
+        <f t="shared" ref="AH20:AP20" si="43">AG20*1.01</f>
+        <v>38.077000000000005</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="33"/>
-        <v>34.201117732213625</v>
+        <f t="shared" si="43"/>
+        <v>38.457770000000004</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="33"/>
-        <v>34.54312890953576</v>
+        <f t="shared" si="43"/>
+        <v>38.842347700000005</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="33"/>
-        <v>34.888560198631119</v>
+        <f t="shared" si="43"/>
+        <v>39.230771177000008</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="33"/>
-        <v>35.237445800617429</v>
+        <f t="shared" si="43"/>
+        <v>39.62307888877001</v>
+      </c>
+      <c r="AM20" s="3">
+        <f t="shared" si="43"/>
+        <v>40.019309677657709</v>
+      </c>
+      <c r="AN20" s="3">
+        <f t="shared" si="43"/>
+        <v>40.419502774434285</v>
+      </c>
+      <c r="AO20" s="3">
+        <f t="shared" si="43"/>
+        <v>40.823697802178629</v>
+      </c>
+      <c r="AP20" s="3">
+        <f t="shared" si="43"/>
+        <v>41.231934780200412</v>
       </c>
     </row>
-    <row r="21" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:P21" si="34">SUM(I14:I20)</f>
+        <f t="shared" ref="I21:P21" si="44">SUM(I14:I20)</f>
         <v>53.499999999999993</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>65.7</v>
       </c>
       <c r="K21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>56.4</v>
       </c>
       <c r="L21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>59.199999999999996</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>61.4</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>64.5</v>
       </c>
       <c r="O21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>58.600000000000009</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="44"/>
         <v>61.399999999999991</v>
       </c>
       <c r="Q21" s="3">
-        <f t="shared" ref="Q21:R21" si="35">SUM(Q14:Q20)</f>
+        <f t="shared" ref="Q21:R21" si="45">SUM(Q14:Q20)</f>
         <v>67.5</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="45"/>
         <v>70.7</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" ref="S21:V21" si="36">SUM(S14:S20)</f>
+        <f t="shared" ref="S21:V21" si="46">SUM(S14:S20)</f>
         <v>70.900000000000006</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>74.399999999999991</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="46"/>
         <v>77.300000000000011</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" si="36"/>
-        <v>75.808400000000006</v>
+        <f t="shared" si="46"/>
+        <v>81.800000000000011</v>
+      </c>
+      <c r="W21" s="3">
+        <f t="shared" ref="W21:Z21" si="47">SUM(W14:W20)</f>
+        <v>83.22</v>
       </c>
       <c r="X21" s="3">
-        <f>SUM(X14:X20)</f>
-        <v>244</v>
+        <f t="shared" si="47"/>
+        <v>85.108000000000004</v>
       </c>
       <c r="Y21" s="3">
-        <f>SUM(Y14:Y20)</f>
-        <v>236.3</v>
+        <f t="shared" si="47"/>
+        <v>86.72045</v>
       </c>
       <c r="Z21" s="3">
-        <f>SUM(Z14:Z20)</f>
-        <v>241.5</v>
-      </c>
-      <c r="AA21" s="3">
-        <f>SUM(AA14:AA20)</f>
-        <v>255.59999999999997</v>
+        <f t="shared" si="47"/>
+        <v>89.884600000000006</v>
       </c>
       <c r="AB21" s="3">
         <f>SUM(AB14:AB20)</f>
-        <v>298.40839999999997</v>
+        <v>244</v>
       </c>
       <c r="AC21" s="3">
-        <f t="shared" ref="AC21:AL21" si="37">SUM(AC14:AC20)</f>
-        <v>274.09959600000002</v>
+        <f>SUM(AC14:AC20)</f>
+        <v>236.3</v>
       </c>
       <c r="AD21" s="3">
-        <f t="shared" si="37"/>
-        <v>285.93562280000003</v>
+        <f>SUM(AD14:AD20)</f>
+        <v>241.5</v>
       </c>
       <c r="AE21" s="3">
-        <f t="shared" si="37"/>
-        <v>298.13972308079997</v>
+        <f>SUM(AE14:AE20)</f>
+        <v>255.59999999999997</v>
       </c>
       <c r="AF21" s="3">
-        <f t="shared" si="37"/>
-        <v>307.09648367048806</v>
+        <f>SUM(AF14:AF20)</f>
+        <v>341.4</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" si="37"/>
-        <v>314.14698859078527</v>
+        <f t="shared" ref="AG21:AP21" si="48">SUM(AG14:AG20)</f>
+        <v>344.93305000000004</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="37"/>
-        <v>319.11024235970706</v>
+        <f t="shared" si="48"/>
+        <v>304.3242276200001</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="37"/>
-        <v>324.15956434397839</v>
+        <f t="shared" si="48"/>
+        <v>318.51973210740005</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="37"/>
-        <v>329.29654393930593</v>
+        <f t="shared" si="48"/>
+        <v>328.21964985037607</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="37"/>
-        <v>334.52280100962446</v>
+        <f t="shared" si="48"/>
+        <v>335.94835583052617</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="37"/>
-        <v>339.83998648326468</v>
+        <f t="shared" si="48"/>
+        <v>341.5233426461827</v>
+      </c>
+      <c r="AM21" s="3">
+        <f t="shared" si="48"/>
+        <v>347.25314730472104</v>
+      </c>
+      <c r="AN21" s="3">
+        <f t="shared" si="48"/>
+        <v>353.15225092598024</v>
+      </c>
+      <c r="AO21" s="3">
+        <f t="shared" si="48"/>
+        <v>359.23772841620888</v>
+      </c>
+      <c r="AP21" s="3">
+        <f t="shared" si="48"/>
+        <v>365.52976144871036</v>
       </c>
     </row>
-    <row r="22" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" ref="I22:P22" si="38">I13-I21</f>
+        <f t="shared" ref="I22:P22" si="49">I13-I21</f>
         <v>16.199999999999996</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>11.699999999999989</v>
       </c>
       <c r="K22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>13.79999999999999</v>
       </c>
       <c r="L22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>12.499999999999993</v>
       </c>
       <c r="M22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>15.999999999999993</v>
       </c>
       <c r="N22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>20.400000000000006</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="49"/>
         <v>21.899999999999991</v>
       </c>
       <c r="Q22" s="8">
-        <f t="shared" ref="Q22:R22" si="39">Q13-Q21</f>
+        <f t="shared" ref="Q22:R22" si="50">Q13-Q21</f>
         <v>23.399999999999991</v>
       </c>
       <c r="R22" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="50"/>
         <v>27.499999999999972</v>
       </c>
       <c r="S22" s="8">
-        <f t="shared" ref="S22:V22" si="40">S13-S21</f>
+        <f t="shared" ref="S22:V22" si="51">S13-S21</f>
         <v>21.199999999999989</v>
       </c>
       <c r="T22" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>17.700000000000003</v>
       </c>
       <c r="U22" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="51"/>
         <v>22.199999999999989</v>
       </c>
       <c r="V22" s="8">
-        <f t="shared" si="40"/>
-        <v>27.01400000000001</v>
+        <f t="shared" si="51"/>
+        <v>28.499999999999986</v>
+      </c>
+      <c r="W22" s="8">
+        <f t="shared" ref="W22:Z22" si="52">W13-W21</f>
+        <v>23.88000000000001</v>
       </c>
       <c r="X22" s="8">
-        <f>X13-X21</f>
-        <v>-6.1999999999999886</v>
+        <f t="shared" si="52"/>
+        <v>23</v>
       </c>
       <c r="Y22" s="8">
-        <f>Y13-Y21</f>
-        <v>40.599999999999966</v>
+        <f t="shared" si="52"/>
+        <v>23.475999999999999</v>
       </c>
       <c r="Z22" s="8">
-        <f>Z13-Z21</f>
-        <v>62.699999999999932</v>
-      </c>
-      <c r="AA22" s="8">
-        <f>AA13-AA21</f>
-        <v>94.800000000000011</v>
+        <f t="shared" si="52"/>
+        <v>26.936300000000003</v>
       </c>
       <c r="AB22" s="8">
         <f>AB13-AB21</f>
-        <v>88.11400000000009</v>
+        <v>-6.1999999999999886</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" ref="AC22:AL22" si="41">AC13-AC21</f>
-        <v>153.40907999999996</v>
+        <f>AC13-AC21</f>
+        <v>40.599999999999966</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="41"/>
-        <v>181.69084840000005</v>
+        <f>AD13-AD21</f>
+        <v>62.699999999999932</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="41"/>
-        <v>193.18287048240012</v>
+        <f>AE13-AE21</f>
+        <v>94.800000000000011</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="41"/>
-        <v>200.88414037786407</v>
+        <f>AF13-AF21</f>
+        <v>52.600000000000023</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" si="41"/>
-        <v>207.54566881775571</v>
+        <f t="shared" ref="AG22:AP22" si="53">AG13-AG21</f>
+        <v>97.292299999999955</v>
       </c>
       <c r="AH22" s="8">
-        <f t="shared" si="41"/>
-        <v>213.01626819700471</v>
+        <f t="shared" si="53"/>
+        <v>185.57301511000003</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="41"/>
-        <v>218.60947642386765</v>
+        <f t="shared" si="53"/>
+        <v>200.03636665470003</v>
       </c>
       <c r="AJ22" s="8">
-        <f t="shared" si="41"/>
-        <v>224.32787764389707</v>
+        <f t="shared" si="53"/>
+        <v>208.50900979842811</v>
       </c>
       <c r="AK22" s="8">
-        <f t="shared" si="41"/>
-        <v>230.1741090052426</v>
+        <f t="shared" si="53"/>
+        <v>215.96134960166233</v>
       </c>
       <c r="AL22" s="8">
-        <f t="shared" si="41"/>
-        <v>236.15086173189974</v>
+        <f t="shared" si="53"/>
+        <v>222.24985553183348</v>
+      </c>
+      <c r="AM22" s="8">
+        <f t="shared" si="53"/>
+        <v>228.78587320147625</v>
+      </c>
+      <c r="AN22" s="8">
+        <f t="shared" si="53"/>
+        <v>235.59598002788601</v>
+      </c>
+      <c r="AO22" s="8">
+        <f t="shared" si="53"/>
+        <v>242.71158320178864</v>
+      </c>
+      <c r="AP22" s="8">
+        <f t="shared" si="53"/>
+        <v>250.16987565571185</v>
       </c>
     </row>
-    <row r="23" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>38</v>
       </c>
@@ -3080,70 +3495,83 @@
         <v>-0.8</v>
       </c>
       <c r="V23" s="3">
-        <v>-0.9</v>
+        <f>-0.3-36.3-0.9</f>
+        <v>-37.499999999999993</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-1</v>
       </c>
       <c r="X23" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>-1</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-10</v>
+      </c>
+      <c r="AB23" s="3">
         <f>29.4+115.4-116.6-0.1</f>
         <v>28.100000000000016</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <f>-1.5-21.5</f>
         <v>-23</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <f>SUM(K23:N23)</f>
         <v>-98.8</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <f>SUM(O23:R23)</f>
         <v>-8.6</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <f>SUM(S23:V23)</f>
-        <v>-3.3000000000000003</v>
-      </c>
-      <c r="AC23" s="3">
-        <f>AB23*1.01</f>
-        <v>-3.3330000000000002</v>
-      </c>
-      <c r="AD23" s="3">
-        <f t="shared" ref="AD23:AL23" si="42">AC23*1.01</f>
-        <v>-3.36633</v>
-      </c>
-      <c r="AE23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.3999933000000002</v>
-      </c>
-      <c r="AF23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.4339932330000003</v>
+        <v>-39.899999999999991</v>
       </c>
       <c r="AG23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.4683331653300002</v>
+        <f t="shared" ref="AG23:AG25" si="54">SUM(W23:Z23)</f>
+        <v>-13</v>
       </c>
       <c r="AH23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.5030164969833004</v>
+        <f t="shared" ref="AH23:AP23" si="55">AG23*1.01</f>
+        <v>-13.13</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.5380466619531337</v>
+        <f t="shared" si="55"/>
+        <v>-13.2613</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.5734271285726651</v>
+        <f t="shared" si="55"/>
+        <v>-13.393913000000001</v>
       </c>
       <c r="AK23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.6091613998583916</v>
+        <f t="shared" si="55"/>
+        <v>-13.527852130000001</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="42"/>
-        <v>-3.6452530138569754</v>
+        <f t="shared" si="55"/>
+        <v>-13.663130651300001</v>
+      </c>
+      <c r="AM23" s="3">
+        <f t="shared" si="55"/>
+        <v>-13.799761957813001</v>
+      </c>
+      <c r="AN23" s="3">
+        <f t="shared" si="55"/>
+        <v>-13.93775957739113</v>
+      </c>
+      <c r="AO23" s="3">
+        <f t="shared" si="55"/>
+        <v>-14.077137173165042</v>
+      </c>
+      <c r="AP23" s="3">
+        <f t="shared" si="55"/>
+        <v>-14.217908544896693</v>
       </c>
     </row>
-    <row r="24" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>39</v>
       </c>
@@ -3189,37 +3617,38 @@
       <c r="V24" s="3">
         <v>0.2</v>
       </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>6.9</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AC24" s="3">
         <v>38.5</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AD24" s="3">
         <f>SUM(K24:N24)</f>
         <v>0.7</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <f>SUM(O24:R24)</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <f>SUM(S24:V24)</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AH24" s="3">
@@ -3237,8 +3666,20 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>40</v>
       </c>
@@ -3282,310 +3723,354 @@
         <v>0.5</v>
       </c>
       <c r="V25" s="3">
-        <v>1</v>
+        <v>1.8</v>
+      </c>
+      <c r="W25" s="3">
+        <v>2</v>
       </c>
       <c r="X25" s="3">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="3">
         <v>1.8</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="AC25" s="3">
         <v>1.2</v>
       </c>
-      <c r="Z25" s="3">
+      <c r="AD25" s="3">
         <f>SUM(K25:N25)</f>
         <v>1</v>
       </c>
-      <c r="AA25" s="3">
+      <c r="AE25" s="3">
         <f>SUM(O25:R25)</f>
         <v>1.9</v>
       </c>
-      <c r="AB25" s="3">
+      <c r="AF25" s="3">
         <f>SUM(S25:V25)</f>
-        <v>3.3</v>
-      </c>
-      <c r="AC25" s="3">
-        <f>AB25*1.01</f>
-        <v>3.3329999999999997</v>
-      </c>
-      <c r="AD25" s="3">
-        <f t="shared" ref="AD25:AL25" si="43">AC25*1.01</f>
-        <v>3.3663299999999996</v>
-      </c>
-      <c r="AE25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.3999932999999998</v>
-      </c>
-      <c r="AF25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.4339932329999998</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AG25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.4683331653299998</v>
+        <f t="shared" si="54"/>
+        <v>8</v>
       </c>
       <c r="AH25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.5030164969833</v>
+        <f t="shared" ref="AH25:AP25" si="56">AG25*1.01</f>
+        <v>8.08</v>
       </c>
       <c r="AI25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.5380466619531332</v>
+        <f t="shared" si="56"/>
+        <v>8.1608000000000001</v>
       </c>
       <c r="AJ25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.5734271285726646</v>
+        <f t="shared" si="56"/>
+        <v>8.2424079999999993</v>
       </c>
       <c r="AK25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.6091613998583911</v>
+        <f t="shared" si="56"/>
+        <v>8.3248320800000002</v>
       </c>
       <c r="AL25" s="3">
-        <f t="shared" si="43"/>
-        <v>3.645253013856975</v>
+        <f t="shared" si="56"/>
+        <v>8.4080804007999994</v>
+      </c>
+      <c r="AM25" s="3">
+        <f t="shared" si="56"/>
+        <v>8.4921612048079993</v>
+      </c>
+      <c r="AN25" s="3">
+        <f t="shared" si="56"/>
+        <v>8.5770828168560787</v>
+      </c>
+      <c r="AO25" s="3">
+        <f t="shared" si="56"/>
+        <v>8.6628536450246401</v>
+      </c>
+      <c r="AP25" s="3">
+        <f t="shared" si="56"/>
+        <v>8.7494821814748871</v>
       </c>
     </row>
-    <row r="26" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>41</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" ref="I26:P26" si="44">SUM(I23:I25)</f>
+        <f t="shared" ref="I26:P26" si="57">SUM(I23:I25)</f>
         <v>1.6</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-8.4</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-4.8</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-2.1999999999999997</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-0.99999999999999989</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-89.100000000000009</v>
       </c>
       <c r="O26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" si="44"/>
+        <f t="shared" si="57"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" ref="Q26:R26" si="45">SUM(Q23:Q25)</f>
+        <f t="shared" ref="Q26:R26" si="58">SUM(Q23:Q25)</f>
         <v>0.4</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="58"/>
         <v>-6.3999999999999995</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" ref="S26:V26" si="46">SUM(S23:S25)</f>
+        <f t="shared" ref="S26:W26" si="59">SUM(S23:S25)</f>
         <v>0.20000000000000007</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="59"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="U26" s="3">
-        <f t="shared" si="46"/>
+        <f t="shared" si="59"/>
         <v>-0.20000000000000007</v>
       </c>
       <c r="V26" s="3">
-        <f t="shared" si="46"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="59"/>
+        <v>-35.499999999999993</v>
+      </c>
+      <c r="W26" s="3">
+        <f t="shared" si="59"/>
+        <v>1</v>
       </c>
       <c r="X26" s="3">
-        <f>SUM(X23:X25)</f>
-        <v>36.800000000000011</v>
+        <f t="shared" ref="X26:Z26" si="60">SUM(X23:X25)</f>
+        <v>1</v>
       </c>
       <c r="Y26" s="3">
-        <f>SUM(Y23:Y25)</f>
-        <v>16.7</v>
+        <f t="shared" si="60"/>
+        <v>1</v>
       </c>
       <c r="Z26" s="3">
-        <f>SUM(Z23:Z25)</f>
-        <v>-97.1</v>
-      </c>
-      <c r="AA26" s="3">
-        <f>SUM(AA23:AA25)</f>
-        <v>-6.1</v>
+        <f t="shared" si="60"/>
+        <v>-8</v>
       </c>
       <c r="AB26" s="3">
         <f>SUM(AB23:AB25)</f>
-        <v>0.59999999999999964</v>
+        <v>36.800000000000011</v>
       </c>
       <c r="AC26" s="3">
-        <f t="shared" ref="AC26:AL26" si="47">SUM(AC23:AC25)</f>
-        <v>0</v>
+        <f>SUM(AC23:AC25)</f>
+        <v>16.7</v>
       </c>
       <c r="AD26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f>SUM(AD23:AD25)</f>
+        <v>-97.1</v>
       </c>
       <c r="AE26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f>SUM(AE23:AE25)</f>
+        <v>-6.1</v>
       </c>
       <c r="AF26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f>SUM(AF23:AF25)</f>
+        <v>-35.199999999999989</v>
       </c>
       <c r="AG26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" ref="AG26:AP26" si="61">SUM(AG23:AG25)</f>
+        <v>-5</v>
       </c>
       <c r="AH26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-5.0500000000000007</v>
       </c>
       <c r="AI26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-5.1005000000000003</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-5.151505000000002</v>
       </c>
       <c r="AK26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-5.203020050000001</v>
       </c>
       <c r="AL26" s="3">
-        <f t="shared" si="47"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-5.2550502505000019</v>
+      </c>
+      <c r="AM26" s="3">
+        <f t="shared" si="61"/>
+        <v>-5.3076007530050013</v>
+      </c>
+      <c r="AN26" s="3">
+        <f t="shared" si="61"/>
+        <v>-5.3606767605350516</v>
+      </c>
+      <c r="AO26" s="3">
+        <f t="shared" si="61"/>
+        <v>-5.4142835281404018</v>
+      </c>
+      <c r="AP26" s="3">
+        <f t="shared" si="61"/>
+        <v>-5.4684263634218055</v>
       </c>
     </row>
-    <row r="27" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:P27" si="48">I22-I26</f>
+        <f t="shared" ref="I27:P27" si="62">I22-I26</f>
         <v>14.599999999999996</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>20.099999999999987</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>18.599999999999991</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>14.699999999999992</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>16.999999999999993</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>109.50000000000001</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="62"/>
         <v>21.999999999999993</v>
       </c>
       <c r="Q27" s="8">
-        <f t="shared" ref="Q27:R27" si="49">Q22-Q26</f>
+        <f t="shared" ref="Q27:R27" si="63">Q22-Q26</f>
         <v>22.999999999999993</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="63"/>
         <v>33.89999999999997</v>
       </c>
       <c r="S27" s="8">
-        <f t="shared" ref="S27:V27" si="50">S22-S26</f>
+        <f t="shared" ref="S27:W27" si="64">S22-S26</f>
         <v>20.999999999999989</v>
       </c>
       <c r="T27" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="64"/>
         <v>17.400000000000002</v>
       </c>
       <c r="U27" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="64"/>
         <v>22.399999999999988</v>
       </c>
       <c r="V27" s="8">
-        <f t="shared" si="50"/>
-        <v>26.714000000000009</v>
+        <f t="shared" si="64"/>
+        <v>63.999999999999979</v>
+      </c>
+      <c r="W27" s="8">
+        <f t="shared" si="64"/>
+        <v>22.88000000000001</v>
       </c>
       <c r="X27" s="8">
-        <f>X22-X26</f>
-        <v>-43</v>
+        <f t="shared" ref="X27:Z27" si="65">X22-X26</f>
+        <v>22</v>
       </c>
       <c r="Y27" s="8">
-        <f>Y22-Y26</f>
-        <v>23.899999999999967</v>
+        <f t="shared" si="65"/>
+        <v>22.475999999999999</v>
       </c>
       <c r="Z27" s="8">
-        <f>Z22-Z26</f>
-        <v>159.79999999999993</v>
-      </c>
-      <c r="AA27" s="8">
-        <f>AA22-AA26</f>
-        <v>100.9</v>
+        <f t="shared" si="65"/>
+        <v>34.936300000000003</v>
       </c>
       <c r="AB27" s="8">
         <f>AB22-AB26</f>
-        <v>87.514000000000095</v>
+        <v>-43</v>
       </c>
       <c r="AC27" s="8">
-        <f t="shared" ref="AC27:AL27" si="51">AC22-AC26</f>
-        <v>153.40907999999996</v>
+        <f>AC22-AC26</f>
+        <v>23.899999999999967</v>
       </c>
       <c r="AD27" s="8">
-        <f t="shared" si="51"/>
-        <v>181.69084840000005</v>
+        <f>AD22-AD26</f>
+        <v>159.79999999999993</v>
       </c>
       <c r="AE27" s="8">
-        <f t="shared" si="51"/>
-        <v>193.18287048240012</v>
+        <f>AE22-AE26</f>
+        <v>100.9</v>
       </c>
       <c r="AF27" s="8">
-        <f t="shared" si="51"/>
-        <v>200.88414037786407</v>
+        <f>AF22-AF26</f>
+        <v>87.800000000000011</v>
       </c>
       <c r="AG27" s="8">
-        <f t="shared" si="51"/>
-        <v>207.54566881775571</v>
+        <f t="shared" ref="AG27:AP27" si="66">AG22-AG26</f>
+        <v>102.29229999999995</v>
       </c>
       <c r="AH27" s="8">
-        <f t="shared" si="51"/>
-        <v>213.01626819700471</v>
+        <f t="shared" si="66"/>
+        <v>190.62301511000004</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="51"/>
-        <v>218.60947642386765</v>
+        <f t="shared" si="66"/>
+        <v>205.13686665470004</v>
       </c>
       <c r="AJ27" s="8">
-        <f t="shared" si="51"/>
-        <v>224.32787764389707</v>
+        <f t="shared" si="66"/>
+        <v>213.66051479842812</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="51"/>
-        <v>230.1741090052426</v>
+        <f t="shared" si="66"/>
+        <v>221.16436965166233</v>
       </c>
       <c r="AL27" s="8">
-        <f t="shared" si="51"/>
-        <v>236.15086173189974</v>
+        <f t="shared" si="66"/>
+        <v>227.50490578233348</v>
+      </c>
+      <c r="AM27" s="8">
+        <f t="shared" si="66"/>
+        <v>234.09347395448125</v>
+      </c>
+      <c r="AN27" s="8">
+        <f t="shared" si="66"/>
+        <v>240.95665678842107</v>
+      </c>
+      <c r="AO27" s="8">
+        <f t="shared" si="66"/>
+        <v>248.12586672992904</v>
+      </c>
+      <c r="AP27" s="8">
+        <f t="shared" si="66"/>
+        <v>255.63830201913365</v>
       </c>
     </row>
-    <row r="28" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>42</v>
       </c>
@@ -3629,614 +4114,645 @@
         <v>4</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" ref="V28" si="52">V27*0.15</f>
-        <v>4.0071000000000012</v>
+        <v>8.4</v>
+      </c>
+      <c r="W28" s="3">
+        <f>W27*0.15</f>
+        <v>3.4320000000000013</v>
       </c>
       <c r="X28" s="3">
-        <v>0</v>
+        <f t="shared" ref="X28:Z28" si="67">X27*0.15</f>
+        <v>3.3</v>
       </c>
       <c r="Y28" s="3">
+        <f t="shared" si="67"/>
+        <v>3.3714</v>
+      </c>
+      <c r="Z28" s="3">
+        <f t="shared" si="67"/>
+        <v>5.2404450000000002</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="Z28" s="3">
+      <c r="AD28" s="3">
         <f>SUM(K28:N28)</f>
         <v>6.7000000000000011</v>
       </c>
-      <c r="AA28" s="3">
+      <c r="AE28" s="3">
         <f>SUM(O28:R28)</f>
         <v>17.5</v>
       </c>
-      <c r="AB28" s="3">
+      <c r="AF28" s="3">
         <f>SUM(S28:V28)</f>
-        <v>12.607100000000001</v>
-      </c>
-      <c r="AC28" s="3">
-        <f>AC27*0.15</f>
-        <v>23.011361999999995</v>
-      </c>
-      <c r="AD28" s="3">
-        <f t="shared" ref="AD28:AL28" si="53">AD27*0.15</f>
-        <v>27.253627260000005</v>
-      </c>
-      <c r="AE28" s="3">
-        <f t="shared" si="53"/>
-        <v>28.977430572360017</v>
-      </c>
-      <c r="AF28" s="3">
-        <f t="shared" si="53"/>
-        <v>30.132621056679611</v>
+        <v>17</v>
       </c>
       <c r="AG28" s="3">
-        <f t="shared" si="53"/>
-        <v>31.131850322663354</v>
+        <f>SUM(W28:Z28)</f>
+        <v>15.343845000000002</v>
       </c>
       <c r="AH28" s="3">
-        <f t="shared" si="53"/>
-        <v>31.952440229550703</v>
+        <f t="shared" ref="AH28:AP28" si="68">AH27*0.15</f>
+        <v>28.593452266500005</v>
       </c>
       <c r="AI28" s="3">
-        <f t="shared" si="53"/>
-        <v>32.791421463580143</v>
+        <f t="shared" si="68"/>
+        <v>30.770529998205006</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="53"/>
-        <v>33.649181646584559</v>
+        <f t="shared" si="68"/>
+        <v>32.049077219764214</v>
       </c>
       <c r="AK28" s="3">
-        <f t="shared" si="53"/>
-        <v>34.526116350786388</v>
+        <f t="shared" si="68"/>
+        <v>33.174655447749345</v>
       </c>
       <c r="AL28" s="3">
-        <f t="shared" si="53"/>
-        <v>35.422629259784962</v>
+        <f t="shared" si="68"/>
+        <v>34.125735867350024</v>
+      </c>
+      <c r="AM28" s="3">
+        <f t="shared" si="68"/>
+        <v>35.114021093172184</v>
+      </c>
+      <c r="AN28" s="3">
+        <f t="shared" si="68"/>
+        <v>36.143498518263158</v>
+      </c>
+      <c r="AO28" s="3">
+        <f t="shared" si="68"/>
+        <v>37.218880009489354</v>
+      </c>
+      <c r="AP28" s="3">
+        <f t="shared" si="68"/>
+        <v>38.345745302870043</v>
       </c>
     </row>
-    <row r="29" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:148" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" ref="I29:P29" si="54">I27-I28</f>
+        <f t="shared" ref="I29:P29" si="69">I27-I28</f>
         <v>9.399999999999995</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>20.799999999999986</v>
       </c>
       <c r="K29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>15.29999999999999</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>13.599999999999993</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>16.799999999999994</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>107.40000000000002</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>14.799999999999992</v>
       </c>
       <c r="P29" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="69"/>
         <v>19.199999999999992</v>
       </c>
       <c r="Q29" s="8">
-        <f t="shared" ref="Q29:R29" si="55">Q27-Q28</f>
+        <f t="shared" ref="Q29:R29" si="70">Q27-Q28</f>
         <v>18.199999999999992</v>
       </c>
       <c r="R29" s="8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="70"/>
         <v>28.599999999999969</v>
       </c>
       <c r="S29" s="8">
-        <f t="shared" ref="S29:V29" si="56">S27-S28</f>
+        <f t="shared" ref="S29:W29" si="71">S27-S28</f>
         <v>18.499999999999989</v>
       </c>
       <c r="T29" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="71"/>
         <v>15.300000000000002</v>
       </c>
       <c r="U29" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="71"/>
         <v>18.399999999999988</v>
       </c>
       <c r="V29" s="8">
-        <f t="shared" si="56"/>
-        <v>22.706900000000008</v>
+        <f t="shared" si="71"/>
+        <v>55.59999999999998</v>
+      </c>
+      <c r="W29" s="8">
+        <f t="shared" si="71"/>
+        <v>19.448000000000008</v>
       </c>
       <c r="X29" s="8">
-        <f>X27-X28</f>
-        <v>-43</v>
+        <f t="shared" ref="X29:Z29" si="72">X27-X28</f>
+        <v>18.7</v>
       </c>
       <c r="Y29" s="8">
-        <f>Y27-Y28</f>
-        <v>15.099999999999966</v>
+        <f t="shared" si="72"/>
+        <v>19.104599999999998</v>
       </c>
       <c r="Z29" s="8">
-        <f>Z27-Z28</f>
-        <v>153.09999999999994</v>
-      </c>
-      <c r="AA29" s="8">
-        <f>AA27-AA28</f>
-        <v>83.4</v>
+        <f t="shared" si="72"/>
+        <v>29.695855000000002</v>
       </c>
       <c r="AB29" s="8">
         <f>AB27-AB28</f>
-        <v>74.906900000000093</v>
+        <v>-43</v>
       </c>
       <c r="AC29" s="8">
-        <f t="shared" ref="AC29:AL29" si="57">AC27-AC28</f>
-        <v>130.39771799999997</v>
+        <f>AC27-AC28</f>
+        <v>15.099999999999966</v>
       </c>
       <c r="AD29" s="8">
-        <f t="shared" si="57"/>
-        <v>154.43722114000005</v>
+        <f>AD27-AD28</f>
+        <v>153.09999999999994</v>
       </c>
       <c r="AE29" s="8">
-        <f t="shared" si="57"/>
-        <v>164.2054399100401</v>
+        <f>AE27-AE28</f>
+        <v>83.4</v>
       </c>
       <c r="AF29" s="8">
-        <f t="shared" si="57"/>
-        <v>170.75151932118445</v>
+        <f>AF27-AF28</f>
+        <v>70.800000000000011</v>
       </c>
       <c r="AG29" s="8">
-        <f t="shared" si="57"/>
-        <v>176.41381849509236</v>
+        <f t="shared" ref="AG29:AP29" si="73">AG27-AG28</f>
+        <v>86.948454999999953</v>
       </c>
       <c r="AH29" s="8">
-        <f t="shared" si="57"/>
-        <v>181.06382796745402</v>
+        <f t="shared" si="73"/>
+        <v>162.02956284350003</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="57"/>
-        <v>185.8180549602875</v>
+        <f t="shared" si="73"/>
+        <v>174.36633665649504</v>
       </c>
       <c r="AJ29" s="8">
-        <f t="shared" si="57"/>
-        <v>190.6786959973125</v>
+        <f t="shared" si="73"/>
+        <v>181.61143757866392</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="57"/>
-        <v>195.6479926544562</v>
+        <f t="shared" si="73"/>
+        <v>187.98971420391297</v>
       </c>
       <c r="AL29" s="8">
-        <f t="shared" si="57"/>
-        <v>200.72823247211477</v>
-      </c>
-      <c r="AM29" s="1">
-        <f>AL29*(1+$AO$40)</f>
-        <v>198.72095014739361</v>
-      </c>
-      <c r="AN29" s="1">
-        <f t="shared" ref="AN29:CY29" si="58">AM29*(1+$AO$40)</f>
-        <v>196.73374064591968</v>
-      </c>
-      <c r="AO29" s="1">
-        <f t="shared" si="58"/>
-        <v>194.76640323946049</v>
-      </c>
-      <c r="AP29" s="1">
-        <f t="shared" si="58"/>
-        <v>192.81873920706587</v>
+        <f t="shared" si="73"/>
+        <v>193.37916991498346</v>
+      </c>
+      <c r="AM29" s="8">
+        <f t="shared" si="73"/>
+        <v>198.97945286130908</v>
+      </c>
+      <c r="AN29" s="8">
+        <f t="shared" si="73"/>
+        <v>204.81315827015791</v>
+      </c>
+      <c r="AO29" s="8">
+        <f t="shared" si="73"/>
+        <v>210.9069867204397</v>
+      </c>
+      <c r="AP29" s="8">
+        <f t="shared" si="73"/>
+        <v>217.29255671626362</v>
       </c>
       <c r="AQ29" s="1">
-        <f t="shared" si="58"/>
-        <v>190.89055181499521</v>
+        <f>AP29*(1+$AS$40)</f>
+        <v>215.11963114910097</v>
       </c>
       <c r="AR29" s="1">
-        <f t="shared" si="58"/>
-        <v>188.98164629684524</v>
+        <f t="shared" ref="AR29:DC29" si="74">AQ29*(1+$AS$40)</f>
+        <v>212.96843483760995</v>
       </c>
       <c r="AS29" s="1">
-        <f t="shared" si="58"/>
-        <v>187.0918298338768</v>
+        <f t="shared" si="74"/>
+        <v>210.83875048923386</v>
       </c>
       <c r="AT29" s="1">
-        <f t="shared" si="58"/>
-        <v>185.22091153553802</v>
+        <f t="shared" si="74"/>
+        <v>208.73036298434153</v>
       </c>
       <c r="AU29" s="1">
-        <f t="shared" si="58"/>
-        <v>183.36870242018264</v>
+        <f t="shared" si="74"/>
+        <v>206.64305935449812</v>
       </c>
       <c r="AV29" s="1">
-        <f t="shared" si="58"/>
-        <v>181.53501539598082</v>
+        <f t="shared" si="74"/>
+        <v>204.57662876095313</v>
       </c>
       <c r="AW29" s="1">
-        <f t="shared" si="58"/>
-        <v>179.71966524202102</v>
+        <f t="shared" si="74"/>
+        <v>202.5308624733436</v>
       </c>
       <c r="AX29" s="1">
-        <f t="shared" si="58"/>
-        <v>177.92246858960081</v>
+        <f t="shared" si="74"/>
+        <v>200.50555384861016</v>
       </c>
       <c r="AY29" s="1">
-        <f t="shared" si="58"/>
-        <v>176.14324390370481</v>
+        <f t="shared" si="74"/>
+        <v>198.50049831012407</v>
       </c>
       <c r="AZ29" s="1">
-        <f t="shared" si="58"/>
-        <v>174.38181146466778</v>
+        <f t="shared" si="74"/>
+        <v>196.51549332702282</v>
       </c>
       <c r="BA29" s="1">
-        <f t="shared" si="58"/>
-        <v>172.63799335002111</v>
+        <f t="shared" si="74"/>
+        <v>194.55033839375258</v>
       </c>
       <c r="BB29" s="1">
-        <f t="shared" si="58"/>
-        <v>170.91161341652088</v>
+        <f t="shared" si="74"/>
+        <v>192.60483500981505</v>
       </c>
       <c r="BC29" s="1">
-        <f t="shared" si="58"/>
-        <v>169.20249728235567</v>
+        <f t="shared" si="74"/>
+        <v>190.67878665971691</v>
       </c>
       <c r="BD29" s="1">
-        <f t="shared" si="58"/>
-        <v>167.5104723095321</v>
+        <f t="shared" si="74"/>
+        <v>188.77199879311974</v>
       </c>
       <c r="BE29" s="1">
-        <f t="shared" si="58"/>
-        <v>165.83536758643677</v>
+        <f t="shared" si="74"/>
+        <v>186.88427880518853</v>
       </c>
       <c r="BF29" s="1">
-        <f t="shared" si="58"/>
-        <v>164.17701391057241</v>
+        <f t="shared" si="74"/>
+        <v>185.01543601713664</v>
       </c>
       <c r="BG29" s="1">
-        <f t="shared" si="58"/>
-        <v>162.5352437714667</v>
+        <f t="shared" si="74"/>
+        <v>183.16528165696528</v>
       </c>
       <c r="BH29" s="1">
-        <f t="shared" si="58"/>
-        <v>160.90989133375203</v>
+        <f t="shared" si="74"/>
+        <v>181.33362884039562</v>
       </c>
       <c r="BI29" s="1">
-        <f t="shared" si="58"/>
-        <v>159.3007924204145</v>
+        <f t="shared" si="74"/>
+        <v>179.52029255199167</v>
       </c>
       <c r="BJ29" s="1">
-        <f t="shared" si="58"/>
-        <v>157.70778449621034</v>
+        <f t="shared" si="74"/>
+        <v>177.72508962647174</v>
       </c>
       <c r="BK29" s="1">
-        <f t="shared" si="58"/>
-        <v>156.13070665124823</v>
+        <f t="shared" si="74"/>
+        <v>175.94783873020702</v>
       </c>
       <c r="BL29" s="1">
-        <f t="shared" si="58"/>
-        <v>154.56939958473575</v>
+        <f t="shared" si="74"/>
+        <v>174.18836034290496</v>
       </c>
       <c r="BM29" s="1">
-        <f t="shared" si="58"/>
-        <v>153.02370558888839</v>
+        <f t="shared" si="74"/>
+        <v>172.44647673947591</v>
       </c>
       <c r="BN29" s="1">
-        <f t="shared" si="58"/>
-        <v>151.49346853299951</v>
+        <f t="shared" si="74"/>
+        <v>170.72201197208116</v>
       </c>
       <c r="BO29" s="1">
-        <f t="shared" si="58"/>
-        <v>149.97853384766952</v>
+        <f t="shared" si="74"/>
+        <v>169.01479185236036</v>
       </c>
       <c r="BP29" s="1">
-        <f t="shared" si="58"/>
-        <v>148.47874850919283</v>
+        <f t="shared" si="74"/>
+        <v>167.32464393383677</v>
       </c>
       <c r="BQ29" s="1">
-        <f t="shared" si="58"/>
-        <v>146.99396102410088</v>
+        <f t="shared" si="74"/>
+        <v>165.65139749449841</v>
       </c>
       <c r="BR29" s="1">
-        <f t="shared" si="58"/>
-        <v>145.52402141385988</v>
+        <f t="shared" si="74"/>
+        <v>163.99488351955341</v>
       </c>
       <c r="BS29" s="1">
-        <f t="shared" si="58"/>
-        <v>144.06878119972129</v>
+        <f t="shared" si="74"/>
+        <v>162.35493468435789</v>
       </c>
       <c r="BT29" s="1">
-        <f t="shared" si="58"/>
-        <v>142.62809338772408</v>
+        <f t="shared" si="74"/>
+        <v>160.7313853375143</v>
       </c>
       <c r="BU29" s="1">
-        <f t="shared" si="58"/>
-        <v>141.20181245384683</v>
+        <f t="shared" si="74"/>
+        <v>159.12407148413917</v>
       </c>
       <c r="BV29" s="1">
-        <f t="shared" si="58"/>
-        <v>139.78979432930836</v>
+        <f t="shared" si="74"/>
+        <v>157.53283076929776</v>
       </c>
       <c r="BW29" s="1">
-        <f t="shared" si="58"/>
-        <v>138.39189638601528</v>
+        <f t="shared" si="74"/>
+        <v>155.95750246160478</v>
       </c>
       <c r="BX29" s="1">
-        <f t="shared" si="58"/>
-        <v>137.00797742215511</v>
+        <f t="shared" si="74"/>
+        <v>154.39792743698874</v>
       </c>
       <c r="BY29" s="1">
-        <f t="shared" si="58"/>
-        <v>135.63789764793356</v>
+        <f t="shared" si="74"/>
+        <v>152.85394816261885</v>
       </c>
       <c r="BZ29" s="1">
-        <f t="shared" si="58"/>
-        <v>134.28151867145422</v>
+        <f t="shared" si="74"/>
+        <v>151.32540868099267</v>
       </c>
       <c r="CA29" s="1">
-        <f t="shared" si="58"/>
-        <v>132.93870348473968</v>
+        <f t="shared" si="74"/>
+        <v>149.81215459418274</v>
       </c>
       <c r="CB29" s="1">
-        <f t="shared" si="58"/>
-        <v>131.60931644989228</v>
+        <f t="shared" si="74"/>
+        <v>148.3140330482409</v>
       </c>
       <c r="CC29" s="1">
-        <f t="shared" si="58"/>
-        <v>130.29322328539334</v>
+        <f t="shared" si="74"/>
+        <v>146.8308927177585</v>
       </c>
       <c r="CD29" s="1">
-        <f t="shared" si="58"/>
-        <v>128.99029105253939</v>
+        <f t="shared" si="74"/>
+        <v>145.36258379058091</v>
       </c>
       <c r="CE29" s="1">
-        <f t="shared" si="58"/>
-        <v>127.70038814201399</v>
+        <f t="shared" si="74"/>
+        <v>143.90895795267511</v>
       </c>
       <c r="CF29" s="1">
-        <f t="shared" si="58"/>
-        <v>126.42338426059385</v>
+        <f t="shared" si="74"/>
+        <v>142.46986837314836</v>
       </c>
       <c r="CG29" s="1">
-        <f t="shared" si="58"/>
-        <v>125.15915041798792</v>
+        <f t="shared" si="74"/>
+        <v>141.04516968941687</v>
       </c>
       <c r="CH29" s="1">
-        <f t="shared" si="58"/>
-        <v>123.90755891380803</v>
+        <f t="shared" si="74"/>
+        <v>139.6347179925227</v>
       </c>
       <c r="CI29" s="1">
-        <f t="shared" si="58"/>
-        <v>122.66848332466995</v>
+        <f t="shared" si="74"/>
+        <v>138.23837081259748</v>
       </c>
       <c r="CJ29" s="1">
-        <f t="shared" si="58"/>
-        <v>121.44179849142326</v>
+        <f t="shared" si="74"/>
+        <v>136.8559871044715</v>
       </c>
       <c r="CK29" s="1">
-        <f t="shared" si="58"/>
-        <v>120.22738050650902</v>
+        <f t="shared" si="74"/>
+        <v>135.48742723342679</v>
       </c>
       <c r="CL29" s="1">
-        <f t="shared" si="58"/>
-        <v>119.02510670144393</v>
+        <f t="shared" si="74"/>
+        <v>134.13255296109253</v>
       </c>
       <c r="CM29" s="1">
-        <f t="shared" si="58"/>
-        <v>117.83485563442949</v>
+        <f t="shared" si="74"/>
+        <v>132.79122743148162</v>
       </c>
       <c r="CN29" s="1">
-        <f t="shared" si="58"/>
-        <v>116.6565070780852</v>
+        <f t="shared" si="74"/>
+        <v>131.46331515716679</v>
       </c>
       <c r="CO29" s="1">
-        <f t="shared" si="58"/>
-        <v>115.48994200730435</v>
+        <f t="shared" si="74"/>
+        <v>130.14868200559513</v>
       </c>
       <c r="CP29" s="1">
-        <f t="shared" si="58"/>
-        <v>114.3350425872313</v>
+        <f t="shared" si="74"/>
+        <v>128.84719518553919</v>
       </c>
       <c r="CQ29" s="1">
-        <f t="shared" si="58"/>
-        <v>113.19169216135899</v>
+        <f t="shared" si="74"/>
+        <v>127.55872323368379</v>
       </c>
       <c r="CR29" s="1">
-        <f t="shared" si="58"/>
-        <v>112.05977523974539</v>
+        <f t="shared" si="74"/>
+        <v>126.28313600134696</v>
       </c>
       <c r="CS29" s="1">
-        <f t="shared" si="58"/>
-        <v>110.93917748734793</v>
+        <f t="shared" si="74"/>
+        <v>125.0203046413335</v>
       </c>
       <c r="CT29" s="1">
-        <f t="shared" si="58"/>
-        <v>109.82978571247445</v>
+        <f t="shared" si="74"/>
+        <v>123.77010159492016</v>
       </c>
       <c r="CU29" s="1">
-        <f t="shared" si="58"/>
-        <v>108.7314878553497</v>
+        <f t="shared" si="74"/>
+        <v>122.53240057897096</v>
       </c>
       <c r="CV29" s="1">
-        <f t="shared" si="58"/>
-        <v>107.6441729767962</v>
+        <f t="shared" si="74"/>
+        <v>121.30707657318125</v>
       </c>
       <c r="CW29" s="1">
-        <f t="shared" si="58"/>
-        <v>106.56773124702823</v>
+        <f t="shared" si="74"/>
+        <v>120.09400580744943</v>
       </c>
       <c r="CX29" s="1">
-        <f t="shared" si="58"/>
-        <v>105.50205393455795</v>
+        <f t="shared" si="74"/>
+        <v>118.89306574937494</v>
       </c>
       <c r="CY29" s="1">
-        <f t="shared" si="58"/>
-        <v>104.44703339521237</v>
+        <f t="shared" si="74"/>
+        <v>117.70413509188118</v>
       </c>
       <c r="CZ29" s="1">
-        <f t="shared" ref="CZ29:EN29" si="59">CY29*(1+$AO$40)</f>
-        <v>103.40256306126025</v>
+        <f t="shared" si="74"/>
+        <v>116.52709374096237</v>
       </c>
       <c r="DA29" s="1">
-        <f t="shared" si="59"/>
-        <v>102.36853743064765</v>
+        <f t="shared" si="74"/>
+        <v>115.36182280355274</v>
       </c>
       <c r="DB29" s="1">
-        <f t="shared" si="59"/>
-        <v>101.34485205634117</v>
+        <f t="shared" si="74"/>
+        <v>114.20820457551721</v>
       </c>
       <c r="DC29" s="1">
-        <f t="shared" si="59"/>
-        <v>100.33140353577775</v>
+        <f t="shared" si="74"/>
+        <v>113.06612252976204</v>
       </c>
       <c r="DD29" s="1">
-        <f t="shared" si="59"/>
-        <v>99.328089500419978</v>
+        <f t="shared" ref="DD29:ER29" si="75">DC29*(1+$AS$40)</f>
+        <v>111.93546130446443</v>
       </c>
       <c r="DE29" s="1">
-        <f t="shared" si="59"/>
-        <v>98.334808605415773</v>
+        <f t="shared" si="75"/>
+        <v>110.81610669141978</v>
       </c>
       <c r="DF29" s="1">
-        <f t="shared" si="59"/>
-        <v>97.351460519361609</v>
+        <f t="shared" si="75"/>
+        <v>109.70794562450558</v>
       </c>
       <c r="DG29" s="1">
-        <f t="shared" si="59"/>
-        <v>96.377945914167995</v>
+        <f t="shared" si="75"/>
+        <v>108.61086616826053</v>
       </c>
       <c r="DH29" s="1">
-        <f t="shared" si="59"/>
-        <v>95.414166455026319</v>
+        <f t="shared" si="75"/>
+        <v>107.52475750657793</v>
       </c>
       <c r="DI29" s="1">
-        <f t="shared" si="59"/>
-        <v>94.460024790476055</v>
+        <f t="shared" si="75"/>
+        <v>106.44950993151215</v>
       </c>
       <c r="DJ29" s="1">
-        <f t="shared" si="59"/>
-        <v>93.515424542571296</v>
+        <f t="shared" si="75"/>
+        <v>105.38501483219703</v>
       </c>
       <c r="DK29" s="1">
-        <f t="shared" si="59"/>
-        <v>92.580270297145589</v>
+        <f t="shared" si="75"/>
+        <v>104.33116468387506</v>
       </c>
       <c r="DL29" s="1">
-        <f t="shared" si="59"/>
-        <v>91.654467594174136</v>
+        <f t="shared" si="75"/>
+        <v>103.28785303703631</v>
       </c>
       <c r="DM29" s="1">
-        <f t="shared" si="59"/>
-        <v>90.7379229182324</v>
+        <f t="shared" si="75"/>
+        <v>102.25497450666595</v>
       </c>
       <c r="DN29" s="1">
-        <f t="shared" si="59"/>
-        <v>89.830543689050074</v>
+        <f t="shared" si="75"/>
+        <v>101.23242476159929</v>
       </c>
       <c r="DO29" s="1">
-        <f t="shared" si="59"/>
-        <v>88.932238252159578</v>
+        <f t="shared" si="75"/>
+        <v>100.2201005139833</v>
       </c>
       <c r="DP29" s="1">
-        <f t="shared" si="59"/>
-        <v>88.04291586963798</v>
+        <f t="shared" si="75"/>
+        <v>99.217899508843459</v>
       </c>
       <c r="DQ29" s="1">
-        <f t="shared" si="59"/>
-        <v>87.162486710941593</v>
+        <f t="shared" si="75"/>
+        <v>98.225720513755022</v>
       </c>
       <c r="DR29" s="1">
-        <f t="shared" si="59"/>
-        <v>86.290861843832175</v>
+        <f t="shared" si="75"/>
+        <v>97.243463308617464</v>
       </c>
       <c r="DS29" s="1">
-        <f t="shared" si="59"/>
-        <v>85.42795322539385</v>
+        <f t="shared" si="75"/>
+        <v>96.271028675531284</v>
       </c>
       <c r="DT29" s="1">
-        <f t="shared" si="59"/>
-        <v>84.573673693139909</v>
+        <f t="shared" si="75"/>
+        <v>95.308318388775973</v>
       </c>
       <c r="DU29" s="1">
-        <f t="shared" si="59"/>
-        <v>83.727936956208509</v>
+        <f t="shared" si="75"/>
+        <v>94.355235204888217</v>
       </c>
       <c r="DV29" s="1">
-        <f t="shared" si="59"/>
-        <v>82.890657586646427</v>
+        <f t="shared" si="75"/>
+        <v>93.411682852839334</v>
       </c>
       <c r="DW29" s="1">
-        <f t="shared" si="59"/>
-        <v>82.061751010779957</v>
+        <f t="shared" si="75"/>
+        <v>92.477566024310946</v>
       </c>
       <c r="DX29" s="1">
-        <f t="shared" si="59"/>
-        <v>81.241133500672163</v>
+        <f t="shared" si="75"/>
+        <v>91.552790364067832</v>
       </c>
       <c r="DY29" s="1">
-        <f t="shared" si="59"/>
-        <v>80.428722165665434</v>
+        <f t="shared" si="75"/>
+        <v>90.637262460427152</v>
       </c>
       <c r="DZ29" s="1">
-        <f t="shared" si="59"/>
-        <v>79.624434944008783</v>
+        <f t="shared" si="75"/>
+        <v>89.730889835822879</v>
       </c>
       <c r="EA29" s="1">
-        <f t="shared" si="59"/>
-        <v>78.828190594568696</v>
+        <f t="shared" si="75"/>
+        <v>88.833580937464646</v>
       </c>
       <c r="EB29" s="1">
-        <f t="shared" si="59"/>
-        <v>78.039908688623015</v>
+        <f t="shared" si="75"/>
+        <v>87.945245128089994</v>
       </c>
       <c r="EC29" s="1">
-        <f t="shared" si="59"/>
-        <v>77.259509601736781</v>
+        <f t="shared" si="75"/>
+        <v>87.065792676809096</v>
       </c>
       <c r="ED29" s="1">
-        <f t="shared" si="59"/>
-        <v>76.486914505719412</v>
+        <f t="shared" si="75"/>
+        <v>86.195134750041007</v>
       </c>
       <c r="EE29" s="1">
-        <f t="shared" si="59"/>
-        <v>75.722045360662221</v>
+        <f t="shared" si="75"/>
+        <v>85.333183402540598</v>
       </c>
       <c r="EF29" s="1">
-        <f t="shared" si="59"/>
-        <v>74.964824907055601</v>
+        <f t="shared" si="75"/>
+        <v>84.479851568515187</v>
       </c>
       <c r="EG29" s="1">
-        <f t="shared" si="59"/>
-        <v>74.21517665798504</v>
+        <f t="shared" si="75"/>
+        <v>83.635053052830031</v>
       </c>
       <c r="EH29" s="1">
-        <f t="shared" si="59"/>
-        <v>73.473024891405188</v>
+        <f t="shared" si="75"/>
+        <v>82.798702522301724</v>
       </c>
       <c r="EI29" s="1">
-        <f t="shared" si="59"/>
-        <v>72.738294642491141</v>
+        <f t="shared" si="75"/>
+        <v>81.9707154970787</v>
       </c>
       <c r="EJ29" s="1">
-        <f t="shared" si="59"/>
-        <v>72.010911696066231</v>
+        <f t="shared" si="75"/>
+        <v>81.151008342107914</v>
       </c>
       <c r="EK29" s="1">
-        <f t="shared" si="59"/>
-        <v>71.290802579105573</v>
+        <f t="shared" si="75"/>
+        <v>80.339498258686831</v>
       </c>
       <c r="EL29" s="1">
-        <f t="shared" si="59"/>
-        <v>70.577894553314522</v>
+        <f t="shared" si="75"/>
+        <v>79.536103276099965</v>
       </c>
       <c r="EM29" s="1">
-        <f t="shared" si="59"/>
-        <v>69.872115607781382</v>
+        <f t="shared" si="75"/>
+        <v>78.740742243338971</v>
       </c>
       <c r="EN29" s="1">
-        <f t="shared" si="59"/>
-        <v>69.173394451703572</v>
+        <f t="shared" si="75"/>
+        <v>77.953334820905582</v>
+      </c>
+      <c r="EO29" s="1">
+        <f t="shared" si="75"/>
+        <v>77.173801472696525</v>
+      </c>
+      <c r="EP29" s="1">
+        <f t="shared" si="75"/>
+        <v>76.402063457969561</v>
+      </c>
+      <c r="EQ29" s="1">
+        <f t="shared" si="75"/>
+        <v>75.638042823389867</v>
+      </c>
+      <c r="ER29" s="1">
+        <f t="shared" si="75"/>
+        <v>74.881662395155971</v>
       </c>
     </row>
-    <row r="30" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>2</v>
       </c>
@@ -4285,194 +4801,226 @@
         <f>89.6</f>
         <v>89.6</v>
       </c>
+      <c r="W30" s="3">
+        <f>89.6</f>
+        <v>89.6</v>
+      </c>
       <c r="X30" s="3">
+        <f t="shared" ref="X30:Z30" si="76">89.6</f>
+        <v>89.6</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="76"/>
+        <v>89.6</v>
+      </c>
+      <c r="Z30" s="3">
+        <f t="shared" si="76"/>
+        <v>89.6</v>
+      </c>
+      <c r="AB30" s="3">
         <v>88.5</v>
       </c>
-      <c r="Y30" s="3">
+      <c r="AC30" s="3">
         <v>88.5</v>
       </c>
-      <c r="Z30" s="3">
+      <c r="AD30" s="3">
         <v>88.5</v>
       </c>
-      <c r="AA30" s="3">
+      <c r="AE30" s="3">
         <v>88.5</v>
       </c>
-      <c r="AB30" s="3">
-        <f t="shared" ref="AB30:AL30" si="60">89.6</f>
+      <c r="AF30" s="3">
+        <f t="shared" ref="AF30:AP30" si="77">89.6</f>
         <v>89.6</v>
       </c>
-      <c r="AC30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AG30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AD30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AH30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AE30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AI30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AF30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AJ30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AG30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AK30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AH30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AL30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AI30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AM30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AJ30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AN30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AK30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AO30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
-      <c r="AL30" s="3">
-        <f t="shared" si="60"/>
+      <c r="AP30" s="3">
+        <f t="shared" si="77"/>
         <v>89.6</v>
       </c>
     </row>
-    <row r="31" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:148" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>44</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" ref="I31:P31" si="61">I29/I30</f>
+        <f t="shared" ref="I31:P31" si="78">I29/I30</f>
         <v>0.10621468926553666</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.23502824858757046</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.17288135593220327</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.15367231638418072</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.18983050847457619</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>1.2135593220338985</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.167231638418079</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="78"/>
         <v>0.21694915254237279</v>
       </c>
       <c r="Q31" s="7">
-        <f t="shared" ref="Q31:R31" si="62">Q29/Q30</f>
+        <f t="shared" ref="Q31:R31" si="79">Q29/Q30</f>
         <v>0.2056497175141242</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="79"/>
         <v>0.32316384180790925</v>
       </c>
       <c r="S31" s="7">
-        <f t="shared" ref="S31:V31" si="63">S29/S30</f>
+        <f t="shared" ref="S31:W31" si="80">S29/S30</f>
         <v>0.20670391061452503</v>
       </c>
       <c r="T31" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="80"/>
         <v>0.1707589285714286</v>
       </c>
       <c r="U31" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="80"/>
         <v>0.20535714285714274</v>
       </c>
       <c r="V31" s="7">
-        <f t="shared" si="63"/>
-        <v>0.25342522321428584</v>
+        <f t="shared" si="80"/>
+        <v>0.62053571428571408</v>
+      </c>
+      <c r="W31" s="7">
+        <f t="shared" si="80"/>
+        <v>0.21705357142857151</v>
       </c>
       <c r="X31" s="7">
-        <f>X29/X30</f>
-        <v>-0.48587570621468928</v>
+        <f t="shared" ref="X31:Z31" si="81">X29/X30</f>
+        <v>0.20870535714285715</v>
       </c>
       <c r="Y31" s="7">
-        <f>Y29/Y30</f>
-        <v>0.17062146892655328</v>
+        <f t="shared" si="81"/>
+        <v>0.21322098214285712</v>
       </c>
       <c r="Z31" s="7">
-        <f>Z29/Z30</f>
-        <v>1.729943502824858</v>
-      </c>
-      <c r="AA31" s="7">
-        <f>AA29/AA30</f>
-        <v>0.94237288135593222</v>
+        <f t="shared" si="81"/>
+        <v>0.33142695312500003</v>
       </c>
       <c r="AB31" s="7">
         <f>AB29/AB30</f>
-        <v>0.83601450892857254</v>
+        <v>-0.48587570621468928</v>
       </c>
       <c r="AC31" s="7">
-        <f t="shared" ref="AC31:AL31" si="64">AC29/AC30</f>
-        <v>1.4553316741071427</v>
+        <f>AC29/AC30</f>
+        <v>0.17062146892655328</v>
       </c>
       <c r="AD31" s="7">
-        <f t="shared" si="64"/>
-        <v>1.7236297002232148</v>
+        <f>AD29/AD30</f>
+        <v>1.729943502824858</v>
       </c>
       <c r="AE31" s="7">
-        <f t="shared" si="64"/>
-        <v>1.8326499989959835</v>
+        <f>AE29/AE30</f>
+        <v>0.94237288135593222</v>
       </c>
       <c r="AF31" s="7">
-        <f t="shared" si="64"/>
-        <v>1.9057089209953622</v>
+        <f>AF29/AF30</f>
+        <v>0.79017857142857162</v>
       </c>
       <c r="AG31" s="7">
-        <f t="shared" si="64"/>
-        <v>1.9689042242755845</v>
+        <f t="shared" ref="AG31:AP31" si="82">AG29/AG30</f>
+        <v>0.97040686383928521</v>
       </c>
       <c r="AH31" s="7">
-        <f t="shared" si="64"/>
-        <v>2.0208016514224778</v>
+        <f t="shared" si="82"/>
+        <v>1.8083656567354915</v>
       </c>
       <c r="AI31" s="7">
-        <f t="shared" si="64"/>
-        <v>2.0738622205389232</v>
+        <f t="shared" si="82"/>
+        <v>1.9460528644698107</v>
       </c>
       <c r="AJ31" s="7">
-        <f t="shared" si="64"/>
-        <v>2.1281104463985772</v>
+        <f t="shared" si="82"/>
+        <v>2.0269133658333027</v>
       </c>
       <c r="AK31" s="7">
-        <f t="shared" si="64"/>
-        <v>2.1835713465899129</v>
+        <f t="shared" si="82"/>
+        <v>2.0980994888829572</v>
       </c>
       <c r="AL31" s="7">
-        <f t="shared" si="64"/>
-        <v>2.2402704516977097</v>
+        <f t="shared" si="82"/>
+        <v>2.1582496642297264</v>
+      </c>
+      <c r="AM31" s="7">
+        <f t="shared" si="82"/>
+        <v>2.2207528221128245</v>
+      </c>
+      <c r="AN31" s="7">
+        <f t="shared" si="82"/>
+        <v>2.2858611414080126</v>
+      </c>
+      <c r="AO31" s="7">
+        <f t="shared" si="82"/>
+        <v>2.3538726196477646</v>
+      </c>
+      <c r="AP31" s="7">
+        <f t="shared" si="82"/>
+        <v>2.4251401419225851</v>
       </c>
     </row>
-    <row r="32" spans="2:144" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:148" x14ac:dyDescent="0.3">
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
-      <c r="Y32" s="9"/>
-      <c r="Z32" s="9"/>
-      <c r="AA32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>92</v>
       </c>
@@ -4481,373 +5029,421 @@
         <v>0.44194756554307113</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:S33" si="65">H3/D3-1</f>
+        <f t="shared" ref="H33:S33" si="83">H3/D3-1</f>
         <v>0.49134948096885833</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.40687679083094563</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.54768392370572183</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.25974025974025983</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.24825986078886308</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.23828920570264756</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.19366197183098599</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.2082474226804123</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.2007434944237918</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.26315789473684204</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.37610619469026552</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="83"/>
         <v>0.63139931740614319</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:T35" si="66">T3/P3-1</f>
+        <f t="shared" ref="T33:T35" si="84">T3/P3-1</f>
         <v>0.43808049535603732</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" ref="U33:U35" si="67">U3/Q3-1</f>
+        <f t="shared" ref="U33:U35" si="85">U3/Q3-1</f>
         <v>0.24869791666666674</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33:V35" si="68">V3/R3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="V33:V35" si="86">V3/R3-1</f>
+        <v>0.2261521972132905</v>
+      </c>
+      <c r="W33" s="10">
+        <f t="shared" ref="W33:W35" si="87">W3/S3-1</f>
+        <v>0.19142259414225959</v>
+      </c>
+      <c r="X33" s="10">
+        <f t="shared" ref="X33:X35" si="88">X3/T3-1</f>
+        <v>0.237588805166846</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33:Z33" si="69">Y3/X3-1</f>
+        <f t="shared" ref="Y33:Y35" si="89">Y3/U3-1</f>
+        <v>0.22203388946819591</v>
+      </c>
+      <c r="Z33" s="10">
+        <f t="shared" ref="Z33:Z35" si="90">Z3/V3-1</f>
+        <v>8.5997377622377691E-2</v>
+      </c>
+      <c r="AC33" s="10">
+        <f t="shared" ref="AC33:AD33" si="91">AC3/AB3-1</f>
         <v>0.47405660377358494</v>
       </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="69"/>
+      <c r="AD33" s="10">
+        <f t="shared" si="91"/>
         <v>0.23146666666666649</v>
       </c>
-      <c r="AA33" s="10">
-        <f>AA3/Z3-1</f>
+      <c r="AE33" s="10">
+        <f>AE3/AD3-1</f>
         <v>0.27024686011260313</v>
       </c>
-      <c r="AB33" s="10">
-        <f>AB3/AA3-1</f>
-        <v>0.31957040572792339</v>
-      </c>
-      <c r="AC33" s="10">
-        <f t="shared" ref="AC33:AL33" si="70">AC3/AB3-1</f>
-        <v>0.17999999999999994</v>
-      </c>
-      <c r="AD33" s="10">
-        <f t="shared" si="70"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AE33" s="10">
-        <f t="shared" si="70"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
       <c r="AF33" s="10">
-        <f t="shared" si="70"/>
+        <f>AF3/AE3-1</f>
+        <v>0.35969996590521625</v>
+      </c>
+      <c r="AG33" s="10">
+        <f t="shared" ref="AG33:AP33" si="92">AG3/AF3-1</f>
+        <v>0.17929576228686095</v>
+      </c>
+      <c r="AH33" s="10">
+        <f t="shared" si="92"/>
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AI33" s="10">
+        <f t="shared" si="92"/>
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AJ33" s="10">
+        <f t="shared" si="92"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AG33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AK33" s="10">
+        <f t="shared" si="92"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AH33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AL33" s="10">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AM33" s="10">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AN33" s="10">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AO33" s="10">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL33" s="10">
-        <f t="shared" si="70"/>
+      <c r="AP33" s="10">
+        <f t="shared" si="92"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>93</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" ref="G34:S34" si="71">G4/C4-1</f>
+        <f t="shared" ref="G34:S34" si="93">G4/C4-1</f>
         <v>0.36752136752136755</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.13087248322147649</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.15309446254071668</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.12068965517241392</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.18124999999999991</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.15430267062314518</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.15254237288135597</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.1461538461538463</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.14021164021164023</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.14395886889460163</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.13480392156862742</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>0.17002237136465315</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="93"/>
         <v>8.1206496519721671E-2</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>0.11460674157303363</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>0.20086393088552934</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="68"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="86"/>
+        <v>0.19120458891013392</v>
+      </c>
+      <c r="W34" s="10">
+        <f t="shared" si="87"/>
+        <v>0.18562231759656656</v>
+      </c>
+      <c r="X34" s="10">
+        <f t="shared" si="88"/>
+        <v>0.12439516129032269</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" ref="Y34:AA34" si="72">Y4/X4-1</f>
+        <f t="shared" si="89"/>
+        <v>2.2434802158273426E-2</v>
+      </c>
+      <c r="Z34" s="10">
+        <f t="shared" si="90"/>
+        <v>-3.2668539325842572E-2</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" ref="AC34:AE34" si="94">AC4/AB4-1</f>
         <v>0.18028643639427111</v>
       </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="72"/>
+      <c r="AD34" s="10">
+        <f t="shared" si="94"/>
         <v>0.15774446823697352</v>
       </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="72"/>
+      <c r="AE34" s="10">
+        <f t="shared" si="94"/>
         <v>0.14796547472256472</v>
       </c>
-      <c r="AB34" s="10">
-        <f t="shared" ref="AB34:AL34" si="73">AB4/AA4-1</f>
-        <v>0.12422126745435036</v>
-      </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="73"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AF34" s="10">
+        <f t="shared" ref="AF34:AP34" si="95">AF4/AE4-1</f>
+        <v>0.14983888292158998</v>
+      </c>
+      <c r="AG34" s="10">
+        <f t="shared" si="95"/>
+        <v>6.5540051377860786E-2</v>
+      </c>
+      <c r="AH34" s="10">
+        <f t="shared" si="95"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AI34" s="10">
+        <f t="shared" si="95"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AJ34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AK34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AL34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AM34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AN34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AK34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AO34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AL34" s="10">
-        <f t="shared" si="73"/>
+      <c r="AP34" s="10">
+        <f t="shared" si="95"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>94</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" ref="G35:S35" si="74">G5/C5-1</f>
+        <f t="shared" ref="G35:S35" si="96">G5/C5-1</f>
         <v>-0.21428571428571419</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.2857142857142857</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.58333333333333326</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.36363636363636376</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>0.5</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>0.25</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.8571428571428571</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.9</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>-0.6</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="74"/>
+        <f t="shared" si="96"/>
         <v>4</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>-0.16666666666666663</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>3</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>1.5</v>
       </c>
+      <c r="W35" s="10">
+        <f t="shared" si="87"/>
+        <v>0.7</v>
+      </c>
+      <c r="X35" s="10">
+        <f t="shared" si="88"/>
+        <v>0.71599999999999997</v>
+      </c>
       <c r="Y35" s="10">
-        <f t="shared" ref="Y35:AA35" si="75">Y5/X5-1</f>
+        <f t="shared" si="89"/>
+        <v>1.1864374999999998</v>
+      </c>
+      <c r="Z35" s="10">
+        <f t="shared" si="90"/>
+        <v>0.85430000000000006</v>
+      </c>
+      <c r="AC35" s="10">
+        <f t="shared" ref="AC35:AE35" si="97">AC5/AB5-1</f>
         <v>-0.31999999999999995</v>
       </c>
-      <c r="Z35" s="10">
-        <f t="shared" si="75"/>
+      <c r="AD35" s="10">
+        <f t="shared" si="97"/>
         <v>8.8235294117646967E-2</v>
       </c>
-      <c r="AA35" s="10">
-        <f t="shared" si="75"/>
+      <c r="AE35" s="10">
+        <f t="shared" si="97"/>
         <v>-0.72972972972972983</v>
       </c>
-      <c r="AB35" s="10">
-        <f t="shared" ref="AB35:AL35" si="76">AB5/AA5-1</f>
+      <c r="AF35" s="10">
+        <f t="shared" ref="AF35:AP35" si="98">AF5/AE5-1</f>
         <v>0.89999999999999991</v>
       </c>
-      <c r="AC35" s="10">
-        <f t="shared" si="76"/>
-        <v>-1</v>
-      </c>
-      <c r="AD35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL35" s="10" t="e">
-        <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
+      <c r="AG35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.8472236842105263</v>
+      </c>
+      <c r="AH35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AI35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AJ35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AK35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AL35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AM35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AN35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AO35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="AP35" s="10">
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="36" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>46</v>
       </c>
@@ -4856,100 +5452,116 @@
         <v>0.20140515222482436</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" ref="N36:R36" si="77">N8/J8-1</f>
+        <f t="shared" ref="N36:R36" si="99">N8/J8-1</f>
         <v>0.17738589211618261</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="99"/>
         <v>0.17221584385763489</v>
       </c>
       <c r="P36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="99"/>
         <v>0.17709437963944863</v>
       </c>
       <c r="Q36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="99"/>
         <v>0.20760233918128645</v>
       </c>
       <c r="R36" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="99"/>
         <v>0.2854625550660792</v>
       </c>
       <c r="S36" s="9">
-        <f t="shared" ref="S36" si="78">S8/O8-1</f>
+        <f t="shared" ref="S36" si="100">S8/O8-1</f>
         <v>0.39764936336924572</v>
       </c>
       <c r="T36" s="9">
-        <f t="shared" ref="T36" si="79">T8/P8-1</f>
+        <f t="shared" ref="T36" si="101">T8/P8-1</f>
         <v>0.28828828828828845</v>
       </c>
       <c r="U36" s="9">
-        <f t="shared" ref="U36" si="80">U8/Q8-1</f>
+        <f t="shared" ref="U36" si="102">U8/Q8-1</f>
         <v>0.2276029055690072</v>
       </c>
       <c r="V36" s="9">
-        <f t="shared" ref="V36" si="81">V8/R8-1</f>
-        <v>0.10116518163125465</v>
-      </c>
-      <c r="X36" s="9"/>
+        <f t="shared" ref="V36" si="103">V8/R8-1</f>
+        <v>0.21041809458533267</v>
+      </c>
+      <c r="W36" s="9">
+        <f t="shared" ref="W36" si="104">W8/S8-1</f>
+        <v>0.19131044148563436</v>
+      </c>
+      <c r="X36" s="9">
+        <f t="shared" ref="X36" si="105">X8/T8-1</f>
+        <v>0.19999999999999996</v>
+      </c>
       <c r="Y36" s="9">
-        <f>Y8/X8-1</f>
+        <f t="shared" ref="Y36" si="106">Y8/U8-1</f>
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="Z36" s="9">
+        <f t="shared" ref="Z36" si="107">Z8/V8-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9">
+        <f>AC8/AB8-1</f>
         <v>0.31809145129224659</v>
       </c>
-      <c r="Z36" s="9">
-        <f t="shared" ref="Z36:AL36" si="82">Z8/Y8-1</f>
+      <c r="AD36" s="9">
+        <f t="shared" ref="AD36:AP36" si="108">AD8/AC8-1</f>
         <v>0.19909502262443413</v>
       </c>
-      <c r="AA36" s="9">
-        <f t="shared" si="82"/>
+      <c r="AE36" s="9">
+        <f t="shared" si="108"/>
         <v>0.2148427672955977</v>
       </c>
-      <c r="AB36" s="9">
-        <f t="shared" si="82"/>
-        <v>0.23930420376889638</v>
-      </c>
-      <c r="AC36" s="9">
-        <f t="shared" si="82"/>
-        <v>0.1338856398088426</v>
-      </c>
-      <c r="AD36" s="9">
-        <f t="shared" si="82"/>
-        <v>9.3840891313279551E-2</v>
-      </c>
-      <c r="AE36" s="9">
-        <f t="shared" si="82"/>
-        <v>5.0673184309673935E-2</v>
-      </c>
       <c r="AF36" s="9">
-        <f t="shared" si="82"/>
-        <v>3.3904466644498532E-2</v>
+        <f t="shared" si="108"/>
+        <v>0.27231310830399669</v>
       </c>
       <c r="AG36" s="9">
-        <f t="shared" si="82"/>
-        <v>2.6993221219562935E-2</v>
+        <f t="shared" si="108"/>
+        <v>0.1424886067708333</v>
       </c>
       <c r="AH36" s="9">
-        <f t="shared" si="82"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="108"/>
+        <v>0.10780000000000034</v>
       </c>
       <c r="AI36" s="9">
-        <f t="shared" si="82"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="108"/>
+        <v>5.8499729192994954E-2</v>
       </c>
       <c r="AJ36" s="9">
-        <f t="shared" si="82"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="108"/>
+        <v>3.5044541815409502E-2</v>
       </c>
       <c r="AK36" s="9">
-        <f t="shared" si="82"/>
-        <v>2.000000000000024E-2</v>
+        <f t="shared" si="108"/>
+        <v>2.8284395682014907E-2</v>
       </c>
       <c r="AL36" s="9">
-        <f t="shared" si="82"/>
-        <v>1.9999999999999796E-2</v>
+        <f t="shared" si="108"/>
+        <v>2.1495350831958415E-2</v>
+      </c>
+      <c r="AM36" s="9">
+        <f t="shared" si="108"/>
+        <v>2.1756660954833196E-2</v>
+      </c>
+      <c r="AN36" s="9">
+        <f t="shared" si="108"/>
+        <v>2.2063106829986356E-2</v>
+      </c>
+      <c r="AO36" s="9">
+        <f t="shared" si="108"/>
+        <v>2.2422285061890479E-2</v>
+      </c>
+      <c r="AP36" s="9">
+        <f t="shared" si="108"/>
+        <v>2.2842995616133788E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>65</v>
       </c>
@@ -4958,93 +5570,109 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="I37" s="10">
-        <f t="shared" ref="I37:R37" si="83">(I8-I9)/I8</f>
+        <f t="shared" ref="I37:R37" si="109">(I8-I9)/I8</f>
         <v>0.98829039812646369</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.99170124481327804</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.99081515499425954</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.98833510074231179</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.99317738791422994</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.99559471365638763</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.9627815866797258</v>
       </c>
       <c r="P37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.98288288288288284</v>
       </c>
       <c r="Q37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.98547215496368046</v>
       </c>
       <c r="R37" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="109"/>
         <v>0.98286497601096645</v>
       </c>
       <c r="S37" s="10">
-        <f t="shared" ref="S37:V37" si="84">(S8-S9)/S8</f>
+        <f t="shared" ref="S37:V37" si="110">(S8-S9)/S8</f>
         <v>0.98458304134548014</v>
       </c>
       <c r="T37" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="110"/>
         <v>0.98391608391608387</v>
       </c>
       <c r="U37" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="110"/>
         <v>0.98553583168967795</v>
       </c>
       <c r="V37" s="10">
-        <f t="shared" si="84"/>
-        <v>0.98</v>
+        <f t="shared" si="110"/>
+        <v>0.98527746319365805</v>
+      </c>
+      <c r="W37" s="10">
+        <f t="shared" ref="W37:Z37" si="111">(W8-W9)/W8</f>
+        <v>0.9900000000000001</v>
       </c>
       <c r="X37" s="10">
-        <f t="shared" ref="X37:AB37" si="85">(X8-X9)/X8</f>
+        <f t="shared" si="111"/>
+        <v>0.99</v>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="111"/>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="Z37" s="10">
+        <f t="shared" si="111"/>
+        <v>0.99</v>
+      </c>
+      <c r="AB37" s="10">
+        <f t="shared" ref="AB37:AF37" si="112">(AB8-AB9)/AB8</f>
         <v>0.98210735586481113</v>
       </c>
-      <c r="Y37" s="10">
-        <f t="shared" si="85"/>
+      <c r="AC37" s="10">
+        <f t="shared" si="112"/>
         <v>0.98763197586726992</v>
       </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="85"/>
+      <c r="AD37" s="10">
+        <f t="shared" si="112"/>
         <v>0.99220125786163516</v>
       </c>
-      <c r="AA37" s="10">
-        <f t="shared" si="85"/>
+      <c r="AE37" s="10">
+        <f t="shared" si="112"/>
         <v>0.979291778836198</v>
       </c>
-      <c r="AB37" s="10">
-        <f t="shared" si="85"/>
-        <v>0.98343548440998574</v>
-      </c>
-      <c r="AC37" s="10"/>
-      <c r="AD37" s="10"/>
-      <c r="AE37" s="10"/>
-      <c r="AF37" s="10"/>
+      <c r="AF37" s="10">
+        <f t="shared" si="112"/>
+        <v>0.98486328125000011</v>
+      </c>
       <c r="AG37" s="10"/>
       <c r="AH37" s="10"/>
       <c r="AI37" s="10"/>
       <c r="AJ37" s="10"/>
       <c r="AK37" s="10"/>
       <c r="AL37" s="10"/>
+      <c r="AM37" s="10"/>
+      <c r="AN37" s="10"/>
+      <c r="AO37" s="10"/>
+      <c r="AP37" s="10"/>
     </row>
-    <row r="38" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>66</v>
       </c>
@@ -5053,39 +5681,39 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="I38" s="10">
-        <f t="shared" ref="I38:Q38" si="86">(I8-I10)/I8</f>
+        <f t="shared" ref="I38:Q38" si="113">(I8-I10)/I8</f>
         <v>0.99063231850117095</v>
       </c>
       <c r="J38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.99066390041493768</v>
       </c>
       <c r="K38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.98966704936854188</v>
       </c>
       <c r="L38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.98833510074231179</v>
       </c>
       <c r="M38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.98830409356725146</v>
       </c>
       <c r="N38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.99030837004405292</v>
       </c>
       <c r="O38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.99020568070519099</v>
       </c>
       <c r="P38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.99189189189189186</v>
       </c>
       <c r="Q38" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="113"/>
         <v>0.99273607748184012</v>
       </c>
       <c r="R38" s="10">
@@ -5093,53 +5721,69 @@
         <v>0.99246058944482529</v>
       </c>
       <c r="S38" s="10">
-        <f t="shared" ref="S38:V38" si="87">(S8-S10)/S8</f>
+        <f t="shared" ref="S38:V38" si="114">(S8-S10)/S8</f>
         <v>0.99369306236860544</v>
       </c>
       <c r="T38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="114"/>
         <v>0.98951048951048948</v>
       </c>
       <c r="U38" s="10">
-        <f t="shared" si="87"/>
+        <f t="shared" si="114"/>
         <v>0.98750821827744906</v>
       </c>
       <c r="V38" s="10">
-        <f t="shared" si="87"/>
-        <v>0.98999999999999988</v>
+        <f t="shared" si="114"/>
+        <v>0.99037372593431494</v>
+      </c>
+      <c r="W38" s="10">
+        <f t="shared" ref="W38:Z38" si="115">(W8-W10)/W8</f>
+        <v>0.9900000000000001</v>
       </c>
       <c r="X38" s="10">
-        <f t="shared" ref="X38:AB38" si="88">(X8-X10)/X8</f>
+        <f t="shared" si="115"/>
+        <v>0.99</v>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="115"/>
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="Z38" s="10">
+        <f t="shared" si="115"/>
+        <v>0.99</v>
+      </c>
+      <c r="AB38" s="10">
+        <f t="shared" ref="AB38:AF38" si="116">(AB8-AB10)/AB8</f>
         <v>0.98528827037773359</v>
       </c>
-      <c r="Y38" s="10">
-        <f t="shared" si="88"/>
+      <c r="AC38" s="10">
+        <f t="shared" si="116"/>
         <v>0.98853695324283553</v>
       </c>
-      <c r="Z38" s="10">
-        <f t="shared" si="88"/>
+      <c r="AD38" s="10">
+        <f t="shared" si="116"/>
         <v>0.98918238993710694</v>
       </c>
-      <c r="AA38" s="10">
-        <f t="shared" si="88"/>
+      <c r="AE38" s="10">
+        <f t="shared" si="116"/>
         <v>0.99192379374611728</v>
       </c>
-      <c r="AB38" s="10">
-        <f t="shared" si="88"/>
-        <v>0.99013033452528154</v>
-      </c>
-      <c r="AC38" s="10"/>
-      <c r="AD38" s="10"/>
-      <c r="AE38" s="10"/>
-      <c r="AF38" s="10"/>
+      <c r="AF38" s="10">
+        <f t="shared" si="116"/>
+        <v>0.990234375</v>
+      </c>
       <c r="AG38" s="10"/>
       <c r="AH38" s="10"/>
       <c r="AI38" s="10"/>
       <c r="AJ38" s="10"/>
       <c r="AK38" s="10"/>
       <c r="AL38" s="10"/>
+      <c r="AM38" s="10"/>
+      <c r="AN38" s="10"/>
+      <c r="AO38" s="10"/>
+      <c r="AP38" s="10"/>
     </row>
-    <row r="39" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>67</v>
       </c>
@@ -5148,39 +5792,39 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="I39" s="10">
-        <f t="shared" ref="I39:Q39" si="89">(I8-I11)/I8</f>
+        <f t="shared" ref="I39:Q39" si="117">(I8-I11)/I8</f>
         <v>0.83723653395784536</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.8205394190871369</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.82548794489092991</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.78366914103923635</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.77290448343079921</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.76211453744493396</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.81096963761018614</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.77567567567567575</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="117"/>
         <v>0.75544794188861986</v>
       </c>
       <c r="R39" s="10">
@@ -5188,70 +5832,86 @@
         <v>0.69773817683344752</v>
       </c>
       <c r="S39" s="10">
-        <f t="shared" ref="S39:V39" si="90">(S8-S11)/S8</f>
+        <f t="shared" ref="S39:V39" si="118">(S8-S11)/S8</f>
         <v>0.66713384723195512</v>
       </c>
       <c r="T39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="118"/>
         <v>0.67062937062937067</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="118"/>
         <v>0.68113083497698879</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="90"/>
-        <v>0.67</v>
+        <f t="shared" si="118"/>
+        <v>0.64892412231030572</v>
+      </c>
+      <c r="W39" s="10">
+        <f t="shared" ref="W39:Z39" si="119">(W8-W11)/W8</f>
+        <v>0.65</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" ref="X39:AB39" si="91">(X8-X11)/X8</f>
+        <f t="shared" si="119"/>
+        <v>0.65</v>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="119"/>
+        <v>0.65</v>
+      </c>
+      <c r="Z39" s="10">
+        <f t="shared" si="119"/>
+        <v>0.65</v>
+      </c>
+      <c r="AB39" s="10">
+        <f t="shared" ref="AB39:AF39" si="120">(AB8-AB11)/AB8</f>
         <v>0.97813121272365811</v>
       </c>
-      <c r="Y39" s="10">
-        <f t="shared" si="91"/>
+      <c r="AC39" s="10">
+        <f t="shared" si="120"/>
         <v>0.8591251885369533</v>
       </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="91"/>
+      <c r="AD39" s="10">
+        <f t="shared" si="120"/>
         <v>0.78389937106918239</v>
       </c>
-      <c r="AA39" s="10">
-        <f t="shared" si="91"/>
+      <c r="AE39" s="10">
+        <f t="shared" si="120"/>
         <v>0.75440049699730782</v>
       </c>
-      <c r="AB39" s="10">
-        <f t="shared" si="91"/>
-        <v>0.67229589279149826</v>
-      </c>
-      <c r="AC39" s="10"/>
-      <c r="AD39" s="10"/>
-      <c r="AE39" s="10"/>
-      <c r="AF39" s="10"/>
+      <c r="AF39" s="10">
+        <f t="shared" si="120"/>
+        <v>0.66617838541666663</v>
+      </c>
       <c r="AG39" s="10"/>
       <c r="AH39" s="10"/>
       <c r="AI39" s="10"/>
       <c r="AJ39" s="10"/>
       <c r="AK39" s="10"/>
       <c r="AL39" s="10"/>
+      <c r="AM39" s="10"/>
+      <c r="AN39" s="10"/>
+      <c r="AO39" s="10"/>
+      <c r="AP39" s="10"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" ref="I40:L40" si="92">I13/I8</f>
+        <f t="shared" ref="I40:L40" si="121">I13/I8</f>
         <v>0.81615925058548</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="121"/>
         <v>0.80290456431535273</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="121"/>
         <v>0.80597014925373123</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="121"/>
         <v>0.76033934252386004</v>
       </c>
       <c r="M40" s="10">
@@ -5259,109 +5919,125 @@
         <v>0.75438596491228072</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" ref="N40:R40" si="93">N13/N8</f>
+        <f t="shared" ref="N40:R40" si="122">N13/N8</f>
         <v>0.74801762114537451</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="122"/>
         <v>0.76395690499510294</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="122"/>
         <v>0.75045045045045045</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="122"/>
         <v>0.73365617433414043</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="122"/>
         <v>0.67306374228923915</v>
       </c>
       <c r="S40" s="10">
-        <f t="shared" ref="S40:V40" si="94">S13/S8</f>
+        <f t="shared" ref="S40:V40" si="123">S13/S8</f>
         <v>0.6454099509460407</v>
       </c>
       <c r="T40" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="123"/>
         <v>0.64405594405594402</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="123"/>
         <v>0.65417488494411569</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="94"/>
-        <v>0.64</v>
+        <f t="shared" si="123"/>
+        <v>0.6245753114382786</v>
+      </c>
+      <c r="W40" s="10">
+        <f t="shared" ref="W40:Z40" si="124">W13/W8</f>
+        <v>0.63</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" ref="X40:AL40" si="95">X13/X8</f>
+        <f t="shared" si="124"/>
+        <v>0.63</v>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="124"/>
+        <v>0.63</v>
+      </c>
+      <c r="Z40" s="10">
+        <f t="shared" si="124"/>
+        <v>0.63</v>
+      </c>
+      <c r="AB40" s="10">
+        <f t="shared" ref="AB40:AP40" si="125">AB13/AB8</f>
         <v>0.94552683896620282</v>
       </c>
-      <c r="Y40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AC40" s="10">
+        <f t="shared" si="125"/>
         <v>0.83529411764705874</v>
       </c>
-      <c r="Z40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AD40" s="10">
+        <f t="shared" si="125"/>
         <v>0.76528301886792449</v>
       </c>
-      <c r="AA40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AE40" s="10">
+        <f t="shared" si="125"/>
         <v>0.7256160695796231</v>
       </c>
-      <c r="AB40" s="10">
-        <f t="shared" si="95"/>
-        <v>0.64586171172676543</v>
-      </c>
-      <c r="AC40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AF40" s="10">
+        <f t="shared" si="125"/>
+        <v>0.64127604166666674</v>
+      </c>
+      <c r="AG40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AD40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AH40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AE40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AI40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AF40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AJ40" s="10">
+        <f t="shared" si="125"/>
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="AK40" s="10">
+        <f t="shared" si="125"/>
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="AL40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AG40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AM40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AH40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AN40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AI40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AO40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AJ40" s="10">
-        <f t="shared" si="95"/>
+      <c r="AP40" s="10">
+        <f t="shared" si="125"/>
         <v>0.63</v>
       </c>
-      <c r="AK40" s="10">
-        <f t="shared" si="95"/>
-        <v>0.62999999999999989</v>
-      </c>
-      <c r="AL40" s="10">
-        <f t="shared" si="95"/>
-        <v>0.63</v>
-      </c>
-      <c r="AN40" t="s">
+      <c r="AR40" t="s">
         <v>52</v>
       </c>
-      <c r="AO40" s="10">
+      <c r="AS40" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>48</v>
       </c>
@@ -5374,123 +6050,139 @@
         <v>0.14999999999999991</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" ref="N41:R41" si="96">N14/J14-1</f>
+        <f t="shared" ref="N41:R41" si="126">N14/J14-1</f>
         <v>-2.3696682464454999E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="126"/>
         <v>-0.18905472636815923</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="126"/>
         <v>-7.4766355140186813E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="126"/>
         <v>0.12077294685990347</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="126"/>
         <v>-0.13592233009708743</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" ref="S41" si="97">S14/O14-1</f>
+        <f t="shared" ref="S41" si="127">S14/O14-1</f>
         <v>7.9754601226993849E-2</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" ref="T41" si="98">T14/P14-1</f>
+        <f t="shared" ref="T41" si="128">T14/P14-1</f>
         <v>-5.555555555555558E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" ref="U41" si="99">U14/Q14-1</f>
+        <f t="shared" ref="U41" si="129">U14/Q14-1</f>
         <v>-9.9137931034482762E-2</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" ref="V41" si="100">V14/R14-1</f>
-        <v>0.25</v>
-      </c>
-      <c r="X41" s="10"/>
+        <f t="shared" ref="V41" si="130">V14/R14-1</f>
+        <v>0.23033707865168518</v>
+      </c>
+      <c r="W41" s="10">
+        <f t="shared" ref="W41" si="131">W14/S14-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="X41" s="10">
+        <f t="shared" ref="X41" si="132">X14/T14-1</f>
+        <v>0.19999999999999996</v>
+      </c>
       <c r="Y41" s="10">
-        <f>Y14/X14-1</f>
+        <f t="shared" ref="Y41" si="133">Y14/U14-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="Z41" s="10">
+        <f t="shared" ref="Z41" si="134">Z14/V14-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AB41" s="10"/>
+      <c r="AC41" s="10">
+        <f>AC14/AB14-1</f>
         <v>1.3422818791946067E-3</v>
       </c>
-      <c r="Z41" s="10">
-        <f t="shared" ref="Z41:AL41" si="101">Z14/Y14-1</f>
+      <c r="AD41" s="10">
+        <f t="shared" ref="AD41:AP41" si="135">AD14/AC14-1</f>
         <v>0.1099195710455767</v>
       </c>
-      <c r="AA41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AE41" s="10">
+        <f t="shared" si="135"/>
         <v>-6.8840579710145122E-2</v>
       </c>
-      <c r="AB41" s="10">
-        <f t="shared" si="101"/>
-        <v>3.0479896238650994E-2</v>
-      </c>
-      <c r="AC41" s="10">
-        <f t="shared" si="101"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="AD41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AF41" s="10">
+        <f t="shared" si="135"/>
+        <v>2.5940337224383825E-2</v>
+      </c>
+      <c r="AG41" s="10">
+        <f t="shared" si="135"/>
+        <v>0.14589127686472847</v>
+      </c>
+      <c r="AH41" s="10">
+        <f t="shared" si="135"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AE41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AI41" s="10">
+        <f t="shared" si="135"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AF41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AJ41" s="10">
+        <f t="shared" si="135"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AK41" s="10">
+        <f t="shared" si="135"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AL41" s="10">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AM41" s="10">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AN41" s="10">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AO41" s="10">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL41" s="10">
-        <f t="shared" si="101"/>
+      <c r="AP41" s="10">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN41" t="s">
+      <c r="AR41" t="s">
         <v>53</v>
       </c>
-      <c r="AO41" s="10">
+      <c r="AS41" s="10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" ref="I42:L42" si="102">I16/I8</f>
+        <f t="shared" ref="I42:L42" si="136">I16/I8</f>
         <v>0.3044496487119438</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="136"/>
         <v>0.30705394190871371</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="136"/>
         <v>0.28013777267508611</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="102"/>
+        <f t="shared" si="136"/>
         <v>0.28632025450689297</v>
       </c>
       <c r="M42" s="10">
@@ -5498,127 +6190,143 @@
         <v>0.27680311890838205</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" ref="N42:R42" si="103">N16/N8</f>
+        <f t="shared" ref="N42:R42" si="137">N16/N8</f>
         <v>0.26519823788546254</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="137"/>
         <v>0.28893241919686585</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="137"/>
         <v>0.26126126126126131</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="137"/>
         <v>0.2623083131557708</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="103"/>
+        <f t="shared" si="137"/>
         <v>0.28032899246058945</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" ref="S42:V42" si="104">S16/S8</f>
+        <f t="shared" ref="S42:V42" si="138">S16/S8</f>
         <v>0.23966362999299234</v>
       </c>
       <c r="T42" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="138"/>
         <v>0.23776223776223776</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="104"/>
+        <f t="shared" si="138"/>
         <v>0.23602892833662065</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="104"/>
-        <v>0.24</v>
+        <f t="shared" si="138"/>
+        <v>0.21574178935447341</v>
+      </c>
+      <c r="W42" s="10">
+        <f t="shared" ref="W42:Z42" si="139">W16/W8</f>
+        <v>0.23</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" ref="X42:AL42" si="105">X16/X8</f>
+        <f t="shared" si="139"/>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="Y42" s="10">
+        <f t="shared" si="139"/>
+        <v>0.23</v>
+      </c>
+      <c r="Z42" s="10">
+        <f t="shared" si="139"/>
+        <v>0.22</v>
+      </c>
+      <c r="AB42" s="10">
+        <f t="shared" ref="AB42:AP42" si="140">AB16/AB8</f>
         <v>0.48071570576540756</v>
       </c>
-      <c r="Y42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AC42" s="10">
+        <f t="shared" si="140"/>
         <v>0.34690799396681749</v>
       </c>
-      <c r="Z42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AD42" s="10">
+        <f t="shared" si="140"/>
         <v>0.27647798742138369</v>
       </c>
-      <c r="AA42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AE42" s="10">
+        <f t="shared" si="140"/>
         <v>0.27314143715054878</v>
       </c>
-      <c r="AB42" s="10">
-        <f t="shared" si="105"/>
-        <v>0.23837583130033752</v>
-      </c>
-      <c r="AC42" s="10">
-        <f t="shared" si="105"/>
-        <v>0.23000000000000004</v>
-      </c>
-      <c r="AD42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AF42" s="10">
+        <f t="shared" si="140"/>
+        <v>0.2314453125</v>
+      </c>
+      <c r="AG42" s="10">
+        <f t="shared" si="140"/>
+        <v>0.22735834004088643</v>
+      </c>
+      <c r="AH42" s="10">
+        <f t="shared" si="140"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AI42" s="10">
+        <f t="shared" si="140"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AJ42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AE42" s="10">
-        <f t="shared" si="105"/>
-        <v>0.21999999999999997</v>
-      </c>
-      <c r="AF42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AK42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AG42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AL42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AH42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AM42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AI42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AN42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AJ42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AO42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AK42" s="10">
-        <f t="shared" si="105"/>
+      <c r="AP42" s="10">
+        <f t="shared" si="140"/>
         <v>0.22</v>
       </c>
-      <c r="AL42" s="10">
-        <f t="shared" si="105"/>
-        <v>0.22</v>
-      </c>
-      <c r="AN42" t="s">
+      <c r="AR42" t="s">
         <v>54</v>
       </c>
-      <c r="AO42" s="3">
-        <f>NPV(AO41,AB29:EN29)</f>
-        <v>1649.0819367687186</v>
+      <c r="AS42" s="3">
+        <f>NPV(AS41,AG29:ER29)</f>
+        <v>1818.7303167933107</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:L43" si="106">I22/I8</f>
+        <f t="shared" ref="I43:L43" si="141">I22/I8</f>
         <v>0.18969555035128802</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="141"/>
         <v>0.12136929460580902</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="141"/>
         <v>0.158438576349024</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="106"/>
+        <f t="shared" si="141"/>
         <v>0.13255567338282073</v>
       </c>
       <c r="M43" s="10">
@@ -5626,127 +6334,143 @@
         <v>0.15594541910331378</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" ref="N43:R43" si="107">N22/N8</f>
+        <f t="shared" ref="N43:R43" si="142">N22/N8</f>
         <v>0.17973568281938332</v>
       </c>
       <c r="O43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="142"/>
         <v>0.19000979431929474</v>
       </c>
       <c r="P43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="142"/>
         <v>0.19729729729729725</v>
       </c>
       <c r="Q43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="142"/>
         <v>0.18886198547215491</v>
       </c>
       <c r="R43" s="10">
-        <f t="shared" si="107"/>
+        <f t="shared" si="142"/>
         <v>0.18848526387936926</v>
       </c>
       <c r="S43" s="10">
-        <f t="shared" ref="S43:V43" si="108">S22/S8</f>
+        <f t="shared" ref="S43:V43" si="143">S22/S8</f>
         <v>0.14856341976173784</v>
       </c>
       <c r="T43" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="143"/>
         <v>0.1237762237762238</v>
       </c>
       <c r="U43" s="10">
-        <f t="shared" si="108"/>
+        <f t="shared" si="143"/>
         <v>0.14595660749506897</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="108"/>
-        <v>0.16814390638615714</v>
+        <f t="shared" si="143"/>
+        <v>0.16138165345413355</v>
+      </c>
+      <c r="W43" s="10">
+        <f t="shared" ref="W43:Z43" si="144">W22/W8</f>
+        <v>0.14047058823529418</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" ref="X43:AL43" si="109">X22/X8</f>
+        <f t="shared" si="144"/>
+        <v>0.13403263403263405</v>
+      </c>
+      <c r="Y43" s="10">
+        <f t="shared" si="144"/>
+        <v>0.13421376096961382</v>
+      </c>
+      <c r="Z43" s="10">
+        <f t="shared" si="144"/>
+        <v>0.14526398101709542</v>
+      </c>
+      <c r="AB43" s="10">
+        <f t="shared" ref="AB43:AP43" si="145">AB22/AB8</f>
         <v>-2.4652087475149059E-2</v>
       </c>
-      <c r="Y43" s="10">
-        <f t="shared" si="109"/>
+      <c r="AC43" s="10">
+        <f t="shared" si="145"/>
         <v>0.1224736048265459</v>
       </c>
-      <c r="Z43" s="10">
-        <f t="shared" si="109"/>
+      <c r="AD43" s="10">
+        <f t="shared" si="145"/>
         <v>0.15773584905660362</v>
       </c>
-      <c r="AA43" s="10">
-        <f t="shared" si="109"/>
+      <c r="AE43" s="10">
+        <f t="shared" si="145"/>
         <v>0.19631393663284327</v>
       </c>
-      <c r="AB43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.1472345687263979</v>
-      </c>
-      <c r="AC43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.22607195087661794</v>
-      </c>
-      <c r="AD43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.24477920208038048</v>
-      </c>
-      <c r="AE43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.24770936651065451</v>
-      </c>
       <c r="AF43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.24913747187728963</v>
+        <f t="shared" si="145"/>
+        <v>8.5611979166666713E-2</v>
       </c>
       <c r="AG43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.25063371987003447</v>
+        <f t="shared" si="145"/>
+        <v>0.13860387922130646</v>
       </c>
       <c r="AH43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.25219613438111249</v>
+        <f t="shared" si="145"/>
+        <v>0.23864392228011344</v>
       </c>
       <c r="AI43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.25374323110286628</v>
+        <f t="shared" si="145"/>
+        <v>0.24302657184691029</v>
       </c>
       <c r="AJ43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.25527516020970092</v>
+        <f t="shared" si="145"/>
+        <v>0.24474317480822153</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.25679207040372343</v>
+        <f t="shared" si="145"/>
+        <v>0.2465179519582919</v>
       </c>
       <c r="AL43" s="10">
-        <f t="shared" si="109"/>
-        <v>0.2582941089291772</v>
-      </c>
-      <c r="AN43" t="s">
+        <f t="shared" si="145"/>
+        <v>0.24835768964817551</v>
+      </c>
+      <c r="AM43" s="10">
+        <f t="shared" si="145"/>
+        <v>0.25021759808957139</v>
+      </c>
+      <c r="AN43" s="10">
+        <f t="shared" si="145"/>
+        <v>0.25210346225091024</v>
+      </c>
+      <c r="AO43" s="10">
+        <f t="shared" si="145"/>
+        <v>0.25402188268331111</v>
+      </c>
+      <c r="AP43" s="10">
+        <f t="shared" si="145"/>
+        <v>0.25598037121527234</v>
+      </c>
+      <c r="AR43" t="s">
         <v>55</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AS43" s="3">
         <f>Main!D8</f>
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>42</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" ref="I44:L44" si="110">I28/I27</f>
+        <f t="shared" ref="I44:L44" si="146">I28/I27</f>
         <v>0.35616438356164393</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="146"/>
         <v>-3.4825870646766191E-2</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="146"/>
         <v>0.17741935483870977</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" si="110"/>
+        <f t="shared" si="146"/>
         <v>7.4829931972789157E-2</v>
       </c>
       <c r="M44" s="10">
@@ -5754,127 +6478,143 @@
         <v>1.1764705882352946E-2</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" ref="N44:R44" si="111">N28/N27</f>
+        <f t="shared" ref="N44:R44" si="147">N28/N27</f>
         <v>1.9178082191780819E-2</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="147"/>
         <v>0.23711340206185574</v>
       </c>
       <c r="P44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="147"/>
         <v>0.12727272727272732</v>
       </c>
       <c r="Q44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="147"/>
         <v>0.20869565217391309</v>
       </c>
       <c r="R44" s="10">
-        <f t="shared" si="111"/>
+        <f t="shared" si="147"/>
         <v>0.15634218289085558</v>
       </c>
       <c r="S44" s="10">
-        <f t="shared" ref="S44:V44" si="112">S28/S27</f>
+        <f t="shared" ref="S44:V44" si="148">S28/S27</f>
         <v>0.11904761904761911</v>
       </c>
       <c r="T44" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="148"/>
         <v>0.12068965517241378</v>
       </c>
       <c r="U44" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="148"/>
         <v>0.17857142857142866</v>
       </c>
       <c r="V44" s="10">
-        <f t="shared" si="112"/>
+        <f t="shared" si="148"/>
+        <v>0.13125000000000006</v>
+      </c>
+      <c r="W44" s="10">
+        <f t="shared" ref="W44:Z44" si="149">W28/W27</f>
         <v>0.15</v>
       </c>
       <c r="X44" s="10">
-        <f t="shared" ref="X44:AL44" si="113">X28/X27</f>
-        <v>0</v>
+        <f t="shared" si="149"/>
+        <v>0.15</v>
       </c>
       <c r="Y44" s="10">
-        <f t="shared" si="113"/>
+        <f t="shared" si="149"/>
+        <v>0.15</v>
+      </c>
+      <c r="Z44" s="10">
+        <f t="shared" si="149"/>
+        <v>0.15</v>
+      </c>
+      <c r="AB44" s="10">
+        <f t="shared" ref="AB44:AP44" si="150">AB28/AB27</f>
+        <v>0</v>
+      </c>
+      <c r="AC44" s="10">
+        <f t="shared" si="150"/>
         <v>0.3682008368200842</v>
       </c>
-      <c r="Z44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AD44" s="10">
+        <f t="shared" si="150"/>
         <v>4.1927409261576995E-2</v>
       </c>
-      <c r="AA44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AE44" s="10">
+        <f t="shared" si="150"/>
         <v>0.1734390485629336</v>
       </c>
-      <c r="AB44" s="10">
-        <f t="shared" si="113"/>
-        <v>0.14405809356217275</v>
-      </c>
-      <c r="AC44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AF44" s="10">
+        <f t="shared" si="150"/>
+        <v>0.19362186788154895</v>
+      </c>
+      <c r="AG44" s="10">
+        <f t="shared" si="150"/>
+        <v>0.15000000000000008</v>
+      </c>
+      <c r="AH44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AD44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AI44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AE44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AJ44" s="10">
+        <f t="shared" si="150"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="AK44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AF44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AL44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AG44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AM44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AH44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AN44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AI44" s="10">
-        <f t="shared" si="113"/>
-        <v>0.14999999999999997</v>
-      </c>
-      <c r="AJ44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AO44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AK44" s="10">
-        <f t="shared" si="113"/>
+      <c r="AP44" s="10">
+        <f t="shared" si="150"/>
         <v>0.15</v>
       </c>
-      <c r="AL44" s="10">
-        <f t="shared" si="113"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN44" t="s">
+      <c r="AR44" t="s">
         <v>56</v>
       </c>
-      <c r="AO44" s="3">
-        <f>AO42+AO43</f>
-        <v>1777.0819367687186</v>
+      <c r="AS44" s="3">
+        <f>AS42+AS43</f>
+        <v>1946.7303167933107</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>51</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" ref="I45:L45" si="114">I29/I8</f>
+        <f t="shared" ref="I45:L45" si="151">I29/I8</f>
         <v>0.11007025761124117</v>
       </c>
       <c r="J45" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="151"/>
         <v>0.21576763485477166</v>
       </c>
       <c r="K45" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="151"/>
         <v>0.17566016073478749</v>
       </c>
       <c r="L45" s="10">
-        <f t="shared" si="114"/>
+        <f t="shared" si="151"/>
         <v>0.14422057264050897</v>
       </c>
       <c r="M45" s="10">
@@ -5882,227 +6622,247 @@
         <v>0.16374269005847947</v>
       </c>
       <c r="N45" s="10">
-        <f t="shared" ref="N45:R45" si="115">N29/N8</f>
+        <f t="shared" ref="N45:R45" si="152">N29/N8</f>
         <v>0.94625550660792968</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="152"/>
         <v>0.1449559255631733</v>
       </c>
       <c r="P45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="152"/>
         <v>0.17297297297297293</v>
       </c>
       <c r="Q45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="152"/>
         <v>0.14689265536723159</v>
       </c>
       <c r="R45" s="10">
-        <f t="shared" si="115"/>
+        <f t="shared" si="152"/>
         <v>0.19602467443454402</v>
       </c>
       <c r="S45" s="10">
-        <f t="shared" ref="S45:V45" si="116">S29/S8</f>
+        <f t="shared" ref="S45:V45" si="153">S29/S8</f>
         <v>0.12964260686755424</v>
       </c>
       <c r="T45" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="153"/>
         <v>0.10699300699300701</v>
       </c>
       <c r="U45" s="10">
-        <f t="shared" si="116"/>
+        <f t="shared" si="153"/>
         <v>0.12097304404996705</v>
       </c>
       <c r="V45" s="10">
-        <f t="shared" si="116"/>
-        <v>0.14133511763973611</v>
+        <f t="shared" si="153"/>
+        <v>0.31483578708946763</v>
+      </c>
+      <c r="W45" s="10">
+        <f t="shared" ref="W45:Z45" si="154">W29/W8</f>
+        <v>0.11440000000000004</v>
       </c>
       <c r="X45" s="10">
-        <f t="shared" ref="X45:AL45" si="117">X29/X8</f>
+        <f t="shared" si="154"/>
+        <v>0.10897435897435898</v>
+      </c>
+      <c r="Y45" s="10">
+        <f t="shared" si="154"/>
+        <v>0.10922219363690935</v>
+      </c>
+      <c r="Z45" s="10">
+        <f t="shared" si="154"/>
+        <v>0.16014590411476029</v>
+      </c>
+      <c r="AB45" s="10">
+        <f t="shared" ref="AB45:AP45" si="155">AB29/AB8</f>
         <v>-0.1709741550695825</v>
       </c>
-      <c r="Y45" s="10">
-        <f t="shared" si="117"/>
+      <c r="AC45" s="10">
+        <f t="shared" si="155"/>
         <v>4.5550527903468974E-2</v>
       </c>
-      <c r="Z45" s="10">
-        <f t="shared" si="117"/>
+      <c r="AD45" s="10">
+        <f t="shared" si="155"/>
         <v>0.38515723270440239</v>
       </c>
-      <c r="AA45" s="10">
-        <f t="shared" si="117"/>
+      <c r="AE45" s="10">
+        <f t="shared" si="155"/>
         <v>0.17270656450610894</v>
       </c>
-      <c r="AB45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.12516609297196152</v>
-      </c>
-      <c r="AC45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.19216115824512525</v>
-      </c>
-      <c r="AD45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.2080623217683234</v>
-      </c>
-      <c r="AE45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21055296153405634</v>
-      </c>
       <c r="AF45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21176685109569618</v>
+        <f t="shared" si="155"/>
+        <v>0.11523437500000003</v>
       </c>
       <c r="AG45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21303866188952927</v>
+        <f t="shared" si="155"/>
+        <v>0.12386790275591388</v>
       </c>
       <c r="AH45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21436671422394565</v>
+        <f t="shared" si="155"/>
+        <v>0.20836742011970091</v>
       </c>
       <c r="AI45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21568174643743634</v>
+        <f t="shared" si="155"/>
+        <v>0.21183974570124289</v>
       </c>
       <c r="AJ45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21698388617824579</v>
+        <f t="shared" si="155"/>
+        <v>0.21317141094985162</v>
       </c>
       <c r="AK45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.21827325984316492</v>
+        <f t="shared" si="155"/>
+        <v>0.21458857994845817</v>
       </c>
       <c r="AL45" s="10">
-        <f t="shared" si="117"/>
-        <v>0.2195499925898006</v>
-      </c>
-      <c r="AN45" t="s">
+        <f t="shared" si="155"/>
+        <v>0.21609554593968314</v>
+      </c>
+      <c r="AM45" s="10">
+        <f t="shared" si="155"/>
+        <v>0.21761903419748641</v>
+      </c>
+      <c r="AN45" s="10">
+        <f t="shared" si="155"/>
+        <v>0.21916378330538089</v>
+      </c>
+      <c r="AO45" s="10">
+        <f t="shared" si="155"/>
+        <v>0.2207351999069955</v>
+      </c>
+      <c r="AP45" s="10">
+        <f t="shared" si="155"/>
+        <v>0.22233943709151302</v>
+      </c>
+      <c r="AR45" t="s">
         <v>57</v>
       </c>
-      <c r="AO45" s="2">
-        <f>AO44/AL30</f>
-        <v>19.83350375857945</v>
+      <c r="AS45" s="2">
+        <f>AS44/AP30</f>
+        <v>21.726900857068202</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="AN46" t="s">
+    <row r="46" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="AR46" t="s">
         <v>58</v>
       </c>
-      <c r="AO46" s="2">
+      <c r="AS46" s="2">
         <f>Main!D3</f>
-        <v>13.45</v>
+        <v>14.31</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.3">
-      <c r="AN47" s="1" t="s">
+    <row r="47" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="AR47" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AO47" s="9">
-        <f>AO45/AO46-1</f>
-        <v>0.47460994487579566</v>
+      <c r="AS47" s="9">
+        <f>AS45/AS46-1</f>
+        <v>0.51830194668540885</v>
       </c>
     </row>
-    <row r="48" spans="2:41" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>45</v>
       </c>
       <c r="K48" s="8">
-        <f t="shared" ref="K48:R48" si="118">K27</f>
+        <f t="shared" ref="K48:R48" si="156">K27</f>
         <v>18.599999999999991</v>
       </c>
       <c r="L48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>14.699999999999992</v>
       </c>
       <c r="M48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>16.999999999999993</v>
       </c>
       <c r="N48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>109.50000000000001</v>
       </c>
       <c r="O48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>19.399999999999991</v>
       </c>
       <c r="P48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>21.999999999999993</v>
       </c>
       <c r="Q48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>22.999999999999993</v>
       </c>
       <c r="R48" s="8">
-        <f t="shared" si="118"/>
+        <f t="shared" si="156"/>
         <v>33.89999999999997</v>
       </c>
       <c r="U48" s="8">
-        <f t="shared" ref="U48" si="119">U27</f>
+        <f t="shared" ref="U48:V48" si="157">U27</f>
         <v>22.399999999999988</v>
       </c>
-      <c r="Z48" s="8">
-        <f>Z27</f>
+      <c r="V48" s="8">
+        <f t="shared" si="157"/>
+        <v>63.999999999999979</v>
+      </c>
+      <c r="AD48" s="8">
+        <f>AD27</f>
         <v>159.79999999999993</v>
       </c>
-      <c r="AA48" s="8">
-        <f>AA27</f>
+      <c r="AE48" s="8">
+        <f>AE27</f>
         <v>100.9</v>
       </c>
-      <c r="AB48" s="8">
-        <f t="shared" ref="AB48:AL48" si="120">AB27</f>
-        <v>87.514000000000095</v>
-      </c>
-      <c r="AC48" s="8">
-        <f t="shared" si="120"/>
-        <v>153.40907999999996</v>
-      </c>
-      <c r="AD48" s="8">
-        <f t="shared" si="120"/>
-        <v>181.69084840000005</v>
-      </c>
-      <c r="AE48" s="8">
-        <f t="shared" si="120"/>
-        <v>193.18287048240012</v>
-      </c>
       <c r="AF48" s="8">
-        <f t="shared" si="120"/>
-        <v>200.88414037786407</v>
+        <f t="shared" ref="AF48:AP48" si="158">AF27</f>
+        <v>87.800000000000011</v>
       </c>
       <c r="AG48" s="8">
-        <f t="shared" si="120"/>
-        <v>207.54566881775571</v>
+        <f t="shared" si="158"/>
+        <v>102.29229999999995</v>
       </c>
       <c r="AH48" s="8">
-        <f t="shared" si="120"/>
-        <v>213.01626819700471</v>
+        <f t="shared" si="158"/>
+        <v>190.62301511000004</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="120"/>
-        <v>218.60947642386765</v>
+        <f t="shared" si="158"/>
+        <v>205.13686665470004</v>
       </c>
       <c r="AJ48" s="8">
-        <f t="shared" si="120"/>
-        <v>224.32787764389707</v>
+        <f t="shared" si="158"/>
+        <v>213.66051479842812</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="120"/>
-        <v>230.1741090052426</v>
+        <f t="shared" si="158"/>
+        <v>221.16436965166233</v>
       </c>
       <c r="AL48" s="8">
-        <f t="shared" si="120"/>
-        <v>236.15086173189974</v>
-      </c>
-      <c r="AN48" t="s">
+        <f t="shared" si="158"/>
+        <v>227.50490578233348</v>
+      </c>
+      <c r="AM48" s="8">
+        <f t="shared" si="158"/>
+        <v>234.09347395448125</v>
+      </c>
+      <c r="AN48" s="8">
+        <f t="shared" si="158"/>
+        <v>240.95665678842107</v>
+      </c>
+      <c r="AO48" s="8">
+        <f t="shared" si="158"/>
+        <v>248.12586672992904</v>
+      </c>
+      <c r="AP48" s="8">
+        <f t="shared" si="158"/>
+        <v>255.63830201913365</v>
+      </c>
+      <c r="AR48" t="s">
         <v>60</v>
       </c>
-      <c r="AO48" s="6" t="s">
-        <v>96</v>
+      <c r="AS48" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>71</v>
       </c>
@@ -6133,26 +6893,17 @@
       <c r="U49" s="3">
         <v>-0.2</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="V49" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="3">
         <f>SUM(K49:N49)</f>
         <v>-7.3</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <f>SUM(O49:R49)</f>
         <v>-1.2</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
@@ -6174,8 +6925,20 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>72</v>
       </c>
@@ -6194,26 +6957,17 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-      <c r="Z50" s="3">
-        <f t="shared" ref="Z50:Z61" si="121">SUM(K50:N50)</f>
+      <c r="V50" s="3">
+        <v>-36.299999999999997</v>
+      </c>
+      <c r="AD50" s="3">
+        <f t="shared" ref="AD50:AD61" si="159">SUM(K50:N50)</f>
         <v>-89.8</v>
       </c>
-      <c r="AA50" s="3">
-        <f t="shared" ref="AA50:AA61" si="122">SUM(O50:R50)</f>
+      <c r="AE50" s="3">
+        <f t="shared" ref="AE50:AE61" si="160">SUM(O50:R50)</f>
         <v>-5</v>
       </c>
-      <c r="AB50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="3">
-        <v>0</v>
-      </c>
       <c r="AF50" s="3">
         <v>0</v>
       </c>
@@ -6235,8 +6989,20 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>73</v>
       </c>
@@ -6255,24 +7021,15 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-      <c r="Z51" s="3">
-        <f t="shared" si="121"/>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="3">
-        <f t="shared" si="122"/>
-        <v>0</v>
-      </c>
-      <c r="AB51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="3">
-        <v>0</v>
+      <c r="V51" s="3">
+        <v>-0.3</v>
       </c>
       <c r="AD51" s="3">
+        <f t="shared" si="159"/>
         <v>0</v>
       </c>
       <c r="AE51" s="3">
+        <f t="shared" si="160"/>
         <v>0</v>
       </c>
       <c r="AF51" s="3">
@@ -6296,8 +7053,20 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>74</v>
       </c>
@@ -6320,26 +7089,17 @@
       <c r="U52" s="3">
         <v>0.2</v>
       </c>
-      <c r="Z52" s="3">
-        <f t="shared" si="121"/>
+      <c r="V52" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="AD52" s="3">
+        <f t="shared" si="159"/>
         <v>0.7</v>
       </c>
-      <c r="AA52" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE52" s="3">
+        <f t="shared" si="160"/>
         <v>0.1</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
       <c r="AF52" s="3">
         <v>0</v>
       </c>
@@ -6361,8 +7121,20 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>33</v>
       </c>
@@ -6393,60 +7165,33 @@
       <c r="U53" s="3">
         <v>4.9000000000000004</v>
       </c>
-      <c r="Z53" s="3">
-        <f t="shared" si="121"/>
+      <c r="V53" s="3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AD53" s="3">
+        <f t="shared" si="159"/>
         <v>13.2</v>
       </c>
-      <c r="AA53" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE53" s="3">
+        <f t="shared" si="160"/>
         <v>15.6</v>
       </c>
-      <c r="AB53" s="3">
-        <f>AA53*1.02</f>
+      <c r="AF53" s="3">
+        <f>AE53*1.02</f>
         <v>15.911999999999999</v>
       </c>
-      <c r="AC53" s="3">
-        <f t="shared" ref="AC53:AL53" si="123">AB53*1.02</f>
-        <v>16.230239999999998</v>
-      </c>
-      <c r="AD53" s="3">
-        <f t="shared" si="123"/>
-        <v>16.554844799999998</v>
-      </c>
-      <c r="AE53" s="3">
-        <f t="shared" si="123"/>
-        <v>16.885941696</v>
-      </c>
-      <c r="AF53" s="3">
-        <f t="shared" si="123"/>
-        <v>17.22366052992</v>
-      </c>
-      <c r="AG53" s="3">
-        <f t="shared" si="123"/>
-        <v>17.568133740518402</v>
-      </c>
-      <c r="AH53" s="3">
-        <f t="shared" si="123"/>
-        <v>17.919496415328769</v>
-      </c>
-      <c r="AI53" s="3">
-        <f t="shared" si="123"/>
-        <v>18.277886343635345</v>
-      </c>
-      <c r="AJ53" s="3">
-        <f t="shared" si="123"/>
-        <v>18.643444070508053</v>
-      </c>
-      <c r="AK53" s="3">
-        <f t="shared" si="123"/>
-        <v>19.016312951918216</v>
-      </c>
-      <c r="AL53" s="3">
-        <f t="shared" si="123"/>
-        <v>19.396639210956582</v>
-      </c>
+      <c r="AG53" s="3"/>
+      <c r="AH53" s="3"/>
+      <c r="AI53" s="3"/>
+      <c r="AJ53" s="3"/>
+      <c r="AK53" s="3"/>
+      <c r="AL53" s="3"/>
+      <c r="AM53" s="3"/>
+      <c r="AN53" s="3"/>
+      <c r="AO53" s="3"/>
+      <c r="AP53" s="3"/>
     </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>75</v>
       </c>
@@ -6477,60 +7222,63 @@
       <c r="U54" s="3">
         <v>8.4</v>
       </c>
-      <c r="Z54" s="3">
-        <f t="shared" si="121"/>
+      <c r="V54" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="AD54" s="3">
+        <f t="shared" si="159"/>
         <v>14.799999999999999</v>
       </c>
-      <c r="AA54" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE54" s="3">
+        <f t="shared" si="160"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="AB54" s="3">
-        <f>AA54*0.8</f>
+      <c r="AF54" s="3">
+        <f>AE54*0.8</f>
         <v>7.0400000000000009</v>
       </c>
-      <c r="AC54" s="3">
-        <f t="shared" ref="AC54:AL54" si="124">AB54*0.8</f>
+      <c r="AG54" s="3">
+        <f t="shared" ref="AG54:AP54" si="161">AF54*0.8</f>
         <v>5.6320000000000014</v>
       </c>
-      <c r="AD54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AH54" s="3">
+        <f t="shared" si="161"/>
         <v>4.5056000000000012</v>
       </c>
-      <c r="AE54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AI54" s="3">
+        <f t="shared" si="161"/>
         <v>3.604480000000001</v>
       </c>
-      <c r="AF54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AJ54" s="3">
+        <f t="shared" si="161"/>
         <v>2.8835840000000008</v>
       </c>
-      <c r="AG54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AK54" s="3">
+        <f t="shared" si="161"/>
         <v>2.3068672000000006</v>
       </c>
-      <c r="AH54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AL54" s="3">
+        <f t="shared" si="161"/>
         <v>1.8454937600000005</v>
       </c>
-      <c r="AI54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AM54" s="3">
+        <f t="shared" si="161"/>
         <v>1.4763950080000006</v>
       </c>
-      <c r="AJ54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AN54" s="3">
+        <f t="shared" si="161"/>
         <v>1.1811160064000006</v>
       </c>
-      <c r="AK54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AO54" s="3">
+        <f t="shared" si="161"/>
         <v>0.94489280512000051</v>
       </c>
-      <c r="AL54" s="3">
-        <f t="shared" si="124"/>
+      <c r="AP54" s="3">
+        <f t="shared" si="161"/>
         <v>0.7559142440960005</v>
       </c>
     </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>76</v>
       </c>
@@ -6561,26 +7309,17 @@
       <c r="U55" s="3">
         <v>0.2</v>
       </c>
-      <c r="Z55" s="3">
-        <f t="shared" si="121"/>
+      <c r="V55" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="AD55" s="3">
+        <f t="shared" si="159"/>
         <v>-0.3</v>
       </c>
-      <c r="AA55" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE55" s="3">
+        <f t="shared" si="160"/>
         <v>-0.10000000000000003</v>
       </c>
-      <c r="AB55" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="3">
-        <v>0</v>
-      </c>
       <c r="AF55" s="3">
         <v>0</v>
       </c>
@@ -6602,8 +7341,20 @@
       <c r="AL55" s="3">
         <v>0</v>
       </c>
+      <c r="AM55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>77</v>
       </c>
@@ -6634,26 +7385,17 @@
       <c r="U56" s="3">
         <v>-5.5</v>
       </c>
-      <c r="Z56" s="3">
-        <f t="shared" si="121"/>
+      <c r="V56" s="3">
+        <v>-11.5</v>
+      </c>
+      <c r="AD56" s="3">
+        <f t="shared" si="159"/>
         <v>-17.600000000000001</v>
       </c>
-      <c r="AA56" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE56" s="3">
+        <f t="shared" si="160"/>
         <v>-20.2</v>
       </c>
-      <c r="AB56" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="3">
-        <v>0</v>
-      </c>
       <c r="AF56" s="3">
         <v>0</v>
       </c>
@@ -6675,8 +7417,20 @@
       <c r="AL56" s="3">
         <v>0</v>
       </c>
+      <c r="AM56" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN56" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP56" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>78</v>
       </c>
@@ -6707,26 +7461,17 @@
       <c r="U57" s="3">
         <v>-0.2</v>
       </c>
-      <c r="Z57" s="3">
-        <f t="shared" si="121"/>
+      <c r="V57" s="3">
+        <v>-1.2</v>
+      </c>
+      <c r="AD57" s="3">
+        <f t="shared" si="159"/>
         <v>-1.0000000000000002</v>
       </c>
-      <c r="AA57" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE57" s="3">
+        <f t="shared" si="160"/>
         <v>-1.8</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
       <c r="AF57" s="3">
         <v>0</v>
       </c>
@@ -6748,8 +7493,20 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>79</v>
       </c>
@@ -6780,26 +7537,17 @@
       <c r="U58" s="3">
         <v>-2.1</v>
       </c>
-      <c r="Z58" s="3">
-        <f t="shared" si="121"/>
+      <c r="V58" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="AD58" s="3">
+        <f t="shared" si="159"/>
         <v>5.3000000000000007</v>
       </c>
-      <c r="AA58" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE58" s="3">
+        <f t="shared" si="160"/>
         <v>23.1</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
@@ -6821,8 +7569,20 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>80</v>
       </c>
@@ -6853,26 +7613,17 @@
       <c r="U59" s="3">
         <v>-0.2</v>
       </c>
-      <c r="Z59" s="3">
-        <f t="shared" si="121"/>
+      <c r="V59" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD59" s="3">
+        <f t="shared" si="159"/>
         <v>9.3000000000000007</v>
       </c>
-      <c r="AA59" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE59" s="3">
+        <f t="shared" si="160"/>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
       <c r="AF59" s="3">
         <v>0</v>
       </c>
@@ -6894,8 +7645,20 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>81</v>
       </c>
@@ -6926,26 +7689,17 @@
       <c r="U60" s="3">
         <v>1.5</v>
       </c>
-      <c r="Z60" s="3">
-        <f t="shared" si="121"/>
+      <c r="V60" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="AD60" s="3">
+        <f t="shared" si="159"/>
         <v>1.2000000000000002</v>
       </c>
-      <c r="AA60" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE60" s="3">
+        <f t="shared" si="160"/>
         <v>-0.10000000000000017</v>
       </c>
-      <c r="AB60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>0</v>
-      </c>
       <c r="AF60" s="3">
         <v>0</v>
       </c>
@@ -6967,8 +7721,20 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>42</v>
       </c>
@@ -6999,26 +7765,17 @@
       <c r="U61" s="3">
         <v>-0.9</v>
       </c>
-      <c r="Z61" s="3">
-        <f t="shared" si="121"/>
+      <c r="V61" s="3">
+        <v>-6.2</v>
+      </c>
+      <c r="AD61" s="3">
+        <f t="shared" si="159"/>
         <v>-6</v>
       </c>
-      <c r="AA61" s="3">
-        <f t="shared" si="122"/>
+      <c r="AE61" s="3">
+        <f t="shared" si="160"/>
         <v>-7.6999999999999993</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -7040,101 +7797,117 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="2:38" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>82</v>
       </c>
       <c r="K62" s="8">
-        <f t="shared" ref="K62:R62" si="125">K48+SUM(K49:K61)</f>
+        <f t="shared" ref="K62:R62" si="162">K48+SUM(K49:K61)</f>
         <v>25.499999999999993</v>
       </c>
       <c r="L62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>15.399999999999993</v>
       </c>
       <c r="M62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>16.099999999999994</v>
       </c>
       <c r="N62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>25.300000000000011</v>
       </c>
       <c r="O62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>30.999999999999993</v>
       </c>
       <c r="P62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>17.299999999999994</v>
       </c>
       <c r="Q62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>35.099999999999994</v>
       </c>
       <c r="R62" s="8">
-        <f t="shared" si="125"/>
+        <f t="shared" si="162"/>
         <v>21.499999999999972</v>
       </c>
       <c r="U62" s="8">
-        <f t="shared" ref="U62" si="126">U48+SUM(U49:U61)</f>
+        <f t="shared" ref="U62:V62" si="163">U48+SUM(U49:U61)</f>
         <v>28.499999999999986</v>
       </c>
-      <c r="Z62" s="8">
-        <f>Z48+SUM(Z49:Z61)</f>
+      <c r="V62" s="8">
+        <f t="shared" si="163"/>
+        <v>39.999999999999979</v>
+      </c>
+      <c r="AD62" s="8">
+        <f>AD48+SUM(AD49:AD61)</f>
         <v>82.29999999999994</v>
       </c>
-      <c r="AA62" s="8">
-        <f>AA48+SUM(AA49:AA61)</f>
+      <c r="AE62" s="8">
+        <f>AE48+SUM(AE49:AE61)</f>
         <v>107.5</v>
       </c>
-      <c r="AB62" s="8">
-        <f t="shared" ref="AB62:AL62" si="127">AB48+SUM(AB49:AB61)</f>
-        <v>110.46600000000009</v>
-      </c>
-      <c r="AC62" s="8">
-        <f t="shared" si="127"/>
-        <v>175.27131999999995</v>
-      </c>
-      <c r="AD62" s="8">
-        <f t="shared" si="127"/>
-        <v>202.75129320000005</v>
-      </c>
-      <c r="AE62" s="8">
-        <f t="shared" si="127"/>
-        <v>213.67329217840012</v>
-      </c>
       <c r="AF62" s="8">
-        <f t="shared" si="127"/>
-        <v>220.99138490778407</v>
+        <f t="shared" ref="AF62:AP62" si="164">AF48+SUM(AF49:AF61)</f>
+        <v>110.75200000000001</v>
       </c>
       <c r="AG62" s="8">
-        <f t="shared" si="127"/>
-        <v>227.4206697582741</v>
+        <f t="shared" si="164"/>
+        <v>107.92429999999996</v>
       </c>
       <c r="AH62" s="8">
-        <f t="shared" si="127"/>
-        <v>232.78125837233347</v>
+        <f t="shared" si="164"/>
+        <v>195.12861511000006</v>
       </c>
       <c r="AI62" s="8">
-        <f t="shared" si="127"/>
-        <v>238.36375777550299</v>
+        <f t="shared" si="164"/>
+        <v>208.74134665470004</v>
       </c>
       <c r="AJ62" s="8">
-        <f t="shared" si="127"/>
-        <v>244.15243772080512</v>
+        <f t="shared" si="164"/>
+        <v>216.54409879842814</v>
       </c>
       <c r="AK62" s="8">
-        <f t="shared" si="127"/>
-        <v>250.13531476228081</v>
+        <f t="shared" si="164"/>
+        <v>223.47123685166233</v>
       </c>
       <c r="AL62" s="8">
-        <f t="shared" si="127"/>
-        <v>256.30341518695229</v>
+        <f t="shared" si="164"/>
+        <v>229.35039954233349</v>
+      </c>
+      <c r="AM62" s="8">
+        <f t="shared" si="164"/>
+        <v>235.56986896248125</v>
+      </c>
+      <c r="AN62" s="8">
+        <f t="shared" si="164"/>
+        <v>242.13777279482107</v>
+      </c>
+      <c r="AO62" s="8">
+        <f t="shared" si="164"/>
+        <v>249.07075953504904</v>
+      </c>
+      <c r="AP62" s="8">
+        <f t="shared" si="164"/>
+        <v>256.39421626322962</v>
       </c>
     </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>83</v>
       </c>
@@ -7165,59 +7938,62 @@
       <c r="U63" s="3">
         <v>3.2</v>
       </c>
-      <c r="Z63" s="3">
-        <f t="shared" ref="Z63:Z65" si="128">SUM(K63:N63)</f>
+      <c r="V63" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AD63" s="3">
+        <f t="shared" ref="AD63:AD65" si="165">SUM(K63:N63)</f>
         <v>1.7999999999999998</v>
       </c>
-      <c r="AA63" s="3">
-        <f t="shared" ref="AA63:AA65" si="129">SUM(O63:R63)</f>
+      <c r="AE63" s="3">
+        <f t="shared" ref="AE63:AE65" si="166">SUM(O63:R63)</f>
         <v>23.2</v>
       </c>
-      <c r="AB63" s="3">
+      <c r="AF63" s="3">
         <v>5</v>
       </c>
-      <c r="AC63" s="3">
-        <f>AB63*1.03</f>
+      <c r="AG63" s="3">
+        <f>AF63*1.03</f>
         <v>5.15</v>
       </c>
-      <c r="AD63" s="3">
-        <f t="shared" ref="AD63:AL63" si="130">AC63*1.03</f>
+      <c r="AH63" s="3">
+        <f t="shared" ref="AH63:AP63" si="167">AG63*1.03</f>
         <v>5.3045000000000009</v>
       </c>
-      <c r="AE63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AI63" s="3">
+        <f t="shared" si="167"/>
         <v>5.4636350000000009</v>
       </c>
-      <c r="AF63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AJ63" s="3">
+        <f t="shared" si="167"/>
         <v>5.6275440500000009</v>
       </c>
-      <c r="AG63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AK63" s="3">
+        <f t="shared" si="167"/>
         <v>5.796370371500001</v>
       </c>
-      <c r="AH63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AL63" s="3">
+        <f t="shared" si="167"/>
         <v>5.9702614826450011</v>
       </c>
-      <c r="AI63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AM63" s="3">
+        <f t="shared" si="167"/>
         <v>6.1493693271243517</v>
       </c>
-      <c r="AJ63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AN63" s="3">
+        <f t="shared" si="167"/>
         <v>6.3338504069380823</v>
       </c>
-      <c r="AK63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AO63" s="3">
+        <f t="shared" si="167"/>
         <v>6.5238659191462247</v>
       </c>
-      <c r="AL63" s="3">
-        <f t="shared" si="130"/>
+      <c r="AP63" s="3">
+        <f t="shared" si="167"/>
         <v>6.7195818967206113</v>
       </c>
     </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>84</v>
       </c>
@@ -7248,24 +8024,15 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-      <c r="Z64" s="3">
-        <f t="shared" si="128"/>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <f t="shared" si="165"/>
         <v>0.3</v>
       </c>
-      <c r="AA64" s="3">
-        <f t="shared" si="129"/>
-        <v>0</v>
-      </c>
-      <c r="AB64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD64" s="3">
-        <v>0</v>
-      </c>
       <c r="AE64" s="3">
+        <f t="shared" si="166"/>
         <v>0</v>
       </c>
       <c r="AF64" s="3">
@@ -7289,8 +8056,20 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:140" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:144" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>86</v>
       </c>
@@ -7321,692 +8100,704 @@
       <c r="U65" s="3">
         <v>2.8</v>
       </c>
-      <c r="Z65" s="3">
-        <f t="shared" si="128"/>
+      <c r="V65" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AD65" s="3">
+        <f t="shared" si="165"/>
         <v>4.3</v>
       </c>
-      <c r="AA65" s="3">
-        <f t="shared" si="129"/>
+      <c r="AE65" s="3">
+        <f t="shared" si="166"/>
         <v>7.2999999999999989</v>
       </c>
-      <c r="AB65" s="3">
-        <f>AA65*1.5</f>
+      <c r="AF65" s="3">
+        <f>AE65*1.5</f>
         <v>10.95</v>
       </c>
-      <c r="AC65" s="3">
-        <f>AB65*1.25</f>
+      <c r="AG65" s="3">
+        <f>AF65*1.25</f>
         <v>13.6875</v>
       </c>
-      <c r="AD65" s="3">
-        <f t="shared" ref="AD65" si="131">AC65*1.2</f>
+      <c r="AH65" s="3">
+        <f t="shared" ref="AH65" si="168">AG65*1.2</f>
         <v>16.425000000000001</v>
       </c>
-      <c r="AE65" s="3">
-        <f>AD65*1.1</f>
+      <c r="AI65" s="3">
+        <f>AH65*1.1</f>
         <v>18.067500000000003</v>
       </c>
-      <c r="AF65" s="3">
-        <f>AE65*1.05</f>
+      <c r="AJ65" s="3">
+        <f>AI65*1.05</f>
         <v>18.970875000000003</v>
       </c>
-      <c r="AG65" s="3">
-        <f t="shared" ref="AG65:AL65" si="132">AF65*1.05</f>
+      <c r="AK65" s="3">
+        <f t="shared" ref="AK65:AP65" si="169">AJ65*1.05</f>
         <v>19.919418750000006</v>
       </c>
-      <c r="AH65" s="3">
-        <f t="shared" si="132"/>
+      <c r="AL65" s="3">
+        <f t="shared" si="169"/>
         <v>20.915389687500006</v>
       </c>
-      <c r="AI65" s="3">
-        <f t="shared" si="132"/>
+      <c r="AM65" s="3">
+        <f t="shared" si="169"/>
         <v>21.961159171875007</v>
       </c>
-      <c r="AJ65" s="3">
-        <f t="shared" si="132"/>
+      <c r="AN65" s="3">
+        <f t="shared" si="169"/>
         <v>23.05921713046876</v>
       </c>
-      <c r="AK65" s="3">
-        <f t="shared" si="132"/>
+      <c r="AO65" s="3">
+        <f t="shared" si="169"/>
         <v>24.212177986992199</v>
       </c>
-      <c r="AL65" s="3">
-        <f t="shared" si="132"/>
+      <c r="AP65" s="3">
+        <f t="shared" si="169"/>
         <v>25.422786886341811</v>
       </c>
     </row>
-    <row r="66" spans="2:140" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:144" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>87</v>
       </c>
       <c r="K66" s="3">
-        <f t="shared" ref="K66:R66" si="133">SUM(K63:K65)</f>
+        <f t="shared" ref="K66:R66" si="170">SUM(K63:K65)</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="L66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>1.2</v>
       </c>
       <c r="M66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>1.9</v>
       </c>
       <c r="N66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>1.9</v>
       </c>
       <c r="O66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>21.599999999999998</v>
       </c>
       <c r="P66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>2.9</v>
       </c>
       <c r="Q66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="R66" s="3">
-        <f t="shared" si="133"/>
+        <f t="shared" si="170"/>
         <v>1.9</v>
       </c>
       <c r="U66" s="3">
-        <f t="shared" ref="U66" si="134">SUM(U63:U65)</f>
+        <f t="shared" ref="U66:V66" si="171">SUM(U63:U65)</f>
         <v>6</v>
       </c>
-      <c r="Z66" s="3">
-        <f>SUM(Z63:Z65)</f>
+      <c r="V66" s="3">
+        <f t="shared" si="171"/>
+        <v>3.5</v>
+      </c>
+      <c r="AD66" s="3">
+        <f>SUM(AD63:AD65)</f>
         <v>6.3999999999999995</v>
       </c>
-      <c r="AA66" s="3">
-        <f>SUM(AA63:AA65)</f>
+      <c r="AE66" s="3">
+        <f>SUM(AE63:AE65)</f>
         <v>30.5</v>
       </c>
-      <c r="AB66" s="3">
-        <f t="shared" ref="AB66:AL66" si="135">SUM(AB63:AB65)</f>
+      <c r="AF66" s="3">
+        <f t="shared" ref="AF66:AP66" si="172">SUM(AF63:AF65)</f>
         <v>15.95</v>
       </c>
-      <c r="AC66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AG66" s="3">
+        <f t="shared" si="172"/>
         <v>18.837499999999999</v>
       </c>
-      <c r="AD66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AH66" s="3">
+        <f t="shared" si="172"/>
         <v>21.729500000000002</v>
       </c>
-      <c r="AE66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AI66" s="3">
+        <f t="shared" si="172"/>
         <v>23.531135000000003</v>
       </c>
-      <c r="AF66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AJ66" s="3">
+        <f t="shared" si="172"/>
         <v>24.598419050000004</v>
       </c>
-      <c r="AG66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AK66" s="3">
+        <f t="shared" si="172"/>
         <v>25.715789121500006</v>
       </c>
-      <c r="AH66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AL66" s="3">
+        <f t="shared" si="172"/>
         <v>26.885651170145007</v>
       </c>
-      <c r="AI66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AM66" s="3">
+        <f t="shared" si="172"/>
         <v>28.110528498999358</v>
       </c>
-      <c r="AJ66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AN66" s="3">
+        <f t="shared" si="172"/>
         <v>29.393067537406843</v>
       </c>
-      <c r="AK66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AO66" s="3">
+        <f t="shared" si="172"/>
         <v>30.736043906138423</v>
       </c>
-      <c r="AL66" s="3">
-        <f t="shared" si="135"/>
+      <c r="AP66" s="3">
+        <f t="shared" si="172"/>
         <v>32.142368783062423</v>
       </c>
     </row>
-    <row r="67" spans="2:140" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:144" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>85</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" ref="K67:R67" si="136">K62-K66</f>
+        <f t="shared" ref="K67:R67" si="173">K62-K66</f>
         <v>24.099999999999994</v>
       </c>
       <c r="L67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>14.199999999999994</v>
       </c>
       <c r="M67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>14.199999999999994</v>
       </c>
       <c r="N67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>23.400000000000013</v>
       </c>
       <c r="O67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>9.399999999999995</v>
       </c>
       <c r="P67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>14.399999999999993</v>
       </c>
       <c r="Q67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>30.999999999999993</v>
       </c>
       <c r="R67" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="173"/>
         <v>19.599999999999973</v>
       </c>
       <c r="U67" s="8">
-        <f t="shared" ref="U67" si="137">U62-U66</f>
+        <f t="shared" ref="U67:V67" si="174">U62-U66</f>
         <v>22.499999999999986</v>
       </c>
-      <c r="Z67" s="8">
-        <f>Z62-Z66</f>
+      <c r="V67" s="8">
+        <f t="shared" si="174"/>
+        <v>36.499999999999979</v>
+      </c>
+      <c r="AD67" s="8">
+        <f>AD62-AD66</f>
         <v>75.899999999999935</v>
       </c>
-      <c r="AA67" s="8">
-        <f>AA62-AA66</f>
+      <c r="AE67" s="8">
+        <f>AE62-AE66</f>
         <v>77</v>
       </c>
-      <c r="AB67" s="8">
-        <f t="shared" ref="AB67:AL67" si="138">AB62-AB66</f>
-        <v>94.516000000000091</v>
-      </c>
-      <c r="AC67" s="8">
-        <f t="shared" si="138"/>
-        <v>156.43381999999994</v>
-      </c>
-      <c r="AD67" s="8">
-        <f t="shared" si="138"/>
-        <v>181.02179320000005</v>
-      </c>
-      <c r="AE67" s="8">
-        <f t="shared" si="138"/>
-        <v>190.14215717840011</v>
-      </c>
       <c r="AF67" s="8">
-        <f t="shared" si="138"/>
-        <v>196.39296585778408</v>
+        <f t="shared" ref="AF67:AP67" si="175">AF62-AF66</f>
+        <v>94.802000000000007</v>
       </c>
       <c r="AG67" s="8">
-        <f t="shared" si="138"/>
-        <v>201.70488063677411</v>
+        <f t="shared" si="175"/>
+        <v>89.086799999999954</v>
       </c>
       <c r="AH67" s="8">
-        <f t="shared" si="138"/>
-        <v>205.89560720218847</v>
+        <f t="shared" si="175"/>
+        <v>173.39911511000005</v>
       </c>
       <c r="AI67" s="8">
-        <f t="shared" si="138"/>
-        <v>210.25322927650365</v>
+        <f t="shared" si="175"/>
+        <v>185.21021165470003</v>
       </c>
       <c r="AJ67" s="8">
-        <f t="shared" si="138"/>
-        <v>214.75937018339829</v>
+        <f t="shared" si="175"/>
+        <v>191.94567974842812</v>
       </c>
       <c r="AK67" s="8">
-        <f t="shared" si="138"/>
-        <v>219.39927085614238</v>
+        <f t="shared" si="175"/>
+        <v>197.75544773016233</v>
       </c>
       <c r="AL67" s="8">
-        <f t="shared" si="138"/>
-        <v>224.16104640388988</v>
-      </c>
-      <c r="AM67" s="1">
-        <f>AL67*(1+$AO$40)</f>
-        <v>221.91943593985098</v>
-      </c>
-      <c r="AN67" s="1">
-        <f t="shared" ref="AN67:CY67" si="139">AM67*(1+$AO$40)</f>
-        <v>219.70024158045248</v>
-      </c>
-      <c r="AO67" s="1">
-        <f t="shared" si="139"/>
-        <v>217.50323916464797</v>
-      </c>
-      <c r="AP67" s="1">
-        <f t="shared" si="139"/>
-        <v>215.32820677300148</v>
+        <f t="shared" si="175"/>
+        <v>202.4647483721885</v>
+      </c>
+      <c r="AM67" s="8">
+        <f t="shared" si="175"/>
+        <v>207.45934046348191</v>
+      </c>
+      <c r="AN67" s="8">
+        <f t="shared" si="175"/>
+        <v>212.74470525741424</v>
+      </c>
+      <c r="AO67" s="8">
+        <f t="shared" si="175"/>
+        <v>218.3347156289106</v>
+      </c>
+      <c r="AP67" s="8">
+        <f t="shared" si="175"/>
+        <v>224.25184748016721</v>
       </c>
       <c r="AQ67" s="1">
-        <f t="shared" si="139"/>
-        <v>213.17492470527148</v>
+        <f>AP67*(1+$AS$40)</f>
+        <v>222.00932900536554</v>
       </c>
       <c r="AR67" s="1">
-        <f t="shared" si="139"/>
-        <v>211.04317545821877</v>
+        <f t="shared" ref="AR67:DC67" si="176">AQ67*(1+$AS$40)</f>
+        <v>219.78923571531189</v>
       </c>
       <c r="AS67" s="1">
-        <f t="shared" si="139"/>
-        <v>208.93274370363659</v>
+        <f t="shared" si="176"/>
+        <v>217.59134335815878</v>
       </c>
       <c r="AT67" s="1">
-        <f t="shared" si="139"/>
-        <v>206.84341626660023</v>
+        <f t="shared" si="176"/>
+        <v>215.41542992457718</v>
       </c>
       <c r="AU67" s="1">
-        <f t="shared" si="139"/>
-        <v>204.77498210393424</v>
+        <f t="shared" si="176"/>
+        <v>213.26127562533142</v>
       </c>
       <c r="AV67" s="1">
-        <f t="shared" si="139"/>
-        <v>202.7272322828949</v>
+        <f t="shared" si="176"/>
+        <v>211.12866286907811</v>
       </c>
       <c r="AW67" s="1">
-        <f t="shared" si="139"/>
-        <v>200.69995996006594</v>
+        <f t="shared" si="176"/>
+        <v>209.01737624038734</v>
       </c>
       <c r="AX67" s="1">
-        <f t="shared" si="139"/>
-        <v>198.69296036046526</v>
+        <f t="shared" si="176"/>
+        <v>206.92720247798346</v>
       </c>
       <c r="AY67" s="1">
-        <f t="shared" si="139"/>
-        <v>196.7060307568606</v>
+        <f t="shared" si="176"/>
+        <v>204.85793045320361</v>
       </c>
       <c r="AZ67" s="1">
-        <f t="shared" si="139"/>
-        <v>194.738970449292</v>
+        <f t="shared" si="176"/>
+        <v>202.80935114867157</v>
       </c>
       <c r="BA67" s="1">
-        <f t="shared" si="139"/>
-        <v>192.79158074479906</v>
+        <f t="shared" si="176"/>
+        <v>200.78125763718484</v>
       </c>
       <c r="BB67" s="1">
-        <f t="shared" si="139"/>
-        <v>190.86366493735107</v>
+        <f t="shared" si="176"/>
+        <v>198.77344506081297</v>
       </c>
       <c r="BC67" s="1">
-        <f t="shared" si="139"/>
-        <v>188.95502828797757</v>
+        <f t="shared" si="176"/>
+        <v>196.78571061020483</v>
       </c>
       <c r="BD67" s="1">
-        <f t="shared" si="139"/>
-        <v>187.06547800509779</v>
+        <f t="shared" si="176"/>
+        <v>194.81785350410277</v>
       </c>
       <c r="BE67" s="1">
-        <f t="shared" si="139"/>
-        <v>185.1948232250468</v>
+        <f t="shared" si="176"/>
+        <v>192.86967496906175</v>
       </c>
       <c r="BF67" s="1">
-        <f t="shared" si="139"/>
-        <v>183.34287499279634</v>
+        <f t="shared" si="176"/>
+        <v>190.94097821937112</v>
       </c>
       <c r="BG67" s="1">
-        <f t="shared" si="139"/>
-        <v>181.50944624286836</v>
+        <f t="shared" si="176"/>
+        <v>189.03156843717741</v>
       </c>
       <c r="BH67" s="1">
-        <f t="shared" si="139"/>
-        <v>179.69435178043969</v>
+        <f t="shared" si="176"/>
+        <v>187.14125275280563</v>
       </c>
       <c r="BI67" s="1">
-        <f t="shared" si="139"/>
-        <v>177.89740826263528</v>
+        <f t="shared" si="176"/>
+        <v>185.26984022527756</v>
       </c>
       <c r="BJ67" s="1">
-        <f t="shared" si="139"/>
-        <v>176.11843418000893</v>
+        <f t="shared" si="176"/>
+        <v>183.41714182302479</v>
       </c>
       <c r="BK67" s="1">
-        <f t="shared" si="139"/>
-        <v>174.35724983820884</v>
+        <f t="shared" si="176"/>
+        <v>181.58297040479454</v>
       </c>
       <c r="BL67" s="1">
-        <f t="shared" si="139"/>
-        <v>172.61367733982675</v>
+        <f t="shared" si="176"/>
+        <v>179.76714070074658</v>
       </c>
       <c r="BM67" s="1">
-        <f t="shared" si="139"/>
-        <v>170.88754056642847</v>
+        <f t="shared" si="176"/>
+        <v>177.96946929373911</v>
       </c>
       <c r="BN67" s="1">
-        <f t="shared" si="139"/>
-        <v>169.17866516076418</v>
+        <f t="shared" si="176"/>
+        <v>176.18977460080171</v>
       </c>
       <c r="BO67" s="1">
-        <f t="shared" si="139"/>
-        <v>167.48687850915653</v>
+        <f t="shared" si="176"/>
+        <v>174.42787685479368</v>
       </c>
       <c r="BP67" s="1">
-        <f t="shared" si="139"/>
-        <v>165.81200972406495</v>
+        <f t="shared" si="176"/>
+        <v>172.68359808624575</v>
       </c>
       <c r="BQ67" s="1">
-        <f t="shared" si="139"/>
-        <v>164.15388962682431</v>
+        <f t="shared" si="176"/>
+        <v>170.95676210538329</v>
       </c>
       <c r="BR67" s="1">
-        <f t="shared" si="139"/>
-        <v>162.51235073055605</v>
+        <f t="shared" si="176"/>
+        <v>169.24719448432947</v>
       </c>
       <c r="BS67" s="1">
-        <f t="shared" si="139"/>
-        <v>160.88722722325048</v>
+        <f t="shared" si="176"/>
+        <v>167.55472253948616</v>
       </c>
       <c r="BT67" s="1">
-        <f t="shared" si="139"/>
-        <v>159.27835495101797</v>
+        <f t="shared" si="176"/>
+        <v>165.8791753140913</v>
       </c>
       <c r="BU67" s="1">
-        <f t="shared" si="139"/>
-        <v>157.68557140150779</v>
+        <f t="shared" si="176"/>
+        <v>164.22038356095038</v>
       </c>
       <c r="BV67" s="1">
-        <f t="shared" si="139"/>
-        <v>156.10871568749272</v>
+        <f t="shared" si="176"/>
+        <v>162.57817972534087</v>
       </c>
       <c r="BW67" s="1">
-        <f t="shared" si="139"/>
-        <v>154.5476285306178</v>
+        <f t="shared" si="176"/>
+        <v>160.95239792808746</v>
       </c>
       <c r="BX67" s="1">
-        <f t="shared" si="139"/>
-        <v>153.00215224531163</v>
+        <f t="shared" si="176"/>
+        <v>159.34287394880658</v>
       </c>
       <c r="BY67" s="1">
-        <f t="shared" si="139"/>
-        <v>151.47213072285851</v>
+        <f t="shared" si="176"/>
+        <v>157.74944520931851</v>
       </c>
       <c r="BZ67" s="1">
-        <f t="shared" si="139"/>
-        <v>149.95740941562991</v>
+        <f t="shared" si="176"/>
+        <v>156.17195075722532</v>
       </c>
       <c r="CA67" s="1">
-        <f t="shared" si="139"/>
-        <v>148.45783532147362</v>
+        <f t="shared" si="176"/>
+        <v>154.61023124965305</v>
       </c>
       <c r="CB67" s="1">
-        <f t="shared" si="139"/>
-        <v>146.97325696825888</v>
+        <f t="shared" si="176"/>
+        <v>153.06412893715651</v>
       </c>
       <c r="CC67" s="1">
-        <f t="shared" si="139"/>
-        <v>145.5035243985763</v>
+        <f t="shared" si="176"/>
+        <v>151.53348764778494</v>
       </c>
       <c r="CD67" s="1">
-        <f t="shared" si="139"/>
-        <v>144.04848915459053</v>
+        <f t="shared" si="176"/>
+        <v>150.01815277130709</v>
       </c>
       <c r="CE67" s="1">
-        <f t="shared" si="139"/>
-        <v>142.60800426304462</v>
+        <f t="shared" si="176"/>
+        <v>148.51797124359402</v>
       </c>
       <c r="CF67" s="1">
-        <f t="shared" si="139"/>
-        <v>141.18192422041417</v>
+        <f t="shared" si="176"/>
+        <v>147.03279153115807</v>
       </c>
       <c r="CG67" s="1">
-        <f t="shared" si="139"/>
-        <v>139.77010497821004</v>
+        <f t="shared" si="176"/>
+        <v>145.5624636158465</v>
       </c>
       <c r="CH67" s="1">
-        <f t="shared" si="139"/>
-        <v>138.37240392842793</v>
+        <f t="shared" si="176"/>
+        <v>144.10683897968804</v>
       </c>
       <c r="CI67" s="1">
-        <f t="shared" si="139"/>
-        <v>136.98867988914364</v>
+        <f t="shared" si="176"/>
+        <v>142.66577058989117</v>
       </c>
       <c r="CJ67" s="1">
-        <f t="shared" si="139"/>
-        <v>135.61879309025221</v>
+        <f t="shared" si="176"/>
+        <v>141.23911288399225</v>
       </c>
       <c r="CK67" s="1">
-        <f t="shared" si="139"/>
-        <v>134.26260515934968</v>
+        <f t="shared" si="176"/>
+        <v>139.82672175515233</v>
       </c>
       <c r="CL67" s="1">
-        <f t="shared" si="139"/>
-        <v>132.91997910775618</v>
+        <f t="shared" si="176"/>
+        <v>138.4284545376008</v>
       </c>
       <c r="CM67" s="1">
-        <f t="shared" si="139"/>
-        <v>131.59077931667861</v>
+        <f t="shared" si="176"/>
+        <v>137.04416999222479</v>
       </c>
       <c r="CN67" s="1">
-        <f t="shared" si="139"/>
-        <v>130.27487152351182</v>
+        <f t="shared" si="176"/>
+        <v>135.67372829230254</v>
       </c>
       <c r="CO67" s="1">
-        <f t="shared" si="139"/>
-        <v>128.97212280827671</v>
+        <f t="shared" si="176"/>
+        <v>134.31699100937951</v>
       </c>
       <c r="CP67" s="1">
-        <f t="shared" si="139"/>
-        <v>127.68240158019394</v>
+        <f t="shared" si="176"/>
+        <v>132.97382109928571</v>
       </c>
       <c r="CQ67" s="1">
-        <f t="shared" si="139"/>
-        <v>126.405577564392</v>
+        <f t="shared" si="176"/>
+        <v>131.64408288829284</v>
       </c>
       <c r="CR67" s="1">
-        <f t="shared" si="139"/>
-        <v>125.14152178874808</v>
+        <f t="shared" si="176"/>
+        <v>130.32764205940992</v>
       </c>
       <c r="CS67" s="1">
-        <f t="shared" si="139"/>
-        <v>123.8901065708606</v>
+        <f t="shared" si="176"/>
+        <v>129.02436563881582</v>
       </c>
       <c r="CT67" s="1">
-        <f t="shared" si="139"/>
-        <v>122.65120550515199</v>
+        <f t="shared" si="176"/>
+        <v>127.73412198242767</v>
       </c>
       <c r="CU67" s="1">
-        <f t="shared" si="139"/>
-        <v>121.42469345010048</v>
+        <f t="shared" si="176"/>
+        <v>126.45678076260339</v>
       </c>
       <c r="CV67" s="1">
-        <f t="shared" si="139"/>
-        <v>120.21044651559947</v>
+        <f t="shared" si="176"/>
+        <v>125.19221295497735</v>
       </c>
       <c r="CW67" s="1">
-        <f t="shared" si="139"/>
-        <v>119.00834205044347</v>
+        <f t="shared" si="176"/>
+        <v>123.94029082542758</v>
       </c>
       <c r="CX67" s="1">
-        <f t="shared" si="139"/>
-        <v>117.81825862993904</v>
+        <f t="shared" si="176"/>
+        <v>122.7008879171733</v>
       </c>
       <c r="CY67" s="1">
-        <f t="shared" si="139"/>
-        <v>116.64007604363965</v>
+        <f t="shared" si="176"/>
+        <v>121.47387903800157</v>
       </c>
       <c r="CZ67" s="1">
-        <f t="shared" ref="CZ67:EJ67" si="140">CY67*(1+$AO$40)</f>
-        <v>115.47367528320325</v>
+        <f t="shared" si="176"/>
+        <v>120.25914024762156</v>
       </c>
       <c r="DA67" s="1">
-        <f t="shared" si="140"/>
-        <v>114.31893853037121</v>
+        <f t="shared" si="176"/>
+        <v>119.05654884514534</v>
       </c>
       <c r="DB67" s="1">
-        <f t="shared" si="140"/>
-        <v>113.1757491450675</v>
+        <f t="shared" si="176"/>
+        <v>117.86598335669389</v>
       </c>
       <c r="DC67" s="1">
-        <f t="shared" si="140"/>
-        <v>112.04399165361683</v>
+        <f t="shared" si="176"/>
+        <v>116.68732352312695</v>
       </c>
       <c r="DD67" s="1">
-        <f t="shared" si="140"/>
-        <v>110.92355173708066</v>
+        <f t="shared" ref="DD67:EN67" si="177">DC67*(1+$AS$40)</f>
+        <v>115.52045028789568</v>
       </c>
       <c r="DE67" s="1">
-        <f t="shared" si="140"/>
-        <v>109.81431621970985</v>
+        <f t="shared" si="177"/>
+        <v>114.36524578501673</v>
       </c>
       <c r="DF67" s="1">
-        <f t="shared" si="140"/>
-        <v>108.71617305751275</v>
+        <f t="shared" si="177"/>
+        <v>113.22159332716656</v>
       </c>
       <c r="DG67" s="1">
-        <f t="shared" si="140"/>
-        <v>107.62901132693761</v>
+        <f t="shared" si="177"/>
+        <v>112.08937739389489</v>
       </c>
       <c r="DH67" s="1">
-        <f t="shared" si="140"/>
-        <v>106.55272121366824</v>
+        <f t="shared" si="177"/>
+        <v>110.96848361995595</v>
       </c>
       <c r="DI67" s="1">
-        <f t="shared" si="140"/>
-        <v>105.48719400153155</v>
+        <f t="shared" si="177"/>
+        <v>109.85879878375638</v>
       </c>
       <c r="DJ67" s="1">
-        <f t="shared" si="140"/>
-        <v>104.43232206151623</v>
+        <f t="shared" si="177"/>
+        <v>108.76021079591882</v>
       </c>
       <c r="DK67" s="1">
-        <f t="shared" si="140"/>
-        <v>103.38799884090106</v>
+        <f t="shared" si="177"/>
+        <v>107.67260868795964</v>
       </c>
       <c r="DL67" s="1">
-        <f t="shared" si="140"/>
-        <v>102.35411885249205</v>
+        <f t="shared" si="177"/>
+        <v>106.59588260108004</v>
       </c>
       <c r="DM67" s="1">
-        <f t="shared" si="140"/>
-        <v>101.33057766396713</v>
+        <f t="shared" si="177"/>
+        <v>105.52992377506924</v>
       </c>
       <c r="DN67" s="1">
-        <f t="shared" si="140"/>
-        <v>100.31727188732746</v>
+        <f t="shared" si="177"/>
+        <v>104.47462453731855</v>
       </c>
       <c r="DO67" s="1">
-        <f t="shared" si="140"/>
-        <v>99.314099168454192</v>
+        <f t="shared" si="177"/>
+        <v>103.42987829194536</v>
       </c>
       <c r="DP67" s="1">
-        <f t="shared" si="140"/>
-        <v>98.320958176769651</v>
+        <f t="shared" si="177"/>
+        <v>102.39557950902591</v>
       </c>
       <c r="DQ67" s="1">
-        <f t="shared" si="140"/>
-        <v>97.337748595001955</v>
+        <f t="shared" si="177"/>
+        <v>101.37162371393565</v>
       </c>
       <c r="DR67" s="1">
-        <f t="shared" si="140"/>
-        <v>96.36437110905193</v>
+        <f t="shared" si="177"/>
+        <v>100.35790747679629</v>
       </c>
       <c r="DS67" s="1">
-        <f t="shared" si="140"/>
-        <v>95.400727397961404</v>
+        <f t="shared" si="177"/>
+        <v>99.354328402028315</v>
       </c>
       <c r="DT67" s="1">
-        <f t="shared" si="140"/>
-        <v>94.446720123981791</v>
+        <f t="shared" si="177"/>
+        <v>98.360785118008025</v>
       </c>
       <c r="DU67" s="1">
-        <f t="shared" si="140"/>
-        <v>93.502252922741974</v>
+        <f t="shared" si="177"/>
+        <v>97.377177266827943</v>
       </c>
       <c r="DV67" s="1">
-        <f t="shared" si="140"/>
-        <v>92.567230393514549</v>
+        <f t="shared" si="177"/>
+        <v>96.403405494159657</v>
       </c>
       <c r="DW67" s="1">
-        <f t="shared" si="140"/>
-        <v>91.641558089579405</v>
+        <f t="shared" si="177"/>
+        <v>95.439371439218064</v>
       </c>
       <c r="DX67" s="1">
-        <f t="shared" si="140"/>
-        <v>90.725142508683604</v>
+        <f t="shared" si="177"/>
+        <v>94.484977724825882</v>
       </c>
       <c r="DY67" s="1">
-        <f t="shared" si="140"/>
-        <v>89.817891083596763</v>
+        <f t="shared" si="177"/>
+        <v>93.540127947577616</v>
       </c>
       <c r="DZ67" s="1">
-        <f t="shared" si="140"/>
-        <v>88.919712172760796</v>
+        <f t="shared" si="177"/>
+        <v>92.604726668101833</v>
       </c>
       <c r="EA67" s="1">
-        <f t="shared" si="140"/>
-        <v>88.030515051033191</v>
+        <f t="shared" si="177"/>
+        <v>91.678679401420808</v>
       </c>
       <c r="EB67" s="1">
-        <f t="shared" si="140"/>
-        <v>87.150209900522853</v>
+        <f t="shared" si="177"/>
+        <v>90.761892607406594</v>
       </c>
       <c r="EC67" s="1">
-        <f t="shared" si="140"/>
-        <v>86.278707801517626</v>
+        <f t="shared" si="177"/>
+        <v>89.854273681332529</v>
       </c>
       <c r="ED67" s="1">
-        <f t="shared" si="140"/>
-        <v>85.415920723502452</v>
+        <f t="shared" si="177"/>
+        <v>88.955730944519203</v>
       </c>
       <c r="EE67" s="1">
-        <f t="shared" si="140"/>
-        <v>84.561761516267424</v>
+        <f t="shared" si="177"/>
+        <v>88.066173635074009</v>
       </c>
       <c r="EF67" s="1">
-        <f t="shared" si="140"/>
-        <v>83.716143901104743</v>
+        <f t="shared" si="177"/>
+        <v>87.185511898723263</v>
       </c>
       <c r="EG67" s="1">
-        <f t="shared" si="140"/>
-        <v>82.878982462093688</v>
+        <f t="shared" si="177"/>
+        <v>86.313656779736036</v>
       </c>
       <c r="EH67" s="1">
-        <f t="shared" si="140"/>
-        <v>82.050192637472747</v>
+        <f t="shared" si="177"/>
+        <v>85.450520211938681</v>
       </c>
       <c r="EI67" s="1">
-        <f t="shared" si="140"/>
-        <v>81.229690711098016</v>
+        <f t="shared" si="177"/>
+        <v>84.596015009819297</v>
       </c>
       <c r="EJ67" s="1">
-        <f t="shared" si="140"/>
-        <v>80.417393803987039</v>
+        <f t="shared" si="177"/>
+        <v>83.750054859721104</v>
+      </c>
+      <c r="EK67" s="1">
+        <f t="shared" si="177"/>
+        <v>82.912554311123898</v>
+      </c>
+      <c r="EL67" s="1">
+        <f t="shared" si="177"/>
+        <v>82.083428768012652</v>
+      </c>
+      <c r="EM67" s="1">
+        <f t="shared" si="177"/>
+        <v>81.262594480332524</v>
+      </c>
+      <c r="EN67" s="1">
+        <f t="shared" si="177"/>
+        <v>80.449968535529194</v>
       </c>
     </row>
-    <row r="70" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO70" s="3">
-        <f>NPV(AO41,AB67:EJ67)</f>
-        <v>1881.9476353380076</v>
+    <row r="70" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS70" s="3">
+        <f>NPV(AS41,AF67:EN67)</f>
+        <v>1808.4520149461894</v>
       </c>
     </row>
-    <row r="71" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO71" s="3">
-        <f>AO43</f>
+    <row r="71" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS71" s="3">
+        <f>AS43</f>
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO72" s="3">
-        <f>AO70+AO71</f>
-        <v>2009.9476353380076</v>
+    <row r="72" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS72" s="3">
+        <f>AS70+AS71</f>
+        <v>1936.4520149461894</v>
       </c>
     </row>
-    <row r="73" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO73" s="2">
-        <f>AO72/AL30</f>
-        <v>22.432451287254551</v>
+    <row r="73" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS73" s="2">
+        <f>AS72/AP30</f>
+        <v>21.612187666810151</v>
       </c>
     </row>
-    <row r="74" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO74" s="2">
+    <row r="74" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS74" s="2">
         <f>Main!D3</f>
-        <v>13.45</v>
+        <v>14.31</v>
       </c>
     </row>
-    <row r="75" spans="2:140" x14ac:dyDescent="0.3">
-      <c r="AO75" s="9">
-        <f>AO73/AO74-1</f>
-        <v>0.6678402444055429</v>
+    <row r="75" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AS75" s="9">
+        <f>AS73/AS74-1</f>
+        <v>0.51028565106989165</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>